--- a/regulatory-compliance/cloud-foundation/9.1/cmmc-2-0/vcf-91-companion-cmmc-2-0.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/cmmc-2-0/vcf-91-companion-cmmc-2-0.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -716,22 +731,24 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a layered identity and access management architecture spanning centralized identity services, role-based access control, group-based access policies, identity provider federation, and programmatic access management through APIs.
-VCF SSO is the centralized authentication service. VCF SSO issues security tokens that grant authenticated users access to VMware vCenter, NSX Manager, VCF Operations, and other platform components without requiring separate credentials for each service. VCF Operations supports importing users and groups from VCF SSO for consistent identity management across the stack. VMware Identity Manager provides a platform for managing users and groups, managing resources and user authentication, and configuring access policies and resource entitlements. vCenter also supports built-in identity source authentication using local domain credentials. The built-in identity provider can also be configured to use Active Directory as an identity source through LDAP/S, OpenLDAP/S, or Integrated Windows Authentication (IWA), depending on the directory environment.
-VCF supports federation with enterprise identity providers. vCenter can be federated to providers such as Microsoft Entra ID, ADFS, and Okta, which enables multifactor authentication and automatic user synchronization with the organization's directory. PingFederate is also supported as a federated identity provider; for these integrations, vCenter uses System for Cross-domain Identity Management (SCIM) to automate the exchange of user and group identity information between the external identity domain and vCenter. VMware Identity Broker allows principals to authenticate to vCenter through an external identity provider. NSX Manager can be configured to authenticate users from identity management providers and can be integrated with Workspace ONE Access for identity management services. The Supervisor component supports registration of OIDC-compliant external identity providers for authentication to VMware Kubernetes Service (VKS) clusters; supported providers include Okta, Workspace ONE Access, and Dex, configured by supplying the Supervisor callback URL to the identity provider.
-Role-based access control is enforced across all VCF components. In vCenter, permissions associate a user or group with a role on a specific inventory object, and predefined roles cover common administrative functions. Custom roles can be created with only the minimum required privileges for a given workflow. Managing identity provider configuration in vCenter requires the VcIdentityProviders Manage privilege. VCF Operations supports group-based access control, allowing administrators to configure groups and assign roles that control access to dashboards, reports, policies, alerts, and administration functions, as well as granular role-based controls for platform operations including approvals, audits, certificates, and content libraries.
-VCF Automation extends access management through organization-level and project-level controls. The VCF Automation Access Control service supports identity operations for managing groups and users, including editing user names, passwords, and role assignments. The organization portal enforces role-based access control, requiring either Organization Administrator or Organization Auditor roles to manage policy templates. Organization administrators can distribute infrastructure and configure group-level access through the organization management functionality. Project access is governed by predefined roles. Users and groups can be disabled at the organization level to revoke access without deleting accounts. The System Administrator role has the right to manage and view Access Control Lists, and the accessControls API allows administrators to view and manage ACL entries for defined entities.
-For Kubernetes workloads within the VCF consumption layer, VKS supports two authentication methods: VCF SSO and OIDC-compliant external identity providers. The OIDC path is implemented through Pinniped and supports providers including Okta, Workspace ONE Access, Dex, GitLab, and Google OAuth. Configuring an external provider requires setting up an OpenID Connect ID Token with a Groups claim type filter to enable group-based access control tied to the organization's directory. Custom ClusterClass configurations allow clusters to authenticate developers using existing corporate identity systems. VKS supports namespace permission roles: Owner (full control including deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). These roles map to Kubernetes ClusterRoles through RoleBindings, and RoleBinding objects can reference VCF SSO users and groups directly to integrate SSO identities with Kubernetes role-based access control. A user with the Namespaces.Edit privilege on a user-created Namespace folder can perform CRUD operations on Kubernetes API resources in the Supervisor. Namespace Self-Service permissions control which users can self-provision namespaces through kubectl.
-Kubernetes RBAC is the primary authorization mechanism within VKS, using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings to bind permissions to users, groups, or service accounts. Kubernetes Attribute-Based Access Control (ABAC) is also available, defining access rights through policies that combine user, namespace, resource, and access mode attributes. Authorization webhooks can interpret field and label selectors to enforce fine-grained access control based on resource attributes such as node names and labels.
-Service accounts provide namespaced workload identity within VKS clusters. For Windows containers, the Group Managed Service Account (gMSA) Webhook allows containers to run as Active Directory identities. VKS service accounts can be annotated with IAM role ARNs to enable pod identity and role assumption for cloud resource access through OIDC federation, replacing long-lived static credentials with short-lived, least-privileged credentials on demand. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege.
-Several supplementary services within the VKS layer extend the IAM surface. Harbor Registry, available as a standard package on VKS clusters, enforces role-based access control to manage access to container image artifacts. The Secret Store Supervisor Service enforces RBAC for administrators, DevOps engineers, and application tenants managing sensitive data. Argo CD supports both OIDC configuration for external identity providers and local account configuration with global RBAC policies that define role-based access through policy rules and group mappings. The Istio service mesh package includes a pluggable policy layer supporting access controls, rate limits, and quotas at the service-to-service level.
-Programmatic access management is available through several APIs. The Identity API authenticates and manages the authorization provider. The Identity Service and Infrastructure as a Service APIs are used to acquire access tokens for REST API authentication. Principal Identity users authenticate using client certificates for service-to-service communications between VCF components.
-NSX integrates with LDAP and external identity management services for administrative access to networking configuration. NSX Manager enforces role-based access control with roles such as auditor and network administrator assignable to LDAP users. vDefend, a separate product that extends NSX with security capabilities, offers an Identity Firewall that integrates with Active Directory for identity-based firewall rules.
-VMware Private AI Services (PAIS) provides OIDC-based authentication and group-based authorization for AI workloads, the primary IAM mechanisms controlling access to model endpoints, the model runtime, Agent Builder, and Data Indexing and Retrieval capabilities. PAIS authentication is configured with an issuer URL, a client ID (pais-authentication-id), and the openid, groups, and offline_access scopes. The OIDC provider must support the .well-known/openid-configuration discovery endpoint. Authorization restricts access to user accounts that are members of named groups listed in the authorizedGroups setting (such as group-for-pais-access-01 or group-for-pais-access-02). A groups claim is included in the Access Token and a corresponding groups scope is created in the OIDC configuration, while the oidc-groups-claim setting selects which claim name carries group membership when the OIDC provider uses a non-default name. The oidc-extra-audiences setting accepts additional OAuth 2.0 client identifiers that PAIS will accept when validating Access Tokens, supporting integration with downstream clients that present their own audience. Activating PAIS in an organization namespace requires coordination with the OIDC provider administrator and an organization administrator account in VCF Automation.
-Identity provider integration for PAIS deployments is configured at the Supervisor level under Workload Management &gt; Supervisors &gt; Configure &gt; Identity Providers. When a PAIS region is created for a Supervisor, an identity provider entry is automatically created in VMware vCenter for that Supervisor, linking the Supervisor namespace to the configured OIDC source.
-The Model Gallery, the curated repository for ML models in PAIS, restricts access to model artifacts and the training data used to tune them through Harbor project access controls. These controls scope which users and service accounts can read, push, or manage sensitive model data, adding an IAM enforcement layer to the model supply chain. A Harbor registry is recommended for PAIS deployments, and OCI-compliant registries from other vendors are also supported.
-PAIS Knowledge Bases extend IAM to ingested data sources. Confluence data sources authenticate with a user name and password or a personal access token, while Microsoft SharePoint On-Premises data sources authenticate with a user name and password. Personal access tokens for Knowledge Bases are generated from user account settings and used for programmatic access to linked data sources.
-PAIS integrates with Grafana for metrics visualization using the same OIDC provider, extending the IAM model to the observability layer so that operators authenticate through the configured identity provider before accessing PAIS dashboards.</t>
+          <t>VCF enforces logical access control permissions through role-based access control (RBAC) mechanisms across its component products, supporting the principle of least privilege at each layer of the platform.
+VMware vCenter implements a granular privilege model where privileges are fine-grained access controls that can be grouped into roles and then mapped to users or groups. The privileges themselves are defined by VMware on the objects and properties contained in the system and are fixed, meaning client applications cannot alter the underlying privilege definitions. The AuthorizationManager service controls access to specific server objects based on the permissions associated with each object, and the authorization model provides consistent security control regardless of operational context.
+vCenter ships with several predefined roles that embody different levels of access. The Read Only role grants only three system-defined privileges: System.Anonymous, System.View, and System.Read. vCenter also includes a No Access role, where users or groups assigned that role cannot view or modify the objects to which it applies. New users and groups receive the No Access role by default, so access must be explicitly granted rather than revoked. The operator role is the most restricted authorization level, allowing users to view information about vCenter but not alter its configuration. When a predefined role does not meet operational needs, administrators can define custom roles containing only the minimum set of required privileges. This custom role capability, combined with permission propagation to vSphere objects, enables organizations to tailor access to the exact scope needed for each user or group.
+Cryptographic operations privileges provide an additional layer of fine-grained access control. The default Administrator system role includes all Cryptographic Operations privileges, while a separate No Cryptography Administrator role supports all Administrator privileges except for cryptographic operations. Administrators can clone the No Cryptography Administrator role and create custom roles with only specific Cryptographic Operations privileges, limiting what users can do with virtual machine encryption and decryption. Only users who are assigned the Cryptographic Operations privileges can perform those operations.
+VCF Operations implements its own RBAC model where users can only perform the actions that their permissions allow. Each user must have a unique account with one or more roles assigned, and administrators can assign roles to user groups and restrict object access based on role permissions. Access rights are fine-grained, covering actions such as adding, editing, or deleting dashboards, and viewing, configuring, or managing objects. Privilege-based access control restricts users without appropriate privileges from viewing collected data for specific objects. The Access Control interface provides granular permission management through expandable category trees where administrators can apply or modify permissions for selected roles. A ReadOnly role is available that provides read-only access, restricting write actions such as create, update, or delete. The platform documentation recommends configuring both local VCF Operations users and vCenter users with only the privileges they need in the environment, rather than assigning overly permissive roles. vCenter roles and privileges cannot be viewed or edited from within VCF Operations, maintaining separation of privilege management between the two components.
+NSX implements role-based access control to restrict system access to authorized users by assigning users roles with specific permissions. NSX defines scoped roles including Network Admin, Network Operator, Security Admin, and Security Operator, where permissions within a project apply only within the scope of that project and not for the entire NSX system. When these roles are assigned in NSX, the scope can be set to all projects and VPCs, or to selected projects and VPCs, enabling fine-grained access boundaries across the networking layer.
+VCF Automation governs project access through predefined roles and supports role-based access control through group membership and role assignment management. System administrators with the Manage General ACL right can create, modify, and remove specific access control lists using the accessControls API, providing programmatic control over access permissions. The cloud_admin service role satisfies the minimum service role requirement for VCF Automation API access, while the Cloud Administrator group has host switch-level permissions, so administrative actions are scoped to defined capabilities.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS) within VCF, access control operates at two layers: the vSphere Namespace layer and the Kubernetes cluster layer. At the namespace layer, vSphere Namespaces support three permission roles assigned to VCF SSO users and groups: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access to VKS cluster objects with no permissions mapped to Kubernetes roles inside the cluster). The VCF Consumption CLI enforces these role assignments: users without sufficient permissions on the vSphere Namespace cannot connect to Supervisor or VKS clusters as VCF SSO users, and the system returns an explicit "Error from server (Forbidden)" response that makes enforcement directly observable. Supervisor applies a role separation pattern where DevOps and Platform Operators receive non-admin or custom roles, while Developers receive read-only or no roles. Specific operations require explicit privilege grants beyond general administrative roles: adding Supervisor Services to VMware vCenter requires the Manage Supervisor Services privilege on the vCenter system, and administering content libraries for VKS clusters requires specific vSphere role permissions that must be individually assigned when using a custom role rather than the vSphere Administrator role. The Namespace Owner, Edit, and View roles do not have access to vSphere Cluster, vSphere Namespace Inventory, or vSphere Namespace resources, while vSphere Administrator and Supervisor Administrator roles have varying levels of access to these resources, maintaining separation of duties between platform and workload operations.
+Within VKS clusters, access control is defined through Kubernetes Role-Based Access Control (RBAC) using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings. These objects specify which API groups, resources, and verbs a subject (user, group, or service account) may act on, scoped either to a specific namespace or across the entire cluster. VKS RoleBinding subjects must contain either a VCF SSO user name or a VCF SSO group name in the name parameter to grant access, tying Kubernetes RBAC directly to the platform identity provider. For VKS clusters deployed on a custom ClusterClass with VKS 3.2.0 and later, RBAC permissions can additionally be granted to users authenticated through an external OIDC provider using ClusterRoleBinding objects that bind ClusterRoles to individual users identified by their OIDC identity or to groups from the OIDC provider. Built-in ClusterRoles support tiered access: the view ClusterRole grants read-only access to most namespace objects without permitting visibility into roles or role bindings, and the edit ClusterRole adds read/write access to most objects but does not permit modification of roles or role bindings, containing the reach of any single identity. Kubernetes RBAC includes a privilege escalation prevention mechanism at the API level: a user can create or update a RoleBinding only if they already hold all the permissions contained in the referenced role, and this restriction applies even when the RBAC authorizer is not otherwise active so that the check remains in force regardless of authorizer configuration. Where explicit delegation is required, administrators can grant the `bind` verb on a specific Role or ClusterRole to authorize a user to create bindings for that named role without requiring the user to hold all of its permissions; the `escalate` verb on roles and clusterroles in the rbac.authorization.k8s.io API group provides a parallel mechanism to authorize controlled role escalation when that operation is intentionally permitted. The Kubernetes documentation included in VCF recommends using specific resources and verbs rather than wildcard entries, enforcing least-privilege access to Secret objects through RBAC, and applying strict RBAC policies that limit access to system namespaces. Service accounts are governed by the same RBAC mechanism, allowing workloads to receive only the minimum permissions required to function correctly, and fine-grained role bindings to particular service accounts are preferred over broader grants. Administrators can scope IAM role trust policies to specific service accounts and namespaces to further constrain workload permissions.
+Pod Security Admission (PSA) provides workload-level enforcement within VKS clusters through three profiles: Privileged (unrestricted, allows privilege escalation), Baseline, and Restricted. The Restricted profile targets least-privilege pod execution by requiring non-root execution, limiting Linux capabilities, and blocking privilege escalation at the pod level. Pods can be further constrained through security contexts, where settings such as runAsUser, capabilities, seccomp, AppArmor, and readOnlyRootFilesystem restrict what container processes may do at runtime. Namespaces that permit privileged workloads should establish access controls that reflect the principle of least privilege. ValidatingAdmissionPolicy resources allow administrators to define fine-grained policy rules specifying which API groups, operations, and resources fall within the scope of enforcement, providing a declarative mechanism to express access control requirements across the cluster.
+The Secret Store service, available as a Supervisor Service, enforces its own RBAC layer with distinct roles for administrators, DevOps engineers, and application tenants, scoping sensitive data distribution to specific roles rather than making it broadly accessible to all cluster users. Harbor, available as a standard package on VKS clusters through VCF Services consumption, enforces role-based access control to manage access to container images and other artifacts stored in the registry. Argo CD, also available as a standard package, supports local account authentication with global RBAC policies that define role-based access control through policy rules and group mappings that control account permissions and resource access.
+VCF SSO supports multiple authentication methods including username token (signed and plaintext), X.509 certificate, and holder-of-key token authentication. Certificate-based authentication enables secure service-to-service communications within the platform.
+VCF provides the platform-level identity and role-based access control infrastructure on which VMware Private AI Services (PAIS) relies. Within that foundation, PAIS adds AI-specific service, data, and catalog access controls that restrict access to authorized users and groups across the AI workload layer.
+PAIS enforces access to model inference endpoints through OIDC group-based authorization configured in the PAISConfiguration custom resource. The authorizedGroups field specifies which identity provider groups are permitted to call PAIS; accounts outside the named groups are denied access. The OIDC integration is configured with issuer URL, client ID, and scopes that include openid, groups, and offline_access, so group membership is evaluated at the identity provider and carried into the service through standard OIDC group claims. The groups claim name itself is configurable, and PAIS supports Extra Audiences for additional OAuth 2.0 clients that PAIS will accept when validating the access token. Activating PAIS requires coordination with an OIDC provider administrator, making access configuration an explicit administrative act rather than a default-open posture.
+The Grafana observability interface for PAIS applies the same OIDC group model for role-based access. A role-mapping expression assigns the Admin role to users whose OIDC group claims match the configured pais-access-group attribute path, and the Viewer role to all other authenticated users. This two-tier assignment scopes administrative control of the observability platform to a designated group while keeping monitoring data accessible to authenticated PAIS users.
+PAIS model endpoints support authentication through a harbor-pull-secret-readonly credential that restricts access to container images stored in private registries, and PAIS integrates with Harbor registries as the model storage backend with authentication and certificate-based trust required for model retrieval. Harbor project-based permissions restrict access to ML model artifacts and training data stored in the Model Gallery; read-write access to a Harbor project is required to upload or modify models, and project membership is scoped to explicitly authorized users.
+PAIS catalog items in VCF Automation are shared with selected project members through project-based permissions. Users requesting AI catalog items must have permissions granted by organization administrators, and the organization administrator must assign the required user role before users can deploy deep learning VMs. VI administrators must have appropriate permissions on the vSphere cluster to deploy deep learning VM templates. This administrator-mediated model scopes AI infrastructure access to explicitly authorized principals. When running VMware vCenter 8.x, VCF SSO must be configured to access PAIS namespaces from VCF Automation; on vCenter 9.x the SSO configuration step can be skipped because the integration is already present.
+Knowledge Bases and linked data sources in PAIS use personal access tokens generated from user account settings for programmatic access, scoping API-driven retrieval to the issuing user. VCF Automation separates provider-level and tenant-level administrative operations through distinct credential scopes: a PROVIDER_ADMIN_ACCESS_TOKEN is required for provider-level operations such as registering vCenter instances, while a TENANT_ADMIN_ACCESS_TOKEN is scoped to organization administrator operations. This separation limits what any single credential can affect across the PAIS deployment.</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
@@ -741,9 +758,12 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to identity and access management by providing identity-aware network enforcement through Identity Firewall, which integrates with Active Directory to apply firewall policy based on authenticated user identity rather than IP address alone. Identity Firewall supports assigning Active Directory users and groups as source criteria in both distributed firewall rules and gateway firewall rules, applying to tier-0 and tier-1 gateways. This allows organizations to enforce network access policy by user or group membership rather than relying solely on IP-based controls.
-Within its management plane, the Security Services Platform implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles govern access to security policy management, analytics, incident response, and diagnostic functions across the platform. Network Detection and Response enforces the same five-role RBAC model for triage operations such as viewing detections and campaigns, and for configuration operations including SIEM integration management. For authentication, the Security Services Platform supports Active Directory and OpenLDAP as external identity sources, with one identity source configurable at a time. The License Hub integrates with external identity providers to store and manage user and group information for access delegation.
-Centralized IAM for organizational users, including VCF SSO, MFA, and directory lifecycle management, is handled by VCF and falls outside vDefend's scope.</t>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -766,11 +786,11 @@
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) incorporates multiple identification and access management mechanisms that support organization-wide IAM controls within the data services layer.
-DSM implements role-based access control with two defined roles: the DSM Admin role, which can create, monitor, and manage all data services in the environment, and the DSM User role, which is restricted to managing and monitoring data services within the namespaces to which the user has been granted access. These roles are assigned at user creation time and govern what each user can see and do within the DSM interface. The Permissions view in the DSM dashboard provides administrators with a centralized location for creating, monitoring, and managing all configured users.
-DSM supports two identity sources, which can be used independently or together. Local users are created directly within DSM, with credentials validated by matching email address and password. LDAPS users are sourced from a configured LDAP identity provider, allowing organizations to extend their existing directory service into DSM. When LDAPS is configured, administrators can import users from the directory provider and assign them DSM Admin or DSM User roles. DSM also supports group-based access control: Directory Service Groups from the LDAP provider can be assigned roles directly, so group membership in the external directory determines access level in DSM without requiring per-user assignments.
-At the database level, DSM extends authentication controls beyond the platform management layer. MySQL database instances support LDAPS authentication using Active Directory. PostgreSQL and other database instances support host-based authentication (HBA) rule configuration, which determines which clients are permitted to authenticate to a given database instance. SQL Server instances support Windows Authentication through Active Directory integration, enabling Kerberos-based authentication so that clients such as SQL Server Management Studio running on domain-joined machines can authenticate via single sign-on. SQL Server also uses contained database users, where identity information resides within the database itself rather than at the server level. Administrators can configure SQL Server instances with either a SQL User or Windows Principal as the primary administrator identity, with Windows Principal available for Active Directory-integrated clusters. An internal dsm_mgmt management login restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context.
-Namespace isolation adds a further access boundary. DSM namespaces enforce role-based access control that allows multiple users to work jointly on data services within a namespace while remaining isolated from data services in other namespaces. This supports least-privilege access within multi-tenant deployments.</t>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
@@ -780,14 +800,15 @@
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides a dedicated administrative identity and access management plane through the Avi Controller, supporting multiple authentication methods and fine-grained authorization controls that allow organizations to implement IAM policies across both the management plane and the application delivery layer.
-For administrative access, the Avi Controller supports local user accounts, LDAP and LDAPS directory integration, SAML-based federated authentication (including integration with Workspace ONE Access for catalog-based application access), basic authentication, and OAuth/OIDC for API access. Auth Mapping Profiles allow organizations to map external directory groups to specific roles and tenants, so that group membership in an external identity provider directly controls what a user can access within Avi.
-Authorization is handled through role-based access control (RBAC) with object-level granularity. Avi's extended granular RBAC uses markers, which are labels assigned to objects, to enable fine-grained authorization based on object ownership and classification. Permission categories cover Operations (including alerts, actions, and traffic capture) and Administration (including controller, tenant, user, role, and system configuration management). This allows restrictions so that a user's permissions apply only to the specific resources matching the markers assigned to their role. RBAC covers object categories including Virtual Services, Application Profiles, SSL/TLS Certificates, Certificate Management Profiles, Cloud definitions, TCP/UDP Profiles, Persistence Profiles, Health Monitors, Analytics Profiles, IP Address Groups, String Groups, SSL/TLS Profiles, PKI Profiles, and Authentication Profiles, with distinct read and write access levels configured per object type.
-For multi-tenant deployments, Auth Mapping Profiles support tenant isolation with configurable user group to role mappings, allowing organizations to enforce separation between teams or business units operating within the same Avi Controller.
-The Avi License Hub supports role-based access control through an external identity provider, with three predefined roles: Enterprise Admin (full access for all operations, including upgrades and authentication configuration), Auditor (view-only access for tracking activity without making changes), and Support Bundle Collector (restricted to collecting system logs and diagnostics). Management interface access is further controlled through restrictions on allowed ciphers and HMACs for management sessions.
-For deployments involving the Avi Kubernetes Operator (AKO), Kubernetes RBAC policies can be applied to AKO Custom Resource Definitions (CRDs) to enforce stricter access control over routing configuration for specific user groups. The Avi Controller also implements RBAC at the Kubernetes and OpenShift cluster level by assigning tenants and roles to user accounts.
-At the application layer, Avi can enforce client authentication using OAuth, SAML, JWT token validation, and mutual TLS with client certificates, extending access control to the traffic flowing through virtual services rather than only to the management interface.
-Organizations are responsible for defining roles, mapping directory groups to permissions, establishing naming conventions for markers, and maintaining user lifecycle processes. Avi provides the technical mechanisms; the governance and operational processes for identity management must be organized by the teams managing the deployment.</t>
+          <t>VMware Avi Load Balancer (Avi) provides a native role-based access control (RBAC) system on the Avi Controller that supports least-privilege access enforcement for all administrative operations on the application delivery plane.
+The Avi Controller RBAC model assigns each user a role that determines their level of access: write, read, or no access to individual resource types. Roles operate at the object level, with write access grantable to specific objects including Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profiles. This granular object-level permission model allows administrators to scope each user's access to only the resources required for their function.
+For more precise scoping, the Avi Controller supports Extended Granular RBAC using markers. Labels attached to Avi resources allow roles to restrict user permissions to a specific subset of objects within a resource type, rather than granting blanket access across all objects of that type. The allow_unlabelled_access parameter in the role object controls whether a role can access resources that do not carry a matching label, and the restrict_cloud_read_access field in controller properties further enforces label-based access on cloud objects. The Avi Controller also supports granular RBAC per field, which allows update permissions to be scoped to specific fields within an object while restricting changes to other fields.
+Auth Mapping Profiles enable integration with external identity directories such as LDAP, SAML, TACACS+, and OAuth/OIDC. Each profile maps external identity groups to specific Avi roles and tenants. The "Any Group or Any Attribute" fallback rule in an Auth Mapping Profile should be configured to the least-privileged role so that users not matched by a more specific mapping receive minimal access by default.
+The Avi Controller's service account for VMware vCenter integration follows a least-privilege model. The vCenter Cloud Connector requires a minimal set of permissions assigned to the vCenter user account. Integration between the Avi vCenter Cloud Connector and vCenter requires two roles: Avi-Global-Role with global privileges (assigned with the "Propagate to children" option to propagate permissions to all child objects) and Avi-Folder-Role assigned to the specific folder or folders containing Service Engine VMs in the vCenter inventory. The vCenter permissions required cover Change Configuration, Edit Inventory, Interaction, and Provisioning capabilities scoped to Service Engine management needs.
+The Avi Cloud Console enforces access control through two tiers: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration operations.
+For Kubernetes environments, the Avi Kubernetes Operator (AKO) custom resource definitions (CRDs) can be governed by Kubernetes RBAC policies to restrict access to a defined group of users, supporting least-privilege enforcement on the Kubernetes control plane.
+The Avi Web Application Firewall (WAF) supports authorization rules that enforce path-based access control by evaluating client domain and request path conditions. When authorization rule conditions are met, access is allowed; otherwise, a 403 response is returned, restricting access to application paths based on defined policies.
+Organizations must define role structures and Auth Mapping Profile rules that reflect the least-privilege assignments appropriate to each administrative function. The RBAC mechanisms described here apply to the Avi application delivery plane; least-privilege enforcement across the broader VCF environment is handled by VCF's own access control systems.</t>
         </is>
       </c>
     </row>
@@ -819,21 +840,23 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>VCF provides account management capabilities for the infrastructure platform's own user, group, system, and service accounts. The broader organizational governance of account management across all enterprise systems is outside VCF's scope.
-VCF SSO is the centralized identity service for the platform. Administrators manage individual and group accounts through VMware vCenter, and can integrate external identity sources (Active Directory, LDAP, OIDC) so that account lifecycle management follows existing enterprise directory services. vCenter also supports System for Cross-domain Identity Management (SCIM), enabling automated provisioning and deprovisioning of user and group accounts when synchronized with a supported external identity provider. VCF Automation also supports LDAP, OIDC, and SAML-compliant identity providers for user authentication, allowing consistent identity federation across the stack.
-VCF Operations provides a consolidated view of accounts across the VCF stack through its password management dashboard, including account statuses and remediation needs. This centralized visibility helps administrators track account states and identify accounts requiring attention. The password management interface, accessible to users with the Administrator role, supports password rotation and remediation for service account passwords across integrated components. Administrators should plan maintenance windows when rotating passwords for multiple accounts to avoid service interruptions.
-At the compute layer, VMware ESX hosts support local account management through the HostLocalAccountManager interface, which allows administrators to create and manage user accounts on individual hosts. In a properly configured VCF environment, access to ESX is brokered through vCenter rather than managed directly on each host. The vSphere Web Services API documentation recommends that user accounts be given the minimal number of privileges required for their roles, consistent with least-privilege principles. For guest virtual machines, vCenter allows administrators to configure VCF SSO user mappings to guest operating system accounts, enabling centralized control over which VCF SSO users can access accounts within guest VMs.
-VCF Operations offers account management capabilities including the ability to add, edit, remove, and import user accounts, manage roles, define object-level access for users assigned to specific roles, and manage user group membership. Each user must have a unique account with one or more roles assigned. User accounts can be associated with specific objects in the VCF Operations cluster to control the scope of access. VCF Operations supports importing user accounts from external sources such as LDAP databases or single sign-on servers, allowing organizations to integrate their existing directory services with VCF Operations access control.
-VCF Operations for Networks supports local user management with role-based access control, where users are assigned roles during account creation.
-NSX Manager supports management of local user accounts through both its user interface and CLI. Through the UI, administrators can configure password expiration, deactivate users, and reset passwords. Through the CLI, the admin user can manage local user account passwords, change user names, and add, delete, or deactivate user accounts. NSX Manager has one active local account out of the box (admin), which cannot be deleted or deactivated, and best practice is to keep all other local user accounts deactivated.
-VCF Automation allows system administrators to create other system administrator and user accounts within the provider organization. Service accounts are created by administrators who hold the View Service Accounts and Manage Service Accounts privileges, providing controlled delegation of service account creation. These service accounts authenticate using API access tokens that rotate after each use. Organization owners can add and manage other users within their scope.
-The VCF Consumption layer (VMware Kubernetes Service (VKS) and vSphere namespaces) introduces a structured model for service and application account management governed through the Kubernetes API. Kubernetes ServiceAccount resources are namespace-scoped objects that provide distinct, non-human identities for application pods, in-cluster services, and other entities that need to authenticate to the Kubernetes API server. Service accounts are created automatically when namespaces are provisioned or on demand through API calls, and each is bound to roles through RoleBinding or ClusterRoleBinding resources, enabling RBAC-governed access at either namespace or cluster scope. The Kubernetes documentation advises against granting cluster-wide roles to all service accounts; per-namespace permission management is the recommended practice to maintain proper access control boundaries. Service account tokens should be scoped to minimize their usage to only the application that requires them, and the Kubernetes RBAC model specifies that user account creation must block reuse of deleted usernames so that newly created accounts with identical names do not inherit the permissions of prior accounts. Service account definitions should be included in configuration bundles for complex containerized workloads to support portability of system component identities.
-Kubernetes provides lifecycle controls for service account credentials. The LegacyServiceAccountTokenCleanup feature gate enables automatic cleanup of Secret-based service account tokens that have not been used within a specified time period, with a default retention period of one year, supporting governance of stale credentials. Infrastructure credentials, including certificates used by service accounts and cluster components, should be configured with short lifetimes and automated rotation to support ongoing account lifecycle management. Separating ServiceAccount creation from human user onboarding enables distinct audit strategies for each account type, and production VKS clusters should be configured with multiple accounts holding differentiated levels of access to different namespaces rather than relying on a single administrative account. IAM role trust policies for VKS workloads should be scoped to specific service accounts and namespaces to enforce least privilege at the workload level.
-For Windows workloads running in VKS clusters, Supervisor supports Group Managed Service Accounts (gMSAs). When Windows node pools are joined to an Active Directory domain, gMSAs provide automatic password management, simplified service principal name (SPN) management, and delegated administration across multiple servers. Access to gMSA credentials is controlled through Active Directory security groups, and the VKS cluster configuration specifies the relevant security group through the gmSAControlSecurityGroupDN setting. Configuring gMSA support for Windows node pools also requires an Active Directory service account with service principal names following Kerberos naming rules, and the VKS Security Group must be granted delegation rights to that account. HostProcess containers running as local user accounts use ephemeral local user accounts that are created and joined to a specified user group at container initialization, eliminating the need to manage passwords for those local accounts.
-The Argo CD Supervisor Service supports local account creation through the spec.localAccounts field, allowing named accounts to be defined for GitOps workflows. Argo CD RBAC policy rules and group mappings control account permissions and role assignments, including the ability to grant administrative roles to specific local accounts. Both local accounts and OIDC-authenticated users can be governed through the same RBAC policy framework. Argo CD cluster registration creates a service account with cluster-level privileges to manage the target cluster, so administrators should review and scope those privileges to what is operationally required.
-Avi Load Balancer uses a combination of roles and tenants to determine user account authorization, supporting multi-tenant access control for load balancing services.
-Role-based access control is available across all VCF components, supporting the principle of least privilege through granular role definitions. User accounts should be given the minimal set of privileges required for their responsibilities.
-While VCF provides these technical account management mechanisms across its components, proactive account governance requires organizational policies and procedures that define account lifecycle management, periodic access reviews, temporary and guest account provisioning standards, and account termination processes. These governance activities fall outside the scope of what VCF provides as a platform.</t>
+          <t>VCF enforces role-based access control across all major platform components, restricting access to technology assets, applications, services, and data based on assigned roles with defined permissions. RBAC is applied consistently throughout the stack, covering compute management, networking, storage, operations management, automation services, and Kubernetes workloads.
+VMware vCenter provides fine-grained authorization through a permissions model that associates roles with users or groups on objects in the vCenter inventory hierarchy. Roles are sets of privileges, and vCenter defines three authorization levels: operator (read-only access to configuration, the most restricted level), administrator (read and write access to configuration but cannot manage user accounts, intended for users who alter vCenter configuration or exercise control functions), and super administrator (full control). When a predefined role is modified, the updated privilege set applies immediately to all users assigned that role. New roles are created with three default system-defined privileges (System.Anonymous, System.Read, System.View), and administrators add specific privileges to match the intended access level. vCenter also supports creation of custom roles with granular privilege assignment and permission propagation to vSphere objects in the inventory hierarchy.
+NSX implements RBAC by assigning users predefined roles with specific permissions. The platform includes 15 built-in roles: Enterprise Admin, Admin, Network Admin, Network Operator, Security Admin, Security Operator, Cloud Admin, Cloud Operator, Cloud Project Admin, Load Balancer Admin, Load Balancer Operator, VPN Admin, GI Platform Admin, NSX Platform Admin, and Support Bundle Collector. These roles follow the principle of least privilege, with each role carrying only the permissions needed for its functional area. NSX RBAC applies across multiple operational domains including inventory, plan and troubleshoot, and system management functions. NSX also supports project-scoped RBAC, where Network Admin, Network Operator, Security Admin, and Security Operator roles assigned within a project have permissions limited to that project's scope rather than the entire NSX system. This project-scoped model extends to VPCs and subnets within the NSX networking hierarchy. For organizations that need role definitions beyond the built-in set, NSX allows creation of custom roles tailored to specific operational requirements. Only an Enterprise Administrator can assign the role management permission to a custom role. NSX Federation extends RBAC to multi-site deployments, applying the same access control model across federated NSX instances. Principal identities, which are used for service-to-service authentication local to NSX, also support RBAC role assignment, so automated integrations operate under the same access control model as human users.
+VCF Operations enforces RBAC through the assignment of service roles to users and groups. Administrators configure role-based permissions through the Roles tab under Infrastructure Operations, where individual permissions can be selected or deselected to define what each role is authorized to do. The System Administrator role includes rights covering approvals, audits, certificates, datastores, edge clusters, integrations, LDAP settings, namespaces, proxy rules, system settings, tokens, and truststore operations. Administrative operations such as password management require authentication with a user assigned the ADMIN role. VCF Operations also defines its own roles within vCenter, with privileges named using a convention that appends the role to the product name (such as VCF Operations ContentAdmin Role and VCF Operations PowerUser Role). The PowerUser role has privileges to perform the actions of the Administrator role except for user management and cluster management. A further restricted PowerUserMinusRemediation role excludes remediation actions in addition to those limitations. A vCenter administrator assigns these roles to users, and VCF Operations maps vCenter users to the appropriate role.
+vSAN supports RBAC and permissions management for authentication and authorization of storage operations. The vSAN Security Configuration Guide provides guidance on configuring these role-based controls for storage infrastructure.
+VCF Automation governs access through multiple RBAC mechanisms at different scopes. At the organization level, rights bundles assign specific API permissions to roles including Organization Administrator, Organization Auditor, and Organization User. Group membership and role assignment are managed through the Access Control interface, and organization administrators can edit role assignments for groups at any time. At the project level, VCF Automation defines three distinct roles: administrators, members, and viewers, providing tiered access to project resources and operations. VCF Automation also governs blueprints, catalogs, content libraries, and custom entities through its role model. The Assembler Administrator role has read and write access to the entire user interface and API resources, while other roles have progressively narrower permissions.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), VCF enforces RBAC through two complementary control layers. At the vSphere layer, vSphere Namespaces assign three permission roles: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). At the Kubernetes layer, the Kubernetes RBAC authorization framework governs access to all API server requests through four core objects: Roles define permissions scoped to a single namespace, ClusterRoles define permissions applying cluster-wide, and RoleBindings and ClusterRoleBindings associate those roles with authenticated subjects such as users, groups, or ServiceAccounts. Permissions are purely additive with no deny rules, and administrators can restrict access to individual resource instances by name using the resourceNames list in role rules.
+VKS clusters integrate with VCF SSO so that Kubernetes RoleBinding objects grant RBAC permissions directly to VCF SSO users and groups. This means the same identity provider that governs VMware vCenter access also governs Kubernetes cluster access, providing a consistent identity model across both the platform and workload layers. Cluster operators use kubectl or the Kubernetes API to assign role permissions to developers and other personas with defined responsibilities.
+Kubernetes RBAC also governs ServiceAccounts, which provide discrete identities for pods and automation processes. This separation allows human access and workload access to be governed independently, with each scoped to the minimum permissions required for its function. ServiceAccounts follow the principle of least privilege by receiving only the minimum set of permissions required to function correctly, and RBAC should be applied to Secret objects to enforce least-privilege access to sensitive data stored within namespaces.
+The Kubernetes RBAC API includes built-in controls against privilege escalation: the API prevents users from editing roles or role bindings to gain permissions beyond those they already hold, and this enforcement applies at the API level regardless of the authorization mode in use. Role-binding authority can be explicitly delegated by granting a user permission to perform the bind verb on a specific Role or ClusterRole, limiting the roles that identity can delegate to others.
+In multi-tenant VKS deployments, RBAC is the primary mechanism for isolating tenants within a shared cluster. Administrators use Role and RoleBinding objects at the namespace level to restrict each tenant's access to its assigned namespaces, and ClusterRole and ClusterRoleBinding objects to control access to cluster-level resources, blocking unprivileged users from crossing tenant boundaries.
+Supervisor services deployed on VKS clusters extend RBAC to their own access models. The Secret Store Supervisor Service enforces role-based access control across administrator, DevOps engineer, and application tenant roles, controlling who can manage and retrieve sensitive data. The Argo CD Supervisor Service implements RBAC through a configurable policy field using Casbin syntax, with the spec.rbac.policy setting defining role assignments and permission rules; policy rules (p rules) control account permissions including the ability to grant admin roles to specific local accounts, and group mappings (g rules) assign accounts to role groups.
+VMware Private AI Services (PAIS) provides role-based access control scoped to its AI services and AI workload delivery components. The central mechanism is OIDC group-based authorization for PAIS. When activating PAIS in an organization namespace, administrators populate the authorizedGroups setting with one or more OIDC group identifiers so that only users who belong to those groups can access the service. The OIDC configuration supports a configurable groups claim name through the oidc-groups-claim setting, with the groups claim carried in the Access Token and evaluated at access time. PAIS requires an OIDC provider configured as a public client application with Authorization Code and Refresh Token grant types, and it can be configured with one OIDC provider. Additional OAuth 2.0 client identifiers can be accepted by configuring Extra Audiences through the oidc-extra-audiences setting when the OIDC provider issues tokens for multiple audiences.
+PAIS extends the same identity model to the Grafana observability platform used for PAIS metrics. Grafana role assignment is configured through the grafana-oidc-role-mapping property using an expression such as contains(groups[*], 'pais-access-group') &amp;&amp; 'Admin' || 'Viewer', so OIDC group membership maps automatically to Grafana Admin or Viewer roles. PAIS uses the same OIDC provider for Grafana authentication that it uses for service access.
+For machine learning model storage, the Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as the model storage backend and requires authentication and certificate-based trust for model retrieval. PAIS is compatible with OCI-compliant registries from other vendors when deployed in a disconnected or air-gapped environment, and the project-scoped access controls apply to the chosen registry.
+Access to PAIS catalog items for GPU-accelerated VKS clusters and other AI workloads is governed through project-based permissions in VCF Automation. PAIS custom forms in blueprints can be modified to control user inputs at request time, scoping which configuration choices a requester can make when provisioning AI workloads. Knowledge Base data sources used by PAIS retrieval augmented generation require authenticated access to external repositories, including user name and password authentication for SharePoint On-Premises data sources and access keys with list and read permissions on the target bucket for Amazon S3 compatible stores. PAIS uses a CA trust bundle for secure communication with external services and databases.
+These PAIS-specific controls operate at the AI services and workload layer. Access to the underlying compute, storage, and networking infrastructure is governed by platform-level RBAC in VCF, including VCF SSO and VMware vCenter role assignments, and database-level access for vector and operational data is governed by Data Services Manager. PAIS adds service-level and workload-level RBAC for AI-specific assets on top of the VCF platform foundation rather than replacing those platform controls.</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -843,9 +866,12 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Within its own management plane, VMware vDefend (vDefend) Security Services Platform (SSP) maintains two built-in local user accounts: an admin user with the Enterprise Admin role providing full management access, and an audit user with the Auditor role providing access to APIs and services for system auditing. In vDefend, SSP defines five roles at the platform level: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector, enabling separation of duties across administration, auditing, security engineering, security operations, and diagnostic support functions.
-SSP enforces password policies for local accounts; passwords must meet defined complexity requirements and can be changed or reset through the Platform and Instance Management interfaces. Remote users and remote user groups are managed through the System &gt; User Management interface, where administrators assign and modify roles. SSP supports directory-managed accounts through external identity providers such as Active Directory over LDAP and OpenLDAP, extending account management to enterprise identity sources; local accounts remain available even when external identity providers are disconnected.
-This coverage is limited to vDefend's own management-plane accounts. Organization-wide account management for individual, group, system, service, application, guest, and temporary accounts across all technology assets is outside vDefend's scope and must be addressed through dedicated identity and access management platforms.</t>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -869,15 +895,11 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides account management mechanisms for the accounts it directly governs: the DSM administrator account, DSM user accounts (local and LDAPS-federated), database owner accounts, and the internal service account DSM uses to authenticate to VMware vCenter.
-DSM supports two identity sources for user accounts. Local users are created directly within DSM using an email address as the login username and a password. LDAPS users are federated from a configured directory server, allowing organizations to manage DSM access through their existing identity infrastructure. Administrators can configure one or both identity sources depending on organizational requirements. For LDAP-federated accounts, DSM supports group-based access control by assigning roles to Directory Service Groups, so that group membership in the directory server determines DSM access. This is configured under Administering Data Services Manager &gt; Managing LDAP Users in Data Services Manager.
-DSM implements role-based access control with two role types. The DSM Administrator role has full visibility and maintenance capabilities across all data services and is responsible for managing DSM settings including LDAPS and SMTP configuration, database backups, and high availability settings. The DSM Administrator also manages namespaces and permissions for database ownership. The DSM User role allows individuals to provision and manage their own databases and perform database lifecycle operations while having no visibility into other users' data services. DSM User roles support namespace-level access controls that can be configured at the time a user account is created, scoping access to specific Supervisor namespaces. This separation restricts administrative capabilities to designated personnel and scopes each user to the resources they own.
-DSM user accounts maintain failed_login_count, last_failed_login_time, locked_state_start_time, and force_password_change attributes to enforce account lockout and password management policies. These fields track authentication failures, record when an account entered a locked state, and flag accounts that must change their password at the next login. This is configured under Administering Data Services Manager &gt; Managing LDAP Users in Data Services Manager &gt; Create Directory Service Groups Using the Data Services Manager UI.
-The initial DSM administrator account is created during deployment of the DSM Provider Appliance and is mandatory; it cannot be deleted. When access needs to be suspended without disrupting running databases, administrators can reset a local user's password and delegate management of the user's databases to a different user rather than deleting the account.
-For database-level accounts, DSM allows database owners to set or change the database administrator password at any time while the database is online. DSM also supports LDAPS user creation for PostgreSQL database authentication and access control, enabling directory-managed credentials for database access rather than locally maintained passwords.
-DSM introduces SQL Server as a managed database engine, with specific account management controls for SQL Server instances. DSM deactivates the default sa account and uses a reserved internal account, dsm_mgmt, with sysadmin privileges for management operations. The dsm_mgmt account restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context. DSM uses contained database users for SQL Server database access, so users authenticate directly against the database rather than through a server-level login. For SQL Server clusters in Active Directory environments, DSM requires a service account that is a standard Active Directory user and a member of the Domain Users group. DSM can also be configured with a privileged Active Directory account to automate the management of service principal names (SPNs) and DNS records for SQL Server clusters. The dbo user is mapped to administrator-controlled identities for SQL Server database access.
-DSM maintains an internal service account for authentication to vCenter. This account is required for DSM to provision and manage infrastructure resources. DSM maintains service account rotation logs that administrators can review to diagnose vCenter authentication failures. Administrators should monitor for alerts indicating that the service account has expired, as an expired service account causes ongoing DSM operations to fail.
-DSM's account management capabilities address the technical layer of this control within its scope. Broader account governance (including formal provisioning and deprovisioning procedures, periodic access reviews, approval workflows for account creation and role changes, and lifecycle management for temporary or guest accounts) requires organizational processes that operate outside DSM. Organizations should establish procedures for reviewing DSM account assignments, managing LDAPS group membership to reflect current job roles, and deprovisioning access when personnel change responsibilities.</t>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
@@ -887,10 +909,14 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer maintains its own account management plane on the Avi Controller, distinct from the underlying VCF infrastructure. User accounts are organized into two categories: local users, whose credentials are stored on the Controller, and remote users, who authenticate through an external authentication, authorization, and accounting (AAA) server such as LDAP or Active Directory. The admin account is a special system account used for initial setup that remains locally authenticated even when the system is configured for remote authentication. Local accounts remain available even if external identity providers such as LDAP or OpenLDAP become disconnected, providing a resilient fallback path for administrative access.
-Account management operations are gated by role-based access control: configuring or managing user accounts requires write access to the Accounts section, as defined by the role assigned to the managing account. Avi provides predefined roles that can be customized or extended by administrators with appropriate access. Each account can be scoped to specific tenants and assigned different roles within each tenant through Tenant and Role assignment, supporting both centralized administration and delegated management across multi-tenant deployments. When a user has access to multiple tenants, the system places them into a default tenant after login. If no additional tenants have been created, all new user accounts are automatically added to the admin tenant. In the VCF for Avi integration, a Provider or Load Balancer Administrator manages resource assignments to enforce quotas and resource boundaries within organization-managed mode.
-User Account Profiles govern account attributes and access controls. All users are attached to the Default-User-Account-Profile by default, which enforces standard lockout thresholds and password policies. Administrators can assign the No-Lockout-User-Account-Profile for accounts that require uninterrupted access, and can create custom UserAccountProfile objects to tailor security policies for different user populations. In the VCF for Avi integration, the system manages two specific accounts for password updates: admin and vcfops-admin, providing a defined account scope for VCF-integrated deployments.
-Account lifecycle operations available through the Controller include account creation, deletion, deactivation, and reactivation. Deletion removes an account from the system entirely. Deactivation suspends access without deleting the account record, and reactivation restores access for a previously deactivated account. These operations are available only to users with write access to the Accounts section, scoping account management authority to authorized administrators. The Avi SaaS Controller supports service account configuration for programmatic and automated access, extending account lifecycle management to service identities within the Avi-managed plane.</t>
+          <t>VMware Avi Load Balancer provides a native, multi-tiered Role-Based Access Control (RBAC) framework that governs all administrative access to the Avi Controller. At the base level, Avi roles assign one of four privilege types to each resource category: Write (full create, read, modify, and delete access), Read (view-only access to configuration, health, and analytics data without modification capability), Assorted (a mixed access level combining permissions across specific operations), and No Access (no access to the resource at all, including the inability to read or list it). Roles are combined with tenants to define the complete authorization settings for each user, scoping what resources a user can interact with and what actions they may take.
+Beyond base privilege levels, the Extended Granular RBAC feature refines access using markers, which are key-value label pairs assigned to Avi objects. A role definition specifies that a user may access only objects bearing labels that match the role's marker set. The allow_unlabelled_access parameter controls whether a user can view objects that lack matching labels, allowing administrators to restrict visibility to labeled objects only. Label groups can be associated with tenants to enforce label-based access policies across the tenant boundary. Multiple label values can be mapped to a single key, enabling flexible classification schemes. This mechanism enables resource-level scoping across tenants and teams: for example, restricting a group of operators to only the virtual services labeled with their team's identifier, without granting visibility into other teams' objects.
+At the finest granularity, Avi implements sub-resource (field-level) RBAC, which scopes which specific fields within a configuration object a given user is authorized to modify. Sub-resource definitions can be combined so that a user can configure multiple fields or features within a single object while remaining restricted from updating others. Label-based permissions for cloud objects extend this field-level control to infrastructure resources managed by the Avi Controller. Virtual service configuration exposes RBAC directly: the RBAC tab in the Virtual Service advanced setup provides label-based access control for health monitors and associated objects, extending role enforcement down to individual service configuration items.
+For GSLB deployments, the Avi Controller enforces RBAC through role references such as Gslb_Group_Enabled and Gslb_Health_Monitor that can be assigned to user accounts with tenant-level scope. These role references apply to follower sites configured with federated JWT profiles, scoping which accounts can modify GSLB configuration.
+The Avi Controller applies RBAC within the License Hub, limiting which users can perform specific actions based on their assigned role.
+For deployments using the Avi Kubernetes Operator (AKO), the Avi Controller implements RBAC by assigning tenants and roles to user accounts at the Kubernetes or OpenShift cluster level. AKO Custom Resource Definitions (CRDs) can leverage Kubernetes RBAC policies to restrict which user groups can configure routing rules, extending the Controller's authorization model into the Kubernetes control plane.
+For deployments on Microsoft Azure, Avi integrates with Azure IAM to control which Azure identities have access to Avi Load Balancer resources hosted in Azure. Administrators can use built-in Azure roles such as Reader (read-only access) or Owner (full access), or define custom roles for finer control over specific resources.
+RBAC configuration is managed through the Users section of the Avi Controller UI. Roles are defined per resource type and then assigned to users within a tenant. Extended Granular RBAC markers are attached to individual Avi objects (virtual services, pools, health monitors, and others) and referenced in the role definition. Sub-resource RBAC is configured as part of the Extended Granular RBAC object, combining field-level restrictions as needed.</t>
         </is>
       </c>
     </row>
@@ -1027,13 +1053,10 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) provides network security controls that contribute to securing cloud instances in line with industry practices. While cloud management spans compute governance, identity management, compliance scanning, and operational monitoring, vDefend addresses the network security dimension through multiple integrated capabilities.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level across all workloads running on VCF. Security policies follow workloads regardless of network location, enabling zero-trust segmentation that limits lateral movement between cloud instances. Administrators define firewall rules using security groups, tags, and dynamic membership criteria, allowing policy to adapt automatically as workloads are provisioned or relocated. Privileged Labels provide a tamper-proof mechanism that anchors firewall rules to immutable labels, preventing virtual machines from leaking out of their assigned security groups. Identity Firewall can be enabled on compute clusters to extend policy enforcement to Active Directory user and group identity, enabling security rules that follow users across workloads. The Gateway Firewall extends protection to north-south traffic at Virtual Private Cloud (VPC) boundaries, and Pre-defined Security Strategies allow administrators to define a baseline security posture for VPCs to establish consistent protection policies.
-vDefend integrates with VCF Automation to allow organizations to define and enforce security postures for workloads within self-service private cloud environments. Groups in vDefend map cloud constructs from VCF Automation into the underlying vDefend infrastructure, enabling policy recognition and enforcement on VPCs, Groups, and virtual machines within namespaces. This integration maintains consistent security postures as workloads are provisioned through automation workflows.
-vDefend IDS/IPS provides signature-based and behavioral intrusion detection and prevention for cloud workloads. Organizations can import custom signatures or integrate with third-party threat feeds, including industry-specific Information Sharing and Analysis Centers (ISACs). Virtual patching capabilities allow deployment of protective signatures before vendor patches are available, reducing the exposure window for cloud instances. In federated deployments, a Global Manager provides centralized management for blocking malicious traffic across all connected Local Manager sites, maintaining and propagating untrustworthy IP address lists based on historical behavior patterns.
-Malware Prevention through Advanced Threat Prevention (ATP) inspects files traversing east-west and north-south network paths. Malware Prevention profiles can be configured to send files to the VMware vDefend ATP Cloud Service for cloud-based analysis, or to process files locally without cloud analysis, without requiring agents on individual instances. Security policies can be defined, propagated, and enforced across Bare Metal servers through Security Services Platform, extending consistent enforcement across physical infrastructure.
-Security Services Platform (SSP) is a modern microservices platform that hosts features that collect, ingest, and correlate network traffic data. SSP includes Security Intelligence, which allows administrators to accept or modify inferred classifications of compute entities as network infrastructure or non-infrastructure services, supporting accurate security policy planning. SSP maintains a centralized repository of current organizational IT assets, including servers, software, and network devices with their configurations, providing an authoritative inventory for policy planning purposes. Network Detection and Response (NDR) provides behavioral analysis and anomaly detection across east-west traffic flows, identifying threats that signature-based detection may miss. NDR data sharing to the vDefend ATP Cloud Service is activated by default and can be configured through System &gt; Privacy, allowing organizations to control whether data is shared to the cloud where data residency requirements apply. SSP has high availability capabilities by default and supports scaling out individual services, including Analytics, Data Storage, Messaging, and Metrics, through System &gt; Platform &amp; Features &gt; Core Services.
-Together, these capabilities address the network security requirements within a broader cloud management control framework, providing workload-level enforcement, threat detection, and traffic visibility for cloud instances.</t>
+          <t>VMware vDefend's Gateway Firewall provides network boundary controls that restrict inbound and outbound traffic to and from publicly accessible systems, limiting network exposure at the perimeter. URL filtering applies access control based on URL categories, URL reputation, and custom URL lists, enabling policy-based governance over what external services and web content internal systems can reach.
+For public web server traffic, IDS/IPS within VMware vDefend includes explicit guidance that such traffic be configured with Prevent or Detect action and never exempted from inspection, treating it as untrusted traffic that requires full IDS/IPS coverage. The Distributed Firewall (DFW) supports App Strategy, an intent-based security mode that allows administrators to select predefined strategies such as "Allow Outgoing Traffic" or "VPC Isolation" to automatically generate read-only system rules, reducing the risk of misconfiguration for publicly exposed workloads. The DFW also supports FQDN-based filtering through allowlist and denylist rules configurable with source groups, destination groups, and DNS context profiles, enabling domain-name-based policy enforcement for traffic to and from publicly reachable systems.
+The Gateway Firewall supports inter-project isolation by denying all inter-project communication except for essential infrastructure protocols such as DHCP, DNS, NTP, and ICMP, helping to contain publicly accessible workloads within defined network boundaries. The Security Services Platform supports publishing environment rules, inventory assets, and policies as distinct operations that can be applied individually or collectively across infrastructure tiers, enabling segmentation of publicly exposed workloads from the broader environment.
+VMware vDefend addresses network-layer controls only and does not govern web application content, content management system publishing workflows, or organizational review processes for publicly accessible information.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1059,12 +1082,9 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that contribute to the implementation of cloud management controls for database-as-a-service workloads deployed on VCF.
-Data service policies are a central control mechanism in DSM. Administrators define and configure these policies to govern how database clusters are provisioned, what infrastructure resources they may consume, and which organizational standards apply. When integrated with VCF Automation, data service policies can be applied across multiple tenants or organizations, with each tenant or organization required to adhere to its prescribed configurations. Administrators can tailor policies to specific requirements and assign them to one or more organizations, supporting consistent governance across a multi-tenant environment. The DSM UI provides a dedicated interface for configuring policies for each supported database type, including SQL Server in addition to PostgreSQL and MySQL. This policy enforcement model gives platform administrators a mechanism for translating organizational cloud management standards into operational constraints that apply at provisioning time.
-Infrastructure policies in DSM control the placement of database VMs within storage and determine which VM classes and datastores are used when database clusters are created. Cloud Administrators configure which infrastructure policies are available within each consumption namespace, restricting database provisioning to resources and configurations that meet organizational standards. This limits how Cloud Users can consume database capacity without requiring explicit administrative approval for each individual deployment.
-DSM manages instance certificates for database clusters and establishes TLS connections to both the DSM Provider VM and individual database instances. Administrators can add trusted certificate authorities to the OS trust store to verify connections, and a Cloud Administrator must obtain and save a TLS certificate for secure communication between the Consumption Operator and the DSM provider before enabling self-service consumption. DSM also establishes secure connections to VMware vCenter using certificate validation, providing certificate-based authentication across the management plane.
-Database provisioning in DSM is self-service within the bounds set by the Cloud Administrator. Cloud Users deploy database clusters through Kubernetes-native resources in namespaces configured and controlled by the Cloud Administrator. This model delegates provisioning authority to end users while preserving administrative control over the infrastructure and policies available to them. The Consumption Operator, installed and managed by the Cloud Administrator, is the mechanism through which this bounded self-service access is enabled.
-Meeting this control fully requires the organization to establish and maintain a cloud management program that defines security standards, monitors compliance posture, and updates policies as requirements evolve. DSM's policy enforcement capabilities support that program for database workloads, but the broader governance activities, including risk assessments, vendor management reviews, and cross-service compliance monitoring, remain organizational responsibilities.</t>
+          <t>VMware Data Services Manager (DSM) supports cloud security architecture requirements through a policy-based configuration framework that administrators can align with organizational technology strategies. DSM data service policies allow administrators to define and enforce consistent configurations across tenants and organizations. These policies can be tailored to specific requirements and assigned to one or more organizations, providing a mechanism to translate architectural decisions into enforceable platform-level controls. When used with VCF Automation, this policy framework extends to multi-tenant environments where DSM maintains data separation and security across different organizations sharing the same infrastructure. In 9.1, data service policy support extends to SQL Server databases alongside PostgreSQL and MySQL, allowing the same policy enforcement model to apply across all three database engines.
+DSM includes several built-in security controls that support a configurable security posture for database services. DSM verifies the SHA256 thumbprint of vCenter during configuration to confirm the identity of the target vCenter before establishing communication. A Cloud Administrator must obtain a TLS certificate for secure communication between the Consumption Operator and the DSM provider. SQL Server clusters use TLS to encrypt communication between clients and the database. PostgreSQL database clusters use SCRAM-SHA-256 password encryption and store host-based authentication configuration in pg_hba.conf. PostgreSQL databases can also enable the pgcrypto extension, which provides cryptographic functions for securing data at the application layer.
+Self-service consumption of DSM database clusters follows a Kubernetes-native model, where authorized cloud users provision databases through the Consumption Operator and custom resources on approved Supervisor clusters. A Cloud Administrator must obtain the list of infrastructure policies supported by the DSM provider and configure the policies allowed for the consumption cluster before self-service provisioning begins. Administrators assign object stores and data service policies to specific tenants, keeping resource consumption within boundaries defined by the data service policy. The separation of provider and consumer roles, with distinct responsibilities for infrastructure administration and organizational resource management, supports defined access and accountability within the cloud security architecture.</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1109,22 +1129,24 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a layered identity and access management architecture spanning centralized identity services, role-based access control, group-based access policies, identity provider federation, and programmatic access management through APIs.
-VCF SSO is the centralized authentication service. VCF SSO issues security tokens that grant authenticated users access to VMware vCenter, NSX Manager, VCF Operations, and other platform components without requiring separate credentials for each service. VCF Operations supports importing users and groups from VCF SSO for consistent identity management across the stack. VMware Identity Manager provides a platform for managing users and groups, managing resources and user authentication, and configuring access policies and resource entitlements. vCenter also supports built-in identity source authentication using local domain credentials. The built-in identity provider can also be configured to use Active Directory as an identity source through LDAP/S, OpenLDAP/S, or Integrated Windows Authentication (IWA), depending on the directory environment.
-VCF supports federation with enterprise identity providers. vCenter can be federated to providers such as Microsoft Entra ID, ADFS, and Okta, which enables multifactor authentication and automatic user synchronization with the organization's directory. PingFederate is also supported as a federated identity provider; for these integrations, vCenter uses System for Cross-domain Identity Management (SCIM) to automate the exchange of user and group identity information between the external identity domain and vCenter. VMware Identity Broker allows principals to authenticate to vCenter through an external identity provider. NSX Manager can be configured to authenticate users from identity management providers and can be integrated with Workspace ONE Access for identity management services. The Supervisor component supports registration of OIDC-compliant external identity providers for authentication to VMware Kubernetes Service (VKS) clusters; supported providers include Okta, Workspace ONE Access, and Dex, configured by supplying the Supervisor callback URL to the identity provider.
-Role-based access control is enforced across all VCF components. In vCenter, permissions associate a user or group with a role on a specific inventory object, and predefined roles cover common administrative functions. Custom roles can be created with only the minimum required privileges for a given workflow. Managing identity provider configuration in vCenter requires the VcIdentityProviders Manage privilege. VCF Operations supports group-based access control, allowing administrators to configure groups and assign roles that control access to dashboards, reports, policies, alerts, and administration functions, as well as granular role-based controls for platform operations including approvals, audits, certificates, and content libraries.
-VCF Automation extends access management through organization-level and project-level controls. The VCF Automation Access Control service supports identity operations for managing groups and users, including editing user names, passwords, and role assignments. The organization portal enforces role-based access control, requiring either Organization Administrator or Organization Auditor roles to manage policy templates. Organization administrators can distribute infrastructure and configure group-level access through the organization management functionality. Project access is governed by predefined roles. Users and groups can be disabled at the organization level to revoke access without deleting accounts. The System Administrator role has the right to manage and view Access Control Lists, and the accessControls API allows administrators to view and manage ACL entries for defined entities.
-For Kubernetes workloads within the VCF consumption layer, VKS supports two authentication methods: VCF SSO and OIDC-compliant external identity providers. The OIDC path is implemented through Pinniped and supports providers including Okta, Workspace ONE Access, Dex, GitLab, and Google OAuth. Configuring an external provider requires setting up an OpenID Connect ID Token with a Groups claim type filter to enable group-based access control tied to the organization's directory. Custom ClusterClass configurations allow clusters to authenticate developers using existing corporate identity systems. VKS supports namespace permission roles: Owner (full control including deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). These roles map to Kubernetes ClusterRoles through RoleBindings, and RoleBinding objects can reference VCF SSO users and groups directly to integrate SSO identities with Kubernetes role-based access control. A user with the Namespaces.Edit privilege on a user-created Namespace folder can perform CRUD operations on Kubernetes API resources in the Supervisor. Namespace Self-Service permissions control which users can self-provision namespaces through kubectl.
-Kubernetes RBAC is the primary authorization mechanism within VKS, using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings to bind permissions to users, groups, or service accounts. Kubernetes Attribute-Based Access Control (ABAC) is also available, defining access rights through policies that combine user, namespace, resource, and access mode attributes. Authorization webhooks can interpret field and label selectors to enforce fine-grained access control based on resource attributes such as node names and labels.
-Service accounts provide namespaced workload identity within VKS clusters. For Windows containers, the Group Managed Service Account (gMSA) Webhook allows containers to run as Active Directory identities. VKS service accounts can be annotated with IAM role ARNs to enable pod identity and role assumption for cloud resource access through OIDC federation, replacing long-lived static credentials with short-lived, least-privileged credentials on demand. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege.
-Several supplementary services within the VKS layer extend the IAM surface. Harbor Registry, available as a standard package on VKS clusters, enforces role-based access control to manage access to container image artifacts. The Secret Store Supervisor Service enforces RBAC for administrators, DevOps engineers, and application tenants managing sensitive data. Argo CD supports both OIDC configuration for external identity providers and local account configuration with global RBAC policies that define role-based access through policy rules and group mappings. The Istio service mesh package includes a pluggable policy layer supporting access controls, rate limits, and quotas at the service-to-service level.
-Programmatic access management is available through several APIs. The Identity API authenticates and manages the authorization provider. The Identity Service and Infrastructure as a Service APIs are used to acquire access tokens for REST API authentication. Principal Identity users authenticate using client certificates for service-to-service communications between VCF components.
-NSX integrates with LDAP and external identity management services for administrative access to networking configuration. NSX Manager enforces role-based access control with roles such as auditor and network administrator assignable to LDAP users. vDefend, a separate product that extends NSX with security capabilities, offers an Identity Firewall that integrates with Active Directory for identity-based firewall rules.
-VMware Private AI Services (PAIS) provides OIDC-based authentication and group-based authorization for AI workloads, the primary IAM mechanisms controlling access to model endpoints, the model runtime, Agent Builder, and Data Indexing and Retrieval capabilities. PAIS authentication is configured with an issuer URL, a client ID (pais-authentication-id), and the openid, groups, and offline_access scopes. The OIDC provider must support the .well-known/openid-configuration discovery endpoint. Authorization restricts access to user accounts that are members of named groups listed in the authorizedGroups setting (such as group-for-pais-access-01 or group-for-pais-access-02). A groups claim is included in the Access Token and a corresponding groups scope is created in the OIDC configuration, while the oidc-groups-claim setting selects which claim name carries group membership when the OIDC provider uses a non-default name. The oidc-extra-audiences setting accepts additional OAuth 2.0 client identifiers that PAIS will accept when validating Access Tokens, supporting integration with downstream clients that present their own audience. Activating PAIS in an organization namespace requires coordination with the OIDC provider administrator and an organization administrator account in VCF Automation.
-Identity provider integration for PAIS deployments is configured at the Supervisor level under Workload Management &gt; Supervisors &gt; Configure &gt; Identity Providers. When a PAIS region is created for a Supervisor, an identity provider entry is automatically created in VMware vCenter for that Supervisor, linking the Supervisor namespace to the configured OIDC source.
-The Model Gallery, the curated repository for ML models in PAIS, restricts access to model artifacts and the training data used to tune them through Harbor project access controls. These controls scope which users and service accounts can read, push, or manage sensitive model data, adding an IAM enforcement layer to the model supply chain. A Harbor registry is recommended for PAIS deployments, and OCI-compliant registries from other vendors are also supported.
-PAIS Knowledge Bases extend IAM to ingested data sources. Confluence data sources authenticate with a user name and password or a personal access token, while Microsoft SharePoint On-Premises data sources authenticate with a user name and password. Personal access tokens for Knowledge Bases are generated from user account settings and used for programmatic access to linked data sources.
-PAIS integrates with Grafana for metrics visualization using the same OIDC provider, extending the IAM model to the observability layer so that operators authenticate through the configured identity provider before accessing PAIS dashboards.</t>
+          <t>VCF enforces logical access control permissions through role-based access control (RBAC) mechanisms across its component products, supporting the principle of least privilege at each layer of the platform.
+VMware vCenter implements a granular privilege model where privileges are fine-grained access controls that can be grouped into roles and then mapped to users or groups. The privileges themselves are defined by VMware on the objects and properties contained in the system and are fixed, meaning client applications cannot alter the underlying privilege definitions. The AuthorizationManager service controls access to specific server objects based on the permissions associated with each object, and the authorization model provides consistent security control regardless of operational context.
+vCenter ships with several predefined roles that embody different levels of access. The Read Only role grants only three system-defined privileges: System.Anonymous, System.View, and System.Read. vCenter also includes a No Access role, where users or groups assigned that role cannot view or modify the objects to which it applies. New users and groups receive the No Access role by default, so access must be explicitly granted rather than revoked. The operator role is the most restricted authorization level, allowing users to view information about vCenter but not alter its configuration. When a predefined role does not meet operational needs, administrators can define custom roles containing only the minimum set of required privileges. This custom role capability, combined with permission propagation to vSphere objects, enables organizations to tailor access to the exact scope needed for each user or group.
+Cryptographic operations privileges provide an additional layer of fine-grained access control. The default Administrator system role includes all Cryptographic Operations privileges, while a separate No Cryptography Administrator role supports all Administrator privileges except for cryptographic operations. Administrators can clone the No Cryptography Administrator role and create custom roles with only specific Cryptographic Operations privileges, limiting what users can do with virtual machine encryption and decryption. Only users who are assigned the Cryptographic Operations privileges can perform those operations.
+VCF Operations implements its own RBAC model where users can only perform the actions that their permissions allow. Each user must have a unique account with one or more roles assigned, and administrators can assign roles to user groups and restrict object access based on role permissions. Access rights are fine-grained, covering actions such as adding, editing, or deleting dashboards, and viewing, configuring, or managing objects. Privilege-based access control restricts users without appropriate privileges from viewing collected data for specific objects. The Access Control interface provides granular permission management through expandable category trees where administrators can apply or modify permissions for selected roles. A ReadOnly role is available that provides read-only access, restricting write actions such as create, update, or delete. The platform documentation recommends configuring both local VCF Operations users and vCenter users with only the privileges they need in the environment, rather than assigning overly permissive roles. vCenter roles and privileges cannot be viewed or edited from within VCF Operations, maintaining separation of privilege management between the two components.
+NSX implements role-based access control to restrict system access to authorized users by assigning users roles with specific permissions. NSX defines scoped roles including Network Admin, Network Operator, Security Admin, and Security Operator, where permissions within a project apply only within the scope of that project and not for the entire NSX system. When these roles are assigned in NSX, the scope can be set to all projects and VPCs, or to selected projects and VPCs, enabling fine-grained access boundaries across the networking layer.
+VCF Automation governs project access through predefined roles and supports role-based access control through group membership and role assignment management. System administrators with the Manage General ACL right can create, modify, and remove specific access control lists using the accessControls API, providing programmatic control over access permissions. The cloud_admin service role satisfies the minimum service role requirement for VCF Automation API access, while the Cloud Administrator group has host switch-level permissions, so administrative actions are scoped to defined capabilities.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS) within VCF, access control operates at two layers: the vSphere Namespace layer and the Kubernetes cluster layer. At the namespace layer, vSphere Namespaces support three permission roles assigned to VCF SSO users and groups: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access to VKS cluster objects with no permissions mapped to Kubernetes roles inside the cluster). The VCF Consumption CLI enforces these role assignments: users without sufficient permissions on the vSphere Namespace cannot connect to Supervisor or VKS clusters as VCF SSO users, and the system returns an explicit "Error from server (Forbidden)" response that makes enforcement directly observable. Supervisor applies a role separation pattern where DevOps and Platform Operators receive non-admin or custom roles, while Developers receive read-only or no roles. Specific operations require explicit privilege grants beyond general administrative roles: adding Supervisor Services to VMware vCenter requires the Manage Supervisor Services privilege on the vCenter system, and administering content libraries for VKS clusters requires specific vSphere role permissions that must be individually assigned when using a custom role rather than the vSphere Administrator role. The Namespace Owner, Edit, and View roles do not have access to vSphere Cluster, vSphere Namespace Inventory, or vSphere Namespace resources, while vSphere Administrator and Supervisor Administrator roles have varying levels of access to these resources, maintaining separation of duties between platform and workload operations.
+Within VKS clusters, access control is defined through Kubernetes Role-Based Access Control (RBAC) using Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings. These objects specify which API groups, resources, and verbs a subject (user, group, or service account) may act on, scoped either to a specific namespace or across the entire cluster. VKS RoleBinding subjects must contain either a VCF SSO user name or a VCF SSO group name in the name parameter to grant access, tying Kubernetes RBAC directly to the platform identity provider. For VKS clusters deployed on a custom ClusterClass with VKS 3.2.0 and later, RBAC permissions can additionally be granted to users authenticated through an external OIDC provider using ClusterRoleBinding objects that bind ClusterRoles to individual users identified by their OIDC identity or to groups from the OIDC provider. Built-in ClusterRoles support tiered access: the view ClusterRole grants read-only access to most namespace objects without permitting visibility into roles or role bindings, and the edit ClusterRole adds read/write access to most objects but does not permit modification of roles or role bindings, containing the reach of any single identity. Kubernetes RBAC includes a privilege escalation prevention mechanism at the API level: a user can create or update a RoleBinding only if they already hold all the permissions contained in the referenced role, and this restriction applies even when the RBAC authorizer is not otherwise active so that the check remains in force regardless of authorizer configuration. Where explicit delegation is required, administrators can grant the `bind` verb on a specific Role or ClusterRole to authorize a user to create bindings for that named role without requiring the user to hold all of its permissions; the `escalate` verb on roles and clusterroles in the rbac.authorization.k8s.io API group provides a parallel mechanism to authorize controlled role escalation when that operation is intentionally permitted. The Kubernetes documentation included in VCF recommends using specific resources and verbs rather than wildcard entries, enforcing least-privilege access to Secret objects through RBAC, and applying strict RBAC policies that limit access to system namespaces. Service accounts are governed by the same RBAC mechanism, allowing workloads to receive only the minimum permissions required to function correctly, and fine-grained role bindings to particular service accounts are preferred over broader grants. Administrators can scope IAM role trust policies to specific service accounts and namespaces to further constrain workload permissions.
+Pod Security Admission (PSA) provides workload-level enforcement within VKS clusters through three profiles: Privileged (unrestricted, allows privilege escalation), Baseline, and Restricted. The Restricted profile targets least-privilege pod execution by requiring non-root execution, limiting Linux capabilities, and blocking privilege escalation at the pod level. Pods can be further constrained through security contexts, where settings such as runAsUser, capabilities, seccomp, AppArmor, and readOnlyRootFilesystem restrict what container processes may do at runtime. Namespaces that permit privileged workloads should establish access controls that reflect the principle of least privilege. ValidatingAdmissionPolicy resources allow administrators to define fine-grained policy rules specifying which API groups, operations, and resources fall within the scope of enforcement, providing a declarative mechanism to express access control requirements across the cluster.
+The Secret Store service, available as a Supervisor Service, enforces its own RBAC layer with distinct roles for administrators, DevOps engineers, and application tenants, scoping sensitive data distribution to specific roles rather than making it broadly accessible to all cluster users. Harbor, available as a standard package on VKS clusters through VCF Services consumption, enforces role-based access control to manage access to container images and other artifacts stored in the registry. Argo CD, also available as a standard package, supports local account authentication with global RBAC policies that define role-based access control through policy rules and group mappings that control account permissions and resource access.
+VCF SSO supports multiple authentication methods including username token (signed and plaintext), X.509 certificate, and holder-of-key token authentication. Certificate-based authentication enables secure service-to-service communications within the platform.
+VCF provides the platform-level identity and role-based access control infrastructure on which VMware Private AI Services (PAIS) relies. Within that foundation, PAIS adds AI-specific service, data, and catalog access controls that restrict access to authorized users and groups across the AI workload layer.
+PAIS enforces access to model inference endpoints through OIDC group-based authorization configured in the PAISConfiguration custom resource. The authorizedGroups field specifies which identity provider groups are permitted to call PAIS; accounts outside the named groups are denied access. The OIDC integration is configured with issuer URL, client ID, and scopes that include openid, groups, and offline_access, so group membership is evaluated at the identity provider and carried into the service through standard OIDC group claims. The groups claim name itself is configurable, and PAIS supports Extra Audiences for additional OAuth 2.0 clients that PAIS will accept when validating the access token. Activating PAIS requires coordination with an OIDC provider administrator, making access configuration an explicit administrative act rather than a default-open posture.
+The Grafana observability interface for PAIS applies the same OIDC group model for role-based access. A role-mapping expression assigns the Admin role to users whose OIDC group claims match the configured pais-access-group attribute path, and the Viewer role to all other authenticated users. This two-tier assignment scopes administrative control of the observability platform to a designated group while keeping monitoring data accessible to authenticated PAIS users.
+PAIS model endpoints support authentication through a harbor-pull-secret-readonly credential that restricts access to container images stored in private registries, and PAIS integrates with Harbor registries as the model storage backend with authentication and certificate-based trust required for model retrieval. Harbor project-based permissions restrict access to ML model artifacts and training data stored in the Model Gallery; read-write access to a Harbor project is required to upload or modify models, and project membership is scoped to explicitly authorized users.
+PAIS catalog items in VCF Automation are shared with selected project members through project-based permissions. Users requesting AI catalog items must have permissions granted by organization administrators, and the organization administrator must assign the required user role before users can deploy deep learning VMs. VI administrators must have appropriate permissions on the vSphere cluster to deploy deep learning VM templates. This administrator-mediated model scopes AI infrastructure access to explicitly authorized principals. When running VMware vCenter 8.x, VCF SSO must be configured to access PAIS namespaces from VCF Automation; on vCenter 9.x the SSO configuration step can be skipped because the integration is already present.
+Knowledge Bases and linked data sources in PAIS use personal access tokens generated from user account settings for programmatic access, scoping API-driven retrieval to the issuing user. VCF Automation separates provider-level and tenant-level administrative operations through distinct credential scopes: a PROVIDER_ADMIN_ACCESS_TOKEN is required for provider-level operations such as registering vCenter instances, while a TENANT_ADMIN_ACCESS_TOKEN is scoped to organization administrator operations. This separation limits what any single credential can affect across the PAIS deployment.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1134,9 +1156,12 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to identity and access management by providing identity-aware network enforcement through Identity Firewall, which integrates with Active Directory to apply firewall policy based on authenticated user identity rather than IP address alone. Identity Firewall supports assigning Active Directory users and groups as source criteria in both distributed firewall rules and gateway firewall rules, applying to tier-0 and tier-1 gateways. This allows organizations to enforce network access policy by user or group membership rather than relying solely on IP-based controls.
-Within its management plane, the Security Services Platform implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles govern access to security policy management, analytics, incident response, and diagnostic functions across the platform. Network Detection and Response enforces the same five-role RBAC model for triage operations such as viewing detections and campaigns, and for configuration operations including SIEM integration management. For authentication, the Security Services Platform supports Active Directory and OpenLDAP as external identity sources, with one identity source configurable at a time. The License Hub integrates with external identity providers to store and manage user and group information for access delegation.
-Centralized IAM for organizational users, including VCF SSO, MFA, and directory lifecycle management, is handled by VCF and falls outside vDefend's scope.</t>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1145,108 +1170,6 @@
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) enforces logical access control through a privilege-based authorization model. A privilege in PNR is the right to perform a specific action, such as creating a recovery plan or modifying a protection group. PNR restricts login access to VMware vCenter administrators by default, and other users must be explicitly granted access by an administrator before they can perform any protection or recovery operations. PNR augments vCenter roles and permissions with additional privileges that allow detailed control over PNR-specific tasks and operations.
-PNR roles follow least privilege through granular role assignment. The vSphere Replication predefined roles can be cloned and customized by adding or removing individual privileges, allowing administrators to create custom roles that grant only the minimum permissions needed for a specific function. The Propagate to Children option can be deselected to create permission hierarchies that override inherited permissions at specific nodes without affecting child object permissions. vSphere Replication enforces permission denial with an error message when users without appropriate privileges attempt restricted operations. PNR roles do not include vSphere Replication privileges, so a user who is not a vCenter administrator but requires both PNR and vSphere Replication operations should be added to two separate user groups rather than granted full vCenter administrator privilege.
-For cross-site operations, PNR enforces dual-site authorization. PNR requires permissions on both vCenter objects and on PNR objects to function properly, and PNR verifies permissions on the remote vCenter instance as part of its access control validation. Removing a user's permission on a protected site stops that user from continuing operations on resources at that site. In shared recovery site configurations, the vCenter administrator must manage permissions so that each user has sufficient privileges to configure and use PNR while no user has access to resources belonging to other organizations. PNR restricts users in shared recovery site configurations from renaming, moving, or deleting data centers or hosts.
-For automatic protection of virtual machines, administrators can assign the SrmAdministrator or SrmProtectionGroupsAdministrator role to the automatic protection user or user group rather than granting global vCenter administrator privilege. The PNR clean room Orchestrator restricts connections to only IP addresses or IP address ranges that have been added to a configured management access list, providing network-layer access enforcement on top of the role-based model. For PNR deployed with VCF Automation, access is controlled through role-based permissions assigned to Provider Administrators, Organization Administrators, Project Administrators, and Project Advanced Users. Provider Administrators select which replication classes each Organization can use, and Organization Administrators manage the pairing of namespaces and assignment of replication classes within their Organization.</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) incorporates multiple identification and access management mechanisms that support organization-wide IAM controls within the data services layer.
-DSM implements role-based access control with two defined roles: the DSM Admin role, which can create, monitor, and manage all data services in the environment, and the DSM User role, which is restricted to managing and monitoring data services within the namespaces to which the user has been granted access. These roles are assigned at user creation time and govern what each user can see and do within the DSM interface. The Permissions view in the DSM dashboard provides administrators with a centralized location for creating, monitoring, and managing all configured users.
-DSM supports two identity sources, which can be used independently or together. Local users are created directly within DSM, with credentials validated by matching email address and password. LDAPS users are sourced from a configured LDAP identity provider, allowing organizations to extend their existing directory service into DSM. When LDAPS is configured, administrators can import users from the directory provider and assign them DSM Admin or DSM User roles. DSM also supports group-based access control: Directory Service Groups from the LDAP provider can be assigned roles directly, so group membership in the external directory determines access level in DSM without requiring per-user assignments.
-At the database level, DSM extends authentication controls beyond the platform management layer. MySQL database instances support LDAPS authentication using Active Directory. PostgreSQL and other database instances support host-based authentication (HBA) rule configuration, which determines which clients are permitted to authenticate to a given database instance. SQL Server instances support Windows Authentication through Active Directory integration, enabling Kerberos-based authentication so that clients such as SQL Server Management Studio running on domain-joined machines can authenticate via single sign-on. SQL Server also uses contained database users, where identity information resides within the database itself rather than at the server level. Administrators can configure SQL Server instances with either a SQL User or Windows Principal as the primary administrator identity, with Windows Principal available for Active Directory-integrated clusters. An internal dsm_mgmt management login restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context.
-Namespace isolation adds a further access boundary. DSM namespaces enforce role-based access control that allows multiple users to work jointly on data services within a namespace while remaining isolated from data services in other namespaces. This supports least-privilege access within multi-tenant deployments.</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) provides a dedicated administrative identity and access management plane through the Avi Controller, supporting multiple authentication methods and fine-grained authorization controls that allow organizations to implement IAM policies across both the management plane and the application delivery layer.
-For administrative access, the Avi Controller supports local user accounts, LDAP and LDAPS directory integration, SAML-based federated authentication (including integration with Workspace ONE Access for catalog-based application access), basic authentication, and OAuth/OIDC for API access. Auth Mapping Profiles allow organizations to map external directory groups to specific roles and tenants, so that group membership in an external identity provider directly controls what a user can access within Avi.
-Authorization is handled through role-based access control (RBAC) with object-level granularity. Avi's extended granular RBAC uses markers, which are labels assigned to objects, to enable fine-grained authorization based on object ownership and classification. Permission categories cover Operations (including alerts, actions, and traffic capture) and Administration (including controller, tenant, user, role, and system configuration management). This allows restrictions so that a user's permissions apply only to the specific resources matching the markers assigned to their role. RBAC covers object categories including Virtual Services, Application Profiles, SSL/TLS Certificates, Certificate Management Profiles, Cloud definitions, TCP/UDP Profiles, Persistence Profiles, Health Monitors, Analytics Profiles, IP Address Groups, String Groups, SSL/TLS Profiles, PKI Profiles, and Authentication Profiles, with distinct read and write access levels configured per object type.
-For multi-tenant deployments, Auth Mapping Profiles support tenant isolation with configurable user group to role mappings, allowing organizations to enforce separation between teams or business units operating within the same Avi Controller.
-The Avi License Hub supports role-based access control through an external identity provider, with three predefined roles: Enterprise Admin (full access for all operations, including upgrades and authentication configuration), Auditor (view-only access for tracking activity without making changes), and Support Bundle Collector (restricted to collecting system logs and diagnostics). Management interface access is further controlled through restrictions on allowed ciphers and HMACs for management sessions.
-For deployments involving the Avi Kubernetes Operator (AKO), Kubernetes RBAC policies can be applied to AKO Custom Resource Definitions (CRDs) to enforce stricter access control over routing configuration for specific user groups. The Avi Controller also implements RBAC at the Kubernetes and OpenShift cluster level by assigning tenants and roles to user accounts.
-At the application layer, Avi can enforce client authentication using OAuth, SAML, JWT token validation, and mutual TLS with client certificates, extending access control to the traffic flowing through virtual services rather than only to the management interface.
-Organizations are responsible for defining roles, mapping directory groups to permissions, establishing naming conventions for markers, and maintaining user lifecycle processes. Avi provides the technical mechanisms; the governance and operational processes for identity management must be organized by the teams managing the deployment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>AC.L2-3.1.2</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>IAC-08, IAC-15</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Limit system access to the types of transactions and functions that authorized users are permitted to execute.</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides account management capabilities for the infrastructure platform's own user, group, system, and service accounts. The broader organizational governance of account management across all enterprise systems is outside VCF's scope.
-VCF SSO is the centralized identity service for the platform. Administrators manage individual and group accounts through VMware vCenter, and can integrate external identity sources (Active Directory, LDAP, OIDC) so that account lifecycle management follows existing enterprise directory services. vCenter also supports System for Cross-domain Identity Management (SCIM), enabling automated provisioning and deprovisioning of user and group accounts when synchronized with a supported external identity provider. VCF Automation also supports LDAP, OIDC, and SAML-compliant identity providers for user authentication, allowing consistent identity federation across the stack.
-VCF Operations provides a consolidated view of accounts across the VCF stack through its password management dashboard, including account statuses and remediation needs. This centralized visibility helps administrators track account states and identify accounts requiring attention. The password management interface, accessible to users with the Administrator role, supports password rotation and remediation for service account passwords across integrated components. Administrators should plan maintenance windows when rotating passwords for multiple accounts to avoid service interruptions.
-At the compute layer, VMware ESX hosts support local account management through the HostLocalAccountManager interface, which allows administrators to create and manage user accounts on individual hosts. In a properly configured VCF environment, access to ESX is brokered through vCenter rather than managed directly on each host. The vSphere Web Services API documentation recommends that user accounts be given the minimal number of privileges required for their roles, consistent with least-privilege principles. For guest virtual machines, vCenter allows administrators to configure VCF SSO user mappings to guest operating system accounts, enabling centralized control over which VCF SSO users can access accounts within guest VMs.
-VCF Operations offers account management capabilities including the ability to add, edit, remove, and import user accounts, manage roles, define object-level access for users assigned to specific roles, and manage user group membership. Each user must have a unique account with one or more roles assigned. User accounts can be associated with specific objects in the VCF Operations cluster to control the scope of access. VCF Operations supports importing user accounts from external sources such as LDAP databases or single sign-on servers, allowing organizations to integrate their existing directory services with VCF Operations access control.
-VCF Operations for Networks supports local user management with role-based access control, where users are assigned roles during account creation.
-NSX Manager supports management of local user accounts through both its user interface and CLI. Through the UI, administrators can configure password expiration, deactivate users, and reset passwords. Through the CLI, the admin user can manage local user account passwords, change user names, and add, delete, or deactivate user accounts. NSX Manager has one active local account out of the box (admin), which cannot be deleted or deactivated, and best practice is to keep all other local user accounts deactivated.
-VCF Automation allows system administrators to create other system administrator and user accounts within the provider organization. Service accounts are created by administrators who hold the View Service Accounts and Manage Service Accounts privileges, providing controlled delegation of service account creation. These service accounts authenticate using API access tokens that rotate after each use. Organization owners can add and manage other users within their scope.
-The VCF Consumption layer (VMware Kubernetes Service (VKS) and vSphere namespaces) introduces a structured model for service and application account management governed through the Kubernetes API. Kubernetes ServiceAccount resources are namespace-scoped objects that provide distinct, non-human identities for application pods, in-cluster services, and other entities that need to authenticate to the Kubernetes API server. Service accounts are created automatically when namespaces are provisioned or on demand through API calls, and each is bound to roles through RoleBinding or ClusterRoleBinding resources, enabling RBAC-governed access at either namespace or cluster scope. The Kubernetes documentation advises against granting cluster-wide roles to all service accounts; per-namespace permission management is the recommended practice to maintain proper access control boundaries. Service account tokens should be scoped to minimize their usage to only the application that requires them, and the Kubernetes RBAC model specifies that user account creation must block reuse of deleted usernames so that newly created accounts with identical names do not inherit the permissions of prior accounts. Service account definitions should be included in configuration bundles for complex containerized workloads to support portability of system component identities.
-Kubernetes provides lifecycle controls for service account credentials. The LegacyServiceAccountTokenCleanup feature gate enables automatic cleanup of Secret-based service account tokens that have not been used within a specified time period, with a default retention period of one year, supporting governance of stale credentials. Infrastructure credentials, including certificates used by service accounts and cluster components, should be configured with short lifetimes and automated rotation to support ongoing account lifecycle management. Separating ServiceAccount creation from human user onboarding enables distinct audit strategies for each account type, and production VKS clusters should be configured with multiple accounts holding differentiated levels of access to different namespaces rather than relying on a single administrative account. IAM role trust policies for VKS workloads should be scoped to specific service accounts and namespaces to enforce least privilege at the workload level.
-For Windows workloads running in VKS clusters, Supervisor supports Group Managed Service Accounts (gMSAs). When Windows node pools are joined to an Active Directory domain, gMSAs provide automatic password management, simplified service principal name (SPN) management, and delegated administration across multiple servers. Access to gMSA credentials is controlled through Active Directory security groups, and the VKS cluster configuration specifies the relevant security group through the gmSAControlSecurityGroupDN setting. Configuring gMSA support for Windows node pools also requires an Active Directory service account with service principal names following Kerberos naming rules, and the VKS Security Group must be granted delegation rights to that account. HostProcess containers running as local user accounts use ephemeral local user accounts that are created and joined to a specified user group at container initialization, eliminating the need to manage passwords for those local accounts.
-The Argo CD Supervisor Service supports local account creation through the spec.localAccounts field, allowing named accounts to be defined for GitOps workflows. Argo CD RBAC policy rules and group mappings control account permissions and role assignments, including the ability to grant administrative roles to specific local accounts. Both local accounts and OIDC-authenticated users can be governed through the same RBAC policy framework. Argo CD cluster registration creates a service account with cluster-level privileges to manage the target cluster, so administrators should review and scope those privileges to what is operationally required.
-Avi Load Balancer uses a combination of roles and tenants to determine user account authorization, supporting multi-tenant access control for load balancing services.
-Role-based access control is available across all VCF components, supporting the principle of least privilege through granular role definitions. User accounts should be given the minimal set of privileges required for their responsibilities.
-While VCF provides these technical account management mechanisms across its components, proactive account governance requires organizational policies and procedures that define account lifecycle management, periodic access reviews, temporary and guest account provisioning standards, and account termination processes. These governance activities fall outside the scope of what VCF provides as a platform.</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Within its own management plane, VMware vDefend (vDefend) Security Services Platform (SSP) maintains two built-in local user accounts: an admin user with the Enterprise Admin role providing full management access, and an audit user with the Auditor role providing access to APIs and services for system auditing. In vDefend, SSP defines five roles at the platform level: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector, enabling separation of duties across administration, auditing, security engineering, security operations, and diagnostic support functions.
-SSP enforces password policies for local accounts; passwords must meet defined complexity requirements and can be changed or reset through the Platform and Instance Management interfaces. Remote users and remote user groups are managed through the System &gt; User Management interface, where administrators assign and modify roles. SSP supports directory-managed accounts through external identity providers such as Active Directory over LDAP and OpenLDAP, extending account management to enterprise identity sources; local accounts remain available even when external identity providers are disconnected.
-This coverage is limited to vDefend's own management-plane accounts. Organization-wide account management for individual, group, system, service, application, guest, and temporary accounts across all technology assets is outside vDefend's scope and must be addressed through dedicated identity and access management platforms.</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Protection and Recovery (PNR) implements role-based access control through purpose-built roles registered in VMware vCenter and through a multi-tenant administrative model for Protection and Recovery for VCF Automation. The SRM Administrator role allows users or user groups to perform all PNR configuration and administration operations. The Protection and Recovery Administrator role can be assigned to user groups to manage permissions. Default roles provide the privileges users require to manage protection groups and perform recoveries, while restricting access to resources belonging to other users.
 For automatic protection of virtual machines within a protection group, administrators assign either the SrmAdministrator or SrmProtectionGroupsAdministrator role to the automatic protection user or user group. This scopes the protection actions performed on the user's behalf to the privileges of the assigned role.
@@ -1255,6 +1178,115 @@
 Underlying directory services, authentication, and enterprise identity governance are provided by VCF SSO and the broader VCF platform. PNR consumes those identities and layers its protection and recovery roles on top of them.</t>
         </is>
       </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) provides a native role-based access control (RBAC) system on the Avi Controller that supports least-privilege access enforcement for all administrative operations on the application delivery plane.
+The Avi Controller RBAC model assigns each user a role that determines their level of access: write, read, or no access to individual resource types. Roles operate at the object level, with write access grantable to specific objects including Virtual Services, Application Profiles, SSL/TLS Certificates, and Certificate Management Profiles. This granular object-level permission model allows administrators to scope each user's access to only the resources required for their function.
+For more precise scoping, the Avi Controller supports Extended Granular RBAC using markers. Labels attached to Avi resources allow roles to restrict user permissions to a specific subset of objects within a resource type, rather than granting blanket access across all objects of that type. The allow_unlabelled_access parameter in the role object controls whether a role can access resources that do not carry a matching label, and the restrict_cloud_read_access field in controller properties further enforces label-based access on cloud objects. The Avi Controller also supports granular RBAC per field, which allows update permissions to be scoped to specific fields within an object while restricting changes to other fields.
+Auth Mapping Profiles enable integration with external identity directories such as LDAP, SAML, TACACS+, and OAuth/OIDC. Each profile maps external identity groups to specific Avi roles and tenants. The "Any Group or Any Attribute" fallback rule in an Auth Mapping Profile should be configured to the least-privileged role so that users not matched by a more specific mapping receive minimal access by default.
+The Avi Controller's service account for VMware vCenter integration follows a least-privilege model. The vCenter Cloud Connector requires a minimal set of permissions assigned to the vCenter user account. Integration between the Avi vCenter Cloud Connector and vCenter requires two roles: Avi-Global-Role with global privileges (assigned with the "Propagate to children" option to propagate permissions to all child objects) and Avi-Folder-Role assigned to the specific folder or folders containing Service Engine VMs in the vCenter inventory. The vCenter permissions required cover Change Configuration, Edit Inventory, Interaction, and Provisioning capabilities scoped to Service Engine management needs.
+The Avi Cloud Console enforces access control through two tiers: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration operations.
+For Kubernetes environments, the Avi Kubernetes Operator (AKO) custom resource definitions (CRDs) can be governed by Kubernetes RBAC policies to restrict access to a defined group of users, supporting least-privilege enforcement on the Kubernetes control plane.
+The Avi Web Application Firewall (WAF) supports authorization rules that enforce path-based access control by evaluating client domain and request path conditions. When authorization rule conditions are met, access is allowed; otherwise, a 403 response is returned, restricting access to application paths based on defined policies.
+Organizations must define role structures and Auth Mapping Profile rules that reflect the least-privilege assignments appropriate to each administrative function. The RBAC mechanisms described here apply to the Avi application delivery plane; least-privilege enforcement across the broader VCF environment is handled by VCF's own access control systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>AC.L2-3.1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>IAC-08, IAC-15</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Limit system access to the types of transactions and functions that authorized users are permitted to execute.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>VCF enforces role-based access control across all major platform components, restricting access to technology assets, applications, services, and data based on assigned roles with defined permissions. RBAC is applied consistently throughout the stack, covering compute management, networking, storage, operations management, automation services, and Kubernetes workloads.
+VMware vCenter provides fine-grained authorization through a permissions model that associates roles with users or groups on objects in the vCenter inventory hierarchy. Roles are sets of privileges, and vCenter defines three authorization levels: operator (read-only access to configuration, the most restricted level), administrator (read and write access to configuration but cannot manage user accounts, intended for users who alter vCenter configuration or exercise control functions), and super administrator (full control). When a predefined role is modified, the updated privilege set applies immediately to all users assigned that role. New roles are created with three default system-defined privileges (System.Anonymous, System.Read, System.View), and administrators add specific privileges to match the intended access level. vCenter also supports creation of custom roles with granular privilege assignment and permission propagation to vSphere objects in the inventory hierarchy.
+NSX implements RBAC by assigning users predefined roles with specific permissions. The platform includes 15 built-in roles: Enterprise Admin, Admin, Network Admin, Network Operator, Security Admin, Security Operator, Cloud Admin, Cloud Operator, Cloud Project Admin, Load Balancer Admin, Load Balancer Operator, VPN Admin, GI Platform Admin, NSX Platform Admin, and Support Bundle Collector. These roles follow the principle of least privilege, with each role carrying only the permissions needed for its functional area. NSX RBAC applies across multiple operational domains including inventory, plan and troubleshoot, and system management functions. NSX also supports project-scoped RBAC, where Network Admin, Network Operator, Security Admin, and Security Operator roles assigned within a project have permissions limited to that project's scope rather than the entire NSX system. This project-scoped model extends to VPCs and subnets within the NSX networking hierarchy. For organizations that need role definitions beyond the built-in set, NSX allows creation of custom roles tailored to specific operational requirements. Only an Enterprise Administrator can assign the role management permission to a custom role. NSX Federation extends RBAC to multi-site deployments, applying the same access control model across federated NSX instances. Principal identities, which are used for service-to-service authentication local to NSX, also support RBAC role assignment, so automated integrations operate under the same access control model as human users.
+VCF Operations enforces RBAC through the assignment of service roles to users and groups. Administrators configure role-based permissions through the Roles tab under Infrastructure Operations, where individual permissions can be selected or deselected to define what each role is authorized to do. The System Administrator role includes rights covering approvals, audits, certificates, datastores, edge clusters, integrations, LDAP settings, namespaces, proxy rules, system settings, tokens, and truststore operations. Administrative operations such as password management require authentication with a user assigned the ADMIN role. VCF Operations also defines its own roles within vCenter, with privileges named using a convention that appends the role to the product name (such as VCF Operations ContentAdmin Role and VCF Operations PowerUser Role). The PowerUser role has privileges to perform the actions of the Administrator role except for user management and cluster management. A further restricted PowerUserMinusRemediation role excludes remediation actions in addition to those limitations. A vCenter administrator assigns these roles to users, and VCF Operations maps vCenter users to the appropriate role.
+vSAN supports RBAC and permissions management for authentication and authorization of storage operations. The vSAN Security Configuration Guide provides guidance on configuring these role-based controls for storage infrastructure.
+VCF Automation governs access through multiple RBAC mechanisms at different scopes. At the organization level, rights bundles assign specific API permissions to roles including Organization Administrator, Organization Auditor, and Organization User. Group membership and role assignment are managed through the Access Control interface, and organization administrators can edit role assignments for groups at any time. At the project level, VCF Automation defines three distinct roles: administrators, members, and viewers, providing tiered access to project resources and operations. VCF Automation also governs blueprints, catalogs, content libraries, and custom entities through its role model. The Assembler Administrator role has read and write access to the entire user interface and API resources, while other roles have progressively narrower permissions.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), VCF enforces RBAC through two complementary control layers. At the vSphere layer, vSphere Namespaces assign three permission roles: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). At the Kubernetes layer, the Kubernetes RBAC authorization framework governs access to all API server requests through four core objects: Roles define permissions scoped to a single namespace, ClusterRoles define permissions applying cluster-wide, and RoleBindings and ClusterRoleBindings associate those roles with authenticated subjects such as users, groups, or ServiceAccounts. Permissions are purely additive with no deny rules, and administrators can restrict access to individual resource instances by name using the resourceNames list in role rules.
+VKS clusters integrate with VCF SSO so that Kubernetes RoleBinding objects grant RBAC permissions directly to VCF SSO users and groups. This means the same identity provider that governs VMware vCenter access also governs Kubernetes cluster access, providing a consistent identity model across both the platform and workload layers. Cluster operators use kubectl or the Kubernetes API to assign role permissions to developers and other personas with defined responsibilities.
+Kubernetes RBAC also governs ServiceAccounts, which provide discrete identities for pods and automation processes. This separation allows human access and workload access to be governed independently, with each scoped to the minimum permissions required for its function. ServiceAccounts follow the principle of least privilege by receiving only the minimum set of permissions required to function correctly, and RBAC should be applied to Secret objects to enforce least-privilege access to sensitive data stored within namespaces.
+The Kubernetes RBAC API includes built-in controls against privilege escalation: the API prevents users from editing roles or role bindings to gain permissions beyond those they already hold, and this enforcement applies at the API level regardless of the authorization mode in use. Role-binding authority can be explicitly delegated by granting a user permission to perform the bind verb on a specific Role or ClusterRole, limiting the roles that identity can delegate to others.
+In multi-tenant VKS deployments, RBAC is the primary mechanism for isolating tenants within a shared cluster. Administrators use Role and RoleBinding objects at the namespace level to restrict each tenant's access to its assigned namespaces, and ClusterRole and ClusterRoleBinding objects to control access to cluster-level resources, blocking unprivileged users from crossing tenant boundaries.
+Supervisor services deployed on VKS clusters extend RBAC to their own access models. The Secret Store Supervisor Service enforces role-based access control across administrator, DevOps engineer, and application tenant roles, controlling who can manage and retrieve sensitive data. The Argo CD Supervisor Service implements RBAC through a configurable policy field using Casbin syntax, with the spec.rbac.policy setting defining role assignments and permission rules; policy rules (p rules) control account permissions including the ability to grant admin roles to specific local accounts, and group mappings (g rules) assign accounts to role groups.
+VMware Private AI Services (PAIS) provides role-based access control scoped to its AI services and AI workload delivery components. The central mechanism is OIDC group-based authorization for PAIS. When activating PAIS in an organization namespace, administrators populate the authorizedGroups setting with one or more OIDC group identifiers so that only users who belong to those groups can access the service. The OIDC configuration supports a configurable groups claim name through the oidc-groups-claim setting, with the groups claim carried in the Access Token and evaluated at access time. PAIS requires an OIDC provider configured as a public client application with Authorization Code and Refresh Token grant types, and it can be configured with one OIDC provider. Additional OAuth 2.0 client identifiers can be accepted by configuring Extra Audiences through the oidc-extra-audiences setting when the OIDC provider issues tokens for multiple audiences.
+PAIS extends the same identity model to the Grafana observability platform used for PAIS metrics. Grafana role assignment is configured through the grafana-oidc-role-mapping property using an expression such as contains(groups[*], 'pais-access-group') &amp;&amp; 'Admin' || 'Viewer', so OIDC group membership maps automatically to Grafana Admin or Viewer roles. PAIS uses the same OIDC provider for Grafana authentication that it uses for service access.
+For machine learning model storage, the Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as the model storage backend and requires authentication and certificate-based trust for model retrieval. PAIS is compatible with OCI-compliant registries from other vendors when deployed in a disconnected or air-gapped environment, and the project-scoped access controls apply to the chosen registry.
+Access to PAIS catalog items for GPU-accelerated VKS clusters and other AI workloads is governed through project-based permissions in VCF Automation. PAIS custom forms in blueprints can be modified to control user inputs at request time, scoping which configuration choices a requester can make when provisioning AI workloads. Knowledge Base data sources used by PAIS retrieval augmented generation require authenticated access to external repositories, including user name and password authentication for SharePoint On-Premises data sources and access keys with list and read permissions on the target bucket for Amazon S3 compatible stores. PAIS uses a CA trust bundle for secure communication with external services and databases.
+These PAIS-specific controls operate at the AI services and workload layer. Access to the underlying compute, storage, and networking infrastructure is governed by platform-level RBAC in VCF, including VCF SSO and VMware vCenter role assignments, and database-level access for vector and operational data is governed by Data Services Manager. PAIS adds service-level and workload-level RBAC for AI-specific assets on top of the VCF platform foundation rather than replacing those platform controls.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend (vDefend) enforces role-based access control across its security management interfaces to restrict access to firewall policy administration, threat analysis functions, and monitoring capabilities based on assigned user roles.
+The vDefend distributed firewall (DFW) implements RBAC to control who can create or modify firewall rules, limiting policy changes to authorized personnel. Access to DFW monitoring features, including Firewall Insights, requires one of three designated roles: Enterprise Admin, Security Admin, or Security Operator. Rule Analysis operations within the platform are also role-gated across the five defined role types.
+Security Services Platform (SSP) implements RBAC with five defined roles governing access to platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; Full Access grants create, read, update, and delete capabilities, while Read-only access is available for monitoring-oriented roles such as Auditor and Support Bundle Collector. Role assignments can be applied to individual remote users or to remote user groups managed through a directory service, allowing administrators to align vDefend access with existing organizational structures. Multiple roles can be assigned to a single user or group to meet varying operational requirements. SSP's RBAC model also applies to License Hub operations, restricting licensing management actions to authorized roles.
+Security Intelligence RBAC in 9.1 uses the same five-role model as SSP (Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector), aligning Security Intelligence access governance with SSP's permission model and providing consistent role boundaries across both the detection and platform layers.
+For organizations using VCF Automation for vDefend firewall management, VCF Automation provides a dedicated Firewall category under RBAC rights, controlling access to the management and viewing of DFW rules, Tenant Gateway Firewall policy, VPC Gateway Firewall policy, and VPC Security Profiles. This allows organizations to scope firewall administration rights independently of other VCF Automation capabilities, supporting separation of duties between network automation and security policy management.
+vDefend's RBAC controls complement the broader VCF RBAC model by restricting access to network security policy management independently of compute, storage, or platform configuration access. An administrator with VMware vCenter privileges does not automatically gain the ability to modify firewall rules or security analytics configurations unless explicitly granted the appropriate vDefend roles. This separation of duties between infrastructure administration and security policy management supports distinct team structures for network security management.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Protection and Recovery (PNR) implements role-based access control through purpose-built roles registered in VMware vCenter and through a multi-tenant administrative model for Protection and Recovery for VCF Automation. The SRM Administrator role allows users or user groups to perform all PNR configuration and administration operations. The Protection and Recovery Administrator role can be assigned to user groups to manage permissions. Default roles provide the privileges users require to manage protection groups and perform recoveries, while restricting access to resources belonging to other users.
+For automatic protection of virtual machines within a protection group, administrators assign either the SrmAdministrator or SrmProtectionGroupsAdministrator role to the automatic protection user or user group. This scopes the protection actions performed on the user's behalf to the privileges of the assigned role.
+Each role is a collection of privileges that defines the actions a user can perform on the protection and recovery site. A user can have at most one role on an object, but roles combine when the user belongs to multiple groups that all have roles on the object. PNR supports propagating roles to child objects in the inventory hierarchy, so administrators can extend privileges from parent objects such as folders to all virtual machines within them.
+Protection and Recovery for VCF Automation introduces a multi-tenant role model with Provider Administrator, Organization Administrator, Project Administrator, and Project Advanced User. Each role has specific authorization levels for disaster recovery operations. Provider Administrators select which replication classes each Organization can use, restricting organizational access to specific recovery configurations. Organization Administrators manage the pairing of namespaces and assignment of replication classes within their tenancy.
+Underlying directory services, authentication, and enterprise identity governance are provided by VCF SSO and the broader VCF platform. PNR consumes those identities and layers its protection and recovery roles on top of them.</t>
+        </is>
+      </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Meets</t>
@@ -1262,15 +1294,11 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides account management mechanisms for the accounts it directly governs: the DSM administrator account, DSM user accounts (local and LDAPS-federated), database owner accounts, and the internal service account DSM uses to authenticate to VMware vCenter.
-DSM supports two identity sources for user accounts. Local users are created directly within DSM using an email address as the login username and a password. LDAPS users are federated from a configured directory server, allowing organizations to manage DSM access through their existing identity infrastructure. Administrators can configure one or both identity sources depending on organizational requirements. For LDAP-federated accounts, DSM supports group-based access control by assigning roles to Directory Service Groups, so that group membership in the directory server determines DSM access. This is configured under Administering Data Services Manager &gt; Managing LDAP Users in Data Services Manager.
-DSM implements role-based access control with two role types. The DSM Administrator role has full visibility and maintenance capabilities across all data services and is responsible for managing DSM settings including LDAPS and SMTP configuration, database backups, and high availability settings. The DSM Administrator also manages namespaces and permissions for database ownership. The DSM User role allows individuals to provision and manage their own databases and perform database lifecycle operations while having no visibility into other users' data services. DSM User roles support namespace-level access controls that can be configured at the time a user account is created, scoping access to specific Supervisor namespaces. This separation restricts administrative capabilities to designated personnel and scopes each user to the resources they own.
-DSM user accounts maintain failed_login_count, last_failed_login_time, locked_state_start_time, and force_password_change attributes to enforce account lockout and password management policies. These fields track authentication failures, record when an account entered a locked state, and flag accounts that must change their password at the next login. This is configured under Administering Data Services Manager &gt; Managing LDAP Users in Data Services Manager &gt; Create Directory Service Groups Using the Data Services Manager UI.
-The initial DSM administrator account is created during deployment of the DSM Provider Appliance and is mandatory; it cannot be deleted. When access needs to be suspended without disrupting running databases, administrators can reset a local user's password and delegate management of the user's databases to a different user rather than deleting the account.
-For database-level accounts, DSM allows database owners to set or change the database administrator password at any time while the database is online. DSM also supports LDAPS user creation for PostgreSQL database authentication and access control, enabling directory-managed credentials for database access rather than locally maintained passwords.
-DSM introduces SQL Server as a managed database engine, with specific account management controls for SQL Server instances. DSM deactivates the default sa account and uses a reserved internal account, dsm_mgmt, with sysadmin privileges for management operations. The dsm_mgmt account restricts users from accessing or modifying system-level objects, keeping administrative operations within an isolated context. DSM uses contained database users for SQL Server database access, so users authenticate directly against the database rather than through a server-level login. For SQL Server clusters in Active Directory environments, DSM requires a service account that is a standard Active Directory user and a member of the Domain Users group. DSM can also be configured with a privileged Active Directory account to automate the management of service principal names (SPNs) and DNS records for SQL Server clusters. The dbo user is mapped to administrator-controlled identities for SQL Server database access.
-DSM maintains an internal service account for authentication to vCenter. This account is required for DSM to provision and manage infrastructure resources. DSM maintains service account rotation logs that administrators can review to diagnose vCenter authentication failures. Administrators should monitor for alerts indicating that the service account has expired, as an expired service account causes ongoing DSM operations to fail.
-DSM's account management capabilities address the technical layer of this control within its scope. Broader account governance (including formal provisioning and deprovisioning procedures, periodic access reviews, approval workflows for account creation and role changes, and lifecycle management for temporary or guest accounts) requires organizational processes that operate outside DSM. Organizations should establish procedures for reviewing DSM account assignments, managing LDAPS group membership to reflect current job roles, and deprovisioning access when personnel change responsibilities.</t>
+          <t>VMware Data Services Manager (DSM) implements role-based access control natively, with two defined role types that govern access to all data service resources. The DSM Admin role is a super-user role with full access to create, monitor, and manage all data services across the environment. The DSM User role is a restricted role that limits a user to viewing and managing only the data service deployments they own. This separation is enforced at the console level: the views and available actions in the DSM interface differ based on the assigned role, so users with the DSM User role cannot see or act on resources outside their own scope.
+Access control is further refined through namespace scoping. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to data services within those assigned namespaces only. Administrators can modify a user's assigned role and namespace access after initial provisioning. DSM namespaces enforce role-based access control that allows multiple users to work on data services within a shared namespace while maintaining appropriate permission boundaries between them.
+DSM supports both local user accounts and directory service integration for identity management. Local users are created through the DSM UI, where administrators specify the user's role, email address, and password. For enterprise directory integration, DSM supports LDAPS-based authentication with Directory Service Group mapping, allowing administrators to assign users to either the DSM Admin or DSM User role based on their LDAP group membership. This group-based mapping is configured through the vSphere Client during DSM setup or through the DSM UI after deployment.
+Access control extends to storage and database resources as well. DSM IAM policies for S3-compatible storage support granular access control through policy statements that allow specific S3 actions, including PutObject, GetObject, DeleteObject, and ListMultipartUploadParts. At the database level, PostgreSQL instances support the CREATE ROLE command to create database roles for LDAPS users with configurable login capabilities, and administrators can configure Host-Based Authentication (HBA) rules to restrict which clients and authentication methods may connect to a PostgreSQL instance. For SQL Server instances, DSM applies least-privilege access by granting the cluster administrator login restricted read-only privileges and specific ALTER privileges for server management and auditing, rather than full administrative access. Data service policies also support allowlist configuration to restrict users to selecting only from a specific set of approved parameters when provisioning databases.
+The DSM Permissions view provides a centralized interface for administrators to create, monitor, and manage configured users. This view supports ongoing governance of who has access to what within the DSM environment, making it straightforward to audit and adjust role assignments as business needs change.</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
@@ -1280,10 +1308,14 @@
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>Avi Load Balancer maintains its own account management plane on the Avi Controller, distinct from the underlying VCF infrastructure. User accounts are organized into two categories: local users, whose credentials are stored on the Controller, and remote users, who authenticate through an external authentication, authorization, and accounting (AAA) server such as LDAP or Active Directory. The admin account is a special system account used for initial setup that remains locally authenticated even when the system is configured for remote authentication. Local accounts remain available even if external identity providers such as LDAP or OpenLDAP become disconnected, providing a resilient fallback path for administrative access.
-Account management operations are gated by role-based access control: configuring or managing user accounts requires write access to the Accounts section, as defined by the role assigned to the managing account. Avi provides predefined roles that can be customized or extended by administrators with appropriate access. Each account can be scoped to specific tenants and assigned different roles within each tenant through Tenant and Role assignment, supporting both centralized administration and delegated management across multi-tenant deployments. When a user has access to multiple tenants, the system places them into a default tenant after login. If no additional tenants have been created, all new user accounts are automatically added to the admin tenant. In the VCF for Avi integration, a Provider or Load Balancer Administrator manages resource assignments to enforce quotas and resource boundaries within organization-managed mode.
-User Account Profiles govern account attributes and access controls. All users are attached to the Default-User-Account-Profile by default, which enforces standard lockout thresholds and password policies. Administrators can assign the No-Lockout-User-Account-Profile for accounts that require uninterrupted access, and can create custom UserAccountProfile objects to tailor security policies for different user populations. In the VCF for Avi integration, the system manages two specific accounts for password updates: admin and vcfops-admin, providing a defined account scope for VCF-integrated deployments.
-Account lifecycle operations available through the Controller include account creation, deletion, deactivation, and reactivation. Deletion removes an account from the system entirely. Deactivation suspends access without deleting the account record, and reactivation restores access for a previously deactivated account. These operations are available only to users with write access to the Accounts section, scoping account management authority to authorized administrators. The Avi SaaS Controller supports service account configuration for programmatic and automated access, extending account lifecycle management to service identities within the Avi-managed plane.</t>
+          <t>VMware Avi Load Balancer provides a native, multi-tiered Role-Based Access Control (RBAC) framework that governs all administrative access to the Avi Controller. At the base level, Avi roles assign one of four privilege types to each resource category: Write (full create, read, modify, and delete access), Read (view-only access to configuration, health, and analytics data without modification capability), Assorted (a mixed access level combining permissions across specific operations), and No Access (no access to the resource at all, including the inability to read or list it). Roles are combined with tenants to define the complete authorization settings for each user, scoping what resources a user can interact with and what actions they may take.
+Beyond base privilege levels, the Extended Granular RBAC feature refines access using markers, which are key-value label pairs assigned to Avi objects. A role definition specifies that a user may access only objects bearing labels that match the role's marker set. The allow_unlabelled_access parameter controls whether a user can view objects that lack matching labels, allowing administrators to restrict visibility to labeled objects only. Label groups can be associated with tenants to enforce label-based access policies across the tenant boundary. Multiple label values can be mapped to a single key, enabling flexible classification schemes. This mechanism enables resource-level scoping across tenants and teams: for example, restricting a group of operators to only the virtual services labeled with their team's identifier, without granting visibility into other teams' objects.
+At the finest granularity, Avi implements sub-resource (field-level) RBAC, which scopes which specific fields within a configuration object a given user is authorized to modify. Sub-resource definitions can be combined so that a user can configure multiple fields or features within a single object while remaining restricted from updating others. Label-based permissions for cloud objects extend this field-level control to infrastructure resources managed by the Avi Controller. Virtual service configuration exposes RBAC directly: the RBAC tab in the Virtual Service advanced setup provides label-based access control for health monitors and associated objects, extending role enforcement down to individual service configuration items.
+For GSLB deployments, the Avi Controller enforces RBAC through role references such as Gslb_Group_Enabled and Gslb_Health_Monitor that can be assigned to user accounts with tenant-level scope. These role references apply to follower sites configured with federated JWT profiles, scoping which accounts can modify GSLB configuration.
+The Avi Controller applies RBAC within the License Hub, limiting which users can perform specific actions based on their assigned role.
+For deployments using the Avi Kubernetes Operator (AKO), the Avi Controller implements RBAC by assigning tenants and roles to user accounts at the Kubernetes or OpenShift cluster level. AKO Custom Resource Definitions (CRDs) can leverage Kubernetes RBAC policies to restrict which user groups can configure routing rules, extending the Controller's authorization model into the Kubernetes control plane.
+For deployments on Microsoft Azure, Avi integrates with Azure IAM to control which Azure identities have access to Avi Load Balancer resources hosted in Azure. Administrators can use built-in Azure roles such as Reader (read-only access) or Owner (full access), or define custom roles for finer control over specific resources.
+RBAC configuration is managed through the Users section of the Avi Controller UI. Roles are defined per resource type and then assigned to users within a tenant. Extended Granular RBAC markers are attached to individual Avi objects (virtual services, pools, health monitors, and others) and referenced in the role definition. Sub-resource RBAC is configured as part of the Extended Granular RBAC object, combining field-level restrictions as needed.</t>
         </is>
       </c>
     </row>
@@ -1315,15 +1347,23 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple layers of access control list (ACL) mechanisms and network traffic restriction capabilities that contribute to data flow enforcement, though full ACL governance across physical and virtual infrastructure requires organizational processes and may benefit from VMware vDefend for advanced stateful firewall rule sets.
-At the network infrastructure layer, VCF uses vSphere Distributed Switches to centrally manage VLAN assignments, port group policies, and traffic shaping rules across all hosts in a workload domain. Distributed switches support traffic shaping policies that limit the bandwidth of incoming traffic, helping restrict which traffic types and volumes can traverse each network segment. Distributed port groups and uplink port groups also support a Traffic Filtering and Marking Policy, where per-rule actions can be set to Allow, Drop, or Tag traffic based on defined match criteria, providing rule-based traffic enforcement at the virtual switch level. Traffic segmentation is built into VCF's architecture: management, vMotion, vSAN, and NFS traffic each run on dedicated VLANs and VMkernel ports, and the vMotion network must be distinct from the vSAN network. This separation restricts which traffic types can traverse each segment by design. Private VLANs (PVLANs) provide additional Layer 2 isolation within a single VLAN through virtual network segmentation on distributed virtual switches, limiting communication between VMs even on the same segment. Distributed switches also support VLAN-based SPAN (VSPAN) for virtual distributed port mirroring, which aids in monitoring and validating traffic flows. At the ESX host level, a built-in firewall operates on a deny-by-default basis, closing all ports except those an administrator explicitly designates as authorized, giving each host an independent network access control point.
-NSX extends these capabilities with software-defined networking constructs including segments, Tier-0 and Tier-1 gateways, and Virtual Private Clouds (VPCs). NSX Tier-0 gateways can be configured with linked Tier-1 gateways to create multi-tier topologies, enabling route-based traffic restrictions between network tiers. NSX edge gateways handle north-south routing. With vDefend deployed, North-South Firewall Rules on these gateways provide traffic protection, and an NSX project's default gateway firewall and distributed firewall rules (a vDefend capability) govern the default behavior of north-south and east-west traffic for workloads in that project. VPCs are self-contained virtual network environments that provide an abstraction layer for setting up isolated virtual private cloud networks with their own topology, IP address management, and permission models, allocatable to discrete projects in a self-service consumption model. NSX Manager enforces approved authorizations for controlling the flow of management information within network devices based on information flow control policies.
-NSX also provides data flow enforcement at the load balancer tier through its Access List Control (ALC) feature. The NSX load balancer compares all traffic flowing through it with ACL statements, which either drop or allow the traffic based on configured rules. This gives administrators another enforcement point for restricting network traffic to only what is authorized.
-At the Consumption layer, VMware Kubernetes Service (VKS) and the Supervisor extend ACL enforcement to containerized workloads through Kubernetes NetworkPolicy resources, which function as Layer 3/4 ACLs for pod-level traffic. NetworkPolicy objects specify allowed ingress and egress traffic by pod selector, namespace selector, IP block, port, and protocol; pods not selected by any NetworkPolicy receive no restriction by default, making explicit policy deployment necessary to enforce a default-deny posture across a cluster. VKS clusters run Antrea as the default CNI plugin, which implements NetworkPolicy enforcement through the AntreaPolicy feature gate and provides per-policy and per-rule packet and byte count statistics through the NetworkPolicyStats capability, giving administrators visibility into which policies are actively restricting traffic. For VKS clusters using NSX VPC networking, NSX-backed network policies apply distributed ACLs at the hypervisor level, extending enforcement beyond the CNI layer. The ovn-kubernetes Transparent network mode similarly supports distributed ACLs applied via Kubernetes NetworkPolicy resources. For Layer 7 traffic control within VKS clusters, the Istio service mesh standard package provides a pluggable policy layer and configuration API supporting access controls, rate limits, and quotas based on workload identity; when deployed in ambient mode with strict mutual TLS, all service-to-service traffic within the mesh is subject to authentication before authorization checks apply, restricting lateral movement to explicitly permitted paths.
-For file-level and storage data flow isolation, the Supervisor uses ACLs to isolate file share access within supervisor namespaces, restricting data access between workloads running in different namespaces. vSAN file services support managing ACLs on SMB shares using the MMC tool, giving administrators granular control over which users and systems can access shared storage resources. Administrators should be aware that ACL-based file share isolation in the Supervisor carries a risk of IP spoofing, which should be addressed through complementary network controls when deploying file shares in multi-tenant environments. Argo CD deployments on the Supervisor implement network segmentation and firewall rules to control communication between Argo CD components, following the principle of restricting inter-component traffic to only what each component requires. The Harbor container registry standard package enforces role-based access control over artifact access, complementing network-layer ACLs with image-level access restrictions.
-For object-level access control, VCF Automation maintains an ACL table that defines which users can access specific defined entities. System administrators with the Manage General ACL right can create, modify, and remove ACL entries through the accessControls API. Those with the View General ACL right can audit ACL assignments on specific entities. Access to runtime defined entities is controlled through rights bundles and ACL entries. This ACL mechanism works alongside role-based access controls so that rights determine what actions a user can perform while ACLs determine which objects those actions apply to.
-VCF Operations for Networks supports ACL visibility through its network assurance and verification capabilities, which allow administrators to validate that ACL configurations are applied as intended across the managed environment. This includes the ability to verify ACL configurations on supported physical network equipment such as Cisco ASR routers, helping validate that physical and virtual network access controls are consistent.
-For workload-level traffic enforcement with stateful firewall rules, microsegmentation, and deep packet inspection, VMware vDefend and Gateway Firewall extend VCF's networking foundation with fine-grained Layer 2-7 policy enforcement. Organizations that require ACL governance beyond what VCF provides natively should establish processes for ACL review cycles, change management for firewall rules, and regular validation of both physical and virtual network access controls.</t>
+          <t>VCF enforces role-based access control across all major platform components, restricting access to technology assets, applications, services, and data based on assigned roles with defined permissions. RBAC is applied consistently throughout the stack, covering compute management, networking, storage, operations management, automation services, and Kubernetes workloads.
+VMware vCenter provides fine-grained authorization through a permissions model that associates roles with users or groups on objects in the vCenter inventory hierarchy. Roles are sets of privileges, and vCenter defines three authorization levels: operator (read-only access to configuration, the most restricted level), administrator (read and write access to configuration but cannot manage user accounts, intended for users who alter vCenter configuration or exercise control functions), and super administrator (full control). When a predefined role is modified, the updated privilege set applies immediately to all users assigned that role. New roles are created with three default system-defined privileges (System.Anonymous, System.Read, System.View), and administrators add specific privileges to match the intended access level. vCenter also supports creation of custom roles with granular privilege assignment and permission propagation to vSphere objects in the inventory hierarchy.
+NSX implements RBAC by assigning users predefined roles with specific permissions. The platform includes 15 built-in roles: Enterprise Admin, Admin, Network Admin, Network Operator, Security Admin, Security Operator, Cloud Admin, Cloud Operator, Cloud Project Admin, Load Balancer Admin, Load Balancer Operator, VPN Admin, GI Platform Admin, NSX Platform Admin, and Support Bundle Collector. These roles follow the principle of least privilege, with each role carrying only the permissions needed for its functional area. NSX RBAC applies across multiple operational domains including inventory, plan and troubleshoot, and system management functions. NSX also supports project-scoped RBAC, where Network Admin, Network Operator, Security Admin, and Security Operator roles assigned within a project have permissions limited to that project's scope rather than the entire NSX system. This project-scoped model extends to VPCs and subnets within the NSX networking hierarchy. For organizations that need role definitions beyond the built-in set, NSX allows creation of custom roles tailored to specific operational requirements. Only an Enterprise Administrator can assign the role management permission to a custom role. NSX Federation extends RBAC to multi-site deployments, applying the same access control model across federated NSX instances. Principal identities, which are used for service-to-service authentication local to NSX, also support RBAC role assignment, so automated integrations operate under the same access control model as human users.
+VCF Operations enforces RBAC through the assignment of service roles to users and groups. Administrators configure role-based permissions through the Roles tab under Infrastructure Operations, where individual permissions can be selected or deselected to define what each role is authorized to do. The System Administrator role includes rights covering approvals, audits, certificates, datastores, edge clusters, integrations, LDAP settings, namespaces, proxy rules, system settings, tokens, and truststore operations. Administrative operations such as password management require authentication with a user assigned the ADMIN role. VCF Operations also defines its own roles within vCenter, with privileges named using a convention that appends the role to the product name (such as VCF Operations ContentAdmin Role and VCF Operations PowerUser Role). The PowerUser role has privileges to perform the actions of the Administrator role except for user management and cluster management. A further restricted PowerUserMinusRemediation role excludes remediation actions in addition to those limitations. A vCenter administrator assigns these roles to users, and VCF Operations maps vCenter users to the appropriate role.
+vSAN supports RBAC and permissions management for authentication and authorization of storage operations. The vSAN Security Configuration Guide provides guidance on configuring these role-based controls for storage infrastructure.
+VCF Automation governs access through multiple RBAC mechanisms at different scopes. At the organization level, rights bundles assign specific API permissions to roles including Organization Administrator, Organization Auditor, and Organization User. Group membership and role assignment are managed through the Access Control interface, and organization administrators can edit role assignments for groups at any time. At the project level, VCF Automation defines three distinct roles: administrators, members, and viewers, providing tiered access to project resources and operations. VCF Automation also governs blueprints, catalogs, content libraries, and custom entities through its role model. The Assembler Administrator role has read and write access to the entire user interface and API resources, while other roles have progressively narrower permissions.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), VCF enforces RBAC through two complementary control layers. At the vSphere layer, vSphere Namespaces assign three permission roles: Owner (full control including namespace deletion), Can Edit (provisioning and operating workloads), and Can View (read-only access). At the Kubernetes layer, the Kubernetes RBAC authorization framework governs access to all API server requests through four core objects: Roles define permissions scoped to a single namespace, ClusterRoles define permissions applying cluster-wide, and RoleBindings and ClusterRoleBindings associate those roles with authenticated subjects such as users, groups, or ServiceAccounts. Permissions are purely additive with no deny rules, and administrators can restrict access to individual resource instances by name using the resourceNames list in role rules.
+VKS clusters integrate with VCF SSO so that Kubernetes RoleBinding objects grant RBAC permissions directly to VCF SSO users and groups. This means the same identity provider that governs VMware vCenter access also governs Kubernetes cluster access, providing a consistent identity model across both the platform and workload layers. Cluster operators use kubectl or the Kubernetes API to assign role permissions to developers and other personas with defined responsibilities.
+Kubernetes RBAC also governs ServiceAccounts, which provide discrete identities for pods and automation processes. This separation allows human access and workload access to be governed independently, with each scoped to the minimum permissions required for its function. ServiceAccounts follow the principle of least privilege by receiving only the minimum set of permissions required to function correctly, and RBAC should be applied to Secret objects to enforce least-privilege access to sensitive data stored within namespaces.
+The Kubernetes RBAC API includes built-in controls against privilege escalation: the API prevents users from editing roles or role bindings to gain permissions beyond those they already hold, and this enforcement applies at the API level regardless of the authorization mode in use. Role-binding authority can be explicitly delegated by granting a user permission to perform the bind verb on a specific Role or ClusterRole, limiting the roles that identity can delegate to others.
+In multi-tenant VKS deployments, RBAC is the primary mechanism for isolating tenants within a shared cluster. Administrators use Role and RoleBinding objects at the namespace level to restrict each tenant's access to its assigned namespaces, and ClusterRole and ClusterRoleBinding objects to control access to cluster-level resources, blocking unprivileged users from crossing tenant boundaries.
+Supervisor services deployed on VKS clusters extend RBAC to their own access models. The Secret Store Supervisor Service enforces role-based access control across administrator, DevOps engineer, and application tenant roles, controlling who can manage and retrieve sensitive data. The Argo CD Supervisor Service implements RBAC through a configurable policy field using Casbin syntax, with the spec.rbac.policy setting defining role assignments and permission rules; policy rules (p rules) control account permissions including the ability to grant admin roles to specific local accounts, and group mappings (g rules) assign accounts to role groups.
+VMware Private AI Services (PAIS) provides role-based access control scoped to its AI services and AI workload delivery components. The central mechanism is OIDC group-based authorization for PAIS. When activating PAIS in an organization namespace, administrators populate the authorizedGroups setting with one or more OIDC group identifiers so that only users who belong to those groups can access the service. The OIDC configuration supports a configurable groups claim name through the oidc-groups-claim setting, with the groups claim carried in the Access Token and evaluated at access time. PAIS requires an OIDC provider configured as a public client application with Authorization Code and Refresh Token grant types, and it can be configured with one OIDC provider. Additional OAuth 2.0 client identifiers can be accepted by configuring Extra Audiences through the oidc-extra-audiences setting when the OIDC provider issues tokens for multiple audiences.
+PAIS extends the same identity model to the Grafana observability platform used for PAIS metrics. Grafana role assignment is configured through the grafana-oidc-role-mapping property using an expression such as contains(groups[*], 'pais-access-group') &amp;&amp; 'Admin' || 'Viewer', so OIDC group membership maps automatically to Grafana Admin or Viewer roles. PAIS uses the same OIDC provider for Grafana authentication that it uses for service access.
+For machine learning model storage, the Model Gallery uses Harbor project access capabilities to restrict access to the sensitive data used to train and tune models. PAIS integrates with Harbor registries as the model storage backend and requires authentication and certificate-based trust for model retrieval. PAIS is compatible with OCI-compliant registries from other vendors when deployed in a disconnected or air-gapped environment, and the project-scoped access controls apply to the chosen registry.
+Access to PAIS catalog items for GPU-accelerated VKS clusters and other AI workloads is governed through project-based permissions in VCF Automation. PAIS custom forms in blueprints can be modified to control user inputs at request time, scoping which configuration choices a requester can make when provisioning AI workloads. Knowledge Base data sources used by PAIS retrieval augmented generation require authenticated access to external repositories, including user name and password authentication for SharePoint On-Premises data sources and access keys with list and read permissions on the target bucket for Amazon S3 compatible stores. PAIS uses a CA trust bundle for secure communication with external services and databases.
+These PAIS-specific controls operate at the AI services and workload layer. Access to the underlying compute, storage, and networking infrastructure is governed by platform-level RBAC in VCF, including VCF SSO and VMware vCenter role assignments, and database-level access for vector and operational data is governed by Data Services Manager. PAIS adds service-level and workload-level RBAC for AI-specific assets on top of the VCF platform foundation rather than replacing those platform controls.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1537,11 +1577,9 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend implements role-based access control across its management plane through the Security Services Platform (SSP). SSP defines five built-in roles with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Permission levels range from Full Access (Create, Read, Update, and Delete) to Read-only or no access, depending on the role and operation. The Enterprise Admin role grants full authority over deployment, configuration, authentication and authorization settings, and backup operations. Modifying role assignments requires Admin privileges, and editing remote user or group role assignments requires LDAP to be configured as an authentication provider.
-The two predefined local accounts, admin and audit, map to the Enterprise Admin and Auditor roles respectively, limiting each account to its designated functional scope. LDAP user account passwords are managed remotely by administrators, keeping credential management under organizational control.
-Beyond its management plane, vDefend's Distributed Firewall (DFW) supports an Identity Firewall (IDFW) feature that enforces network access controls based on Active Directory user identity. Administrators create security groups in Active Directory and configure DFW rules that allow or deny user access to application servers based on group membership, applying role-based access controls at the network layer.
-vDefend's Malware Prevention Service applies additional access restrictions to its service VMs: SSH access is disabled by default on the Malware Prevention Service virtual machine and must be explicitly activated by a vCenter administrator when needed for troubleshooting, then deactivated after use. The Malware Prevention Service VM ships with a default root password that must be changed on first login.
-vDefend's contribution to this control is scoped to its own management interfaces and network-layer access enforcement. Controlling privileged access across the broader IT environment, identity lifecycle governance, and access controls for systems outside vDefend's domain require organizational processes and tooling beyond what vDefend provides.</t>
+          <t>VMware vDefend's Security Services Platform (SSP) maintains a defined set of privileged local accounts within its management plane. SSP has two built-in local accounts: an admin user with the Enterprise Admin role and an audit user with the Auditor role. These accounts are system-defined and remain accessible even when external identity providers such as LDAP or OpenLDAP are unavailable, providing continuity of management access independent of external directory connectivity. The SSP Installer ships with the same two predefined local accounts (admin with full privilege and audit with auditor access) to support the deployment phase.
+For broader access governance within SSP, vDefend implements role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Each role carries differentiated permissions; the Enterprise Admin role holds full access including deployment, management, upgrade, backup and restore, and authentication and authorization configuration. Accounts from external identity providers such as LDAP can be assigned to any of these roles. Administrators can view and manage all role assignments through the User Management interface, which requires Admin privileges to access.
+vDefend's contribution to this control is bounded to its own management plane. SSP provides the technical mechanisms for inventorying and managing privileged access within vDefend itself, but inventorying privileged accounts across the broader organizational environment and validating that each account holder has been authorized by the appropriate level of organizational management are outside the product's scope.</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -1566,12 +1604,13 @@
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides role-based access control that restricts privileged access to database platform resources. The platform defines two built-in roles: DSM Admin and DSM User. The DSM Admin role is a super user role with full access to all data services in the environment, while the DSM User role restricts users to viewing and managing only the objects they own. This separation means that standard database consumers cannot affect or view resources belonging to other users or managed by administrators. The DSM console enforces this separation by restricting the views and actions available to each user based on their assigned role.
-Privileged access within DSM is further scoped through namespaces. DSM User role assignments can be restricted to one or more specific namespaces, limiting access to only those assigned workspaces. This namespace-level scoping provides a granular mechanism for controlling who can access which database workloads. Namespace RBAC is enforced at the platform level, preventing users within a shared namespace from accessing resources in other namespaces.
-Role and user management is performed through the vSphere Client Permissions interface under the DSM Configure tab, and through the DSM administrator UI Permissions view, where administrators can create, monitor, and manage configured users. DSM supports both local users and LDAPS-authenticated directory service groups, enabling organizations to align DSM role assignments with their existing enterprise identity management systems. Directory Service Groups can be assigned either the DSM Admin or DSM User role. When local and LDAPS users share the same username, login precedence must be considered to avoid authentication conflicts.
-At the platform infrastructure level, DSM uses a dedicated VMware vCenter service account rather than persisting administrator credentials. During initial setup, the deploying user must provide local vCenter administrator credentials. DSM uses those credentials to create a dedicated vCenter service account and then discards the original credentials after successful registration. Ongoing operations use only the service account, which is configured with the minimum permissions required for service account creation, plug-in registration, and resource management. The service account credentials for the target vCenter can be verified and updated in Settings &gt; System Settings under Target vCenter.
-For SQL Server databases, DSM applies additional engine-level privileged access controls. DSM deactivates the default sa account and uses a reserved internal account, dsm_mgmt, with sysadmin privileges for management operations. The cluster administrator login is granted restricted read-only privileges and specific ALTER privileges for server management and auditing rather than full system privileges. When Windows Authentication is configured for SQL Server, DSM requires a Privileged Account configured in Active Directory to automate management of service principal names (SPNs) and DNS records.
-Because DSM relies on vCenter for underlying infrastructure privilege management, achieving full coverage of this control requires organizational processes that are outside DSM's scope: maintaining an inventory of privileged accounts, conducting periodic access reviews, and managing approval workflows for new privileged account requests. DSM provides the technical enforcement mechanisms for restricting privileged platform access; the organization is responsible for the operational privileged access management procedures required to fully satisfy this control.</t>
+          <t>VMware Data Services Manager (DSM) contributes to this control through its role-based access control model, which defines a clear privileged account tier and supports integration with enterprise directory services.
+DSM implements RBAC with two predefined roles. The DSM Admin role provides super-user access, allowing the account holder to view and manage all data services and objects in the DSM environment. The DSM User role restricts access to objects the user owns, with namespace-level access controls configurable during user creation. This structure makes it possible to identify all privileged accounts within DSM: any account assigned the Admin role holds elevated privileges.
+DSM user accounts originate from one of two identity sources: a local database (Local users) or a configured LDAPS server (LDAPS users). Administrators can assign the Admin role to individual LDAPS users or to Directory Service Groups, which enables group-based access control when LDAPS is configured. When an organization manages DSM Admin assignments through an LDAPS group, changes to privileged access can be governed through the same directory management processes used elsewhere in the environment. The initial DSM administrator account is created as a Local user during deployment of the DSM Provider Appliance and cannot be deleted. A vSphere administrator must assign DSM Admin and DSM User roles to users before they can access DSM.
+DSM also depends on platform-level privileged accounts. Deploying DSM requires a VMware vCenter (vCenter) administrator account with sufficient credentials to create a dedicated vCenter service account. DSM does not retain the vCenter administrator credentials after this step; they are discarded once the service account is created and plug-in registration completes. Administrators can verify and update the target vCenter service account credentials in Settings &gt; System Settings under Target vCenter.
+For SQL Server deployments, DSM introduces additional privileged account types that organizations must include in their inventory. DSM deactivates the default SQL Server sa account and uses a reserved internal account, dsm_mgmt, with sysadmin privileges for management operations. The cluster administrator login receives restricted read-only privileges and specific ALTER privileges for server management and auditing rather than full sysadmin access. SQL Server deployments support two administrator user identity types: SQL User or Windows Principal, with the Windows Principal option available for clusters integrated with Active Directory. Organizations that configure the optional Active Directory privileged account for automated SPN and DNS record management must include that account in their inventory.
+When self-service consumption is configured, a Cloud Administrator account must map to a DSM user account to install and operate the Consumption Operator. Organizations should include any such mapped accounts in their privileged account inventory based on the DSM role assigned to the mapping.
+For this control to be fully met, organizations must establish processes outside DSM to enumerate all accounts assigned the Admin role (both local and LDAP-sourced), account for the vCenter service account, any SQL Server-specific privileged accounts, and any Active Directory accounts configured for SQL Server automation, and confirm that each privileged account has been authorized by the appropriate level of organizational management. DSM's RBAC model provides the technical structure to support that review, but the inventory compilation and authorization validation steps require organizational governance processes.</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -1581,13 +1620,11 @@
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides a native role-based access control (RBAC) system on the Avi Controller that restricts and controls privileged access to application delivery resources. The RBAC model assigns each user a role that governs their access level, with three permission states available per resource: write, read, or no access. The No Access privilege level is a distinct state that blocks users from accessing, reading, or listing resources entirely. Administrators can create custom roles through the Controller UI that grant precisely scoped access to specific system areas, with each resource configured independently. This supports least-privilege configurations tailored to distinct operational roles such as application operators, application admins, and system administrators.
-For environments requiring finer-grained control, Avi's Extended Granular RBAC applies and enforces label-based permissions on cloud objects. The restrict_cloud_read_access field in controller properties governs whether label-based access scoping applies to cloud object reads. Roles can be configured with write_access type and the resource permission_pool setting to restrict role privileges to specific pool sub-resources such as subresource_pool_enabled, providing field-level access scoping within a resource type. Auth Mapping rules can be updated to deny privileges to specific users, blocking them from obtaining any roles or tenants upon login. Multi-tenant deployments can scope access by tenant: user groups can be mapped to a limited set of tenants with read-only privileges, while separate groups hold application owner privileges within those same tenants, enabling separation of duties between groups managing different applications or environments within a shared Avi deployment.
-Avi supports TACACS+ server integration for centralized authentication and role assignment. Authorization attributes from a TACACS+ server map Avi users to roles and tenants, allowing organizations to govern privileged access through their existing network access control or identity infrastructure. The Avi Controller also supports LDAP authentication with the Administrator Bind configuration for user authentication and group membership validation. LDAP user account passwords are managed remotely and set by an administrator, not locally.
-Administrators can create custom user account security profiles with organization-specific thresholds for password history, login failure, session limits, and credential timeout policies. The Controller implements Super User Accounts as a separate user account security mechanism. The admin account is maintained as a locally authenticated account even in systems configured for remote authentication. The avidebuguser account has sudo privileges on the Avi Controller for Linux CLI access, and access to this account should be restricted to authorized personnel. Using role-based access control, the ability to export certificates and private keys must be restricted to the fewest administrators possible.
-Avi Cloud Console enforces access control through two access levels: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration operations.
-When Avi is deployed in a VMware vCenter environment, the Cloud Connector uses a dedicated vCenter account configured with a minimal set of permissions. Two vCenter roles are required: one with global privileges and another with folder-level privileges. The Avi-Folder-Role scopes the account's permissions to the specific folders containing Service Engine VMs in the vCenter inventory. In VCF deployments with a vSphere Supervisor, the Avi Controller cloud configuration supports either a vCenter administrator account or a dedicated account with lesser, precisely defined permissions. The Cloud Connector role requires specific vCenter privileges covering Virtual Machine Guest Operations, Host Local Operations, and other provisioning capabilities, following the principle of least privilege for service account access to the underlying platform.
-Several permissions classified under Operations and Administration are not supported for per-application label-based RBAC, including L4POLICYSET, WAFPOLICYPSMGROUP, PINGACCESSAGENT, NETWORKSERVICE, and NATPOLICY, among others. These permissions remain under global administration scope and cannot be delegated to application-scoped roles.</t>
+          <t>VMware Avi Load Balancer provides role-based access control mechanisms on the Avi Controller that restrict which accounts hold privileged access. The Controller enforces Tenant and Role assignment during account creation, scoping each user's access to specific areas of the system based on their assigned role and tenant membership. Roles can be predefined or custom; administrators can create custom roles tailored to specific access requirements when predefined roles do not meet the needs of a given account. Role assignment is available at account creation or at any time thereafter through the Role drop-down menu in user account configuration.
+The admin user account is the standard administrative account for Avi Load Balancer and is authorized to perform the highest-level operations, including user creation and authorization, tenant creation, and all infrastructure operations associated with the admin tenant. The admin account is maintained as a locally authenticated account even on systems configured for remote authentication. Once a user is assigned Super User privileges, the Super User Rule takes effect: no subsequent tenant or role mapping assignments can override that access level, making superuser designation a high-consequence privilege that requires an explicit administrative action to grant or revoke.
+Within each user account, the assigned role is mapped to a tenant, so users can access resources only to the extent permitted by their role within that tenant. Privileged access in one tenant does not carry over to other tenants. This tenant-scoped role assignment allows organizations to enforce fine-grained access boundaries across multi-tenant deployments.
+In global server load balancing (GSLB) deployments, Avi Load Balancer supports creation of non-admin users with assigned roles for granular access control. Dedicated role accounts can be assigned specific GSLB roles, such as the gslbsitemembadmin account assigned the Gslb_Group_Member_Enabled role, restricting each account's capabilities to its designated function. The Avi Kubernetes Operator (AKO) extends role-based access control to Kubernetes workloads through Custom Resource Definitions (CRDs) that can be governed by Kubernetes RBAC policies, allowing stricter access control over which users can configure routing rules and related resources.
+The License Hub component within Avi Load Balancer enforces role-based access through two distinct local user accounts: an Admin account with the enterprise_admin role for full system management, and an Audit account with the auditor role scoped to system auditing purposes. This separation keeps high-privilege management access distinct from read-oriented audit access.</t>
         </is>
       </c>
     </row>
@@ -2122,20 +2159,12 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several built-in mechanisms for controlling and securing remote access to infrastructure components across the platform.
-Centralized identity and authentication. All administrative access to VCF components flows through authenticated interfaces with centralized identity management via VCF SSO. VCF SSO supports identity provider federation, allowing vCenter to replace its built-in identity source with an external identity provider such as AD FS, Azure AD, or Okta. This integration enables organizations to enforce their existing authentication policies, including multi-factor authentication, across VCF management interfaces. VCF SSO provides centralized authentication that reduces the need for direct ESX host login with local credentials.
-SSH access controls. ESX hosts include the TSM-SSH service, which can be started and stopped to enable or disable SSH access on a per-host basis. SSH access is also available for NSX Manager, VCF Operations appliances, and cloud proxy instances. VCF Operations Cloud Proxy disables SSH by default, requiring initial access through the vCenter console before SSH can be enabled. When SSH is active on VCF Operations nodes, a restricted access banner is displayed to users upon connection. ESX host advanced options allow administrators to configure shell timeouts and host client session timeouts, limiting the duration of interactive remote sessions. For VCF Automation deployments, remote access supports both password and public-private key authentication via SSH, providing a stronger alternative to password-based login. VCF Operations orchestrator can also register a public key on an SSH host to enable key-based authentication.
-DCUI and lockdown mode. ESX supports configuration of the DCUI.Access setting, which specifies which users can override lockdown mode and access the Direct Console User Interface. When lockdown mode is enabled, this restricts the set of accounts that can interact with the host locally or through the DCUI, reducing the available remote management surface. ESX hosts support an Exception Users list for lockdown mode, providing granular control over which accounts retain access during restricted operation. ESX supports two lockdown mode levels: Normal mode keeps the DCUI service running and allows local console access alongside vCenter management, while Strict mode stops the DCUI service entirely and restricts access to vCenter only. ESX Shell and SSH services operate independently of lockdown mode and must be separately deactivated, since lockdown mode itself does not restrict those services.
-Console and management access. Access to ESX hosts requires login at the host's HTTPS URL as a user with the Administrator role. Virtual machine console access via the VNC protocol can be individually enabled or disabled through the RemoteDisplay.vnc.enabled setting in vCenter, giving administrators control over which remote console methods are available. The virtual serial port proxy can act as a gateway to enforce security policies for remote serial port connections. Management port access on network devices within the VCF environment must be password protected, and console port access must require authentication.
-Role-based access control for remote sessions. Role-based access control governs what authenticated users can do once connected. vCenter allows creation of custom roles with granular privilege assignment and permission propagation to vSphere objects. The CloudAdmin role model in VCF Automation restricts administrative scope. NSX implements RBAC to restrict system access to authorized users by assigning roles with specific permissions, including the ability to create custom roles that suit operational requirements. NSX Federation also supports RBAC across federated environments. These layered RBAC controls enforce granular permissions on remote sessions across the platform.
-Remote access to provisioned workloads. Remote sessions to provisioned machines in VCF Automation for VM Apps require connecting to the machine's IP address or FQDN and authenticating with a username and password. VCF Automation cloud templates also support remoteAccess authentication using public-private key pairs with SSH key input parameters.
-These controls give administrators granular ability to enable, disable, and restrict specific remote access methods across VCF infrastructure. However, defining which remote access methods are organization-approved, establishing policies governing their use, and conducting periodic reviews of remote access configurations are organizational responsibilities that fall outside VCF's scope.
-VMware Private AI Services (PAIS) provides mechanisms for controlling remote access to its AI workload components, supporting the organizational processes for defining and reviewing approved access methods.
-PAIS enforces user access through OIDC group-based authorization. Access is granted only to user accounts belonging to groups listed in the authorizedGroups configuration (and the oidc-authorized-groups setting when activation is performed through the VCF Automation UI). Group names such as group-for-pais-access-01 are specified on the OIDC provider, and HTTPS-based communication to the OIDC provider is required. PAIS also uses a CA trust bundle (ca-trust-bundle) for secure communication with external services and databases, including Harbor registries and MCP servers. When PAIS is consumed under VMware vCenter 8.x, VCF SSO must be configured to access Private AI Services namespaces and their resources from VCF Automation; under vCenter 9.x or later this SSO step is not required.
-Deep Learning VMs (DL VMs) deployed through VCF Automation require user password configuration and support optional SSH public key authentication for remote administrator access. DL VMs are exposed through LoadBalancer services that provide public IP addresses and mapped ports for SSH on port 22 and JupyterLab notebook access on port 8888. DL VMs that include the NVIDIA Triton Inference Server use the same password and SSH public key authentication pattern, and are accessed over SSH as the vmware user. The PyTorch profile for DL VMs restricts JupyterLab to the local machine only by default, listening on port 9400, which reduces the remote attack surface for development notebooks.
-API access to PAIS administrative endpoints goes through authenticated channels. The VCF Consumption CLI authenticates to VCF Automation endpoints using an API token, the FQDN or IP address of the endpoint, and an optional CA certificate for TLS verification. The vcf context create command issued through this CLI requires the same credentials, and VCF Automation Provider Management exposes an API Token endpoint that allows provider administrators to create and manage API tokens. VCF Automation organization administrator access tokens are obtained through a POST request to a sessions endpoint using Basic authentication. PAIS provides a dedicated VCF Automation API endpoint for registering vCenter instances using Bearer token authentication, and Broadcom recommends using the FQDN of the vCenter instance rather than its IP address when registering it.
-For AI agent and knowledge base integrations, PAIS adds review controls on remote endpoints. Remote MCP servers connected to PAIS must be accessible over HTTP or HTTPS using the Streamable HTTP or Server-Sent Events transport, can optionally use static authentication tokens, and require examination and approval of their tools and capabilities before use in agents. The PAIS Agent Builder maintains a list of approved tools for use in AI agents when connecting to MCP servers, giving administrators a control point over which remote services agents are allowed to call. Microsoft SharePoint data sources used as PAIS Knowledge Bases require username and password authentication and are limited to SharePoint On-Premises deployments.
-For model artifact distribution, the PAIS Model Gallery uses Harbor project access capabilities to restrict access to sensitive data used to train and tune models, and the oras login command authenticates to a private Harbor registry using username and password credentials before any push operations.</t>
+          <t>VCF provides several mechanisms that contribute to automated monitoring and control of remote access sessions across its infrastructure components. These capabilities span session lifecycle management, configurable timeouts, service-level access controls, audit event tracking, and integration with operational monitoring tools.
+At the core of vCenter session management, the SessionManager managed object controls user access to the server through methods for logging in, obtaining a session, and logging out. The SessionManager provides an interface to the authentication infrastructure on the target server system, enabling programmatic session lifecycle management. Session persistence controls in the vSphere Web Services API allow client applications to save sessions locally to secure files for later reconnection, with the server maintaining control over session validity. SessionManager also supports session impersonation, where one user session can adopt the authorization level of another, subject to appropriate permissions. Complementing this, the CIS Session service allows principals to manage session tokens, including creation and deletion of session identifiers and obtaining information about active sessions. The vSphere Automation SDK builds on these capabilities by supporting session-based authentication where a session ID is generated and used to establish a security context for subsequent API calls. These interfaces support both interactive session termination and programmatic session monitoring from external tooling.
+ESX hosts provide granular control over remote access sessions through advanced configuration options. These settings include SOAP session timeout, shell timeout, host client session timeout, login attempts before lockout, and seconds delay after lockout. Each of these parameters can be configured to enforce automated session controls, such as terminating idle sessions after a defined period or locking out accounts after repeated failed login attempts. The TSM-SSH service on ESX hosts can be started and stopped to enable or disable SSH access entirely, giving administrators the ability to restrict remote shell access when it is not needed. SSH access is disabled by default on certain components such as VCF Operations Cloud Proxy, where the first login must be performed via the vCenter console. VNC-based console access to virtual machines can also be controlled through the RemoteDisplay.vnc.enabled setting in vCenter.
+ESX lockdown mode provides an additional layer of remote access control. When lockdown mode is enabled, the DCUI.Access setting determines which users can override lockdown mode and access the Direct Console User Interface. This restricts remote management pathways to the vCenter, reducing the number of access points that require monitoring. Lockdown mode is available in two configurations: Normal mode leaves the DCUI service running and accessible to users with administrator privileges who are listed as Exception Users, while Strict mode stops the DCUI service entirely and disallows all direct host access when vCenter is unavailable. In either configuration, ESX Shell and SSH services operate independently of lockdown mode and must be explicitly deactivated to make lockdown mode an effective access restriction.
+VCF Operations captures audit events for platform interactions including user logins, logouts, and configuration changes, providing visibility into remote session activity. The User Activity Audit report provides traceability of user activities including logging in, actions on clusters and nodes, changes to system passwords, activating certificates, and logging out. VCF Operations also supports alert automation, which can trigger notifications based on defined conditions, enabling automated detection of unusual access patterns. The policy engine in VCF Operations can monitor and generate events to react to changing conditions, enabling automated responses to session-related events. Administrators can configure custom monitoring actions including custom scripts, remote checks, Windows service monitoring, and Linux process monitoring. VCF Automation integrates with VCF Operations to surface insights and alerts for monitored objects.
+These session management, timeout configuration, audit, and monitoring mechanisms operate automatically across VCF components. Thresholds, policy values, and alert conditions are configurable so administrators can align session control behavior with organizational policy.</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -2145,11 +2174,10 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to remote access governance through network-level enforcement and behavioral detection. The Distributed Firewall (DFW) can enforce policies controlling which sources and protocols, such as SSH and RDP, may reach management interfaces, while Identity Firewall (IDFW) adds user-aware policy enforcement for remote user groups. IDFW supports Virtual Desktop Infrastructure (VDI) environments, Remote Desktop Session Hosts (RDSH), and physical machines, where multiple users may log in simultaneously; in RDSH deployments, administrators create Active Directory security groups to allow or deny user access to application servers through DFW rules based on the user's assigned role. IDFW supports the multi-user RDSH use case for both TCP and UDP protocols.
-The Security Services Platform (SSP) includes Security Intelligence, which detects suspicious behavior for remote connections such as telnet, SSH, and VNC, providing visibility into remote access activity. SSP also correlates lateral movement events with subsequent infection-type activity, such as detecting RDP connections from one workload to another followed by command-and-control activity originating from the destination.
-SSH access to Malware Prevention Service virtual machines is disabled by default and must be explicitly activated by the vCenter administrator. SSH to these service VMs uses key-based authentication with a public-private key pair; a public key is required at deployment time and a private key is required to initiate an SSH session. Administrators should deactivate SSH access once troubleshooting or debugging tasks are complete.
-Role-based access control within SSP limits which users can administer vDefend components remotely. SSP defines five built-in roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. These roles can be assigned to individual remote users or remote user groups, including Active Directory groups, integrating with existing enterprise directory services for remote administrator management. CLI commands for Distributed IDS/IPS must be run on ESX hosts, with available commands and viewable modes differing based on the user's assigned role.
-Defining organization-approved remote access methods, VPN provisioning, and centralized remote access governance remain outside vDefend's scope.</t>
+          <t>VMware vDefend contributes to automated monitoring and control of remote access sessions through network-level traffic analysis, protocol detection, and firewall policy enforcement. While session lifecycle management (authentication, idle timeouts, and forced termination) is handled by VMware vCenter and VCF SSO, vDefend provides the network security layer that monitors, detects, and controls remote access traffic traversing the virtualized infrastructure.
+Security Intelligence continuously monitors network traffic flows and detects new, unapproved, or unexpected connections between segments. It identifies remote access protocols such as SSH, RDP, VNC, and telnet as suspicious behavior in a datacenter context, and categorizes detected events using MITRE tactics and techniques, recording the number of occurrences over a selected time period. The Remote Services detector within Security Services Platform flags suspicious behavior on these remote connections, alerting administrators to potentially unauthorized remote sessions. Security Services Platform's campaign correlation rules extend this detection by correlating RDP activity between workloads with subsequent command-and-control events, automatically surfacing multi-stage remote access attacks in a single alert. Security Intelligence Policy Recommendations includes a Monitoring capability that checks for changes in the scope of input entities every hour when enabled, providing near-continuous automated oversight of access patterns.
+The Identity Firewall (IDFW) provides session-level awareness for remote access scenarios. IDFW supports Virtual Desktops (VDI), Remote Desktop Sessions (RDSH), and physical machines, tracking simultaneous logins by multiple users with independent user environments. IDFW detects logins using Event Log Scraping, which monitors login events in domain controller event log servers. With IDFW and RDSH, administrators create Active Directory security groups to allow or deny user access to application servers based on their assigned role. Security Intelligence displays the number of IDFW active user sessions, giving administrators visibility into the current population of remote sessions. Identity Firewall supports the Multi-User (RDSH) use case with TCP and UDP protocols.
+The Distributed Firewall and Gateway Firewall can enforce automated controls on remote access traffic through microsegmentation policy. Administrators can define rules that restrict remote access protocols to approved source networks, limit which segments are reachable via SSH or RDP, and block unauthorized remote access attempts. Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments. Security Intelligence generates policy recommendations for applications based on monitoring data, supporting the transition from observation to enforcement for remote access controls. The Environments monitoring window within Security Services Platform provides a high-level overview of all environments, including the number of inter-environment pairs that lack inter-environment policies.</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -2179,13 +2207,10 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several native mechanisms for controlling remote administrative access to the Controller and Service Engines. Administrators reach the Avi Controller through SSH for command-line management or through the HTTPS-based web UI and REST API. SSH is also the secure channel used between the Controller and Service Engines for management communication.
-To restrict which hosts may initiate remote access sessions, the Client Management Access feature allows configuration of separate IP allowlists for SSH clients, CLI shell clients, external HTTP(S) clients, and external SNMP clients. Each allowlist accepts individual IP addresses, ranges, or IP groups. Separate IP access lists must be configured per management interface to restrict access through each channel individually. The web interface, SSH daemon, CLI Shell, and SNMP each require their own access list configuration.
-SSH management sessions also support configuration of allowed HMAC algorithms. Administrators can restrict which HMAC algorithms are accepted for SSH clients rather than relying on the default of allowing all standard HMACs. This capability restricts the set of cryptographic options available during SSH session establishment.
-For Service Engine remote access, Avi supports SSH key-based authentication. By default, Service Engines allow direct SSH access using the system's admin credentials; this default should be reviewed and restricted through allowlists and key-based authentication to align with site access policies.
-For identity binding, Avi supports remote authentication through LDAP, TACACS+, and SAML. Administrators configure an Authentication Profile and, optionally, a Mapping Profile that binds enterprise directory group membership to Avi roles. When remote authentication is active, local user login can be retained as a fallback for emergency access or deactivated entirely to enforce remote authentication for all administrator logins.
-In Kubernetes deployments, Avi Kubernetes Operator (AKO) Custom Resource Definitions (CRDs) can be governed through Kubernetes Role-Based Access Control (RBAC) policies to restrict which users and groups may configure ingress routing rules and load balancing resources.
-The organization must designate approved remote access methods in policy, document them, and conduct periodic reviews to verify that allowlists, HMAC algorithm restrictions, and authentication profiles remain consistent with current access requirements.</t>
+          <t>VMware Avi Load Balancer provides several mechanisms that support automated monitoring and control of administrative remote access sessions. Administrative access to the Avi Controller is available through SSH, the web UI, and the REST API. Remote users are authenticated through external identity providers including LDAP, TACACS+, or SAML, and local user login can be deactivated when remote authentication is enabled. TACACS+ integration is particularly relevant to session monitoring because TACACS+ separates authentication, authorization, and accounting, allowing a centralized TACACS+ server to log every administrative session with user identity, commands executed, and session details.
+The Avi Controller generates metric-based alerts that can be configured to monitor specific controller metrics and trigger notifications when thresholds are exceeded. Alert notifications can be delivered to remote syslog servers for centralized monitoring and audit trail collection, forwarded to Webhook URLs or Slack channels via ControlScripts, or routed to external monitoring platforms including Prometheus. This enables integration with existing SIEM and observability infrastructure.
+ControlScripts extend this framework to programmatic automated response. These Python-based scripts run on the Avi Controller control plane in response to defined system events and can trigger alerts, alter Avi configuration, or communicate to remote systems. For broader automation, Python can be integrated into CI/CD pipelines and data analytics workflows to provision Avi infrastructure, monitor load balancer events, analyze logs, and trigger alerts based on specific event types. Avi also provides direct session control: administrators can invalidate all active sessions using the --clear-sessions shell command when session limits are reached or a security event warrants immediate termination.
+At the platform level, VCF provides complementary session controls through VCF SSO, which governs identity for the broader infrastructure environment. Effective implementation of this control requires the organization to configure TACACS+ or syslog forwarding to a SIEM, define alerting thresholds appropriate to their session monitoring requirements, and operate those integrations on an ongoing basis.</t>
         </is>
       </c>
     </row>
@@ -2948,13 +2973,10 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) provides network security controls that contribute to securing cloud instances in line with industry practices. While cloud management spans compute governance, identity management, compliance scanning, and operational monitoring, vDefend addresses the network security dimension through multiple integrated capabilities.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level across all workloads running on VCF. Security policies follow workloads regardless of network location, enabling zero-trust segmentation that limits lateral movement between cloud instances. Administrators define firewall rules using security groups, tags, and dynamic membership criteria, allowing policy to adapt automatically as workloads are provisioned or relocated. Privileged Labels provide a tamper-proof mechanism that anchors firewall rules to immutable labels, preventing virtual machines from leaking out of their assigned security groups. Identity Firewall can be enabled on compute clusters to extend policy enforcement to Active Directory user and group identity, enabling security rules that follow users across workloads. The Gateway Firewall extends protection to north-south traffic at Virtual Private Cloud (VPC) boundaries, and Pre-defined Security Strategies allow administrators to define a baseline security posture for VPCs to establish consistent protection policies.
-vDefend integrates with VCF Automation to allow organizations to define and enforce security postures for workloads within self-service private cloud environments. Groups in vDefend map cloud constructs from VCF Automation into the underlying vDefend infrastructure, enabling policy recognition and enforcement on VPCs, Groups, and virtual machines within namespaces. This integration maintains consistent security postures as workloads are provisioned through automation workflows.
-vDefend IDS/IPS provides signature-based and behavioral intrusion detection and prevention for cloud workloads. Organizations can import custom signatures or integrate with third-party threat feeds, including industry-specific Information Sharing and Analysis Centers (ISACs). Virtual patching capabilities allow deployment of protective signatures before vendor patches are available, reducing the exposure window for cloud instances. In federated deployments, a Global Manager provides centralized management for blocking malicious traffic across all connected Local Manager sites, maintaining and propagating untrustworthy IP address lists based on historical behavior patterns.
-Malware Prevention through Advanced Threat Prevention (ATP) inspects files traversing east-west and north-south network paths. Malware Prevention profiles can be configured to send files to the VMware vDefend ATP Cloud Service for cloud-based analysis, or to process files locally without cloud analysis, without requiring agents on individual instances. Security policies can be defined, propagated, and enforced across Bare Metal servers through Security Services Platform, extending consistent enforcement across physical infrastructure.
-Security Services Platform (SSP) is a modern microservices platform that hosts features that collect, ingest, and correlate network traffic data. SSP includes Security Intelligence, which allows administrators to accept or modify inferred classifications of compute entities as network infrastructure or non-infrastructure services, supporting accurate security policy planning. SSP maintains a centralized repository of current organizational IT assets, including servers, software, and network devices with their configurations, providing an authoritative inventory for policy planning purposes. Network Detection and Response (NDR) provides behavioral analysis and anomaly detection across east-west traffic flows, identifying threats that signature-based detection may miss. NDR data sharing to the vDefend ATP Cloud Service is activated by default and can be configured through System &gt; Privacy, allowing organizations to control whether data is shared to the cloud where data residency requirements apply. SSP has high availability capabilities by default and supports scaling out individual services, including Analytics, Data Storage, Messaging, and Metrics, through System &gt; Platform &amp; Features &gt; Core Services.
-Together, these capabilities address the network security requirements within a broader cloud management control framework, providing workload-level enforcement, threat detection, and traffic visibility for cloud instances.</t>
+          <t>VMware vDefend's Gateway Firewall provides network boundary controls that restrict inbound and outbound traffic to and from publicly accessible systems, limiting network exposure at the perimeter. URL filtering applies access control based on URL categories, URL reputation, and custom URL lists, enabling policy-based governance over what external services and web content internal systems can reach.
+For public web server traffic, IDS/IPS within VMware vDefend includes explicit guidance that such traffic be configured with Prevent or Detect action and never exempted from inspection, treating it as untrusted traffic that requires full IDS/IPS coverage. The Distributed Firewall (DFW) supports App Strategy, an intent-based security mode that allows administrators to select predefined strategies such as "Allow Outgoing Traffic" or "VPC Isolation" to automatically generate read-only system rules, reducing the risk of misconfiguration for publicly exposed workloads. The DFW also supports FQDN-based filtering through allowlist and denylist rules configurable with source groups, destination groups, and DNS context profiles, enabling domain-name-based policy enforcement for traffic to and from publicly reachable systems.
+The Gateway Firewall supports inter-project isolation by denying all inter-project communication except for essential infrastructure protocols such as DHCP, DNS, NTP, and ICMP, helping to contain publicly accessible workloads within defined network boundaries. The Security Services Platform supports publishing environment rules, inventory assets, and policies as distinct operations that can be applied individually or collectively across infrastructure tiers, enabling segmentation of publicly exposed workloads from the broader environment.
+VMware vDefend addresses network-layer controls only and does not govern web application content, content management system publishing workflows, or organizational review processes for publicly accessible information.</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2980,12 +3002,9 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that contribute to the implementation of cloud management controls for database-as-a-service workloads deployed on VCF.
-Data service policies are a central control mechanism in DSM. Administrators define and configure these policies to govern how database clusters are provisioned, what infrastructure resources they may consume, and which organizational standards apply. When integrated with VCF Automation, data service policies can be applied across multiple tenants or organizations, with each tenant or organization required to adhere to its prescribed configurations. Administrators can tailor policies to specific requirements and assign them to one or more organizations, supporting consistent governance across a multi-tenant environment. The DSM UI provides a dedicated interface for configuring policies for each supported database type, including SQL Server in addition to PostgreSQL and MySQL. This policy enforcement model gives platform administrators a mechanism for translating organizational cloud management standards into operational constraints that apply at provisioning time.
-Infrastructure policies in DSM control the placement of database VMs within storage and determine which VM classes and datastores are used when database clusters are created. Cloud Administrators configure which infrastructure policies are available within each consumption namespace, restricting database provisioning to resources and configurations that meet organizational standards. This limits how Cloud Users can consume database capacity without requiring explicit administrative approval for each individual deployment.
-DSM manages instance certificates for database clusters and establishes TLS connections to both the DSM Provider VM and individual database instances. Administrators can add trusted certificate authorities to the OS trust store to verify connections, and a Cloud Administrator must obtain and save a TLS certificate for secure communication between the Consumption Operator and the DSM provider before enabling self-service consumption. DSM also establishes secure connections to VMware vCenter using certificate validation, providing certificate-based authentication across the management plane.
-Database provisioning in DSM is self-service within the bounds set by the Cloud Administrator. Cloud Users deploy database clusters through Kubernetes-native resources in namespaces configured and controlled by the Cloud Administrator. This model delegates provisioning authority to end users while preserving administrative control over the infrastructure and policies available to them. The Consumption Operator, installed and managed by the Cloud Administrator, is the mechanism through which this bounded self-service access is enabled.
-Meeting this control fully requires the organization to establish and maintain a cloud management program that defines security standards, monitors compliance posture, and updates policies as requirements evolve. DSM's policy enforcement capabilities support that program for database workloads, but the broader governance activities, including risk assessments, vendor management reviews, and cross-service compliance monitoring, remain organizational responsibilities.</t>
+          <t>VMware Data Services Manager (DSM) supports cloud security architecture requirements through a policy-based configuration framework that administrators can align with organizational technology strategies. DSM data service policies allow administrators to define and enforce consistent configurations across tenants and organizations. These policies can be tailored to specific requirements and assigned to one or more organizations, providing a mechanism to translate architectural decisions into enforceable platform-level controls. When used with VCF Automation, this policy framework extends to multi-tenant environments where DSM maintains data separation and security across different organizations sharing the same infrastructure. In 9.1, data service policy support extends to SQL Server databases alongside PostgreSQL and MySQL, allowing the same policy enforcement model to apply across all three database engines.
+DSM includes several built-in security controls that support a configurable security posture for database services. DSM verifies the SHA256 thumbprint of vCenter during configuration to confirm the identity of the target vCenter before establishing communication. A Cloud Administrator must obtain a TLS certificate for secure communication between the Consumption Operator and the DSM provider. SQL Server clusters use TLS to encrypt communication between clients and the database. PostgreSQL database clusters use SCRAM-SHA-256 password encryption and store host-based authentication configuration in pg_hba.conf. PostgreSQL databases can also enable the pgcrypto extension, which provides cryptographic functions for securing data at the application layer.
+Self-service consumption of DSM database clusters follows a Kubernetes-native model, where authorized cloud users provision databases through the Consumption Operator and custom resources on approved Supervisor clusters. A Cloud Administrator must obtain the list of infrastructure policies supported by the DSM provider and configure the policies allowed for the consumption cluster before self-service provisioning begins. Administrators assign object stores and data service policies to specific tenants, keeping resource consumption within boundaries defined by the data service policy. The separation of provider and consumer roles, with distinct responsibilities for infrastructure administration and organizational resource management, supports defined access and accountability within the cloud security architecture.</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
@@ -3133,17 +3152,15 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to maintaining network architecture diagrams and data flow documentation, though the organizational process of creating, maintaining, reviewing, and governing formal diagram artifacts remains a customer responsibility.
-VCF Operations for Networks includes an end-to-end interactive network map that displays a detailed model of both physical and virtual devices in the environment, including physical switches, physical firewalls, routers, load balancers, transport nodes, and NSX virtual entities. The Network Map Summary presents a view of the data center that includes these entities along with an alert chart showing alert status across the inventory. Users can scope the view to focus on specific portions of the network. Because the map updates based on data collected from configured sources, it reflects the discovered state of the monitored infrastructure rather than a static diagram, providing a foundation for understanding the current network architecture and validating formal network diagrams.
-NSX network connectivity workflows include a built-in topology visualization that correlates user configuration inputs with the resulting network topology, helping administrators understand the architecture before committing changes and reducing the risk of misconfiguration by providing a view of the entire setup. The NSX Manager Network Topology feature allows users to view network connectivity by zooming in to see details about logical entities and their logical paths, along with the services configured on those entities. The NSX Main Dashboard displays the topology of a selected object and how it connects to elements in the network, with a view of related alerts. The vSphere Client provides topology views of compute, storage, and network relationships, displaying logical and physical components such as segments, transport zones, and resource dependencies. The vSphere Distributed Switch topology diagram specifically shows information about the physical adapter connecting virtual adapters to the external network, with filters that default to displaying up to 32 port groups, 32 hosts, and 1,024 virtual machines.
-The vSphere Network Inventory Dashboard provides a dedicated topology view of the vSphere network inventory, including information related to vSphere environments, vCenter instances, data centers, distributed vSwitches, distributed port groups, virtual machines, and associated properties and metrics. The Network Configuration Dashboard displays key configuration information including bar charts focused on critical security settings for vSphere distributed switches, providing visibility into the security-relevant configuration state of the network infrastructure.
-For data flow analysis, VCF Operations for Networks collects flow data defined by 5-tuple values: source IP address, source port, destination IP address, destination port, and protocol. At the virtual switch level, vSphere Distributed Switches also support NetFlow export, configured with an Observation Domain ID that identifies the switch within the flow collection infrastructure, so flow data can be sent to external collectors for analysis alongside data collected by VCF Operations for Networks. The Access Flow Insight page in Network Operations allows analysis of all flows available in the environment, where each dot in the graph represents multiple flows and users can drill into individual flow details. The Custom Analysis section within Flow Insight provides two-dimensional visualization of flow data on user-selected dimensions to identify outliers in network traffic patterns. Flow metrics display traffic flow data collected from flow-enabled data sources, aggregated to show metrics such as total bytes and traffic rate. Flow analytics can also be run to understand bandwidth and packet rates.
-VCF Operations for Networks supports flow-based application discovery, accessible by navigating to Infrastructure Operations, then Analyze, and selecting the Flows tab. This allows administrators to discover applications by analyzing traffic patterns and network flows in the environment, with the ability to modify the scope, naming preference, and duration of the discovery process. The application topology map displays traffic flows between application tiers, internet endpoints, shared services, and other applications, showing how data moves between workload groups. The map shows tier overviews, lists of members (including VMs, Kubernetes services, and physical IPs), flows between tiers, and the physical IPs and shared services that applications depend on.
-VCF Operations for Networks also provides a Security Planning capability that analyzes flows and displays traffic flow patterns and micro-segmentation views. This feature supports security assessment by making it possible to see how traffic moves through the environment, which is directly relevant to documenting sensitive or regulated data flows and assessing the security posture of the network architecture. The platform also provides planning and recommendations for implementing micro-segmentation security, and the micro-segmentation flow analysis interface allows filtering by protection status to view allowed and blocked flows.
-VCF Operations for Networks includes a PCI Compliance page that presents a network flow diagram showing data flow paths, firewall placements, connections, and other details associated with the network. This built-in visualization is oriented toward compliance assessment and can supplement organizational network architecture documentation.
-For multi-site environments, VCF Operations for Networks supports flow visualization for SDDC-to-SDDC communication through VMware Transit Connect via the VMware Managed Transit Gateway (VTGW), providing visibility into cross-data-center network flows. The Streaming Databus supports cross-data center network flow analysis by grouping query results by source data center, destination data center, and flow type.
-Firewall rules can be exported to CSV files using the run_fw_rule_export CLI command, producing files that can be transferred via secure copy for integration into formal documentation. VCF also documents its own internal network ports and protocols at ports.broadcom.com, which provides reference material for documenting the platform's own communication paths.
-While VCF provides tools for network topology visualization, flow analysis, application discovery, and security-oriented network views, the control requires a formal organizational process for maintaining network architecture diagrams and data flow diagrams that are kept current and contain sufficient detail for security assessment. VCF's capabilities provide the underlying data and visualization tools that inform these diagrams, but the creation, review, approval, and maintenance lifecycle of the formal documentation is an organizational responsibility.</t>
+          <t>VCF provides multiple layers of access control list (ACL) mechanisms and network traffic restriction capabilities that contribute to data flow enforcement, though full ACL governance across physical and virtual infrastructure requires organizational processes and may benefit from VMware vDefend for advanced stateful firewall rule sets.
+At the network infrastructure layer, VCF uses vSphere Distributed Switches to centrally manage VLAN assignments, port group policies, and traffic shaping rules across all hosts in a workload domain. Distributed switches support traffic shaping policies that limit the bandwidth of incoming traffic, helping restrict which traffic types and volumes can traverse each network segment. Distributed port groups and uplink port groups also support a Traffic Filtering and Marking Policy, where per-rule actions can be set to Allow, Drop, or Tag traffic based on defined match criteria, providing rule-based traffic enforcement at the virtual switch level. Traffic segmentation is built into VCF's architecture: management, vMotion, vSAN, and NFS traffic each run on dedicated VLANs and VMkernel ports, and the vMotion network must be distinct from the vSAN network. This separation restricts which traffic types can traverse each segment by design. Private VLANs (PVLANs) provide additional Layer 2 isolation within a single VLAN through virtual network segmentation on distributed virtual switches, limiting communication between VMs even on the same segment. Distributed switches also support VLAN-based SPAN (VSPAN) for virtual distributed port mirroring, which aids in monitoring and validating traffic flows. At the ESX host level, a built-in firewall operates on a deny-by-default basis, closing all ports except those an administrator explicitly designates as authorized, giving each host an independent network access control point.
+NSX extends these capabilities with software-defined networking constructs including segments, Tier-0 and Tier-1 gateways, and Virtual Private Clouds (VPCs). NSX Tier-0 gateways can be configured with linked Tier-1 gateways to create multi-tier topologies, enabling route-based traffic restrictions between network tiers. NSX edge gateways handle north-south routing. With vDefend deployed, North-South Firewall Rules on these gateways provide traffic protection, and an NSX project's default gateway firewall and distributed firewall rules (a vDefend capability) govern the default behavior of north-south and east-west traffic for workloads in that project. VPCs are self-contained virtual network environments that provide an abstraction layer for setting up isolated virtual private cloud networks with their own topology, IP address management, and permission models, allocatable to discrete projects in a self-service consumption model. NSX Manager enforces approved authorizations for controlling the flow of management information within network devices based on information flow control policies.
+NSX also provides data flow enforcement at the load balancer tier through its Access List Control (ALC) feature. The NSX load balancer compares all traffic flowing through it with ACL statements, which either drop or allow the traffic based on configured rules. This gives administrators another enforcement point for restricting network traffic to only what is authorized.
+At the Consumption layer, VMware Kubernetes Service (VKS) and the Supervisor extend ACL enforcement to containerized workloads through Kubernetes NetworkPolicy resources, which function as Layer 3/4 ACLs for pod-level traffic. NetworkPolicy objects specify allowed ingress and egress traffic by pod selector, namespace selector, IP block, port, and protocol; pods not selected by any NetworkPolicy receive no restriction by default, making explicit policy deployment necessary to enforce a default-deny posture across a cluster. VKS clusters run Antrea as the default CNI plugin, which implements NetworkPolicy enforcement through the AntreaPolicy feature gate and provides per-policy and per-rule packet and byte count statistics through the NetworkPolicyStats capability, giving administrators visibility into which policies are actively restricting traffic. For VKS clusters using NSX VPC networking, NSX-backed network policies apply distributed ACLs at the hypervisor level, extending enforcement beyond the CNI layer. The ovn-kubernetes Transparent network mode similarly supports distributed ACLs applied via Kubernetes NetworkPolicy resources. For Layer 7 traffic control within VKS clusters, the Istio service mesh standard package provides a pluggable policy layer and configuration API supporting access controls, rate limits, and quotas based on workload identity; when deployed in ambient mode with strict mutual TLS, all service-to-service traffic within the mesh is subject to authentication before authorization checks apply, restricting lateral movement to explicitly permitted paths.
+For file-level and storage data flow isolation, the Supervisor uses ACLs to isolate file share access within supervisor namespaces, restricting data access between workloads running in different namespaces. vSAN file services support managing ACLs on SMB shares using the MMC tool, giving administrators granular control over which users and systems can access shared storage resources. Administrators should be aware that ACL-based file share isolation in the Supervisor carries a risk of IP spoofing, which should be addressed through complementary network controls when deploying file shares in multi-tenant environments. Argo CD deployments on the Supervisor implement network segmentation and firewall rules to control communication between Argo CD components, following the principle of restricting inter-component traffic to only what each component requires. The Harbor container registry standard package enforces role-based access control over artifact access, complementing network-layer ACLs with image-level access restrictions.
+For object-level access control, VCF Automation maintains an ACL table that defines which users can access specific defined entities. System administrators with the Manage General ACL right can create, modify, and remove ACL entries through the accessControls API. Those with the View General ACL right can audit ACL assignments on specific entities. Access to runtime defined entities is controlled through rights bundles and ACL entries. This ACL mechanism works alongside role-based access controls so that rights determine what actions a user can perform while ACLs determine which objects those actions apply to.
+VCF Operations for Networks supports ACL visibility through its network assurance and verification capabilities, which allow administrators to validate that ACL configurations are applied as intended across the managed environment. This includes the ability to verify ACL configurations on supported physical network equipment such as Cisco ASR routers, helping validate that physical and virtual network access controls are consistent.
+For workload-level traffic enforcement with stateful firewall rules, microsegmentation, and deep packet inspection, VMware vDefend and Gateway Firewall extend VCF's networking foundation with fine-grained Layer 2-7 policy enforcement. Organizations that require ACL governance beyond what VCF provides natively should establish processes for ACL review cycles, change management for firewall rules, and regular validation of both physical and virtual network access controls.</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -3153,11 +3170,12 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Intelligence capability, delivered through the Security Services Platform (SSP), provides live network traffic flow visualization and security posture mapping that directly support the creation and maintenance of network architecture diagrams and data flow documentation. While maintaining formal network diagrams is an organizational responsibility, Security Intelligence generates interactive visualizations of network traffic patterns, security group relationships, and Distributed Firewall (DFW) rule coverage that serve as authoritative inputs to those diagrams.
-Security Intelligence collects and displays network flow data through a visualization canvas covering groups, computes, destination ports, and Layer 7 application IDs. The visualization displays network traffic flows with color-coded indicators: red-hued dashed lines for unprotected flows, blue-hued solid lines for blocked flows, and green-hued solid lines for allowed flows. The Flow Details dialog shows completed network flows and the firewall rules in effect associated with each flow, linking observed traffic patterns to the policies governing them. Flow data includes the groups flows belong to, services used, Layer 7 application ID, and FQDN information. Network flow data is analyzed within a 15-minute window for near-real-time security status, and administrators can select a time period parameter to examine historical traffic flow data for architecture documentation.
-Network traffic flows displayed in Security Intelligence are based on DFW rules in effect and observed traffic during the selected period, covering all traffic matching stateful Layer 4 DFW rules using IPv4 or IPv6. This directly supports the control's requirement that architecture diagrams reflect the current network environment and document how traffic flows through it. The Flow Insights Dashboard categorizes network objects into Rules, Groups, Computes, Destination Ports, and Layer 7 Application IDs, providing a structured multi-dimensional view of the environment's traffic architecture. Security Intelligence also monitors network flows between application pairs and tracks Policy Protection Status to indicate which application communication paths are being monitored.
-Security Intelligence generates DFW security policy recommendations for application and environment categories based on analysis of traffic flows over a specified time period. These recommendations, grounded in observed traffic patterns, provide data-driven support for documenting how data flows through the environment and what security controls apply to those flows.
-Network Detection and Response (NDR) extends this visibility by collecting and presenting detection events representing security-relevant activity in the network, helping security analysts understand threat patterns and the paths through which activity traverses the environment.</t>
+          <t>VMware vDefend provides the primary data flow enforcement mechanism within VCF through its Distributed Firewall, Gateway Firewall, and Security Intelligence capabilities. These capabilities function as software-defined access control lists governing traffic between workloads, segments, and external networks.
+The vDefend distributed firewall enforces Layer 2-7 access policies at the vNIC level on every workload. Administrators define firewall rules that explicitly permit or deny traffic based on source and destination groups, ports, protocols, application identity, user identity via Active Directory integration through Identity Firewall, and fully qualified domain names (FQDN filtering). Because enforcement happens at the workload's virtual network interface, traffic is filtered before it reaches the physical network, and policies follow the workload as it moves between hosts. The Application Connectivity Strategy's "Allow Intra, Deny Other Traffic" mode automatically generates an intra-group ALLOW rule with optional logging plus a default ANY/ANY/DROP rule to isolate the group, providing a structured default-deny posture that restricts traffic to only what is explicitly authorized.
+URL filtering provides an additional access control layer, enabling rule-based restrictions based on URL categories, URL reputation scores, and custom URL lists applied to both HTTP and HTTPS traffic. Identity Firewall rules can specify source users or groups, destination resources, services, and context profiles to allow or deny traffic based on Active Directory group membership. These rules support Allow and Reject actions and can be applied to physical devices where users log in, as well as to tier-0 and tier-1 gateways. Role-based access control within the Distributed Firewall governs who can create or modify firewall rules, restricting policy changes to authorized personnel.
+The vDefend gateway firewall provides stateful North-South traffic inspection at Tier-0 and Tier-1 gateways, enforcing ACL-equivalent rules on traffic entering or leaving network segments. The Gateway Firewall supports Identity Firewall integration with Active Directory for identity-based access control at the perimeter. Together, the Distributed and Gateway Firewalls address both East-West (inter-workload) and North-South (perimeter) data flow enforcement.
+Security Intelligence, hosted on the Security Services Platform, supports ACL governance by observing traffic flows between applications and environments. Security Intelligence classifies flows as allowed, blocked, or unprotected and generates policy recommendations with segmentation strategy actions of Allow (creates a default traffic flow allow rule) or Drop (creates a default traffic flow drop rule). When a security policy is published, a rule is automatically generated to allow intra-application traffic. The View Impacted Flows capability displays unprotected traffic flows used to generate policy recommendations, helping administrators identify unauthorized communication patterns and tighten ACL governance over time.
+The Security Services Platform governs access to Security Intelligence operations through role-based access control with five defined roles: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Three permission levels apply across operations: Full Access (Create, Read, Update, and Delete), Read, and None. This restricts policy recommendation and enforcement actions to authorized security personnel.</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -3786,15 +3804,1040 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.4</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>MON-05</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Alert in the event of an audit logging process failure.</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in mechanisms to detect log processing failures, alert operations personnel, and support remediation of disruptions across its monitoring stack.
+VCF Operations monitors the health of its own alerting and log processing infrastructure. When no SNMP targets are configured for alert delivery, VCF Operations generates a critical alert (vmwSNMPNotConfiguredEvent), flagging that the alerting pipeline is not operational. It also generates critical alerts for invalid SNMP connection events (vmwSNMPConnectionInvalidEvent). At the network layer, VCF Operations monitors the status of the NSX Management Node SNMP Service and generates a warning-severity alert when the service stops running. NSX-T itself generates an alert event when the Syslog Service has stopped running on NSX-T Manager nodes. The NSX Manager Logging Monitor adds a further detection mechanism through the System Health Agent framework, tracking each log's generation rate and rotation settings to estimate how long log data will be retained and raising log duration alarms when abnormal rates risk flushing log data before it is collected, so operators can intervene before records are lost. These self-monitoring capabilities detect failures in the event log processing and alert delivery chain before administrators need to discover them manually.
+The alert framework in VCF Operations supports definitions built from one or more symptom sets. Symptom definitions identify conditions on attributes, properties, metrics, and events. The framework supports multiple event types relevant to log processing failures, including System Degradation, Data Availability, Collector Down, and Object Error. Administrators can create alert definitions with tighter symptom parameters to track problems before users encounter further issues. Recommendations can be attached to alert definitions so that engineers know how to resolve the alert when it fires, providing clear remediation guidance tied to specific failure conditions. Alerts are generated when collected data for an object is compared against the alert definitions for that object type and the defined symptoms evaluate to true.
+For alert delivery, VCF supports multiple notification channels. vCenter can send both SNMP traps and email notifications when alarms are triggered, with configurable recipient addresses and subject lines. The vCenter SNMP agent supports SNMPv1, v2c, and v3 trap formats, including SNMPv3 with all security levels. VCF Operations supports outbound SNMP trap notifications to up to four destinations and can filter notifications based on defined criteria. As a fallback, VCF Operations can log alerts to a file on each of its nodes, providing an on-node record that persists even if external alert delivery is disrupted. This multi-channel approach helps ensure that alerts about log processing disruptions reach the appropriate personnel even if one delivery mechanism is impaired.
+VCF Operations provides log-based alerting through Symptom Definitions, accessible under Infrastructure Operations &gt; Configurations. Administrators can create log-based conditions and symptoms that trigger alerts when specific log patterns are detected, including patterns that indicate log processing failures or disruptions. The Log File plug-in supports notification rules that filter and route alerts to the appropriate teams. Log-based alert definitions can monitor host systems for specific conditions such as cluster performance failures, and they generate alerts when those conditions are detected. These alerts can be forwarded to external monitoring systems via SNMP traps.
+VCF Log Management is a centralized log collection platform that pulls tasks, events, and alerts from vCenter instances and receives syslog feeds from ESX hosts. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. This centralized architecture makes it possible to detect when expected log streams stop arriving, which is itself an indicator of a log processing failure. When audit record transmission is active on ESX hosts, the syslog daemon (vmsyslogd) emits records documenting its own operational status, including daemon start, stop, and error conditions, enabling detection of syslog service disruptions at the host level. vCenter event streaming to a remote syslog server is configured via the vpxd.event.syslog.enabled option in the vCenter Management Interface.
+VCF Operations logs task execution details including Script Return Result status, script names, target object types, parameters passed, and unexpected exceptions. When automated remediation tasks fail, these logs provide the diagnostic detail needed to understand what went wrong and why. Task events are displayed in the messages area, allowing administrators to troubleshoot failed tasks directly.
+Adapters for external monitored systems and the REST API are inbound channels for collecting events from external sources. VCF Operations correlates a subset of events published by monitored systems and delivers them as faults. Fault symptoms can be defined based on these events and added to alert definitions, so failures in external log sources are surfaced within the central monitoring platform. For organizations that forward logs to external SIEM systems via syslog, any disruption in log forwarding is itself a monitorable condition, since VCF components generate alerts when syslog services stop running.
+At the Kubernetes consumption layer, VMware Kubernetes Service (VKS) clusters include instrumentation to detect and report log processing failures in workload environments. The Kubernetes API server exposes the apiserver_audit_error_total metric, which counts audit events dropped due to export errors, and the companion apiserver_audit_event_total metric, which tracks total audit event volume; a sustained rise in the error count relative to the event count indicates a failure in the audit export pipeline. When Prometheus is installed as a standard package on a VKS cluster, Prometheus instances are configured to send alerts to Alertmanager in the tanzu-system-monitoring namespace. Alertmanager is deployed as a StatefulSet with multiple replicas in that namespace, and administrators can configure alert rules targeting these metrics to route notifications to designated personnel when audit event exports fail. Prometheus discovers Alertmanager pods through Kubernetes service discovery, filtering by namespace, app label, and component label.
+VKS clusters include Fluent Bit logging agents for cluster-wide log collection and forwarding. Fluent Bit supports output to Syslog, HTTP, Elasticsearch, Kafka, and Splunk destinations, so disruptions in log forwarding are detectable through the health of the centralized log collection infrastructure. For workloads running in vSphere Namespaces, the LogAgentConfiguration Custom Resource streams logs to a remote Syslog server once applied to the namespace; each log message includes namespace name, pod UID, pod name, container name, and ESX host name as metadata fields, allowing operations teams to correlate forwarding gaps with specific workloads or nodes.
+The Node Problem Detector provides a SystemLogMonitor daemon that monitors system logs and reports problems to the API server as NodeConditions or Events, according to predefined rules covering log sources such as filelog, kmsg, and kernel logs. This surfaces node-level log source failures as cluster events that can be queried or routed through alert management infrastructure. In Kubernetes audit logging batch mode, if the rate of incoming events overflows the buffer, events are dropped without notification from the logging subsystem itself, which makes metric-based monitoring of apiserver_audit_error_total the primary signal for detecting silent audit pipeline failures. VM Operator logs record reconciliation events for VirtualMachineService resources in VKS clusters, providing additional log sources for troubleshooting provisioning and service failures.</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides event logging with configurable alarms that can alert administrators to operational failures across the disaster recovery environment. Each event type has a corresponding alarm that can be configured to send email notifications, SNMP traps, or execute a script when triggered, giving administrators multiple channels to reach appropriate personnel when problems occur. For email notifications, mail settings must be configured in the vCenter Settings menu before alarm-triggered notifications function. PNR also requires an administrator email address to be configured during appliance registration with vCenter.
+The PNR Server logging level can be configured to one of five levels: error, warning, info, verbose, or trivia, by modifying the log configuration. Error and warning levels capture conditions that indicate problems in the environment. When recovery plan execution encounters failures, PNR logs diagnostic details in the recovery site server logs, including plan identifiers, plan names, and detailed error messages with fault codes.
+The PNR Appliance can forward log files to a remote syslog server for centralized log analysis and monitoring. vSphere Replication maintains separate audit logs at /opt/vmware/support/logs/hms/hms-audit.log for tracking security-relevant events, including authorization errors with timestamps and component information.
+The Clean Room Orchestrator provides an additional monitoring layer for ransomware recovery workflows. Administrators can configure email alerts for critical events in the clean room environment. The orchestrator can forward events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud; event forwarding to VCF Log Management requires version 9.0 or above.
+VCF Operations provides an alert system that notifies administrators when specific symptoms of monitored objects are detected, including health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites. In environments with more than one vCenter, PNR displays all events from PNR servers registered as extensions.
+PNR logs when a protected consistency group has errors or warnings, recording this as an Error-level event. These mechanisms surface operational failures and log-related disruptions as part of broader recovery environment monitoring. Dedicated log pipeline health monitoring and log processing failure detection are provided by the underlying VCF platform monitoring stack.</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) supports log processing failure detection and personnel notification through its audit record failure logging capability and event alerting framework.
+Avi Controller and Avi Service Engine explicitly record audit record failures for three log destinations: Events, Syslog, and Splunk. The failure categories captured include initiation and termination of trusted channel connections, failure of trusted channel functions, unsuccessful certificate validation attempts, client authentication failures, SSH session establishment failures, and identification of the initiators and targets of failed trusted channel establishment attempts. This capability is configured in the Application Monitoring section of the Avi documentation under Audit Logging &gt; Audit Record Failures.
+When log processing failures or system events occur, Avi Controller can route notifications to four destinations: the local Controller UI (displayed as colored bell icons), email, syslog, and SNMP trap servers. These notification channels are configured under Operations &gt; Notifications in the Controller UI. Avi supports both SNMPv2c and SNMPv3 protocols for SNMP trap notifications, and SNMP notification channels can be configured with TLS encryption and strict certificate verification for secure transport. The Avi Controller cluster leader issues SNMP trap notifications and supports multiple SNMP servers, providing redundancy for alert delivery. The Syslog-Audit-Persistence alert action template is available for configuring alert actions that stream events to external syslog servers, which can feed into a centralized log management or SIEM platform.
+Auditors should be aware of two scoping boundaries when evaluating this control. First, Avi debug logs and Event Logs are not transmitted to remote syslog servers through the OS-level syslog configuration; Event Logs require the Syslog notification configuration within the Controller UI or API-based export. Second, configuring Syslog notifications in Avi Controller pushes alerts to syslog servers but does not export virtual service logs; virtual service logs must be pulled from an external logging system through the API or scripted to be pushed from the Controller to a remote destination.
+Auditors verifying this control should confirm that Alert Actions are configured in the Operations section of the Avi Controller UI, that notification destinations (email addresses, SNMP trap server addresses, or syslog server targets) are defined, and that organizational runbooks or response procedures define who receives these alerts and what remediation steps follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.5</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>MON-02, MON-02.1</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Correlate audit record review, analysis, and reporting processes for investigation and response to indications of unlawful, unauthorized, suspicious, or unusual activity.</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
+VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
+VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
+NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
+VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
+VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
+VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
+Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
+The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
+For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
+VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend Network Detection and Response (NDR) correlates detection events into campaigns, comparing new detection data against existing events to identify related activity. Campaigns provide a view of a threat by correlating detection events to identify the different stages of an attack, and security analysts can view and triage threat campaigns through a campaign timeline. NDR supports SIEM integration, sending campaign and event logs to a connected SIEM in real time, allowing network security event data to be exported for broader correlation with other enterprise data sources.
+Security Intelligence detects and categorizes suspicious events using MITRE ATT&amp;CK tactics and techniques, recording event occurrences during selected time periods, and provides a View Full Event History capability that displays all events associated with a given signature ID and intrusion severity. Security Intelligence also correlates IDS events from the same source and destination hosts to connect related events and build a broader picture of an attack. This structured, MITRE-tagged event data can support SIEM-based analysis and enterprise-wide threat correlation.
+The Security Services Platform (SSP) can be configured to forward log messages to external syslog servers for centralized log collection. SSP syslog configuration supports TCP, TLS, and UDP protocols and allows administrators to specify server address and port, integrating with existing SIEM ingestion pipelines. NDR Sensors report metrics covering health, traffic trends, and data processing activity, available as point-in-time measurements or aggregated data over time.
+vDefend correlates only technical network security data and has no capability to ingest or correlate non-technical information such as HR records, physical access logs, or operational data. Satisfying the full scope of this control, which requires correlation of both technical and non-technical information across the enterprise, requires an external SIEM or equivalent platform.</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) generates security-relevant event logs and supports forwarding them to centralized log collection and SIEM platforms through multiple native mechanisms.
+The Protection and Recovery Appliance provides built-in syslog forwarding to remote syslog servers. The forwarding configuration supports a selectable transport protocol and a configurable destination port (default 514). PNR includes a test message capability to verify that a remote syslog server is receiving messages before relying on it operationally. REST API endpoints are available for managing syslog configuration, including endpoints to list all configured syslog servers, update syslog server settings, and send test messages programmatically.
+PNR's event subsystem integrates with VMware vCenter, registering protection and recovery-specific events in the vCenter event infrastructure. Each event type has a corresponding alarm that PNR can trigger when the event occurs, enabling automated notification and downstream forwarding through vCenter's event pipeline to external SIEM platforms. PNR logs security-relevant events including login activity with timestamps, user identity, session keys, and locale information; authorization error messages with timestamps and component identification; and protection group configuration changes. The SrmDpxAgentUser role enables the DPX agent service to log events directly to vCenter Event Manager.
+The Clean Room Orchestrator component supports native event forwarding to VCF Log Management (version 9.0 or later), Microsoft Sentinel, and Splunk Cloud. Integration with Microsoft Sentinel uses Data Collection Rules (DCR) and Data Collection Endpoints (DCE) within an Azure Log Analytics Workspace, with DCE and Log Analytics Workspace required in the same Azure subscription and resource group. Splunk Cloud integration is configured using a Splunk URL and authentication token. Clean Room Orchestrator logs events for protection group creation and deletion, replication tasks, and snapshot operations. Event records include timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type.
+vSphere Replication, as a PNR component, maintains audit logs at /opt/vmware/support/logs/hms/hms-audit.log and broker logs at /opt/vmware/support/logs/hbr on the Appliance and at /var/run/log on VMware ESX hosts. vSphere Replication generates typed audit events for host and virtual machine replication configuration and unconfiguration changes, using structured event type identifiers.</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
+The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
+For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
+The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
+Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
+Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
+The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
+The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
+Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
+To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.6</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>MON-02, MON-06</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Provide audit record reduction and report generation to support on-demand analysis and reporting.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides event log report generation capabilities through VCF Operations and its integrated logging infrastructure, allowing administrators and auditors to generate, schedule, and customize reports from event log data to support the detection and assessment of anomalous activities.
+VCF Operations includes a reporting engine that generates scheduled snapshots of views and dashboards covering objects, metrics, and alerts. Administrators can create reports using predefined report templates or build custom reports tailored to their monitoring requirements. Reports can be scheduled to run at regular intervals, providing recurring visibility into resource utilization, operational health, and potential risks. The reporting functions capture details related to both current and predicted resource needs, giving operations teams a forward-looking view of the environment. VCF Operations also provides audit reports that offer traceability of objects and users across the environment.
+For event-specific analysis, VCF Operations provides an Event Trends capability where administrators can construct and run queries against collected log events, apply filters, and view results in the Event Trends tab. This feature supports trend and anomaly analysis by allowing comparison of query results against the same time period immediately prior, making it straightforward to identify deviations from normal activity patterns. The Log Analysis Widget further allows customization of the visual representation of events through aggregation queries, enabling tailored views of event data for different reporting needs. The troubleshooting incident page highlights anomalies in collected metrics and supports filtering by metric name, entity name, and other parameters for targeted investigation.
+Event auditing within VCF provides visibility into platform interaction changes across the infrastructure and surfaces suspicious access events and policy violations. The VCF Operations Audit Events framework captures interactions such as searches, logins, logouts, capability checks, and configuration modifications across vSphere, vSAN, and NSX resources. Each action is registered as an event with relevant metadata, enabling detection of suspicious access patterns and policy violations while providing user accountability through detailed activity tracking. Audit logs across VCF components record security-related events with timestamps, source identifiers, results, and event descriptions. For Common Criteria evaluated configurations, all auditable events are logged for each applicable requirement.
+VCF Log Management extends these capabilities by collecting tasks, events, and alerts from vCenter instances and receiving syslog feeds from ESX hosts through its Log Collections configuration. The Logging Monitor feature generates reports with detailed information about logging anomalies such as log spew problems, helping administrators identify unusual logging patterns that may indicate security events. The VCF Operations audit log is integrated with syslog, and the syslog collector can be configured to aggregate all audit logs centrally.
+The VCF consumption layer, encompassing VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides Kubernetes-native audit logging and log collection capabilities that extend event reporting to containerized workloads. The Kubernetes API server on VKS clusters generates structured audit events in the audit.k8s.io API group; each event records the requesting user identity, timestamp, target resource, unique audit ID, and event stage. Administrators configure the scope and detail of captured events through an audit policy file, selecting from four detail levels: None, Metadata (recording user, timestamp, resource, and verb), Request (which adds the request body), and RequestResponse (which adds the full response body). Audit events can be written to a local log file through the --audit-log-path flag or forwarded to an external log aggregation or SIEM platform through the webhook backend. The kube-apiserver exposes the apiserver_audit_event_total Prometheus metric, allowing operators to monitor audit event volume and detect sudden changes in activity that may indicate anomalous behavior. The metric carries 'allowed' and 'denied' label dimensions that distinguish events by authorization decision; a companion apiserver_audit_level_total counter tracks the distribution of audit events across policy levels, with one increment per request. Fluent Bit logging agents, deployed as a standard package on VKS clusters, collect logs from across cluster nodes and can forward them to Syslog, HTTP, Elasticsearch, Kafka, and Splunk destinations, supporting integration with centralized log analysis and reporting platforms. Fluent Bit on VKS clusters also collects Kubernetes API audit logs in JSON format, Linux authentication logs, and container runtime interface logs through configurable parsers and filters. At the Supervisor control plane level, Fluent Bit separately collects the Supervisor's own kube-apiserver audit logs using the audit.apiserver.* tag from the path /var/log/vmware/audit/kube-apiserver.log and stores them for forwarding to external monitoring systems. Administrators can configure the Supervisor to preserve the source IP addresses of authentication and Kubernetes API server requests, making those addresses available in the resulting audit log entries to support more precise attribution of access events. For workloads running in vSphere Namespaces, the LogAgentConfiguration custom resource streams syslog messages from vSphere Pods to a remote syslog server, with each message carrying the namespace name, pod UID, pod name, container name, and ESX host name as metadata to support structured querying and reporting. The SystemLogMonitor component of the Node Problem Detector monitors file-based logs, journald, and kmsg sources on Linux nodes and surfaces node-level problems as Kubernetes conditions and events. Seccomp profiles on VKS workloads support the SCMP_ACT_LOG action, which logs all syscalls to syslog or auditd without restricting execution, providing syscall-level audit trails for workloads where that granularity is required. VKS support bundles collect logs from control-plane and infrastructure components including CAPI, CAPV, VM Operator, and VKS Controller Manager, as well as containerd journal logs from Linux nodes and Windows Event Log data from System, Security, and Application sources on Windows nodes.
+VCF Automation maintains audit logs that display status values or messages for each reportable action type, including timestamps, user names, project names, and trace identifiers, providing granular audit trail data available for report generation.
+At the infrastructure level, ESX hosts maintain local logging with configurable retention and rotation policies. ESX log files rotate at each power cycle by default or at a configured file size. ESX hosts support configurable syslog log levels that can be set and reloaded using esxcli commands, and can forward syslog messages to remote log servers for centralized collection. Audit records specifically can be directed to remote syslog hosts using the `Syslog.global.auditRecord.remote` parameter. VCF supports syslog forwarding from vCenter to up to three remote servers using TCP, UDP, TLS, and RELP protocols, with TLS encryption available for confidentiality in transit. Event streaming from vCenter is enabled via the `vpxd.event.syslog.enabled` setting; each forwarded event includes fields for event ID, event type, severity, user, target object, chain ID, and description, providing a structured record suitable for SIEM ingestion. This enables integration with external log management and SIEM platforms for consolidated report generation and correlation.
+The vSphere Web Services API provides programmatic access to event data through custom event structures (EventEx) with metadata and event filtering through EventFilterSpec, which allows collection criteria based on user name, entity type, time, and state. EventHistoryCollector objects can be created with filters to collect events matching specific criteria, and the server automatically appends new events meeting the filter criteria to the collection as they occur. This API-level access supports automated report generation and integration with external monitoring tools.
+VMware Private AI Services (PAIS) provides several mechanisms for collecting metrics, traces, and logs from AI workloads, giving organizations the data needed for event log report generation and anomaly detection on AI infrastructure.
+The core observability mechanism is a managed Prometheus server pod that PAIS operates to collect metrics on Private AI Services components, including PAIS Controller activity, model endpoint behavior, and knowledge base indexing. Observability collection is activated by updating optional sections of the PAISConfiguration custom resource, which configures Prometheus metrics collection with a customer-specified storage class and retention period and configures LLM trace forwarding to an OpenTelemetry Collector. Trace forwarding is configurable for HTTP/protobuf or gRPC transport using the spec.observability.llmTraces section of the PAISConfiguration CR, allowing detailed traces from agents and knowledge base indexing operations to be examined for anomalous behavior patterns.
+Metrics collected by the managed Prometheus server can be visualized in observability platforms such as Grafana, where MLOps engineers and application developers track AI application health, quality, and behavior. Grafana dashboards surface LLM completion API response times at the 95th percentile, inference engine tokens-per-second generation rate, and GPU compute and memory usage, providing visibility into operational patterns that can reveal anomalies. PAIS also integrates with VCF Operations for controller-level monitoring: PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, and controller pod metrics streaming can be activated to view those metrics in VCF Operations. Collection is performed through Telegraf with namepass filters that capture controller-runtime workers, work queue depth, and similar reconciliation metrics, and VI administrators can use the VCF Consumption CLI to connect to the Supervisor endpoint and stream metrics from the PAIS controller pod. The PAIS Supervisor Service additionally exposes service-level metrics through pais.vmware.com for monitoring the health of the service itself.
+At the model inference layer, the vLLM inference server logging level is configurable through the VLLM_LOGGING_LEVEL environment variable, with DEBUG as a supported value for detailed trace capture. Deep Learning VMs record cloud-init script logs in /var/log/dl.log and GPU driver installation logs in /var/log/gpu-install.log for post-deployment review, and they expose vGPU performance metrics through Prometheus that can be collected and visualized for monitoring purposes. JupyterLab instances on Deep Learning VMs provide additional logs that can be examined to verify installation and operation of components.</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend provides event log generation and monitoring capabilities across its security components in 9.1, directly supporting anomaly detection and assessment within the network security domain.
+The IDS/IPS subsystem generates detailed security event logs for event analysis. Remote syslog must be configured on ESX hosts to receive IDS/IPS events exported directly from those hosts; the `ids_events_to_syslog` setting controls whether IDS/IPS events are forwarded to external syslog consumers (the default is disabled). vDefend components write log data to /var/log, with syslog messages conforming to RFC 5424 on vDefend appliances and RFC 3164 on ESX hosts, enabling consistent ingestion by syslog-compatible platforms. The Security Explorer Computes view in Security Intelligence provides a full record of all IDS/IPS events for analysis over a 30-day timeframe. Security Intelligence also provides a View Full Event History capability that displays all events associated with a given signature ID along with their intrusion severity. The Threat Event Monitoring dashboard in Security Services Platform displays the trend in intrusion events over time, categorized by Intrusion Severity, giving security teams visibility into detection activity patterns.
+Malware Prevention Service generates structured event logs with detailed metadata per file analysis event. Event log fields include the verdict (BENIGN, malicious, or other classification status), a numeric risk score, malware classification, malware family, error codes and messages, HTTP domain, HTTP method, user agent, file upload status, submission status, analysis completion status, and gateway identification. File event statistics appear on the Monitor &amp; Plan &gt; Overview &gt; Threat Monitoring dashboard in Security Services Platform, with graphs covering a configurable time period (defaulting to the last hour).
+Network Detection and Response (NDR) generates and sends event logs to a SIEM endpoint when a detection event occurs, enabling integration with external correlation and reporting platforms.
+The Security Services Platform Monitor &amp; Plan Overview dashboard provides a view of security posture that includes the latest security segmentation report, flow trends, a summary of detected suspicious traffic events, pending actions, and current settings requiring attention. Security Intelligence generates bar graphs showing the number of anomalies detected, categorized by severity. The Policy Recommendations section tracks Security Intelligence recommendations with status indicators such as Ready to Publish, allowing security teams to act on recommended policy changes.
+vDefend Identity Firewall Event Log Sources can be integrated with VCF Log Management for centralized logging and monitoring. VCF Log Management supports Top-N queries using Interactive Analytics, enabling report generation from the aggregated log streams that vDefend supplies. VCF Log Management handles organization-level scheduled report generation, while vDefend provides the network-security-specific event data and dashboards that feed those reporting workflows.</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides event logging and report generation capabilities across its replication, recovery, and clean room components, scoped to disaster recovery operations.
+The PNR Appliance maintains security audit logs for tracking security-relevant events, including authorization error messages with timestamps and component information. vSphere Replication logs are maintained at /opt/vmware/support/logs/hms/hms-audit.log on the Appliance and at /opt/vmware/support/logs/hbr on VMware ESX hosts. The PNR Log Manager records events at six severity levels: panic, error, warning, information, verbose, and trivia. The PNR Appliance can forward log files to a remote syslog server for centralized collection.
+PNR generates structured audit events for significant replication and recovery operations. vSphere Replication produces events when virtual machines are configured or unconfigured for replication (com.vmware.vcHms.replicationConfiguredEvent, com.vmware.vcHms.replicationUnconfiguredEvent) and when hosts are added to or removed from the replication infrastructure (com.vmware.vcHms.hostConfiguredForHbrEvent, com.vmware.vcHms.hostUnconfiguredForHbrEvent). PNR monitors connections to remote sites by sending periodic ping requests and logs connection status events, triggering corresponding alarms to track system health and surface conditions such as unexpected replication failures or RPO violations. Protection groups log error- and info-level events when consistency groups have issues or are added to protection groups.
+Report generation capabilities cover the full recovery workflow. PNR can generate and export reports about each run of a recovery plan, test of a recovery plan, or test cleanup for audit trail purposes. It maintains a history log for each recovery plan that records reprotect operations, which can be exported to verify whether errors occurred. The number of history reports exported is configurable. Snapshot Reports display total replication snapshots, snapshot summaries, and snapshots with issues. Health finding status history tracking covers customizable time periods, defaulting to 24 hours, to identify status changes over time. The health monitor service checks each finding every five minutes and updates the results with a last-checked timestamp.
+The Clean Room Orchestrator maintains a running list of all clean room events including both system-generated events and user actions, which can be filtered for monitoring and audit purposes. It logs events related to protection groups (creating or deleting protection groups and replications), snapshot task completions, and alert notifications. Events from the Clean Room can be forwarded to VCF Log Management (version 9.0 and above), Microsoft Sentinel, Splunk Cloud, or Microsoft Azure Log Analytics via Data Collection Rules and Data Collection Endpoints. PNR dashboards in VCF Operations provide monitoring and reporting for vSAN snapshots, replication, and recovery plan status. The Recovery Plans Dashboard displays all alerts related to protection groups for monitoring and audit purposes.
+Broader log analytics, anomaly detection, and cross-platform event correlation across the environment are provided by the underlying VCF platform's monitoring infrastructure.</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides event log generation and reporting capabilities that support detection and assessment of anomalous activities within the database-as-a-service layer.
+DSM's primary audit interface is the System Audit Events view, accessible through the System Audit section in the Provider UI. This view is the only location in the DSM interface where administrators can track non-database-related operations and tasks. Each audit entry records a Component field identifying the DSM component that performed the operation, an Event Type field identifying the nature of the audited event, Event Details providing operation-specific information, Event Time in UTC, and a Status field indicating the outcome of the event. The Source field records either a user identifier (Email ID) for user-initiated events or "System" for events initiated by DSM without user intervention, enabling attribution of each audit record to a specific actor. Standard Kubernetes audit events are also captured through the Gateway Audit Logs capability.
+Audit events can be exported in CSV or XLSX format using the ACTIONS dropdown menu in the System Audit Events view. Exports include all events visible to the requesting user regardless of page size, covering the Component, Event Type, Event Details, Event Time (UTC), Status, and Source fields. These exports can be brought into external reporting and analysis tools to support audit review and anomaly assessment.
+For persistent retention, DSM archives gateway audit log files periodically to an S3 repository subpath when a default S3 provider log repository is configured. Audit log files are also stored locally on the Provider VM at /var/log/tdm/provider/audit/ in files named with a gateway-audit-timestamp.log format, supporting direct access for investigation. Support bundles can be generated and downloaded to aggregate control plane and data plane logs from a database cluster for diagnosis. The Provider VM also includes a System Logs capability for managing system log collection.
+DSM provides operational monitoring that can surface indicators of abnormal behavior. The Monitoring tab for database instances displays metrics including Active Connections, Data Disk Usage, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage %, InnoDB Reads and Writes, and Command Reads and Writes, with the time range adjustable through the Time Range Last dropdown. The Alerts pane in the Monitoring tab surfaces triggered alerts. DSM raises metrics-based alerts when metrics are successfully collected from a database cluster, status-condition-based alerts for critical failure conditions including database engine degradation and backup failures, and real-time alerts for resource or connectivity issues to support root cause identification. Webhook-based alerting supports integration with external notification systems for threshold-triggered database monitoring events. DSM can also be monitored through VCF Operations for additional troubleshooting and status visibility.
+Satisfying this control fully requires organizational processes to review exported audit data and monitoring output, establish baselines for normal activity, and investigate deviations. DSM does not include built-in anomaly detection, correlation, or security information and event management capabilities. Organizations typically forward DSM logs to a centralized log management platform for automated detection and reporting at scale.</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer provides event log generation, anomaly detection, and report generation mechanisms at the application delivery layer.
+The Avi Controller Event Log captures detailed records of system activities, configuration changes, and operational events, including an audit trail that tracks who made each configuration change and when. The Avi Controller and Avi Service Engine also log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk. The CLI commands `show report` and `generate report` are available for listing existing reports, retrieving their status, and generating new reports for virtual services over a specified duration. Virtual Service Analytics reports cover periods up to seven days.
+For anomaly detection, the Service Engine Analytics Anomalies Overlay records anomalous metric values and deviations across virtual services and Service Engines, capturing the entity name and type reporting the metric, the metric value, a prediction interval representing an acceptable range, and a severity level (High, Medium, or Low). The Anomalies Overlay displays filtered system-level alert events that are critical enough to notify an administrator, including anomalous traffic conditions such as spikes in server response time with corresponding timestamps and resource names. The Alert feature processes system events and metrics against user-defined rules and generates alerts that initiate configured actions such as sending an email, a syslog message, or an SNMP trap. The Avi Controller also logs denial-of-service attack events with detailed fields including event identifier, attack count, threshold values, and alert level.
+Events and alerts can be forwarded to external systems through the Syslog-Audit-Persistence alert action template, which streams audit compliance events to external syslog servers. Syslog notifications push alerts to configured syslog servers; virtual service logs are pulled from an external logging system through the API or scripted to be pushed from the Controller to a remote destination. Avi Load Balancer supports integration with external monitoring tools such as Prometheus for metrics collection. When event logs exceed 10,000 entries for a query period, the analytics API can be used to retrieve logs for shorter time periods.
+At the application security layer, WAF App Log Analytics captures events when a WAF Application Rule is triggered, recording information about the type of attack detected. For cross-site scripting detection, the Avi WAF logs matched XSS data including the matched variable name and matched variable content. A Splunk add-on and application displays Avi logs and events in dashboards in an easily consumable format. In the Avi for VCF deployment, Virtual Service Analytics captures and reports logs and events for application performance monitoring as part of standard operational validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.7</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>MON-07.1, SEA-20</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Provide a system capability that compares and synchronizes internal system clocks with an authoritative source to generate time stamps for audit records.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides built-in Network Time Protocol (NTP) configuration across all components in the stack, enabling synchronization of internal system clocks with an authoritative time source. VCF Operations is the central point for NTP management: it uses NTP servers to synchronize time between VCF core components, and when an administrator updates the NTP server configuration, VCF Operations propagates those settings to vCenter instances, ESX hosts, NSX Managers, and NSX Edge nodes. If an NTP configuration update fails on any component, VCF Operations rolls back the NTP settings for that failed component. VCF Operations must be able to reach all VCF components over SSH to perform NTP configuration updates. It is recommended that all VCF systems receive their time from the same NTP source, even when configured with different time zones, to maintain consistency across the environment.
+At the infrastructure layer, ESX hosts support NTP server configuration directly, and VCF management components can be configured to use the ESX host NTP server as their time source. vCenter time synchronization can be configured to use either an NTP server or VMware Tools as the synchronization method; native NTP is preferred because it is typically more accurate than VMware Tools periodic time synchronization. The vSAN Witness Host is also configured with NTP servers to synchronize time. NSX Manager supports NTP server configuration through both the management UI and the API (PUT https://&lt;nsx-mgr&gt;/api/v1/node/services/ntp), and accurate time synchronization on NSX Manager is an operational necessity because it uses its internal system clock to generate timestamps for audit records. NSX Node Profiles also support configuration of time zone and NTP servers, and some NSX features require that NTP be configured on all components in the NSX environment. Only one NTP service can be running at a time on NSX appliances and transport nodes. NSX transport nodes use the default time service provided by their underlying operating system: chronyd on RHEL/CentOS 7.6 and 7.7, systemd-timesyncd on Ubuntu (including edge nodes), and systemd-timedated on SLES 12 SP4.
+VCF Operations supports two NTP synchronization modes. In self-managed mode, the primary node is the NTP server by default, and the time of all nodes is synchronized to the primary node, with the primary and replica nodes managing synchronization across the cluster. Alternatively, VCF Operations can synchronize with an external NTP server by entering a URL or IP address. VCF Operations for Networks provides CLI commands for NTP management: "ntp show" displays the current configuration and status, "ntp set" resets NTP servers with support for IP/FQDN and secure flags, and "ntp sync" forces synchronization of NTP settings. Time synchronization between endpoint VMs, vCenter, ESX hosts, cloud proxy, and VCF Operations must be maintained using NTP, as time synchronization is a prerequisite for TLS and SSO communication between client and server. Administrators should configure NTP to synchronize the server system time of the VCF SSO source and VCF Operations.
+HCX also requires a valid NTP server with synchronized time for integrated systems operations. Administrators should schedule NTP server configuration updates at a time that minimizes impact to system users, as updates can take significant time depending on the size of the environment. VCF Operations restore procedures also require NTP server details to be configured for the appliance.
+Accurate and consistent time synchronization is important for several operational functions across VCF. Kerberos authentication is sensitive to clock skew, and clock skew between systems can cause Kerberos authentication failures. Log correlation across components depends on consistent timestamps, and certificate validation relies on accurate system time. Time synchronization across ESX host environments should be verified as part of operational best practices.
+At the Consumption layer, VMware Kubernetes Service (VKS) cluster nodes support NTP server configuration through the Cluster API. Administrators configure NTP servers for VKS cluster nodes by setting `osConfiguration.ntp.servers` in the cluster definition, available in ClusterClass versions v3.2.0 and later. In earlier releases, the `ntp` cluster variable serves the same purpose. When `osConfiguration.ntp.servers` is not set, VKS cluster nodes inherit NTP configuration from the Supervisor automatically, so clusters receive authoritative time settings from the underlying platform without additional configuration. Consistent time synchronization across VKS cluster nodes is a requirement for correct Kubernetes operation: certificate validity checks, service account token expiration, audit log timestamp accuracy, and workload scheduling behaviors all depend on coordinated clocks. Clock skew between control plane and worker nodes can cause operational issues, including DaemonSet controllers misreading rollout progress when `.spec.minReadySeconds` is configured. Auditors evaluating a VKS environment should verify that `osConfiguration.ntp.servers` is configured in cluster definitions, or confirm that the Supervisor is configured with authoritative NTP sources that VKS clusters inherit by default.
+For workloads requiring higher precision than NTP provides, VCF supports the Precision Time Protocol (PTP) at the hypervisor level. PTP is a high-precision time protocol for synchronization used in measurement and control systems on a local area network, with accuracy in the sub-microsecond range achievable with low-cost implementations. The HostDateTimeSystem supports both NTP and PTP configuration. A precision clock device can be added to a virtual machine class to provide VMs with access to the system time of the primary ESX host, enabling PTP time passthrough to guest workloads. The Precision Clock device supports time synchronization protocols including Any, NTP, and PTP, giving administrators flexibility to match the synchronization method to guest workload requirements.</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend both depends on and validates time synchronization across its enforcement and management components. Accurate clock synchronization is a prerequisite for time-based firewall policy enforcement, log correlation, certificate validation, and secure communications throughout the vDefend stack.
+vDefend (DFW) and vDefend (GFW) support time-based firewall policies that allow administrators to define rules that activate or deactivate based on configurable time windows. Network Time Protocol (NTP) service must be running on each transport node when using time-based rule publishing in either the Distributed Firewall or the Gateway Firewall. Time windows for both can be configured to use either Coordinated Universal Time (UTC) or the local time of the transport node. Gateway Firewall time windows support either a weekly or one-time frequency. When local time zones are used for DFW policies, the entire time window must fall within the same UTC calendar day. For Edge transport nodes, if the time zone is changed after the node is deployed, the Edge node must be reloaded or the data plane service restarted for the new time zone to take effect.
+Identity Firewall, which enforces access policies based on Active Directory user identity, has additional time synchronization requirements. When using Identity Firewall event log scraping to track user login events, NTP must be correctly configured across all participating devices. Administrators should schedule Active Directory full synchronization during off-peak or non-business hours, as a full sync can take considerable time.
+Security Services Platform (SSP), the management and orchestration layer for vDefend, requires accurate time synchronization for certificate validation, log correlation, and secure communications to function correctly. The SSP installer validates time synchronization as part of its deployment prerequisites and requires configuration of one or more NTP servers, which can be updated if they become unreachable. For bare metal deployments, the bare metal server should be configured to use the same NTP server as SSP to maintain consistent time synchronization across all components.
+Network Detection and Response (NDR) sensor appliances require NTP to be configured and synchronizing before they can successfully register with SSP. Administrators should verify NTP synchronization status using the get clock command on the NDR sensor CLI before initiating registration. The NDR sensor monitoring view within SSP displays the NTP servers configured for each sensor, providing visibility into time synchronization configuration across deployed sensors.
+SSP Segmentation Monitoring can monitor NTP infrastructure services on UDP/123, providing visibility into time synchronization infrastructure health alongside other monitored services. SSP Inventory tracks environment synchronization status and identifies environments that are timed out or out of sync, supporting troubleshooting of time-related connectivity issues.
+Accurate timestamps across all vDefend components are necessary for correlating security events across the Distributed Firewall, IDS/IPS, malware prevention, and NDR capabilities. When investigating a security incident, analysts rely on consistent timestamps to reconstruct the sequence of events across multiple enforcement points.</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) provides native time synchronization mechanisms within the Protection and Recovery Appliance. The appliance supports three configurable time synchronization modes: NTP, which enables direct synchronization against administrator-specified NTP server addresses; Host, which synchronizes with the underlying ESX host time via VMware Tools; and Disabled. In NTP mode, administrators configure the appliance to synchronize directly with the organization's authoritative time source, independent of the underlying VCF platform's host-level NTP configuration.
+PNR enforces clock alignment across its server components through the maximum-clock-skew setting, which defines the maximum allowed time difference between server clocks (default: 20 seconds). Time zone and time synchronization settings are editable through the appliance configuration interface when network time settings change.
+For VCF Automation environments, the Protection and Recovery Proxy also requires explicit NTP server configuration, specified as an IP address or FQDN. PNR deployment guidance recommends using a persistent synchronization agent such as network time protocol daemon (NTPD), W32Time, or VMware Tools time synchronization to maintain consistent time across recovery infrastructure and avoid conflicts in time management across systems.</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) requires configuration of a Network Time Protocol (NTP) service with a reliable time source to synchronize the clocks of all deployed VMs. This requirement is documented as a deployment prerequisite in the DSM installation guide. The Provider Appliance and all managed database instances must use the same NTP server, enforcing clock uniformity across the entire DSM environment.
+NTP server configuration is managed through the DSM System Settings interface. The Provider VM's System Settings panel includes an NTP Servers field where administrators specify one or more NTP servers as a list of IP addresses or fully qualified domain names. DSM applies NTP settings from the system configuration to synchronize database time with system time, helping maintain consistent timekeeping across the Provider Appliance and all managed database VMs.
+DSM monitors time synchronization health through its global alerts system. When Provider NTP synchronization fails, DSM generates an NTP_SYNC_FAILED alert. At the database level, DSM generates an NTP_NOT_APPLIED alert when NTP settings from the system configuration have not been applied to a database instance, indicating that the system is not synchronizing database time. NTP synchronization failures can result in authentication failures, backup and restore corruptions, and certificate errors, which is why DSM enforces NTP synchronization as a deployment prerequisite rather than a recommendation. Administrators can configure webhooks to receive notification of these alerts. When NTP_SYNC_FAILED is triggered, DSM documentation directs administrators to verify and correct any invalid entries in the NTP Servers field in System Settings.
+DSM uses Coordinated Universal Time (UTC) for system-generated timestamps, including timestamps on downloaded support bundles. Maintenance Policy schedules for software updates also require start time specification in UTC, reinforcing consistent time reference across operational activities.
+DSM does not provision or manage the authoritative time source itself, which is standard for any product that synchronizes to an external NTP server. Organizations establish and maintain the NTP infrastructure that DSM references.</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) provides built-in NTP synchronization for both the Controller and Service Engines, covering the full application delivery stack without requiring external time-management tooling.
+The Avi Controller is configured with a list of NTP servers through the DNS/NTP Settings section of Controller Settings, using the ntp_configuration.ntp_servers parameter. Multiple servers can be specified to provide redundancy. Service Engines synchronize time with the Avi Controller as part of normal operation, so time consistency flows from the authoritative NTP source through the Controller to every Service Engine in the deployment. Service Engines can also synchronize directly with an NTP server configured at the cloud level, rather than through the Controller hierarchy.
+For deployments where Service Engines need direct access to NTP infrastructure, Avi supports configuring NTP servers directly on Service Engines for both virtual machine and LSC-based (bare metal) deployments via the ntp-servers setting. Service Engines synchronize time with configured NTP servers at startup and periodically monitor time synchronization status thereafter. The platform supports ntpd (Network Time Protocol daemon) and chronyd as NTP daemon implementations on Service Engines.
+Avi provides operational visibility into time synchronization health. Service Engines periodically verify that configured NTP daemons can acquire and synchronize time with the configured servers, and raise an event if synchronization fails. This built-in monitoring means time sync failures surface in the Avi event log rather than going undetected. Accurate time synchronization is also required for correct operation of Avi's logging and analytics features.
+In Avi for VCF deployments, NTP server addresses can be configured for the environment when deploying a vSphere Supervisor with Avi, covering the integrated VCF deployment pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.8</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>MON-02, MON-03.1, MON-08</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Protect audit information and audit logging tools from unauthorized access, modification, and deletion.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides several technical mechanisms that help protect event logs from unauthorized access, modification, and deletion, though full satisfaction of this control requires organizational policies and additional tooling beyond the platform itself.
+Remote syslog forwarding is the primary mechanism for protecting log integrity across the VCF stack. VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP and port. The Syslog.global.auditRecord.remote parameter specifically controls whether ESX audit records are forwarded to the remote hosts defined by Syslog.global.logHost, providing a dedicated configuration knob for audit record remote transmission separate from general message forwarding. The NSX networking components send audit logs directly to the configured remote syslog server, separating them from the local syslog file and storing them in /var/log/audit/audit.log on the local host. NSX API audit logging is always enabled and cannot be disabled, providing a persistent record of all API-driven administrative actions. VCF Log Management can be configured to pull tasks, events, and alerts from VMware vCenter instances and receive syslog feeds from ESX hosts, acting as a centralized log aggregation point within the VCF environment. VCF Operations itself integrates its audit log with syslog and supports forwarding user activity audit logs to an external syslog server. VCF Operations HCX similarly supports configuring a remote syslog server so that logs generated on both the HCX manager and appliance virtual machines are forwarded off-host.
+Log forwarding supports encrypted transport to protect log data in transit. NSX Manager syslog supports the TLS protocol and requires port 6514 to be open on both the NSX Manager and the remote log server for TLS-encrypted log transmission. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols, and Foundation Load Balancer syslog communication requires a certificate for secure log forwarding. vCenter event streaming to a remote syslog server is separately enabled through the vpxd.event.syslog.enabled option in the vCenter Management Interface, providing a dedicated control for event export independent of the syslog API.
+By forwarding logs to remote collection infrastructure, VCF reduces the risk that a compromised host or component could modify or delete its own log records. The local copies remain on each component, but the remote copies provide an independent record that local administrators cannot alter.
+Access controls on log data are handled through the role-based access model within each VCF component. Access to VCF Log Management is governed by role-based access controls, restricting who can view and manage log data. Within VCF Operations for Networks, only users with the Admin role can view audit logs and configure whether personally identifiable information is included in those logs. For Windows-based domain controllers in the environment, read-only security log access can be enabled, and membership in the Event Log Readers group governs which accounts have permission to read event logs. The NSX documentation notes that core files and audit logs may contain sensitive information such as passwords or encryption keys.
+VCF Operations provides an Audit Events page accessible through the Security menu, where administrators can review audit records that capture interactions within the platform including searches, logins, logouts, capability checks, and configuration modifications. Audit logs across VCF Operations capture actions from the API, user interface, and CLI, including regular create, read, update, and delete operations as well as login and logout events. VCF Operations audit data can be filtered by user ID, user name, authentication source, session, client IP, category, and message, supporting targeted review of specific activities. VCF Operations for Networks audit logs similarly capture API, UI, and CLI actions. These audit records include structured metadata such as timestamps, thread identifiers, source IP addresses, log levels, and component class names.
+NSX audit logs use a structured syslog format with an audit flag (audit="true") in the structured-data field to distinguish security-relevant events from operational messages. Dedicated log files separate audit records: nsx-audit.log contains all messages with the audit flag, while nsx-audit-write.log contains messages flagged as both audit and update operations. NSX audit log messages include metadata fields such as component identifier, log level, request ID, split ID, and subcomponent classification, and each API-associated audit log entry includes a request ID parameter (req-id) to identify a specific API call. NSX logs all auditable events to support compliance requirements.
+The Consumption layer of VCF, comprising VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, adds its own audit logging mechanisms that extend event log protection to the Kubernetes control plane. The Kubernetes API server generates a security-relevant, chronological audit log documenting all actions in the cluster, including activities from users, applications using the Kubernetes API, and the control plane itself. Each audit event in the audit.k8s.io API group carries structured fields including apiVersion, kind, level, auditID, and stage, along with an AuthenticationMetadata block that records impersonation constraints when constrained impersonation was used to authorize a request. Audit event delivery is configured through the kube-apiserver --audit-log-path and --audit-log-mode parameters; the delivery mode defaults to blocking, which writes each event synchronously before the API server returns a response, reducing the risk of event loss under load. An audit policy file, mounted at /etc/kubernetes/audit-policy.yaml, governs the scope of the audit stream by defining which event types are recorded at which detail level; if the audit logging flag is omitted from the policy, no events are logged. Audit event truncation is disabled by default and must be explicitly enabled, so audit records are written in their entirety unless an administrator opts into size-based truncation. Backends include local log files written to /var/log/kubernetes/audit/ and webhook endpoints for forwarding to external systems. Pod Security Standards (PSA) audit mode, when enabled on a VKS cluster, records security policy violations as audit annotations in the audit log stream, extending audit coverage to workload-level security events. Kubernetes seccomp profiles using the SCMP_ACT_LOG action allow individual syscalls of a process to be logged to syslog or auditd, providing fine-grained syscall-level audit recording for sensitive workloads.
+Fluent Bit agents deployed by VCF in the vmware-system-logging namespace on VKS clusters collect and forward logs to external destinations, with access to that namespace restricted to cluster administrators. Fluent Bit processes Kubernetes API server audit logs separately from container logs and Linux daemon logs when forwarding to VCF Log Management, maintaining the distinction of audit records in the forwarded stream. On vSphere Supervisor control plane nodes, Fluent Bit collects kube-apiserver audit logs from /var/log/vmware/audit/kube-apiserver.log using the tag audit.apiserver.* and stores them in a local database at /var/log/vmware/fluentbit/flb_audit_apiserver before forwarding; on VKS worker cluster nodes, audit logs are collected in JSON format from /var/log/kubernetes/kube-apiserver.log with a 50 MB memory buffer limit. Fluent Bit also collects Linux authentication logs and container runtime interface logs from VKS cluster nodes, extending the set of log types forwarded to external destinations. The Supervisor can be configured to preserve the source IP addresses of authentication and Kubernetes API server requests for later inspection in audit logs, supporting attribution of actions to specific network origins. Supported forwarding targets include VCF Log Management, Syslog servers, Elasticsearch, Kafka, and Splunk. For workloads running in vSphere Namespaces as vSphere Pods, the LogAgentConfiguration custom resource can be applied to a namespace to stream syslog messages to a remote Syslog server; each forwarded message includes metadata fields for namespace name, pod UID, pod name, container name, and ESX host name. By routing audit records to an external log management system, the platform creates a copy of the audit trail outside the cluster, so that a compromise or administrative action affecting the cluster does not also destroy audit evidence.
+To fully satisfy this control, organizations deploying VCF should implement log forwarding to a dedicated, hardened log management or SIEM platform where retention, integrity verification, and access controls can be managed independently of the VCF infrastructure. VCF does not provide immutable or tamper-evident log storage on its own; protection against log modification or deletion at the storage layer requires integration with a write-once-read-many (WORM) log repository or equivalent storage. For high-assurance environments, Kubernetes guidance recommends deploying cryptographic protections to produce tamper-evident and confidential logs. Organizations should also establish policies governing who may access log data, how long logs are retained, and how log integrity is validated over time.
+VMware Private AI Services (PAIS) generates audit-relevant logs across its AI infrastructure components and exposes an observability subsystem with configurable retention and external forwarding that contributes to event log protection.
+Deep Learning VMs record cloud-init script logs in /var/log/dl.log and GPU driver installation logs for the vGPU guest driver or NVIDIA data center GPU driver in /var/log/gpu-install.log. JupyterLab instances on Deep Learning VMs surface logs that can be examined to verify component installation and operation. Model endpoints support configurable log verbosity through the VLLM_LOGGING_LEVEL environment variable, letting operators control what the vLLM inference server records.
+PAIS observability is activated by updating the PAISConfiguration custom resource. Operators set a Prometheus storage class policy through observability.prometheusRuntime.storageClassName and a retention period through observability.prometheusRuntime.metricsRetention.period, which define where collected metrics are stored and how long they are preserved. LLM traces can be forwarded to an external OpenTelemetry Collector over HTTP/protobuf or gRPC by uncommenting the spec.observability.llmTraces section of the PAISConfiguration custom resource, externalizing trace data away from the system where it was generated. PAIS Controller metrics are exposed at the Prometheus metrics endpoint on the pais-controller-manager service and can be streamed from the Supervisor cluster to VCF Operations for consolidated observability. PAIS integrates with Grafana for metrics visualization using OIDC provider authentication, restricting who can view the collected observability data.
+Access to the underlying log files on Deep Learning VM filesystems and the persistent volumes backing Prometheus storage is governed by the Kubernetes RBAC and persistent volume access controls provided by VCF. Organizations should configure the Prometheus storage class and retention parameters to align with their log protection requirements and route LLM traces and observability data to a protected external platform such as Grafana, VCF Operations, or another OpenTelemetry-compatible backend.</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend generates structured security event logs across its Distributed Firewall, Gateway Firewall, IDS/IPS, and Malware Prevention components, with several mechanisms that support protection of those logs from suppression or loss.
+The Security Services Platform audit log is enabled by default and cannot be disabled through configuration. All access events to the Security Services Platform, including access to the License Hub, are recorded in these audit logs, preventing log suppression at the platform level.
+The Distributed IDS/IPS can be configured to forward events directly to external syslog consumers via the ids_events_to_syslog setting; this forwarding is disabled by default and requires explicit configuration. When remote syslog is enabled on ESX hosts, IDS/IPS events are exported directly from those hosts to external receivers. vDefend components write log files to /var/log, with syslog messages conforming to RFC 5424 on vDefend appliances and RFC 3164 on ESX hosts. Gateway Firewall isolation rules log blocked traffic attempts to the unifiedsyslog.log file on Edge Nodes.
+Malware Prevention produces structured event logs in JSON format that include standard attributes (date, log level, module) along with detailed file analysis metadata: file hashes (SHA256, SHA1, and MD5), file type, file size, inspection timestamp, client and server VM identifiers, submission source, detection status, verdict, analysis status, malware classification, malware family, HTTP domain, HTTP method, and user agent. These records capture the full analysis lifecycle, including file intercepted, verdict cache hit, local static analysis submission, cloud dynamic analysis submission, verdict obtained, and policy enforced events. In 9.1, the Malware Prevention Service can be configured to forward logs to a remote logging server using TLS encryption with mutual certificate authentication (requiring server CA certificate, client CA certificate, client certificate, and client key), providing an off-appliance copy of event records with in-transit protection.
+Identity Firewall event log sources can be integrated with VCF Log Management for centralized log collection and monitoring, providing an additional path to off-appliance log preservation.
+Protection of forwarded or archived logs from unauthorized access and modification at rest is outside vDefend's scope and depends on the receiving log management or SIEM platform's controls.</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) contributes to this control through role-based log access controls, syslog forwarding to external platforms, and audit event generation that captures user identity and action details.
+PNR generates audit events across a broad range of recovery and replication operations, including configuration changes, recovery plan executions, and protection group modifications. Each audit event record includes the event name, user identity, and source IP address from which the action was initiated. Login events include timestamps, session keys, and user identity information in a structured format. Events covering protection group and consistency group changes are logged at appropriate severity levels (Info or Error), and corresponding alarms can be configured to trigger notification when specific events occur.
+PNR log files are designed to exclude sensitive data such as private keys and passwords. The vSphere Replication component maintains security-relevant audit logs at defined paths on the appliance, including authorization error messages, login events, and certificate verification errors, each recorded with timestamps and component information to support forensic review.
+To move logs off the local appliance, PNR supports syslog forwarding from the PNR Appliance to a remote syslog server. The Clean Room Orchestrator supports forwarding events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud, enabling integration with enterprise log management and security monitoring platforms. Event forwarding to VCF Log Management requires version 9.0 or later. Centralizing logs in an external platform removes them from local storage where an attacker with appliance access could otherwise modify or delete them.
+PNR does not provide write-once or tamper-evident local log storage. Organizations should forward PNR logs to a centralized SIEM or write-once-read-many log repository to protect against modification or deletion at the storage layer.</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) produces structured audit logs that record platform-level and gateway-level operations, and provides several mechanisms that contribute to protecting those logs from unauthorized access and loss.
+At the platform level, DSM maintains gateway audit log files on the Provider VM at /var/log/tdm/provider/audit/, with individual files named using a timestamp format (gateway-audit-timestamp.log). Local retention covers the last five days of log files; once files are successfully uploaded to a configured S3 repository, DSM removes them from the local filesystem after five days. Each log entry captures structured fields including Component, Event Type, Event Details, Event Time (UTC), Status, and Source. The Source field records the email identifier of the user who initiated the operation, or "System" for events initiated by DSM without user intervention. The System Audit Events view, accessible through the Provider interface, is the designated location for reviewing non-database-related platform operations. Access to the Provider interface is scoped to the administrative role, restricting which users can read or interact with the system-level audit record.
+DSM supports offloading audit logs to external storage as the primary mechanism for durable protection. When a default S3 provider log repository is configured, DSM periodically archives gateway audit log files to an S3 subpath named "gateway audit." DSM does not delete audit logs stored in the S3 repository, which means the archived log record persists beyond the five-day local retention window. Externalizing audit logs to S3 separates the log record from the Provider VM that generated it, reducing the risk that a compromise or failure of the Provider VM affects the integrity or availability of the audit trail. Organizations apply bucket-level access controls and retention policies on the S3 repository to restrict who can read, modify, or delete the archived logs.
+DSM supports log forwarding, allowing DSM logs to be sent to a centralized log management or security information and event management (SIEM) platform via the System Logs capability. Forwarding logs to an external system provides a second copy of the audit record under access controls and integrity protections that are independent of the DSM platform itself.
+For SQL Server databases provisioned through DSM, the SQL Server data service uses server-level DDL triggers to restrict the file paths available for audit logs, limiting where audit log files can be written. DSM supports enabling audit logging for SQL Server with configurable levels of auditing for system logins and a configurable log retention period. DSM can automatically create a simple audit for login events based on the Login Auditing option selected during cluster creation. For custom audit requirements, the standard T-SQL CREATE AUDIT and CREATE AUDIT SPECIFICATION DDL statements are available.
+DSM can generate and download log bundles that aggregate relevant logs from database VMs, supporting diagnosis and out-of-band preservation of the operational log record.
+Audit events can be exported from the System Audit Events view in CSV or XLSX format using the ACTIONS menu. Exports include all events visible to the authenticated user regardless of pagination, supporting external archival and out-of-band preservation of the audit record.</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer supports the protection of event logs and audit tools through real-time log forwarding to external systems, structured audit record content, and access controls on the Controller's audit interfaces. The 9.1 release adds License Hub audit logging capabilities that are always active and optionally forwarded to external syslog.
+The primary off-system protection mechanism is the Syslog-Audit-Persistence feature, configured under Alert Actions in the Avi Controller. When enabled, audit events stream to one or more external syslog servers in real time; once forwarded, the records reside outside the Controller where local administrative access cannot modify or remove them. The Controller supports syslog delivery over TCP in addition to UDP, and syslog server targets are specified in Controller Settings. Any compatible syslog receiver, including VCF Log Management configured as a log forwarder, can serve as a destination.
+An important architectural boundary applies: Avi Load Balancer debug logs and Event Logs are not forwarded to remote syslog servers through the OS-level syslog configuration. Debug logs are accessible only through Tech Support generation. Event Logs require a separate API pull or a scripted push from the Controller to a remote logging system, which means organizations should configure explicit export or retrieval processes for off-system preservation.
+The Avi Controller's Event Logs provide detailed records of system activities, configuration changes, and operational events, including an audit trail that identifies who made each change and when. Object-specific event logs are accessible via the Events tab on detail pages for Virtual Services, Pools, Service Engines, and Controllers, automatically filtered to the relevant object. The API supports querying events over extended periods, including a one-year lookback using the CONFIG_DELETE endpoint with the appropriate duration parameter.
+Avi WAF generates audit log records for matched security events, such as cross-site scripting detection, capturing the matched variable name and content when audit log parts are configured to include event data (ctl:auditLogParts=+E). This extends event log coverage to L7 application protection events beyond configuration and access activity.
+In 9.1, the License Hub provides dedicated audit logging that records all access events and cannot be disabled. License Hub can be configured to transmit log messages to a remote syslog server. A built-in Audit local user account with the auditor role provides dedicated access to APIs and services for system auditing, separate from the administrative account.
+Both the Controller and Service Engines log delivery failures when transmitting to Events, Syslog, and Splunk targets, including failed trusted channel initiations and function failures. Disruptions to the log forwarding pipeline are captured as auditable events in their own right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>AU.L2-3.3.9</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>MON-02, MON-08.2</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Limit management of audit logging functionality to a subset of privileged users.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>VCF provides role-based access control mechanisms across its components that can be used to restrict access to event log management to a defined set of privileged users.
+In VMware vCenter, privileges are fine-grained access controls that can be grouped into roles and then mapped to users or groups. Role-based access control in vCenter allows creation of custom roles with granular privilege assignment and permission propagation to vSphere objects. Administrators can create purpose-built roles that grant or withhold access to log-related functions, assigning those roles only to personnel with a documented business need. Privilege checks can be filtered and retrieved by managed object IDs, principals, privileges, and session identifiers, providing visibility into who accessed what. User permission events are sourced from vCenter logs and can be filtered by event type, status, user, object name, and object type, supporting after-the-fact review of access changes. vCenter can also be configured to stream events to a remote syslog server by enabling the vpxd.event.syslog.enabled option through the vCenter Management Interface, and this configuration option is itself restricted to administrative users.
+VCF Operations provides its own layered access control model. User groups in VCF Operations Access Control have an associated role and scope that define the permissions and organizational context for group members. Scopes enable access control by associating defined scopes with user accounts and user groups, restricting visibility and actions to specific segments of the managed environment. The administrators role should be assigned only to specific users who must access objects and perform actions across the entire environment. To simplify access management, roles should be assigned to user groups rather than individual users. When a user is a member of a specific user group, the associated access group provides that user with access to configuration, dashboards, and templates, or to specific navigation areas such as Administration. The VCF Operations orchestrator enforces role-based access control that restricts users to specific permissions based on assigned roles and group membership.
+For log-specific operations, VCF Operations requires the Security &gt; Security Operations permission to be assigned to users performing log integration. This permission is configured through the VCF Operations console under Administrator &gt; Control Panel &gt; Access Control &gt; Roles, allowing organizations to limit log integration capabilities to a controlled set of users. VCF Log Management provides its own access control management, granting permissions to VCF SSO users and groups to control who can view, search, and manage collected log data.
+In VCF Operations for Networks, only Admin role users are permitted to view and enable or disable personally identifiable information in audit logs, restricting audit log management to a narrow set of privileged accounts. The Networks backup configuration also allows selective inclusion or exclusion of audit logs containing PII, giving administrators control over what log data is accessible through backup operations.
+For Windows-based components in the VCF environment, the Event Log Readers group controls which accounts have permissions to read event logs on the local computer. Read-only security log access can be configured on Windows Server-based domain controllers to grant specific accounts read-only access to security event logs, and the event log reader account must be explicitly granted read permissions for security event logs.
+On VMware ESX hosts, syslog configuration, including log levels and remote syslog server destinations, is managed through esxcli commands that require administrative access to the host. The ESX syslog directory location can be configured via the Syslog.global.logDir parameter, and these configuration changes are restricted to users with sufficient host-level privileges. The Syslog.global.auditRecord.remote parameter specifically controls whether ESX audit records are forwarded to the remote host defined by Syslog.global.logHost, and like other advanced syslog settings, requires administrative privileges to configure.
+For workloads running on VMware Kubernetes Service (VKS) and the vSphere Supervisor, access to log resources is governed by Kubernetes role-based access control. Logs generated by Supervisor and workloads running on it fall into several categories with distinct access controls: Kubernetes API audit logs, pod and container logs, Kubernetes Event objects, and system component logs. The Kubernetes API server audit log captures all API requests, including the requesting user, timestamp, resource accessed, and action taken, with Event objects in the audit.k8s.io API group recording these details at one of four configurable levels: None, Metadata, Request, or RequestResponse. The audit policy passed to the kube-apiserver via the --audit-policy-file flag determines which events are recorded, and audit log output is written to a file path on the control-plane node; both the policy file and the log file path are control-plane-level configurations accessible only to vSphere infrastructure administrators. On the vSphere Supervisor, the kube-apiserver audit log is collected by Fluent Bit from /var/log/vmware/audit/kube-apiserver.log using the audit.apiserver.* tag; the log path resides on the control-plane node and is accessible only to vSphere infrastructure administrators. The Supervisor can also be configured to preserve the source IP addresses of authentication requests and Kubernetes API server requests in audit log entries, a capability configured through the Supervisor management proxy settings and restricted to vSphere infrastructure administrators. Pod and container logs accessible through the Kubernetes API require the get verb on the pods/log subresource within the relevant namespace, granted through a Role and RoleBinding; because RBAC is namespace-scoped by default, a user with log access in one namespace does not have it in another unless an additional binding is created, and cluster-wide log access through ClusterRoles is reserved for infrastructure administrators. Kubernetes guidance specifies that cluster-admin access should not be granted to regular users in multi-tenant clusters, and even administrative personnel should use least-privilege RBAC bindings for routine operations, reserving cluster-admin for break-glass scenarios. The Fluent Bit logging agents deployed in the vmware-system-logging namespace handle log collection and forwarding to external destinations including Syslog servers, HTTP endpoints, Elasticsearch, Kafka, and Splunk targets; access to modify this namespace's configuration is restricted to cluster administrators, and the selection of forwarding destinations and any authentication credentials is accessible only to users with administrative access to that namespace. For workloads running in a vSphere Namespace, log streaming to a remote Syslog server is configured through the LogAgentConfiguration Custom Resource; each syslog message includes metadata fields (namespace name, pod UID, pod name, container name, and ESX host name) that attribute log data to its source, and applying or modifying the LogAgentConfiguration CR requires namespace-administrative access.
+The organizational component of this control, defining which users have a business need for log access and enforcing least-privilege policies, requires administrative process and governance outside of what VCF provides. VCF supplies the technical mechanisms for restricting and auditing log access, but the organization must define and manage the access policies.</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Meets</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend's Security Services Platform (SSP) restricts access to event log management through role-based access control. SSP defines five distinct roles with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. The Auditor role is scoped to viewing and tracking system activity without administrative access, keeping log review separate from configuration authority. Modifying role assignments requires Enterprise Admin privileges, so access to user management is restricted to authorized personnel.
+Role assignments can be applied to both local accounts and directory-managed remote users or user groups, allowing log access rights to be scoped to personnel with a specific business need. SSP audit logs are enabled by default and cannot be disabled, providing a persistent record of access and administrative activity.</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>VCF Protection and Recovery (PNR) restricts access to event log management through role-based access controls that govern which users may manage log bundles, log manager settings, recovery workflows, and event forwarding configurations.
+PNR defines distinct roles including Protection and Recovery Administrator and VRM Administrator, each scoping privileges to specific operations. In deployments using PNR for VCF Automation, four predefined roles govern access: Provider Administrator, Organization Administrator, Project Administrator, and Project Advanced User. Each role grants specific privileges while restricting access to resources belonging to other users. A user holds at most one role per protected object; roles can be combined through group membership, enabling administrators to construct privilege sets aligned with job function.
+Log manager configuration, including verbosity settings for licensing (logManager.Licensing) and server authorization events (logManager.ServerAuthorization), is restricted to administrative users through PNR's Advanced Configuration interface. The SrmDpxAgentUser role specifically scopes event logging to the vCenter Event Manager for the DPX agent service account, illustrating how PNR applies role-based restrictions at the component level. Execution of PNR workflows through the VCF Operations orchestrator plug-in requires administrator login, and creation of protection groups and array-based replication groups is restricted to administrative users.
+PNR logs security-relevant events including authorization failures for remote site manager operations (recording method name, fault type, object reference, and privilege ID), login events with timestamps and user identity, and replication configuration changes. Security audit records are maintained in the vSphere Replication security audit log at /opt/vmware/support/logs/hms/hms-audit.log. The PNR Appliance supports forwarding log files to a remote syslog server; the Clean Room Orchestrator component can forward events to VCF Log Management (version 9.0 and above) or to Microsoft Azure Log Analytics using Data Collection Rules and Data Collection Endpoints.
+The organizational process of determining which users have a business need for log management access and assigning appropriate roles accordingly falls outside PNR's technical scope.</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>VMware Data Services Manager (DSM) provides role-based access control that scopes access to audit log viewing and management functions based on user role assignments. DSM defines two roles: the DSM Admin role, which grants super-user access to all data services and administrative functions including the System Audit Events view and log management settings; and the DSM User role, which restricts access to only the objects owned by that user within the assigned namespaces. Users in the DSM User role cannot access the System Audit Events view or log management configuration settings. The DSM console enforces these restrictions directly, limiting the views and actions available to those permitted for the logged-in user's role.
+The System Audit Events view is accessible through the Provider interface and is the only location in the DSM UI where non-database-related operations and tasks can be tracked. Because this view resides in the Provider interface, access to it is scoped to users assigned the DSM Admin role. Administrators assign roles to users either directly through local user creation in the DSM UI or through Directory Service Groups mapped to LDAP users via LDAPS integration, enabling group-based access control for organizations with directory service infrastructure.
+Gateway audit log files are stored on the Provider VM at /var/log/tdm/provider/audit/ with filenames in the format gateway-audit-timestamp.log. These logs track user read and write operations to DSM data services or infrastructure objects performed in the DSM UI or through the DSM Gateway Kubernetes interface, covering both UI-driven and API-driven management activity. Each log entry records the Source field as either a user identifier (Email ID) for user-initiated events or System for events initiated by DSM without user intervention. When a default S3 provider log repository is configured, DSM archives these files periodically to an S3 subpath named "gateway audit." The Log Forwarding setting in DSM's Settings area, configurable by Admins, controls whether logs are forwarded to external log management systems. Provider Log Storage settings require an Access Key credential for authentication to the object store. Audit events can be exported in CSV or XLSX format through the ACTIONS drop-down menu in the System Audit Events view, and exports include Component, Event Type, Event Details, Event Time (UTC), Status, and Source fields.
+For SQL Server data services, DSM provides additional log access controls. When creating a SQL Server cluster, DSM can automatically configure a Login Auditing option that creates a simple audit for login events. DSM also uses server-level DDL triggers to restrict the file paths available for audit logs, and the internal dsm_mgmt management login operates within a secure, isolated context to prevent administrative operations from being accessible to or exploitable by users with general database privileges.
+For this control to be fully met, organizations need to implement a formal process for identifying personnel with a specific business need to access event log management functions, document that authorization, and review it periodically. Access to the underlying Provider VM file system and the S3 storage bucket where logs are archived should also be controlled at the infrastructure level, as those paths are outside DSM's own access controls. DSM's RBAC provides the technical mechanism to scope log management access to Admin-role users, but the assignment of that role must be governed by an organizational policy tying role grants to documented business justification.</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) provides role-based access control mechanisms that allow administrators to restrict access to event log management functions to users with a defined business need. The Operations permission category within Avi's RBAC system includes distinct granular permissions for alert and syslog configuration: PERMISSION_ALERT, PERMISSION_ALERTCONFIG, PERMISSION_ALERTEMAILCONFIG, and PERMISSION_ALERTSYSLOGCONFIG, among others. By assigning these permissions only to designated roles, organizations can restrict which users can configure syslog forwarding targets, manage alert actions, or modify the Syslog-Audit-Persistence template used for streaming audit events to external syslog servers. Access to the Operations tab and global event logs in the Avi Controller can also be restricted by user role.
+Avi's Extended Granular RBAC allows privilege scope to be set through the `allow_unlabelled_access` parameter in role objects, combined with resource-level markers that tie user permissions to specific labeled resources. Auth Mapping Profiles let user groups from external identity sources (LDAP, SAML, TACACS+) be mapped to Avi roles and tenants, aligning directory group membership with specific administrative responsibilities. The "Any Group or Any Attribute" fallback rule in Auth Mapping Profiles should be configured for least-privilege access, so users who do not match a more specific group rule receive no elevated permissions by default.
+Avi's tiered access model supports multiple privilege levels within the same deployment. The Tenant Application Operators group can be configured with read-only access limited to a defined set of tenants, while the Tenant Application Admins group can be given application owner privileges within a specific tenant scope. The Super Admins group maps to a role granting access to all tenants and all settings, and this is the tier where log management authority would typically reside. The Super User Rule, when applied, overrides all other role and tenant mappings, granting unrestricted access across all tenants; the is_superuser flag on individual accounts can be disabled to restrict those privileges.
+When administrative changes are made to the Avi Controller, configuration events are recorded with the event type, object name, tenant, timestamp, and the identity of the user who performed the action. The Avi Event Logs system provides a detailed audit trail tracking what was changed, who made the change, and when. Avi Controller and Avi Service Engine also log audit records for trusted channel initiation, termination, and failures, forwarding those records to Events, Syslog, and Splunk. For Kubernetes environments, Avi Kubernetes Operator (AKO) custom resource definitions can benefit from Kubernetes RBAC policies to apply stricter access controls to load balancer configuration resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>CA.L2-3.12.1</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>CPL-02, CPL-02.1, CPL-03, IAO-02</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Periodically assess the security controls in organizational systems to determine if the controls are effective in their application.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>CA.L2-3.12.2</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>IAO-05</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Develop and implement plans of action designed to correct deficiencies and reduce or eliminate vulnerabilities in organizational systems.</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>CA.L2-3.12.3</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>CPL-02, THR-01, THR-03</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Monitor security controls on an ongoing basis to ensure the continued effectiveness of the controls.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to this control through its threat intelligence consumption and detection infrastructure. The IDS/IPS engine applies knowledge-based signatures that encode specific patterns corresponding to known attack types, detecting intrusions based on known malicious instruction sequences at distributed and gateway enforcement points within vDefend-protected segments. Threat metadata feeds for Network Detection and Response are distributed and can be refreshed from online sources, or downloaded and applied manually in air-gapped environments through NSX Manager or a workstation connected to the Security Services Platform.
+Network Detection and Response (NDR) correlates related detection events into campaigns and organizes them into a chronological timeline for security analyst review and triage. The Campaign view displays total detections and threats identified under Malicious Activity, and Campaign Correlation Rules provide structured visibility into how individual detections relate to broader attack patterns.
+Security Intelligence maps detected suspicious events to adversarial tactics and techniques from the MITRE ATT&amp;CK framework, recording the count of each tactic and technique observed during a selected time period. This TTP-level categorization supports the situational awareness the control describes for traffic traversing vDefend-protected segments. The threat visualization canvas aids rapid containment, identification of compromised assets, and adjustment of microsegmentation policies in response to detected activity. The blast radius analysis capability displays which communication paths a threat has affected, helping analysts determine whether an attack targets specific systems or represents a wider campaign.
+Security Intelligence also collects related IDS events across the same source and destination hosts to connect relevant events and build a fuller picture of an attack sequence. The vDefend Security Assessment generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows to support protection planning. Security teams investigate individual events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take mitigation actions.
+While vDefend delivers technical mechanisms for consuming threat intelligence feeds and mapping observed behavior to adversarial TTPs at the network layer, the broader organizational threat intelligence program, including sourcing intelligence from external providers, integrating with threat sharing platforms, and disseminating findings to other teams and tools, requires complementary processes and tooling outside the product.</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>VMware Avi Load Balancer (Avi) contributes to situational awareness of evolving threats at the application delivery layer through its Live Security Threat Intelligence service, which delivers security threat feeds for multiple attack vectors in real time to protect applications from continuously changing threats. The Live Security Threat Intelligence service encompasses four components: an IP Reputation Service, an Application Rules Service, a WAF Signatures Service, and a Bot Management Service. The service is opt-in and must be explicitly enabled through Cloud Services configuration on the Avi Controller.
+The IP Reputation Service classifies incoming client IP addresses against a regularly updated database, covering threat categories including botnets, phishing, spam sources, and DoS/DDoS attack sources. The service performs real-time automatic IP Reputation updates and operates across globally distributed Avi Load Balancer Controller clusters. Administrators attach an IP Reputation database to virtual services, and enforcement actions such as blocking or rate-limiting are applied per classification result.
+The Application Rules Service provides rules specifically designed to block attacks on known application vulnerabilities, many of them mapped to CVEs, covering protection for over 5,000 applications including WordPress, Drupal, and Apache. Application Rules are automatically updated on the Avi Controller, and administrators can enable auto-sync to receive Application Rules Database updates automatically when new rules are published.
+The WAF Signatures Service allows Avi to receive notifications when new Core Rule Set (CRS) data is available and to automatically download updated WAF CRS rules. This keeps application-layer defenses aligned with current vulnerability intelligence without requiring manual administrator action.
+The Bot Management Service delivers a real-time feed for the User-Agent database, a core bot detection component. User Agent Database Sync can be enabled to receive continuous User-Agent updates for threat detection. Traffic is classified into categories including Bad Bot, Dangerous Bot, Good Bot, Human, Unknown, and User-defined Bot, and HTTP security policy rules apply enforcement actions including connection termination for dangerous bot classifications.
+When Avi detects security events such as SYN flood or DDoS conditions, its alerting and ControlScript framework supports automated compensating responses. Alert actions can invoke a ControlScript that adds offending client IP addresses to a blocklist IP group attached to a network security policy for rate shaping or blocking. ControlScripts receive alert parameters including attack count, event ID, and alert level, and can execute automated remediation in response to system events rather than requiring manual intervention. The DDoS Policy within the Network Security policy detects and mitigates a range of Layer 4 through Layer 7 network attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>CA.L2-3.12.4</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>IAO-03, IAO-03.2</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Develop, document, and periodically update system security plans that describe system boundaries, system environments of operation, how security requirements are implemented, and the relationships with or connections to other systems.28</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>CA.L3-3.12.1e</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>VPM-07</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Penetration Testing</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>CM.L2-3.4.1</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>AST-01, AST-02, CFG-02</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Establish and maintain baseline configurations and inventories of organizational systems (including hardware, software, firmware, and documentation) throughout the respective system development life cycles.</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
 VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
@@ -3814,12 +4857,12 @@
 Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
 vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
@@ -3828,1072 +4871,6 @@
 Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
 Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
 vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable security baseline mechanisms for its replication and recovery infrastructure. The PNR appliance includes a security reference section that identifies configuration files containing settings that affect environment security, and PNR documentation establishes that secure operation depends on proper configuration and maintenance of the PNR server. The security reference also documents network port requirements, providing the technical specifications needed to develop and maintain secure baseline configurations for disaster recovery infrastructure.
-PNR includes a Configuration Import/Export Tool that captures the complete set of protection and recovery configuration settings, including server version, build number, local and remote site names, inventory mappings, placeholder datastores, advanced settings, and array managers. The tool supports both UI-based and scripted exports and can transfer configuration data without requiring credential entry when using the bundled generated script. This gives organizations a mechanism to document, back up, and restore known-good baseline configurations for their disaster recovery infrastructure. The underlying system configuration is stored in the va-configurator.xml file and is accessible through Advanced Settings on the Site Pair tab in the management interface, providing a defined location for baseline review and modification.
-The PNR appliance management interface allows administrators to configure appliance security settings after deployment. The Advanced Settings system provides privileged users with the ability to adjust default values governing protection and recovery features. When modifying the minimum protocol version for TLS, PNR requires that the change be applied consistently across all configuration occurrences in the system, supporting systematic baseline management for transport security settings.
-For cyber recovery deployments, PNR documentation recommends using standard VCF topology with separate workload and management domains to achieve better isolation and align with security best practices at the recovery site.
-Full compliance with this control requires an organizational baseline configuration management program, documentation practices, version control, and hardening tooling extending beyond what PNR provides directly.</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
-        </is>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.4</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>MON-05</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Alert in the event of an audit logging process failure.</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides built-in mechanisms to detect log processing failures, alert operations personnel, and support remediation of disruptions across its monitoring stack.
-VCF Operations monitors the health of its own alerting and log processing infrastructure. When no SNMP targets are configured for alert delivery, VCF Operations generates a critical alert (vmwSNMPNotConfiguredEvent), flagging that the alerting pipeline is not operational. It also generates critical alerts for invalid SNMP connection events (vmwSNMPConnectionInvalidEvent). At the network layer, VCF Operations monitors the status of the NSX Management Node SNMP Service and generates a warning-severity alert when the service stops running. NSX-T itself generates an alert event when the Syslog Service has stopped running on NSX-T Manager nodes. The NSX Manager Logging Monitor adds a further detection mechanism through the System Health Agent framework, tracking each log's generation rate and rotation settings to estimate how long log data will be retained and raising log duration alarms when abnormal rates risk flushing log data before it is collected, so operators can intervene before records are lost. These self-monitoring capabilities detect failures in the event log processing and alert delivery chain before administrators need to discover them manually.
-The alert framework in VCF Operations supports definitions built from one or more symptom sets. Symptom definitions identify conditions on attributes, properties, metrics, and events. The framework supports multiple event types relevant to log processing failures, including System Degradation, Data Availability, Collector Down, and Object Error. Administrators can create alert definitions with tighter symptom parameters to track problems before users encounter further issues. Recommendations can be attached to alert definitions so that engineers know how to resolve the alert when it fires, providing clear remediation guidance tied to specific failure conditions. Alerts are generated when collected data for an object is compared against the alert definitions for that object type and the defined symptoms evaluate to true.
-For alert delivery, VCF supports multiple notification channels. vCenter can send both SNMP traps and email notifications when alarms are triggered, with configurable recipient addresses and subject lines. The vCenter SNMP agent supports SNMPv1, v2c, and v3 trap formats, including SNMPv3 with all security levels. VCF Operations supports outbound SNMP trap notifications to up to four destinations and can filter notifications based on defined criteria. As a fallback, VCF Operations can log alerts to a file on each of its nodes, providing an on-node record that persists even if external alert delivery is disrupted. This multi-channel approach helps ensure that alerts about log processing disruptions reach the appropriate personnel even if one delivery mechanism is impaired.
-VCF Operations provides log-based alerting through Symptom Definitions, accessible under Infrastructure Operations &gt; Configurations. Administrators can create log-based conditions and symptoms that trigger alerts when specific log patterns are detected, including patterns that indicate log processing failures or disruptions. The Log File plug-in supports notification rules that filter and route alerts to the appropriate teams. Log-based alert definitions can monitor host systems for specific conditions such as cluster performance failures, and they generate alerts when those conditions are detected. These alerts can be forwarded to external monitoring systems via SNMP traps.
-VCF Log Management is a centralized log collection platform that pulls tasks, events, and alerts from vCenter instances and receives syslog feeds from ESX hosts. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. This centralized architecture makes it possible to detect when expected log streams stop arriving, which is itself an indicator of a log processing failure. When audit record transmission is active on ESX hosts, the syslog daemon (vmsyslogd) emits records documenting its own operational status, including daemon start, stop, and error conditions, enabling detection of syslog service disruptions at the host level. vCenter event streaming to a remote syslog server is configured via the vpxd.event.syslog.enabled option in the vCenter Management Interface.
-VCF Operations logs task execution details including Script Return Result status, script names, target object types, parameters passed, and unexpected exceptions. When automated remediation tasks fail, these logs provide the diagnostic detail needed to understand what went wrong and why. Task events are displayed in the messages area, allowing administrators to troubleshoot failed tasks directly.
-Adapters for external monitored systems and the REST API are inbound channels for collecting events from external sources. VCF Operations correlates a subset of events published by monitored systems and delivers them as faults. Fault symptoms can be defined based on these events and added to alert definitions, so failures in external log sources are surfaced within the central monitoring platform. For organizations that forward logs to external SIEM systems via syslog, any disruption in log forwarding is itself a monitorable condition, since VCF components generate alerts when syslog services stop running.
-At the Kubernetes consumption layer, VMware Kubernetes Service (VKS) clusters include instrumentation to detect and report log processing failures in workload environments. The Kubernetes API server exposes the apiserver_audit_error_total metric, which counts audit events dropped due to export errors, and the companion apiserver_audit_event_total metric, which tracks total audit event volume; a sustained rise in the error count relative to the event count indicates a failure in the audit export pipeline. When Prometheus is installed as a standard package on a VKS cluster, Prometheus instances are configured to send alerts to Alertmanager in the tanzu-system-monitoring namespace. Alertmanager is deployed as a StatefulSet with multiple replicas in that namespace, and administrators can configure alert rules targeting these metrics to route notifications to designated personnel when audit event exports fail. Prometheus discovers Alertmanager pods through Kubernetes service discovery, filtering by namespace, app label, and component label.
-VKS clusters include Fluent Bit logging agents for cluster-wide log collection and forwarding. Fluent Bit supports output to Syslog, HTTP, Elasticsearch, Kafka, and Splunk destinations, so disruptions in log forwarding are detectable through the health of the centralized log collection infrastructure. For workloads running in vSphere Namespaces, the LogAgentConfiguration Custom Resource streams logs to a remote Syslog server once applied to the namespace; each log message includes namespace name, pod UID, pod name, container name, and ESX host name as metadata fields, allowing operations teams to correlate forwarding gaps with specific workloads or nodes.
-The Node Problem Detector provides a SystemLogMonitor daemon that monitors system logs and reports problems to the API server as NodeConditions or Events, according to predefined rules covering log sources such as filelog, kmsg, and kernel logs. This surfaces node-level log source failures as cluster events that can be queried or routed through alert management infrastructure. In Kubernetes audit logging batch mode, if the rate of incoming events overflows the buffer, events are dropped without notification from the logging subsystem itself, which makes metric-based monitoring of apiserver_audit_error_total the primary signal for detecting silent audit pipeline failures. VM Operator logs record reconciliation events for VirtualMachineService resources in VKS clusters, providing additional log sources for troubleshooting provisioning and service failures.</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides event logging with configurable alarms that can alert administrators to operational failures across the disaster recovery environment. Each event type has a corresponding alarm that can be configured to send email notifications, SNMP traps, or execute a script when triggered, giving administrators multiple channels to reach appropriate personnel when problems occur. For email notifications, mail settings must be configured in the vCenter Settings menu before alarm-triggered notifications function. PNR also requires an administrator email address to be configured during appliance registration with vCenter.
-The PNR Server logging level can be configured to one of five levels: error, warning, info, verbose, or trivia, by modifying the log configuration. Error and warning levels capture conditions that indicate problems in the environment. When recovery plan execution encounters failures, PNR logs diagnostic details in the recovery site server logs, including plan identifiers, plan names, and detailed error messages with fault codes.
-The PNR Appliance can forward log files to a remote syslog server for centralized log analysis and monitoring. vSphere Replication maintains separate audit logs at /opt/vmware/support/logs/hms/hms-audit.log for tracking security-relevant events, including authorization errors with timestamps and component information.
-The Clean Room Orchestrator provides an additional monitoring layer for ransomware recovery workflows. Administrators can configure email alerts for critical events in the clean room environment. The orchestrator can forward events to VCF Log Management, Microsoft Sentinel, or Splunk Cloud; event forwarding to VCF Log Management requires version 9.0 or above.
-VCF Operations provides an alert system that notifies administrators when specific symptoms of monitored objects are detected, including health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites. In environments with more than one vCenter, PNR displays all events from PNR servers registered as extensions.
-PNR logs when a protected consistency group has errors or warnings, recording this as an Error-level event. These mechanisms surface operational failures and log-related disruptions as part of broader recovery environment monitoring. Dedicated log pipeline health monitoring and log processing failure detection are provided by the underlying VCF platform monitoring stack.</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) supports log processing failure detection and personnel notification through its audit record failure logging capability and event alerting framework.
-Avi Controller and Avi Service Engine explicitly record audit record failures for three log destinations: Events, Syslog, and Splunk. The failure categories captured include initiation and termination of trusted channel connections, failure of trusted channel functions, unsuccessful certificate validation attempts, client authentication failures, SSH session establishment failures, and identification of the initiators and targets of failed trusted channel establishment attempts. This capability is configured in the Application Monitoring section of the Avi documentation under Audit Logging &gt; Audit Record Failures.
-When log processing failures or system events occur, Avi Controller can route notifications to four destinations: the local Controller UI (displayed as colored bell icons), email, syslog, and SNMP trap servers. These notification channels are configured under Operations &gt; Notifications in the Controller UI. Avi supports both SNMPv2c and SNMPv3 protocols for SNMP trap notifications, and SNMP notification channels can be configured with TLS encryption and strict certificate verification for secure transport. The Avi Controller cluster leader issues SNMP trap notifications and supports multiple SNMP servers, providing redundancy for alert delivery. The Syslog-Audit-Persistence alert action template is available for configuring alert actions that stream events to external syslog servers, which can feed into a centralized log management or SIEM platform.
-Auditors should be aware of two scoping boundaries when evaluating this control. First, Avi debug logs and Event Logs are not transmitted to remote syslog servers through the OS-level syslog configuration; Event Logs require the Syslog notification configuration within the Controller UI or API-based export. Second, configuring Syslog notifications in Avi Controller pushes alerts to syslog servers but does not export virtual service logs; virtual service logs must be pulled from an external logging system through the API or scripted to be pushed from the Controller to a remote destination.
-Auditors verifying this control should confirm that Alert Actions are configured in the Operations section of the Avi Controller UI, that notification destinations (email addresses, SNMP trap server addresses, or syslog server targets) are defined, and that organizational runbooks or response procedures define who receives these alerts and what remediation steps follow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.5</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>MON-02, MON-02.1</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Correlate audit record review, analysis, and reporting processes for investigation and response to indications of unlawful, unauthorized, suspicious, or unusual activity.</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
-VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
-VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
-NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
-VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
-VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
-VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
-Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
-For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
-VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend Network Detection and Response (NDR) correlates detection events into campaigns, comparing new detection data against existing events to identify related activity. Campaigns provide a view of a threat by correlating detection events to identify the different stages of an attack, and security analysts can view and triage threat campaigns through a campaign timeline. NDR supports SIEM integration, sending campaign and event logs to a connected SIEM in real time, allowing network security event data to be exported for broader correlation with other enterprise data sources.
-Security Intelligence detects and categorizes suspicious events using MITRE ATT&amp;CK tactics and techniques, recording event occurrences during selected time periods, and provides a View Full Event History capability that displays all events associated with a given signature ID and intrusion severity. Security Intelligence also correlates IDS events from the same source and destination hosts to connect related events and build a broader picture of an attack. This structured, MITRE-tagged event data can support SIEM-based analysis and enterprise-wide threat correlation.
-The Security Services Platform (SSP) can be configured to forward log messages to external syslog servers for centralized log collection. SSP syslog configuration supports TCP, TLS, and UDP protocols and allows administrators to specify server address and port, integrating with existing SIEM ingestion pipelines. NDR Sensors report metrics covering health, traffic trends, and data processing activity, available as point-in-time measurements or aggregated data over time.
-vDefend correlates only technical network security data and has no capability to ingest or correlate non-technical information such as HR records, physical access logs, or operational data. Satisfying the full scope of this control, which requires correlation of both technical and non-technical information across the enterprise, requires an external SIEM or equivalent platform.</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) generates security-relevant event logs and supports forwarding them to centralized log collection and SIEM platforms through multiple native mechanisms.
-The Protection and Recovery Appliance provides built-in syslog forwarding to remote syslog servers. The forwarding configuration supports a selectable transport protocol and a configurable destination port (default 514). PNR includes a test message capability to verify that a remote syslog server is receiving messages before relying on it operationally. REST API endpoints are available for managing syslog configuration, including endpoints to list all configured syslog servers, update syslog server settings, and send test messages programmatically.
-PNR's event subsystem integrates with VMware vCenter, registering protection and recovery-specific events in the vCenter event infrastructure. Each event type has a corresponding alarm that PNR can trigger when the event occurs, enabling automated notification and downstream forwarding through vCenter's event pipeline to external SIEM platforms. PNR logs security-relevant events including login activity with timestamps, user identity, session keys, and locale information; authorization error messages with timestamps and component identification; and protection group configuration changes. The SrmDpxAgentUser role enables the DPX agent service to log events directly to vCenter Event Manager.
-The Clean Room Orchestrator component supports native event forwarding to VCF Log Management (version 9.0 or later), Microsoft Sentinel, and Splunk Cloud. Integration with Microsoft Sentinel uses Data Collection Rules (DCR) and Data Collection Endpoints (DCE) within an Azure Log Analytics Workspace, with DCE and Log Analytics Workspace required in the same Azure subscription and resource group. Splunk Cloud integration is configured using a Splunk URL and authentication token. Clean Room Orchestrator logs events for protection group creation and deletion, replication tasks, and snapshot operations. Event records include timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type.
-vSphere Replication, as a PNR component, maintains audit logs at /opt/vmware/support/logs/hms/hms-audit.log and broker logs at /opt/vmware/support/logs/hbr on the Appliance and at /var/run/log on VMware ESX hosts. vSphere Replication generates typed audit events for host and virtual machine replication configuration and unconfiguration changes, using structured event type identifiers.</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N39" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
-The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
-For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
-The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
-Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
-Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
-The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
-The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
-Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
-To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.6</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>MON-02, MON-06</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Provide audit record reduction and report generation to support on-demand analysis and reporting.</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
-VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
-VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
-NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
-VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
-VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
-VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
-Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
-For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
-VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend provides event log generation and monitoring capabilities across its security components in 9.1, directly supporting anomaly detection and assessment within the network security domain.
-The IDS/IPS subsystem generates detailed security event logs for event analysis. Remote syslog must be configured on ESX hosts to receive IDS/IPS events exported directly from those hosts; the `ids_events_to_syslog` setting controls whether IDS/IPS events are forwarded to external syslog consumers (the default is disabled). vDefend components write log data to /var/log, with syslog messages conforming to RFC 5424 on vDefend appliances and RFC 3164 on ESX hosts, enabling consistent ingestion by syslog-compatible platforms. The Security Explorer Computes view in Security Intelligence provides a full record of all IDS/IPS events for analysis over a 30-day timeframe. Security Intelligence also provides a View Full Event History capability that displays all events associated with a given signature ID along with their intrusion severity. The Threat Event Monitoring dashboard in Security Services Platform displays the trend in intrusion events over time, categorized by Intrusion Severity, giving security teams visibility into detection activity patterns.
-Malware Prevention Service generates structured event logs with detailed metadata per file analysis event. Event log fields include the verdict (BENIGN, malicious, or other classification status), a numeric risk score, malware classification, malware family, error codes and messages, HTTP domain, HTTP method, user agent, file upload status, submission status, analysis completion status, and gateway identification. File event statistics appear on the Monitor &amp; Plan &gt; Overview &gt; Threat Monitoring dashboard in Security Services Platform, with graphs covering a configurable time period (defaulting to the last hour).
-Network Detection and Response (NDR) generates and sends event logs to a SIEM endpoint when a detection event occurs, enabling integration with external correlation and reporting platforms.
-The Security Services Platform Monitor &amp; Plan Overview dashboard provides a view of security posture that includes the latest security segmentation report, flow trends, a summary of detected suspicious traffic events, pending actions, and current settings requiring attention. Security Intelligence generates bar graphs showing the number of anomalies detected, categorized by severity. The Policy Recommendations section tracks Security Intelligence recommendations with status indicators such as Ready to Publish, allowing security teams to act on recommended policy changes.
-vDefend Identity Firewall Event Log Sources can be integrated with VCF Log Management for centralized logging and monitoring. VCF Log Management supports Top-N queries using Interactive Analytics, enabling report generation from the aggregated log streams that vDefend supplies. VCF Log Management handles organization-level scheduled report generation, while vDefend provides the network-security-specific event data and dashboards that feed those reporting workflows.</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) generates security-relevant event logs and supports forwarding them to centralized log collection and SIEM platforms through multiple native mechanisms.
-The Protection and Recovery Appliance provides built-in syslog forwarding to remote syslog servers. The forwarding configuration supports a selectable transport protocol and a configurable destination port (default 514). PNR includes a test message capability to verify that a remote syslog server is receiving messages before relying on it operationally. REST API endpoints are available for managing syslog configuration, including endpoints to list all configured syslog servers, update syslog server settings, and send test messages programmatically.
-PNR's event subsystem integrates with VMware vCenter, registering protection and recovery-specific events in the vCenter event infrastructure. Each event type has a corresponding alarm that PNR can trigger when the event occurs, enabling automated notification and downstream forwarding through vCenter's event pipeline to external SIEM platforms. PNR logs security-relevant events including login activity with timestamps, user identity, session keys, and locale information; authorization error messages with timestamps and component identification; and protection group configuration changes. The SrmDpxAgentUser role enables the DPX agent service to log events directly to vCenter Event Manager.
-The Clean Room Orchestrator component supports native event forwarding to VCF Log Management (version 9.0 or later), Microsoft Sentinel, and Splunk Cloud. Integration with Microsoft Sentinel uses Data Collection Rules (DCR) and Data Collection Endpoints (DCE) within an Azure Log Analytics Workspace, with DCE and Log Analytics Workspace required in the same Azure subscription and resource group. Splunk Cloud integration is configured using a Splunk URL and authentication token. Clean Room Orchestrator logs events for protection group creation and deletion, replication tasks, and snapshot operations. Event records include timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type.
-vSphere Replication, as a PNR component, maintains audit logs at /opt/vmware/support/logs/hms/hms-audit.log and broker logs at /opt/vmware/support/logs/hbr on the Appliance and at /var/run/log on VMware ESX hosts. vSphere Replication generates typed audit events for host and virtual machine replication configuration and unconfiguration changes, using structured event type identifiers.</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides event log generation and reporting capabilities that support detection and assessment of anomalous activities within the database-as-a-service layer.
-DSM's primary audit interface is the System Audit Events view, accessible through the System Audit section in the Provider UI. This view is the only location in the DSM interface where administrators can track non-database-related operations and tasks. Each audit entry records a Component field identifying the DSM component that performed the operation, an Event Type field identifying the nature of the audited event, Event Details providing operation-specific information, Event Time in UTC, and a Status field indicating the outcome of the event. The Source field records either a user identifier (Email ID) for user-initiated events or "System" for events initiated by DSM without user intervention, enabling attribution of each audit record to a specific actor. Standard Kubernetes audit events are also captured through the Gateway Audit Logs capability.
-Audit events can be exported in CSV or XLSX format using the ACTIONS dropdown menu in the System Audit Events view. Exports include all events visible to the requesting user regardless of page size, covering the Component, Event Type, Event Details, Event Time (UTC), Status, and Source fields. These exports can be brought into external reporting and analysis tools to support audit review and anomaly assessment.
-For persistent retention, DSM archives gateway audit log files periodically to an S3 repository subpath when a default S3 provider log repository is configured. Audit log files are also stored locally on the Provider VM at /var/log/tdm/provider/audit/ in files named with a gateway-audit-timestamp.log format, supporting direct access for investigation. Support bundles can be generated and downloaded to aggregate control plane and data plane logs from a database cluster for diagnosis. The Provider VM also includes a System Logs capability for managing system log collection.
-DSM provides operational monitoring that can surface indicators of abnormal behavior. The Monitoring tab for database instances displays metrics including Active Connections, Data Disk Usage, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage %, InnoDB Reads and Writes, and Command Reads and Writes, with the time range adjustable through the Time Range Last dropdown. The Alerts pane in the Monitoring tab surfaces triggered alerts. DSM raises metrics-based alerts when metrics are successfully collected from a database cluster, status-condition-based alerts for critical failure conditions including database engine degradation and backup failures, and real-time alerts for resource or connectivity issues to support root cause identification. Webhook-based alerting supports integration with external notification systems for threshold-triggered database monitoring events. DSM can also be monitored through VCF Operations for additional troubleshooting and status visibility.
-Satisfying this control fully requires organizational processes to review exported audit data and monitoring output, establish baselines for normal activity, and investigate deviations. DSM does not include built-in anomaly detection, correlation, or security information and event management capabilities. Organizations typically forward DSM logs to a centralized log management platform for automated detection and reporting at scale.</t>
-        </is>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N40" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
-The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
-For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
-The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
-Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
-Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
-The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
-The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
-Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
-To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.7</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>MON-07.1, SEA-20</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Provide a system capability that compares and synchronizes internal system clocks with an authoritative source to generate time stamps for audit records.</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides time synchronization across all platform components using Network Time Protocol (NTP), with Precision Time Protocol (PTP) available for workloads requiring sub-microsecond accuracy.
-At the foundation layer, NTP service must be configured on all VMware ESX hosts. This is configured through the VMware Host Client by navigating to Manage &gt; System tab &gt; Time &amp; date &gt; Edit NTP Settings. The NTP client must be enabled by selecting the "Use Network Time Protocol" radio button, and the NTP service startup policy should be set to "Start and stop with host" so that time synchronization is maintained across host reboots. Using at least three NTP servers is a best practice for ESX host time synchronization, providing resilience against any single time source becoming unavailable. VMware Knowledge Base article 317537 provides detailed guidance on ESX host NTP configuration, and article 318888 provides procedures for verifying time synchronization across ESX host environments. ESX also supports PTP configuration through the HostDateTimeSystem, giving administrators a choice between NTP and PTP depending on the precision requirements of the environment.
-VMware vCenter must also be configured with NTP to maintain clock synchronization with managed ESX hosts. Time synchronization between vCenter and ESX hosts is a stated requirement for VMware Infrastructure operation. Consistent time across these components is critical for accurate logging, troubleshooting, and event correlation. The NTP daemon should be activated on ESX hosts for this reason. For environments running vSphere Supervisor, the same NTP servers must be configured for the vCenter instance, all hosts in the cluster, NSX, and the Supervisor.
-VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor extend NTP synchronization to Kubernetes control-plane and worker nodes through the ClusterClass variable framework. When provisioning VKS clusters using the Cluster v1beta1/v1beta2 API, administrators specify NTP servers in the osConfiguration.ntp.servers parameter (VKS 3.2.0 and later) or in the ntp cluster variable (VKS 3.1.0 and earlier); both parameters accept an array of NTP server hostnames or IP addresses. If left unset, VKS nodes inherit default NTP server addresses from the Supervisor, which in turn derives its time configuration from the underlying infrastructure. Post-creation changes to NTP server configuration require manually updating the ClusterClass cluster variable, as NTP changes are not automatically propagated to running clusters; administrators should account for this in change management processes. Clock accuracy within VKS clusters is operationally significant: clock skew between control-plane and worker nodes can cause DaemonSet rollout progress to be reported incorrectly when spec.minReadySeconds is in use, and correct timestamps are required for Kubernetes audit log reliability, certificate validity checks, and bootstrap token expiry enforcement.
-VCF Operations is the central point for NTP configuration across VCF core components. When you update the NTP server configuration through VCF Operations, it propagates the change to VCF Operations itself, all vCenter instances, ESX hosts, NSX Manager nodes, and NSX Edge nodes. If an NTP update fails for any component, VCF Operations rolls back the NTP settings for the failed component. NTP configuration changes go through a precheck validation step before deployment. VCF management components can also be configured to use the ESX NTP server for time synchronization through the time-sync-mode setting, allowing centralized time management where management components inherit their time from the underlying ESX infrastructure.
-VCF Operations supports two NTP synchronization modes: self-managed synchronization, where all nodes synchronize with the primary and replica node, or external NTP server synchronization using a URL or IP address. The NTP setting synchronizes time across VCF Operations cluster nodes. When configuring VCF SSO integration, NTP should be configured to synchronize the server system time of the identity source and VCF Operations. The ntp sync command is available to force synchronization of NTP settings within VCF Operations.
-NSX Manager appliances require NTP server configuration. NSX recommends using a node profile to configure NTP for all appliances rather than configuring each one individually. If NTP is configured individually on an NSX appliance, the same NTP server must be used on all appliances to maintain consistency. NTP is recommended for all NSX environment components regardless of which NSX features are in use.
-VCF Operations for Networks depends on clock synchronization with NTP for service health; if the system clock drifts out of sync, some services may become unhealthy or stop working. HCX similarly requires a valid NTP server with synchronized time for integrated systems operations.
-VCF provides built-in tools for validating time synchronization status. The SoS (Suite of Services) Utility offers an --ntp-health option that verifies whether the time on VCF components is synchronized with the NTP server configured in the VCF Installer appliance, allowing administrators to validate synchronization without relying on external tools. VCF Health Diagnostics also monitors NTP configuration data across VCF components and provides per-component NTP status information.
-Accurate time synchronization across the platform is a prerequisite for TLS and VCF SSO communication, Kerberos authentication (which fails on clock skew), certificate validation, and consistent log timestamps for auditing and troubleshooting.
-For workloads requiring higher precision than NTP provides, vSphere supports a precision clock device that gives a virtual machine access to the system time of the primary ESX host. PTP is also available for environments requiring sub-microsecond accuracy on a local area network. When an ESX host is configured for PTP, the NTP service must not be running concurrently; NTP and PTP are mutually exclusive at the host level.</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend both depends on and validates time synchronization across its enforcement and management components. Accurate clock synchronization is a prerequisite for time-based firewall policy enforcement, log correlation, certificate validation, and secure communications throughout the vDefend stack.
-vDefend (DFW) and vDefend (GFW) support time-based firewall policies that allow administrators to define rules that activate or deactivate based on configurable time windows. Network Time Protocol (NTP) service must be running on each transport node when using time-based rule publishing in either the Distributed Firewall or the Gateway Firewall. Time windows for both can be configured to use either Coordinated Universal Time (UTC) or the local time of the transport node. Gateway Firewall time windows support either a weekly or one-time frequency. When local time zones are used for DFW policies, the entire time window must fall within the same UTC calendar day. For Edge transport nodes, if the time zone is changed after the node is deployed, the Edge node must be reloaded or the data plane service restarted for the new time zone to take effect.
-Identity Firewall, which enforces access policies based on Active Directory user identity, has additional time synchronization requirements. When using Identity Firewall event log scraping to track user login events, NTP must be correctly configured across all participating devices. Administrators should schedule Active Directory full synchronization during off-peak or non-business hours, as a full sync can take considerable time.
-Security Services Platform (SSP), the management and orchestration layer for vDefend, requires accurate time synchronization for certificate validation, log correlation, and secure communications to function correctly. The SSP installer validates time synchronization as part of its deployment prerequisites and requires configuration of one or more NTP servers, which can be updated if they become unreachable. For bare metal deployments, the bare metal server should be configured to use the same NTP server as SSP to maintain consistent time synchronization across all components.
-Network Detection and Response (NDR) sensor appliances require NTP to be configured and synchronizing before they can successfully register with SSP. Administrators should verify NTP synchronization status using the get clock command on the NDR sensor CLI before initiating registration. The NDR sensor monitoring view within SSP displays the NTP servers configured for each sensor, providing visibility into time synchronization configuration across deployed sensors.
-SSP Segmentation Monitoring can monitor NTP infrastructure services on UDP/123, providing visibility into time synchronization infrastructure health alongside other monitored services. SSP Inventory tracks environment synchronization status and identifies environments that are timed out or out of sync, supporting troubleshooting of time-related connectivity issues.
-Accurate timestamps across all vDefend components are necessary for correlating security events across the Distributed Firewall, IDS/IPS, malware prevention, and NDR capabilities. When investigating a security incident, analysts rely on consistent timestamps to reconstruct the sequence of events across multiple enforcement points.</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) provides native time synchronization mechanisms within the Protection and Recovery Appliance. The appliance supports three configurable time synchronization modes: NTP, which enables direct synchronization against administrator-specified NTP server addresses; Host, which synchronizes with the underlying ESX host time via VMware Tools; and Disabled. In NTP mode, administrators configure the appliance to synchronize directly with the organization's authoritative time source, independent of the underlying VCF platform's host-level NTP configuration.
-PNR enforces clock alignment across its server components through the maximum-clock-skew setting, which defines the maximum allowed time difference between server clocks (default: 20 seconds). Time zone and time synchronization settings are editable through the appliance configuration interface when network time settings change.
-For VCF Automation environments, the Protection and Recovery Proxy also requires explicit NTP server configuration, specified as an IP address or FQDN. PNR deployment guidance recommends using a persistent synchronization agent such as network time protocol daemon (NTPD), W32Time, or VMware Tools time synchronization to maintain consistent time across recovery infrastructure and avoid conflicts in time management across systems.</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) integrates NTP synchronization as a core operational requirement across all of its managed components. DSM requires configuration of a Network Time Protocol (NTP) service with a reliable time source to synchronize the clocks of all deployed VMs. Administrators configure NTP servers through the System Settings interface in the DSM UI, and DSM mandates that the Provider Appliance and all managed database instances use the same NTP server. Both the Provider Appliance and database cluster nodes communicate with NTP servers over UDP on port 123.
-DSM enforces UTC as the standard time representation for maintenance policies and support bundle timestamps, reducing ambiguity in scheduled operations and log interpretation. DSM MySQL instances support configurable time zone settings, with UTC as the default value.
-DSM monitors synchronization health at two levels. When NTP synchronization fails on the Provider Appliance, DSM generates an NTP_SYNC_FAILED global alert; administrators can resolve this by verifying and correcting the NTP servers field in System Settings. DSM also generates an NTP_NOT_APPLIED alert when NTP settings from the system configuration do not apply to a database instance, indicating that the database time is not being refreshed or synchronized. Together, these alerts surface clock synchronization failures within DSM's scope and make them actionable rather than silent.
-DSM does not control clock synchronization for the broader infrastructure on which it runs, including ESX hosts, VMware vCenter, and network devices. Organizations must configure and maintain NTP synchronization for those layers independently through vCenter and ESX host configuration.</t>
-        </is>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) maintains synchronized clocks across its Controller and Service Engine components through a configurable NTP stack. Administrators specify NTP servers in the Controller system configuration via the ntp_configuration.ntp_servers setting, accessible through the Controller UI, API, or CLI. The Controller synchronizes its own clock against the configured NTP servers, and Avi Service Engines in turn synchronize their clocks with the Controller by default, or directly with an NTP server configured at the cloud level. In Avi for VCF deployments, public NTP servers are used by default, making explicit NTP configuration optional when public NTP access is available; in most enterprise environments, administrators should configure the organization's approved NTP servers explicitly.
-For VM-deployed Service Engines, NTP servers can also be configured directly at the Service Engine level via the ntp-servers setting, enabling them to synchronize independently with NTP infrastructure where needed. For bare metal (LSC) deployments, Service Engine time synchronization supports ntpd (Network Time Protocol daemon) and chronyd as NTP daemon implementations, selectable via the ntp_daemon setting. NTP traffic uses UDP port 123 on the management interface.
-Avi monitors time synchronization health continuously. Service Engines synchronize with configured NTP servers at startup and periodically monitor synchronization status. When synchronization fails, Avi raises an event until synchronization is restored, providing administrators with ongoing visibility into the time synchronization status of the load balancing infrastructure.
-One configuration requirement applies to VM deployments: when Avi Controller and Service Engine VMs run on VMware ESX hosts, ESX host time synchronization must be disabled for those VMs. Allowing both the hypervisor VMware Tools time sync mechanism and the in-guest NTP daemon to operate simultaneously causes clock conflicts. The Avi documentation requires that ESX time synchronization be disabled on all Avi Controller and Service Engine virtual machines so that NTP is the sole time authority for those VMs.
-In Avi for VCF deployments, NTP server addresses can be configured when deploying a vSphere Supervisor with the Avi Load Balancer, supporting consistent time synchronization across the VCF environment.
-Administrators responsible for this control should configure the ntp_configuration.ntp_servers field in Avi Controller system settings with the organization's approved NTP servers, verify that Service Engines are synchronized, and confirm that ESX time synchronization (VMware Tools) is disabled for the relevant VMs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.8</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>MON-02, MON-03.1, MON-08</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Protect audit information and audit logging tools from unauthorized access, modification, and deletion.</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
-VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
-VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
-NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
-VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
-VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
-VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
-Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
-For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
-VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend generates structured security event logs across its Distributed Firewall, Gateway Firewall, IDS/IPS, and Malware Prevention components, with several mechanisms that support protection of those logs from suppression or loss.
-The Security Services Platform audit log is enabled by default and cannot be disabled through configuration. All access events to the Security Services Platform, including access to the License Hub, are recorded in these audit logs, preventing log suppression at the platform level.
-The Distributed IDS/IPS can be configured to forward events directly to external syslog consumers via the ids_events_to_syslog setting; this forwarding is disabled by default and requires explicit configuration. When remote syslog is enabled on ESX hosts, IDS/IPS events are exported directly from those hosts to external receivers. vDefend components write log files to /var/log, with syslog messages conforming to RFC 5424 on vDefend appliances and RFC 3164 on ESX hosts. Gateway Firewall isolation rules log blocked traffic attempts to the unifiedsyslog.log file on Edge Nodes.
-Malware Prevention produces structured event logs in JSON format that include standard attributes (date, log level, module) along with detailed file analysis metadata: file hashes (SHA256, SHA1, and MD5), file type, file size, inspection timestamp, client and server VM identifiers, submission source, detection status, verdict, analysis status, malware classification, malware family, HTTP domain, HTTP method, and user agent. These records capture the full analysis lifecycle, including file intercepted, verdict cache hit, local static analysis submission, cloud dynamic analysis submission, verdict obtained, and policy enforced events. In 9.1, the Malware Prevention Service can be configured to forward logs to a remote logging server using TLS encryption with mutual certificate authentication (requiring server CA certificate, client CA certificate, client certificate, and client key), providing an off-appliance copy of event records with in-transit protection.
-Identity Firewall event log sources can be integrated with VCF Log Management for centralized log collection and monitoring, providing an additional path to off-appliance log preservation.
-Protection of forwarded or archived logs from unauthorized access and modification at rest is outside vDefend's scope and depends on the receiving log management or SIEM platform's controls.</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) generates security-relevant event logs and supports forwarding them to centralized log collection and SIEM platforms through multiple native mechanisms.
-The Protection and Recovery Appliance provides built-in syslog forwarding to remote syslog servers. The forwarding configuration supports a selectable transport protocol and a configurable destination port (default 514). PNR includes a test message capability to verify that a remote syslog server is receiving messages before relying on it operationally. REST API endpoints are available for managing syslog configuration, including endpoints to list all configured syslog servers, update syslog server settings, and send test messages programmatically.
-PNR's event subsystem integrates with VMware vCenter, registering protection and recovery-specific events in the vCenter event infrastructure. Each event type has a corresponding alarm that PNR can trigger when the event occurs, enabling automated notification and downstream forwarding through vCenter's event pipeline to external SIEM platforms. PNR logs security-relevant events including login activity with timestamps, user identity, session keys, and locale information; authorization error messages with timestamps and component identification; and protection group configuration changes. The SrmDpxAgentUser role enables the DPX agent service to log events directly to vCenter Event Manager.
-The Clean Room Orchestrator component supports native event forwarding to VCF Log Management (version 9.0 or later), Microsoft Sentinel, and Splunk Cloud. Integration with Microsoft Sentinel uses Data Collection Rules (DCR) and Data Collection Endpoints (DCE) within an Azure Log Analytics Workspace, with DCE and Log Analytics Workspace required in the same Azure subscription and resource group. Splunk Cloud integration is configured using a Splunk URL and authentication token. Clean Room Orchestrator logs events for protection group creation and deletion, replication tasks, and snapshot operations. Event records include timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type.
-vSphere Replication, as a PNR component, maintains audit logs at /opt/vmware/support/logs/hms/hms-audit.log and broker logs at /opt/vmware/support/logs/hbr on the Appliance and at /var/run/log on VMware ESX hosts. vSphere Replication generates typed audit events for host and virtual machine replication configuration and unconfiguration changes, using structured event type identifiers.</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) produces structured audit logs that record platform-level and gateway-level operations, and provides several mechanisms that contribute to protecting those logs from unauthorized access and loss.
-At the platform level, DSM maintains gateway audit log files on the Provider VM at /var/log/tdm/provider/audit/, with individual files named using a timestamp format (gateway-audit-timestamp.log). Local retention covers the last five days of log files; once files are successfully uploaded to a configured S3 repository, DSM removes them from the local filesystem after five days. Each log entry captures structured fields including Component, Event Type, Event Details, Event Time (UTC), Status, and Source. The Source field records the email identifier of the user who initiated the operation, or "System" for events initiated by DSM without user intervention. The System Audit Events view, accessible through the Provider interface, is the designated location for reviewing non-database-related platform operations. Access to the Provider interface is scoped to the administrative role, restricting which users can read or interact with the system-level audit record.
-DSM supports offloading audit logs to external storage as the primary mechanism for durable protection. When a default S3 provider log repository is configured, DSM periodically archives gateway audit log files to an S3 subpath named "gateway audit." DSM does not delete audit logs stored in the S3 repository, which means the archived log record persists beyond the five-day local retention window. Externalizing audit logs to S3 separates the log record from the Provider VM that generated it, reducing the risk that a compromise or failure of the Provider VM affects the integrity or availability of the audit trail. Organizations apply bucket-level access controls and retention policies on the S3 repository to restrict who can read, modify, or delete the archived logs.
-DSM supports log forwarding, allowing DSM logs to be sent to a centralized log management or security information and event management (SIEM) platform via the System Logs capability. Forwarding logs to an external system provides a second copy of the audit record under access controls and integrity protections that are independent of the DSM platform itself.
-For SQL Server databases provisioned through DSM, the SQL Server data service uses server-level DDL triggers to restrict the file paths available for audit logs, limiting where audit log files can be written. DSM supports enabling audit logging for SQL Server with configurable levels of auditing for system logins and a configurable log retention period. DSM can automatically create a simple audit for login events based on the Login Auditing option selected during cluster creation. For custom audit requirements, the standard T-SQL CREATE AUDIT and CREATE AUDIT SPECIFICATION DDL statements are available.
-DSM can generate and download log bundles that aggregate relevant logs from database VMs, supporting diagnosis and out-of-band preservation of the operational log record.
-Audit events can be exported from the System Audit Events view in CSV or XLSX format using the ACTIONS menu. Exports include all events visible to the authenticated user regardless of pagination, supporting external archival and out-of-band preservation of the audit record.</t>
-        </is>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
-The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
-For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
-The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
-Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
-Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
-The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
-The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
-Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
-To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>AU.L2-3.3.9</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>MON-02, MON-08.2</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Limit management of audit logging functionality to a subset of privileged users.</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides centralized collection and management of security-related event logs across all platform components. Every major subsystem supports syslog forwarding to external log aggregation infrastructure, enabling integration with any SIEM or centralized logging platform that accepts standard syslog input. In addition, VCF Log Management provides a built-in log aggregation and analysis capability within the platform itself.
-VMware ESX hosts can be configured to send syslog messages to a remote log server using the esxcli system syslog config set command, specifying the target server IP address and port. ESX syslog messages conform to RFC 3164. Configurable syslog log levels allow administrators to tune the verbosity of forwarded events using esxcli system syslog commands. The syslog directory location on ESX hosts is controlled through the Syslog.global.logDir parameter. The Syslog.global.auditRecord.remote parameter separately controls whether security audit records are transmitted to the remote hosts configured in Syslog.global.logHost. ESX hosts maintain local logging with configurable retention and rotation policies, maintaining six log files that rotate at each power-cycle by default or at a configured file size. When the configured file limit is reached, the oldest file is deleted. The ESX Dump Collector and vSphere Syslog Collector can be configured to redirect ESX memory dumps and system logs to a network server for persistent log storage.
-VMware vCenter provides syslog forwarding through both its management API and direct configuration. The vCenter Management API exposes endpoints to set the syslog forwarding configuration (PUT), retrieve the current configuration (GET), and test the connection with remote syslog servers (POST). vCenter syslog forwarding supports TCP, UDP, TLS, and RELP protocols, giving administrators flexibility in how log data is transmitted to the collection infrastructure. The remote syslog target must be a server running rsyslog. vCenter event streaming to a remote syslog server is activated through the vpxd.event.syslog.enabled option in the vCenter Management Interface, and the Appliance Management Interface supports a maximum of three remote syslog destination hosts. vCenter retains performance data with configurable intervals and automatic purge policies.
-NSX Manager can export syslog to a remote server with configurable protocol, port, and log level. NSX audit logs, which record security-related events such as logon, logoff, and access to resources, are sent directly to the configured remote syslog server. NSX Manager audit logs also record failed login attempts with username and timestamp information, and log user account role changes for remote users authenticated through identity sources. Each audit log entry contains the timestamp, source, result, and a description of the event. API calls from all sources and users are audited, and each audit log associated with an API call includes a request ID parameter for traceability. This logging is always enabled and cannot be disabled. NSX also captures logical switch messages and other operational events in its audit log. On ESX hosts, NSX syslog data is stored in /var/log/nsx-syslog and can be forwarded alongside other host logs. NSX Manager syslog supports TLS protocol on port 6514 for encrypted log transmission.
-VCF Log Management is the centralized log collection platform within the VCF stack, gathering logs from vCenter, ESX hosts, NSX, VCF Operations, and VCF Operations for Networks. It can be configured to pull tasks, events, and alerts from vCenter instances and receive syslog feeds from ESX hosts through its Log Collections configuration. VCF Log Management provides an analysis interface where administrators can search and filter log events, create queries based on timestamp, text, source, and structured fields, and build dashboards for operational and security scenarios. Content packs for VCF components provide pre-built dashboards, alerts, and queries for common use cases, including a content pack for VCF Operations for Networks. Log-based alert definitions allow administrators to trigger notifications when specific log patterns are detected.
-VCF Operations supports centralized log collection and editing of log sources through Infrastructure Operations, under Configurations and Log Collection. VCF Operations Host System Properties allow configuration of a remote syslog host for centralized log collection. The audit log in VCF Operations is integrated with syslog, and the syslog collector can be configured to collect all audit logs. VCF Operations can also send user activity audit logs to an external syslog server. Audit logs capture administrative actions carried out through the API, the user interface, and the CLI, including regular CRUD operations and login/logout alerts. Note that SSH login logs are not captured in VCF Operations audit logs; SSH logs can be found in /var/log/auth.log. VCF Operations supports outbound integrations that distribute alerts and log data to external systems via email, SNMP traps, REST webhooks, log files, and Slack notification plugins.
-VCF Operations for Networks supports centralized log collection and editing of log sources through its own Infrastructure Operations configuration. Remote syslog servers must be configured to accept syslog traffic over UDP. All platform servers in a VCF Operations for Networks cluster use the same remote syslog server, though individual collectors can be pointed to different remote syslog servers. The audit log in VCF Operations for Networks is integrated with syslog.
-Additional VCF components also support centralized log forwarding. The Foundation Load Balancer supports forwarding logs to a syslog server via IP address configuration, with certificate-based secure communication for log forwarding. VCF Operations HCX supports configuring a remote syslog server that receives logs from both the HCX manager and appliance virtual machines, and appliances deployed after adding the external syslog server automatically forward log messages. VCF Identity Broker supports log collection as well.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) clusters running on vSphere Supervisor, provides its own log collection and forwarding capabilities that integrate with the broader platform logging infrastructure. Kubernetes audit logging within VKS generates a security-relevant, chronological record of cluster activity, documenting the sequence of API calls made by users, applications, and the control plane. This includes authentication events, authorization decisions, resource creation and modification, and user impersonation requests, with each impersonation request recorded individually in the audit log. Audit verbosity is governed by a Kubernetes audit policy that specifies which events to capture and at what level of detail; available backends for writing audit records include log files at /var/log/kubernetes/audit/ and external webhook endpoints. Kubernetes system component logs are configurable for verbosity, ranging from coarse-grained error reporting to fine-grained trace output covering HTTP access logs, pod state changes, and other operational detail. Fluent Bit is available as a standard package for VKS clusters and serves as the log forwarding agent. Once deployed as a DaemonSet on every node, Fluent Bit collects Kubernetes container logs, API audit logs, Linux daemon logs, and Linux authentication logs, then forwards them to a configured destination. Supported forwarding destinations include Syslog (port 514 for UDP, port 6514 for TCP), HTTP endpoints, Elasticsearch, Kafka, and Splunk. When integrated with VCF Log Management, Fluent Bit forwards over the CFAPI protocol; VCF Log Management accepts log forwarding connections on HTTPS port 9543 or HTTP port 9000 at the /api/v2/events endpoint. A logging management server must be deployed and accessible from the VKS cluster to receive, store, and analyze forwarded logs; the Consumption layer provides the collection and forwarding mechanisms rather than the SIEM itself. The Supervisor control plane also forwards its VM system logs to external syslog servers in RFC 5424 format over TCP, managed by Fluent Bit pods in the vmware-system-logging namespace whose status can be queried using kubectl commands.
-For workloads running as vSphere Pods within vSphere Namespaces, administrators configure the LogAgentConfiguration custom resource to stream syslog messages directly to a remote syslog server. Log messages from vSphere Pods include structured metadata fields covering namespace name, pod UID, pod name, container name, and ESX host name, enabling precise attribution and filtering at the receiving SIEM or log aggregation platform.
-VCF also aligns with global compliance logging requirements: auditable events are logged across the platform. This baseline of audit event generation feeds into the centralized collection mechanisms described above.</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>Meets</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend's Security Services Platform (SSP) restricts access to event log management through role-based access control. SSP defines five distinct roles with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. The Auditor role is scoped to viewing and tracking system activity without administrative access, keeping log review separate from configuration authority. Modifying role assignments requires Enterprise Admin privileges, so access to user management is restricted to authorized personnel.
-Role assignments can be applied to both local accounts and directory-managed remote users or user groups, allowing log access rights to be scoped to personnel with a specific business need. SSP audit logs are enabled by default and cannot be disabled, providing a persistent record of access and administrative activity.</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>VCF Protection and Recovery (PNR) generates security-relevant event logs and supports forwarding them to centralized log collection and SIEM platforms through multiple native mechanisms.
-The Protection and Recovery Appliance provides built-in syslog forwarding to remote syslog servers. The forwarding configuration supports a selectable transport protocol and a configurable destination port (default 514). PNR includes a test message capability to verify that a remote syslog server is receiving messages before relying on it operationally. REST API endpoints are available for managing syslog configuration, including endpoints to list all configured syslog servers, update syslog server settings, and send test messages programmatically.
-PNR's event subsystem integrates with VMware vCenter, registering protection and recovery-specific events in the vCenter event infrastructure. Each event type has a corresponding alarm that PNR can trigger when the event occurs, enabling automated notification and downstream forwarding through vCenter's event pipeline to external SIEM platforms. PNR logs security-relevant events including login activity with timestamps, user identity, session keys, and locale information; authorization error messages with timestamps and component identification; and protection group configuration changes. The SrmDpxAgentUser role enables the DPX agent service to log events directly to vCenter Event Manager.
-The Clean Room Orchestrator component supports native event forwarding to VCF Log Management (version 9.0 or later), Microsoft Sentinel, and Splunk Cloud. Integration with Microsoft Sentinel uses Data Collection Rules (DCR) and Data Collection Endpoints (DCE) within an Azure Log Analytics Workspace, with DCE and Log Analytics Workspace required in the same Azure subscription and resource group. Splunk Cloud integration is configured using a Splunk URL and authentication token. Clean Room Orchestrator logs events for protection group creation and deletion, replication tasks, and snapshot operations. Event records include timestamp, priority level, message content, component name, severity level, configuration ID, component ID, and event type.
-vSphere Replication, as a PNR component, maintains audit logs at /opt/vmware/support/logs/hms/hms-audit.log and broker logs at /opt/vmware/support/logs/hbr on the Appliance and at /var/run/log on VMware ESX hosts. vSphere Replication generates typed audit events for host and virtual machine replication configuration and unconfiguration changes, using structured event type identifiers.</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides role-based access control that scopes access to audit log viewing and management functions based on user role assignments. DSM defines two roles: the DSM Admin role, which grants super-user access to all data services and administrative functions including the System Audit Events view and log management settings; and the DSM User role, which restricts access to only the objects owned by that user within the assigned namespaces. Users in the DSM User role cannot access the System Audit Events view or log management configuration settings. The DSM console enforces these restrictions directly, limiting the views and actions available to those permitted for the logged-in user's role.
-The System Audit Events view is accessible through the Provider interface and is the only location in the DSM UI where non-database-related operations and tasks can be tracked. Because this view resides in the Provider interface, access to it is scoped to users assigned the DSM Admin role. Administrators assign roles to users either directly through local user creation in the DSM UI or through Directory Service Groups mapped to LDAP users via LDAPS integration, enabling group-based access control for organizations with directory service infrastructure.
-Gateway audit log files are stored on the Provider VM at /var/log/tdm/provider/audit/ with filenames in the format gateway-audit-timestamp.log. These logs track user read and write operations to DSM data services or infrastructure objects performed in the DSM UI or through the DSM Gateway Kubernetes interface, covering both UI-driven and API-driven management activity. Each log entry records the Source field as either a user identifier (Email ID) for user-initiated events or System for events initiated by DSM without user intervention. When a default S3 provider log repository is configured, DSM archives these files periodically to an S3 subpath named "gateway audit." The Log Forwarding setting in DSM's Settings area, configurable by Admins, controls whether logs are forwarded to external log management systems. Provider Log Storage settings require an Access Key credential for authentication to the object store. Audit events can be exported in CSV or XLSX format through the ACTIONS drop-down menu in the System Audit Events view, and exports include Component, Event Type, Event Details, Event Time (UTC), Status, and Source fields.
-For SQL Server data services, DSM provides additional log access controls. When creating a SQL Server cluster, DSM can automatically configure a Login Auditing option that creates a simple audit for login events. DSM also uses server-level DDL triggers to restrict the file paths available for audit logs, and the internal dsm_mgmt management login operates within a secure, isolated context to prevent administrative operations from being accessible to or exploitable by users with general database privileges.
-For this control to be fully met, organizations need to implement a formal process for identifying personnel with a specific business need to access event log management functions, document that authorization, and review it periodically. Access to the underlying Provider VM file system and the S3 storage bucket where logs are archived should also be controlled at the infrastructure level, as those paths are outside DSM's own access controls. DSM's RBAC provides the technical mechanism to scope log management access to Admin-role users, but the assignment of that role must be governed by an organizational policy tying role grants to documented business justification.</t>
-        </is>
-      </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides multiple mechanisms for forwarding security-relevant event logs to external centralized collection systems, including SIEM platforms, syslog aggregators, and log analytics tools.
-The Avi Controller exports logs through syslog forwarding, configured via the `configure systemconfiguration` CLI command or through the Controller Settings interface. The `syslog_servers` setting specifies one or more external syslog destinations. Syslog configuration is synchronized from the Controller to Service Engines, so data-plane events from Service Engines are also forwarded to the same targets.
-For audit-focused event streaming, Avi provides Syslog-Audit-Persistence, a built-in alert action template that streams audit and security events to external syslog servers. Events forwarded in this mode are encoded in SYSLOG_RFC5425_ENHANCED format, which includes event type, object name, tenant identifier, timestamp, and the identity of the user who performed the action. Syslog transport supports both TCP (with TLS) and UDP with a configurable destination port (default 514 per RFC 5426). This covers administrative configuration changes, object-level audit events, and security alert notifications.
-The Avi Controller and Service Engines log audit records for trusted channel initiation, termination, and failures to Events, Syslog, and Splunk, providing complete traceability of encrypted communication lifecycle events. The Avi DataScript engine supports logging of security events such as blocklisted IP access attempts using the `log()` function, making application-layer policy enforcement decisions available to the central log collector.
-Beyond the audit stream, Avi supports streaming client application logs to external syslog or logging servers for centralized monitoring and compliance audit trails. WAF Application Rule events are captured when a WAF rule fires, recording the type of attack detected and matched variable content, and these events can be forwarded to the same external collection targets. The Avi Controller also logs denial of service attack events with structured details including event ID, attack count, threshold values, and alert level.
-Avi supports integration with VCF Log Management. A VCF Log Management Log Forwarder can be configured as a syslog destination in the Avi Controller to receive events. The VCF Log Management agent, installed on an external syslog server, can parse JSON log data and forward it to the Log Forwarder. The recommended integration pattern routes logs through an intermediate proxy for JSON parsing, enabling key extraction and facilitating querying of client logs. Note that virtual service client logs should not be sent directly from the Service Engine to a Log Forwarder; the recommended path routes through an intermediate syslog server.
-The Avi Analytics Profile supports streaming of client logs to multiple external servers simultaneously, including IPv6 destinations. For assured retention of all logs, Avi documentation recommends streaming logs directly to an external server such as Splunk rather than relying on local storage. In air-gap environments, the remote syslog server must be located within the environment perimeter.
-The Avi Event Log system records all system activities, configuration changes, and operational events, including who made each change and when. Global event logs are accessible via the Operations &gt; All Events page in the Avi UI, covering all objects including deleted objects and sub-objects such as profiles and certificates. A REST API endpoint allows retrieval of event logs for a specific time period to support automated log collection workflows. Events can be filtered by type using parameters such as `event_id=CONFIG_CREATE` or `event_id=CONFIG_UPDATE` to identify configuration activity.
-Note that system component debug logs are not sent to remote syslog servers and are available only through the Tech Support generation mechanism. Similarly, virtual service logs are not pushed automatically via syslog notification; they must be pulled from an external logging system through the API or configured separately to be pushed from the Controller.
-To configure centralized log forwarding, navigate to Controller Settings and enter the target syslog server address in the Syslog configuration. For audit event streaming specifically, configure the Syslog-Audit-Persistence alert action template. For VCF Log Management integration, configure a Log Forwarder as a syslog destination in the Controller and optionally deploy the VCF Log Management agent on an intermediate syslog server for JSON parsing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>CA.L2-3.12.1</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>CPL-02, CPL-02.1, CPL-03, IAO-02</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Periodically assess the security controls in organizational systems to determine if the controls are effective in their application.</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>CA.L2-3.12.2</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>IAO-05</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Develop and implement plans of action designed to correct deficiencies and reduce or eliminate vulnerabilities in organizational systems.</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M45" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N45" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>CA.L2-3.12.3</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>CPL-02, THR-01, THR-03</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>Monitor security controls on an ongoing basis to ensure the continued effectiveness of the controls.</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend contributes to this control through its threat intelligence consumption and detection infrastructure. The IDS/IPS engine applies knowledge-based signatures that encode specific patterns corresponding to known attack types, detecting intrusions based on known malicious instruction sequences at distributed and gateway enforcement points within vDefend-protected segments. Threat metadata feeds for Network Detection and Response are distributed and can be refreshed from online sources, or downloaded and applied manually in air-gapped environments through NSX Manager or a workstation connected to the Security Services Platform.
-Network Detection and Response (NDR) correlates related detection events into campaigns and organizes them into a chronological timeline for security analyst review and triage. The Campaign view displays total detections and threats identified under Malicious Activity, and Campaign Correlation Rules provide structured visibility into how individual detections relate to broader attack patterns.
-Security Intelligence maps detected suspicious events to adversarial tactics and techniques from the MITRE ATT&amp;CK framework, recording the count of each tactic and technique observed during a selected time period. This TTP-level categorization supports the situational awareness the control describes for traffic traversing vDefend-protected segments. The threat visualization canvas aids rapid containment, identification of compromised assets, and adjustment of microsegmentation policies in response to detected activity. The blast radius analysis capability displays which communication paths a threat has affected, helping analysts determine whether an attack targets specific systems or represents a wider campaign.
-Security Intelligence also collects related IDS events across the same source and destination hosts to connect relevant events and build a fuller picture of an attack sequence. The vDefend Security Assessment generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows to support protection planning. Security teams investigate individual events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take mitigation actions.
-While vDefend delivers technical mechanisms for consuming threat intelligence feeds and mapping observed behavior to adversarial TTPs at the network layer, the broader organizational threat intelligence program, including sourcing intelligence from external providers, integrating with threat sharing platforms, and disseminating findings to other teams and tools, requires complementary processes and tooling outside the product.</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M46" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N46" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to situational awareness of evolving threats at the application delivery layer through its Live Security Threat Intelligence service, which delivers security threat feeds for multiple attack vectors in real time to protect applications from continuously changing threats. The Live Security Threat Intelligence service encompasses four components: an IP Reputation Service, an Application Rules Service, a WAF Signatures Service, and a Bot Management Service. The service is opt-in and must be explicitly enabled through Cloud Services configuration on the Avi Controller.
-The IP Reputation Service classifies incoming client IP addresses against a regularly updated database, covering threat categories including botnets, phishing, spam sources, and DoS/DDoS attack sources. The service performs real-time automatic IP Reputation updates and operates across globally distributed Avi Load Balancer Controller clusters. Administrators attach an IP Reputation database to virtual services, and enforcement actions such as blocking or rate-limiting are applied per classification result.
-The Application Rules Service provides rules specifically designed to block attacks on known application vulnerabilities, many of them mapped to CVEs, covering protection for over 5,000 applications including WordPress, Drupal, and Apache. Application Rules are automatically updated on the Avi Controller, and administrators can enable auto-sync to receive Application Rules Database updates automatically when new rules are published.
-The WAF Signatures Service allows Avi to receive notifications when new Core Rule Set (CRS) data is available and to automatically download updated WAF CRS rules. This keeps application-layer defenses aligned with current vulnerability intelligence without requiring manual administrator action.
-The Bot Management Service delivers a real-time feed for the User-Agent database, a core bot detection component. User Agent Database Sync can be enabled to receive continuous User-Agent updates for threat detection. Traffic is classified into categories including Bad Bot, Dangerous Bot, Good Bot, Human, Unknown, and User-defined Bot, and HTTP security policy rules apply enforcement actions including connection termination for dangerous bot classifications.
-When Avi detects security events such as SYN flood or DDoS conditions, its alerting and ControlScript framework supports automated compensating responses. Alert actions can invoke a ControlScript that adds offending client IP addresses to a blocklist IP group attached to a network security policy for rate shaping or blocking. ControlScripts receive alert parameters including attack count, event ID, and alert level, and can execute automated remediation in response to system events rather than requiring manual intervention. The DDoS Policy within the Network Security policy detects and mitigates a range of Layer 4 through Layer 7 network attacks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>CA.L2-3.12.4</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>IAO-03, IAO-03.2</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>Develop, document, and periodically update system security plans that describe system boundaries, system environments of operation, how security requirements are implemented, and the relationships with or connections to other systems.28</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L47" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M47" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N47" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>CA.L3-3.12.1e</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>VPM-07</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Penetration Testing</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M48" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>CM.L2-3.4.1</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>AST-01, AST-02, CFG-02</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Establish and maintain baseline configurations and inventories of organizational systems (including hardware, software, firmware, and documentation) throughout the respective system development life cycles.</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>VCF contributes to IT Asset Management programs through built-in inventory, discovery, and integration capabilities that provide the technical foundation for asset tracking and governance.
-VCF Operations groups discovered objects logically and provides detailed inventory lists across the environment, covering compute, storage, and networking resources. The inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group.
-The Service Discovery adapter automatically discovers applications, services, and their associated metrics (CPU, memory) running on managed infrastructure. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be exported in CSV format for use in external asset tracking systems.
-For organizations using ServiceNow, VCF provides two integration paths. The Management Pack for ServiceNow in VCF Operations populates the ServiceNow CMDB with discovered resources through the ServiceNow Table API and CMDB Meta API, providing CMDB visibility within VCF Operations. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation provides a structured data source that captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-VCF Automation adds governance through its project model, which controls who can deploy what resources and where those resources are deployed. Projects link users, catalog items, and IaaS resources together. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources.
-Tags within VCF Automation express capabilities and constraints that define deployments. Cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-The broader ITAM program responsibilities of establishing asset governance policies, defining ownership lifecycles, and maintaining organizational accountability remain outside VCF's scope.</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend's Security Services Platform (SSP) maintains an inventory of network-visible workloads organized into a hierarchical asset collection spanning regions, zones, environments, applications, and application tiers. The Publish Inventory Assets tab in SSP displays infrastructure asset details including asset names, asset types, IP addresses, and total VM counts for assets sourced from imported CSV files, discovered services, or published infrastructure assets, providing accurate, granular records of network-visible assets.
-Platform Inventory monitoring supports ongoing inventory accuracy through several mechanisms. Administrators can filter infrastructure assets by Name and Status, identifying assets that are timed out or out of sync. The inventory hierarchy view shows regions, zones, and VMs so administrators can verify correct definition. SSP Inventory displays assigned tags for each infrastructure asset, and environment rows can be expanded to view tag assignments and confirm hierarchy accuracy. The platform also collects and displays VM tags with their respective scopes, supporting classification and tracking. Published applications and their application types are verifiable in the Inventory &gt; Applications interface.
-SSP identifies and publishes application assets, classifying them as either critical or regular applications. Application Asset Collections represent groups of workloads delivering enterprise software functions. Security Intelligence within SSP displays application associations for compute entities, indicating the tiers within each application to which a given compute entity belongs. Administering compute entity classifications in Security Intelligence requires appropriate privileges, supporting access control over classification changes. Consistent naming conventions are recommended when preparing inventory data for import, and the Asset Prefix setting enables standardized naming during segmentation planning and monitoring.
-In disconnected mode, usage files include an asset_id field providing a unique asset identifier, supporting asset tracking in environments without continuous connectivity.
-vDefend's inventory scope is limited to network-visible workloads and does not replace enterprise-wide TAASD inventory tools, authorized software catalogs with business justification records, or data asset registries required for full AST-02 compliance.</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -5249,16 +5226,22 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several technical capabilities that support the separation of development, testing, and operational environments, though the organizational policies and governance processes that define environment boundaries and enforce segregation must be established independently.
-VCF workload domains provide infrastructure-level separation, allowing administrators to deploy distinct domains for development, testing, and production workloads with independent compute, storage, and networking configurations. Each workload domain operates with its own resource boundaries and management policies, and configuration settings appropriate for one environment tier may differ from those used in another. VCF documentation explicitly notes that configuration appropriate for development environments may not be suitable for production environments within the same deployment.
-VCF Operations includes an environment classification feature that allows administrators to tag Business Application environments as Development, Production, Staging, Test, or DR. This classification enables differentiated monitoring and management across environment tiers. Administrators can configure custom groups with distinct alert policies and capacity calculations for production environments versus testing environments, allowing each tier to operate under monitoring rules appropriate to its purpose. The VM Performance and VM Contention dashboards note that development environments can tolerate a small amount of contention in CPU and memory, while production environments should not, reinforcing the need for distinct operational treatment per environment.
-VCF Automation provides organizational and project-level isolation boundaries that map naturally to environment separation. Each organization in VCF Automation operates in an isolated environment with dedicated network setup and network isolation, where users can access only allocated services and resources. Within an organization, projects create additional isolation boundaries between teams, and namespace-level isolation adds a further layer of separation. Security groups and vDefend firewall rules support network isolation between project environments. When stronger isolation is required between environment tiers, multiple projects or organizations can be used; when isolation requirements are lower, fewer projects simplify the operating model. These constructs give administrators the building blocks to enforce separation between development, testing, and production workloads.
-NSX Projects enable isolation of networking and security configurations for multiple departments or organizational units within a single NSX deployment, allowing network-level separation between environment tiers. NSX multi-tenancy isolates security and networking objects across tenants, supporting the use of separate tenant configurations for development, testing, and production environments.
-vSphere provides workload isolation at multiple levels. Each VM runs as an isolated system protected from interference by other VMs or workloads. Resource pools isolate virtual machine performance from other users of the same pool. Namespaces provide additional isolation for containerized workloads, and administrators can assign different port groups as the network for each namespace, providing layer 2 isolation between namespaces. Cross-namespace communication is blocked unless explicitly permitted. vSphere Auto Deploy requires secure network separation between the production network and the management or deployment networks, making this separation a prerequisite for stateless or stateful ESX host provisioning workflows.
-The VCF CLI supports context-based environment switching, enabling administrators to move between local development, staging, and production clusters without requiring constant configuration updates. This helps maintain clear boundaries between environments during day-to-day operations and reduces the risk of accidental changes to production systems.
-VCF also supports a test-before-production discipline across several components. VCF Operations allows test runs before final deployment to verify that management packs collect correct data and accurately represent the target system. The documentation recommends testing newly created configuration files for the Management Pack for Aggregator with a test instance before applying them to production systems. For VM-based workloads on vSphere Supervisors, administrators are directed to create production images with the latest patches and required security settings that follow corporate security policies, establishing a controlled promotion path from development to production. Administrators can also configure more restrictive VIB acceptance levels for ESX hosts in production than for hosts in testing environments, limiting which software packages can be installed on production infrastructure.
-vSphere administrators set guardrails for the policy and governance of VMs, delivering VM resources such as VM classes and VM templates to DevOps engineers. This separation of administrative and consumer roles restricts who can modify production infrastructure versus who can consume resources in development or testing namespaces.
-Defining which environments are designated as development, testing, or production, establishing access policies for each, and managing the lifecycle of changes across those environments requires organizational processes beyond what VCF provides. VCF supplies the isolation mechanisms and classification tools; the organization must define the policies that govern how those mechanisms are used.</t>
+          <t>VCF provides layered configuration restriction mechanisms across its component products that control which users can make changes and what types of changes they are permitted to perform.
+At the infrastructure layer, VMware vCenter uses the AuthorizationManager to control access to server objects based on permissions associated with each object. This privilege-based model restricts access to specific operations, and privileges are static within a given product version, providing a stable and predictable authorization framework. vCenter includes predefined roles such as the Read-Only role, which includes all non-mutable privileges and allows users to read data or properties and call query methods without being able to make changes to the system. The No Access role provides a stricter option, preventing users from viewing or changing an assigned object in any way. Administrators assign roles and permissions at the object level, so users can be granted change access only to the specific resources they are responsible for. Cryptographic operations in vSphere can be restricted through custom roles that grant only specific privileges. The No Cryptography Administrator system role supports all Administrator privileges except Cryptographic Operations privileges, and administrators can clone this role to create custom roles that allow a group of users to encrypt virtual machines but not decrypt them, or vice versa. vSphere Host Profiles provide an additional enforcement layer at the VMware ESX host level, capturing an approved host configuration as a reference and automatically identifying hosts that deviate from it.
+VCF Automation enforces change restrictions through a layered rights and roles model. Only a System Administrator can modify the rights in a predefined role, and the System Administrator role includes all rights in the system. System Administrators can unpublish rights and global roles from individual organizations, edit or delete predefined global roles, and create and publish other global roles. The platform supports cloning rights bundles to create custom access control configurations with specific rights assignments. When cloning a rights bundle, administrators can enable the Modify Selected Rights toggle to select or deselect specific rights for the cloned role, and the new set of rights is applied to all organizations to which the bundle is published. When a runtime defined entity type is created, a rights bundle is generated for the type with five type-specific rights: View, Edit, Full Control, Administrator View, and Administrator Full Control, each assignable to specific user roles. Entity type access control allows administrators to grant access to an entity type only to specific users and organizations, and different access restrictions can be set on different versions of an entity type. System administrators with the Manage General ACL right can create, modify, and remove specific access control lists through the accessControls API, and organization users can use only those rights from their roles that are published to their organizations. For day 2 operations, administrators define permitted action lists so that users cannot initiate destructive or costly changes. Day 2 action policies can be filtered to apply only to deployments created by specific users, providing granular control over who can modify what. Administrators can create policies with hard enforcement that cannot be overridden by less-privileged users, and deployment limit policies support hard enforcement mode to apply mandatory resource usage restrictions. A restrictive security policy created at the organization level by an administrator cannot be overwritten by a less restrictive policy at the project level, enforcing a top-down restriction model.
+VCF Operations enforces configuration restrictions through role-based access control. The Roles tab under Infrastructure Operations allows administrators to select or deselect specific permissions when adding or editing a role. Access group permissions define what actions each group can perform, such as adding, editing, or deleting dashboards, or viewing, configuring, or managing objects. The Policy Workspace restricts who can modify settings in existing policies, and policy creation or modification requires adequate permissions. For global settings such as Reclamation Settings, the Manage Global Settings permission grants modification access, while deselecting it grants read-only access. The administrators role should be assigned only to specific users who must access objects and perform actions in the entire environment. VCF Operations can also enforce host security configuration hardening rules through workflows such as Apply Host Security Configuration Rules and Configure Host Security Config Data, which allow selective enforcement of specific hardening rules through configurable enforcement options.
+For container workloads, vDefend (a separate product that provides security services in VCF) supports a policy lock feature for security policies in Antrea Kubernetes clusters, which restricts multiple users from making concurrent changes to a policy. At the VMware Kubernetes Service layer, a restrictive security policy created by an organization administrator at the organization level cannot be overwritten by a less restrictive policy at the project level, enforcing a top-down restriction model for configuration changes.
+The Consumption layer of the VCF platform, which includes vSphere Supervisor, VMware Kubernetes Service (VKS), and vSphere Namespaces, provides Kubernetes-native access restriction mechanisms that govern configuration changes to cluster resources and workloads. Each vSphere Namespace carries a Permissions component that governs user and service account access through role-based access control, and the Namespaces.Owner.ModifyPermissions vCenter privilege controls who can define or update those permission rules on a given namespace entity; changing the content library on a Supervisor is permitted only at the Supervisor level, preventing tenant-level modifications. The Kubernetes RBAC API restricts users from escalating privileges by editing Roles or RoleBindings, with enforcement applied at the API server level regardless of which authorizer is active. RBAC Roles and ClusterRoles define the permitted operations on each resource type, while RoleBindings and ClusterRoleBindings bind those permissions to specific users, groups, or service accounts. Administrators following a least-privilege design reserve cluster-admin credentials for break-glass scenarios and operate under scoped kubeconfig files for routine work, and careful control over CustomResourceDefinition authorization is needed to avoid creating privilege escalation paths through workload creation or volume mounting. Attribute-Based Access Control (ABAC) provides an alternative authorization model in which policy rules can specify a readonly access mode, restricting individual users or groups to read-only operations on specified resources. The Kubernetes authorization configuration file approach also supports explicit Deny rules, enabling fine-grained control over authorization chains so that specific requests can be rejected regardless of other authorizers in the chain.
+Admission controllers add a second enforcement layer applied at the moment a change request reaches the API server. The OwnerReferencesPermissionEnforcement admission controller restricts modification of object ownership metadata so that only users with the appropriate delete or update permission on the referenced object can alter it. ValidatingAdmissionPolicy is the recommended mechanism for preventing specific resource changes, such as protecting platform namespaces from modification; it uses Common Expression Language (CEL)-based rules to reject non-conforming resource configurations without requiring a webhook server, and cluster administrators can also use it to restrict deletion or update of ResourceQuota objects. Access to edit mutating webhook configuration resources is separately restricted to prevent privilege escalation through that path. VKS cluster management custom policies can be created in Dry Run mode to test their impact before enforcement is enabled, allowing administrators to validate change restrictions before they take effect.
+Pod Security Admission (PSA), which replaced the earlier Pod Security Policy mechanism in VKS 1.25 and later, restricts what configurations workloads may use at the namespace level. PSA enforces one of three Pod Security Standards: privileged (unrestricted), baseline (blocking known privilege escalation paths), or restricted (heavily restricted, following pod hardening best practices). The podSecurityStandard variable supports enforce, audit, warn, and deactivated modes with configurable profile versions and namespace exemptions, and administrators can stage adoption by setting audit and warn to the restricted profile while keeping enforce at baseline. VKS ships with a default vmware-system-restricted Pod Security Policy that defines a restricted set of workload permissions for authenticated users, and cluster administrators can create additional custom pod security policies and bind them to specific users or groups. Pod Security Standards also restrict seccomp profiles and prohibit explicit Unconfined configuration.
+At the workload runtime level, VKS supports kernel-level controls that restrict what a running workload can do even after it has been deployed by an authorized user. Kubernetes supports SELinux for policy-based mandatory access control on Linux nodes, AppArmor profiles that can run in enforcing mode to block access to disallowed resources, and seccomp profiles that restrict the system calls available to container processes; default configurations for each provide baseline protections out of the box. For GitOps-based change workflows, the Argo CD Supervisor Service provides access restriction through policy rules that define permissions for accounts and role assignments, allowing fine-grained control over who can trigger and approve changes to cluster state; access controls are enforced across all Argo CD components and secrets are managed outside of Git. The immutable infrastructure pattern offers a complementary approach: Kubernetes deployments can be managed in a GitOps model where an automated reconciliation loop overwrites unauthorized out-of-band changes, or where the admission control chain rejects changes that do not match the declared state.
+Defining the change-management policy (which configuration changes require approval, which require segregation of duties, what constitutes an unauthorized change in the organization's context) and operating the approval workflow remain organizational responsibilities. VCF supplies the technical enforcement layer; the policy and workflow that determine when restrictions apply sit above the platform.
+VMware Private AI Services (PAIS) provides several application-layer access restriction mechanisms that help limit unauthorized changes to AI infrastructure components.
+Access to PAIS is governed by OIDC-based group membership. The authorizedGroups setting in the PAIS configuration restricts service access to members of specified identity provider groups, and group identification can be tuned through a configurable groups claim name on the OIDC provider. Issuing refresh tokens for the PAIS UI may require the offline_access scope depending on OIDC server support. Identity and access management for PAIS is configured in coordination with an OIDC provider administrator.
+Catalog items for Deep Learning VM and GPU-accelerated VMware Kubernetes Service (VKS) cluster deployments are distributed through VCF Automation with project-based permissions, so only members of selected projects can request or modify those workloads. Custom forms in PAIS blueprints can be modified to control user inputs at request time, narrowing what a catalog consumer can change. SupervisorNamespaceClass specifications for storageClasses and vmClasses control which VM classes and storage classes are available to users, with wildcard and override behavior that lets administrators scope access explicitly. GPU-capable VM classes with GPU reservations restrict GPU usage to a particular namespace and can be confined to a single zone or supervisor for isolation. VCF Automation organization resource limits can be changed only by enabling an Override toggle and entering new values, gating that change to administrators.
+The Model Gallery uses Harbor project access controls to restrict access to sensitive data used to train and tune models, and read-write permissions to a Harbor project are required to store models in PAIS. Harbor Registry replication rules support administrator-configured filters, target namespace, and trigger mode, including a manual trigger mode that requires explicit execution of replications. Deep Learning VMs can be configured with cloud-init files that set file permissions, including executable permissions (0755) for application scripts and restricted permissions (0600) for network configuration files, limiting modification of initialization and workload execution code. The PAIS DSM database can be configured for sharing between developers and catalog users through a toggle that creates a new DSM database catalog item, keeping that change behind a defined configuration action.
+Disconnected PAIS environments using local registries for GPU Operator components are required to provide a registry URL, user name, and password, restricting which sources can supply container images for AI infrastructure components.
+Full satisfaction of this control requires combining PAIS application-layer access controls with the platform-level RBAC provided by VCF, organizational change management processes, and approval workflows that operate outside PAIS itself.</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -5268,12 +5251,12 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides network-level enforcement mechanisms that support separating development, testing, and operational environments, reducing the risk of unauthorized access or cross-environment changes.
-The Distributed Firewall enables environment isolation through microsegmentation, dividing the data center into broader security zones such as production, development, testing, and PCI environments. Distributed Firewall rules are enforced at the vNIC level, so environment boundaries are maintained even when workloads from different environments share the same physical hosts or network segments. The Gateway Firewall in vDefend can enforce isolation between projects by denying all inter-project communication except for essential infrastructure protocols such as DHCP, DNS, NTP, and ICMP, while permitting internal team communication within isolated development virtual private clouds.
-Security Services Platform provides purpose-built tools for defining environment hierarchies and configuring segmentation policies. Administrators define environments by specifying which virtual machines, IP addresses, distributed virtual port groups, and network segments belong to each environment using CSV files, which Security Intelligence uses to create groups and apply appropriate tags. When implementing environment pair controls, the recommended approach is to apply a broad block policy between sensitive pairs such as Testing and Production as an initial step, then identify all inter-environment flows and add specific policies before enforcing a strict block. Security Intelligence administrators can monitor traffic leakage between environments, establish permitted exceptions, and apply lockdown protection rules to control inter-environment traffic.
-The Security Segmentation Score provides a quantitative view of segmentation coverage. The Environment Protection component evaluates whether workloads are protected by environment-specific segmentation policies such as Dev, Prod, and Test, contributing five points to the overall score. The security segmentation score breakdown report details total environments and pairs, protection rule actions, and highlights environment pairs that lack inter-environment policies. The Environments monitoring window shows the total number of inter-environment pairs and how many are without inter-environment policies. Segmentation Planning supports the design phase by allowing administrators to publish environments together with related applications to maintain proper correlation between them. Security Services Platform Inventory monitoring allows administrators to view the infrastructure hierarchy, including regions, zones, and virtual machines, to verify that the environment hierarchy is correctly defined before enforcement begins.
-For Virtual Desktop Infrastructure deployments, Security Services Platform recommends isolating VDI servers from server-based traffic patterns and preventing separate VDI environments from communicating with one another.
-Defining which workloads belong to which environment, determining which environment pairs may communicate, and managing the lifecycle of configuration changes across environments require organizational processes and decisions that vDefend does not govern. vDefend enforces the network boundaries once those decisions are made.</t>
+          <t>VMware vDefend enforces configuration restrictions across its firewall, IDS/IPS, and TLS Inspection policy management lifecycle, restricting the ability of users to modify security policies outside approved workflows. Role-based access control governs who can create, modify, and publish security policies, while policy locking mechanisms block concurrent edits and restrict modification of locked configurations.
+vDefend (DFW) supports a draft-based configuration management workflow where security policies are authored in draft form before being published to the enforcement plane. Drafts can be locked to prevent multiple users from simultaneously opening and editing a manual draft, and a comment is required when locking. Auto drafts and manual drafts can also be cloned and saved with the option to lock the configuration with a required comment. Manual drafts can be reverted to the original configuration, providing a rollback path when a draft change needs to be undone. Policy section locking is available from the Global Manager and restricts editing to specific portions of the firewall rule base while leaving other sections available for authorized changes. When a security policy is locked, no other user can modify it until the lock is released.
+Gateway Firewall supports the same section-level locking model, with a required comment when locking a section. Gateway Firewall locking is off by default and must be explicitly enabled through Gateway Specific Settings. Organization Admin ownership of firewall rules prevents project members from accessing rule modifications.
+vDefend IDS/IPS policies support section-level locking for both Distributed and Gateway deployments. Distributed IDS/IPS provides a Locked option that prevents multiple users from editing the same policy sections, with a required comment when locking. Gateway Firewall IDS/IPS policy sections support the same locking model with the same comment requirement.
+TLS Inspection policies on the Gateway Firewall support an Advanced Configuration option to lock policies and prevent concurrent changes by multiple users.
+Security Services Platform (SSP) enforces an additional restriction: initial security policies cannot be modified through the user interface after they have been published. This immutability requires administrators to follow a controlled change process rather than directly editing production policies. SSP role-based access control defines five distinct roles with differentiated permissions across Rule Analysis and other platform operations: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. The Auditor role grants read-only access to view information and track activity without the ability to make changes. Access to User Management and role assignment modifications requires Admin privileges.</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -5319,11 +5302,12 @@
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides mechanisms at the application delivery layer to support separation between development, testing, and operational environments. The primary isolation mechanism is Avi's multi-tenant architecture: a single Avi Controller cluster can host each environment in a dedicated tenant with RBAC-enforced access boundaries, or organizations can deploy separate Controller clusters per environment. Controller cluster topology supports this separation; each Controller cluster can be configured as a one-node cluster for development and testing, or a three-node cluster for production, giving organizations a clear infrastructure-level distinction between environment tiers.
-Within a single-cluster deployment, Avi's tenant model provides administrative isolation, scoping visibility and access to objects within tenant boundaries. Service Engine Groups provide data-plane isolation: virtual services for test and production environments should be deployed on different Service Engine Groups, so application traffic from test workloads is handled by different data-plane VMs than production traffic, reducing the risk of cross-environment data flows. An administrator can deploy virtual services for the same application in both test and production environments on different Service Engine Groups within the same tenant, or across separate tenants for stronger isolation.
-In 9.1, the Avi for VCF integration adds dedicated environment isolation constructs. Service Engine Group allocation within VCF Automation blueprints for Layer 4 and Layer 7 virtual services provides operational isolation, keeping each project within its designated boundaries. Namespace allocation in the Avi Controller similarly scopes each project's resources. In Organization-Managed Mode, organization administrators manage their own Service Engine Group configurations and infrastructure settings, reinforcing the organizational boundary between environment owners. VCF Automation integration supports infrastructure-as-code workflows, which can be used to apply consistent environment configurations across development, testing, and production tiers.
-Service Engine deployments using dedicated management mode provide network isolation between data and management traffic, separating the management plane from application traffic paths.
-Organizations should define which Avi tenants map to which environments, establish RBAC policies that restrict personnel from operating across environment boundaries, and configure distinct Service Engine Groups for each tier. The Avi Controller's configuration audit log supports review of whether environment boundaries have been respected during configuration changes.</t>
+          <t>VMware Avi Load Balancer provides role-based access control (RBAC) on the Avi Controller that restricts which administrators can modify specific configuration objects. Each user is assigned a role that defines their permission level (write, read, or no access) for each category of Avi resource. The Controller also supports a No Access privilege level that prevents users from accessing, reading, or listing resources entirely. The admin account on the Avi Controller and Avi Service Engine cannot be modified, protecting the built-in administrative identity.
+Beyond standard RBAC, Extended Granular RBAC allows write access to be scoped at the sub-resource level within individual objects. Administrators can apply flags when defining a role to restrict update rights to named sub-resources only, or to permit modification of all fields except those explicitly excluded. This allows, for example, a user to enable or disable a virtual service without being able to modify any other aspect of that virtual service's configuration, or to add and remove pool servers without access to other pool settings. Granular permissions extend to cloud objects through label-based permissions and marker-based access control, allowing access to be scoped to specific objects rather than entire object types. Certain permissions classified under Operations and Administration are not supported for label-based RBAC and remain enforced at the role level.
+Auth Mapping Profiles bind external identity group memberships to specific roles within specific tenants, enabling tenant isolation. Auth Mapping rules can be configured to deny all roles and tenants to specific users at login. User accounts include a superuser flag that grants access to all tenants with every role; disabling this flag restricts a user to their explicitly assigned roles and tenants.
+Network-level access to the Avi Controller management interface can be restricted to specific IP addresses, address ranges, subnets, or predefined IP groups through the Client Management Access settings. Trusted host profiles provide an additional layer of host-based access control by restricting which hosts are permitted to reach the Controller. Custom user account security profiles support configurable thresholds for login failures, account lockout duration, password history, concurrent sessions, and credential timeouts. Configuration warnings can be enabled to notify users when supported configuration changes are made.
+In Avi for VCF deployments, the Avi Cloud Console enforces role-based access through two levels: Full Access (User Administrator or Product Administrator role) and Read-Only (Site Access role), with differentiated permissions for license visibility, management, and administration.
+Administrators should assign roles aligned with the principle of least privilege based on job function and review role assignments as part of change management procedures. Avi's RBAC mechanisms support these practices but do not substitute for the organizational governance process of deciding which personnel are authorized to modify which configuration elements.</t>
         </is>
       </c>
     </row>
@@ -5451,22 +5435,17 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in mechanisms for periodically reviewing system configurations to identify unnecessary or non-secure functions, ports, protocols, and services. These capabilities span configuration drift detection, compliance benchmarking, software image validation, dedicated review dashboards, and scheduled reporting.
-VCF Operations includes a Configuration Drift feature that provides scheduled drift detection for VMware vCenter instances and vSphere clusters. Configuration templates define the desired state for each setting, and the Detect Drift function compares current values against template values, displaying any deviations in a drift dashboard. Drift detection can be scheduled to run automatically, and drift status reports can be downloaded for review. Configuration templates can also be integrated with a source control repository to support versioning, auditing, and change control of the desired configuration state.
-For structured configuration review workflows, VCF Operations provides a suite of eight Configuration Review dashboards that form an integrated optimization flow. These dashboards are designed as a set and should be used together when conducting configuration review cycles. They include the Consumer Optimize it?, Consumer Correct it?, Consumer Update it?, Provider Optimize it?, and Provider Update it? dashboards, among others. Each dashboard presents configuration data in a list view format that can be reviewed independently, allowing administrators to systematically work through configuration items that require attention. The dashboards surface configuration elements that deviate from expected baselines, allowing reviewers to identify settings that need correction or optimization. The Network Configuration dashboard specifically targets network-related configuration review, displaying network configurations that need attention and including five bar charts focused on critical security settings. This provides a consolidated view of network security posture, making it straightforward to identify non-secure configurations across the environment's networking layer.
-For security-specific configuration review, VCF Operations continuously monitors infrastructure against compliance benchmarks. The VMware SDDC Benchmark monitors objects for violations of the vSphere Security Configuration Guide, vSAN Security Configuration Guide, and NSX Security Configuration Guide. These benchmarks include both automated compliance assessments and manual checks based on industry-standard best practices. Non-compliant objects and their associated violations are identified automatically, giving administrators a clear view of where configurations have deviated from security baselines.
-At the host level, VCF Operations provides the Configure Host Security Config Data workflow, which allows administrators to selectively enforce host security hardening rules by configuring individual configuration elements under Enforce Options. This supports both the review of current host configurations against hardening standards and the remediation of non-compliant settings. VCF Operations also collects VMware ESX security properties including service running status, firewall rulesets, service policies, and TLS disabled protocols when the vSphere Hardening Guide policy is applied.
-VCF provides granular control over port group security policies at the virtual networking layer. Security policies on port groups can be reviewed and modified to control behaviors such as promiscuous mode, which governs whether virtual machines can monitor traffic on the port group. Reviewing and restricting these settings is part of identifying and disabling unnecessary or non-secure network functions.
-vSphere Lifecycle Manager (vLCM) adds another layer of periodic review by defining a desired software image for each cluster and performing compliance checks to determine whether hosts conform to that image. When the current state of a host differs from the desired specification, vLCM can apply remediation to bring the host back into compliance. For baseline-based deployments, the compliance check schedule can be configured with a specific frequency and starting point, allowing organizations to align automated checks with their periodic review cadence. vSphere Host Profiles provide a complementary mechanism by capturing a reference host's complete desired configuration state and verifying that other ESX hosts conform to it, covering the full range of host configuration settings beyond software image compliance.
-For Kubernetes workloads running on VMware Kubernetes Service (VKS), the platform provides analogous mechanisms for periodic configuration review at the cluster and workload level. Kubernetes role-based access control configurations, including Roles, ClusterRoles, RoleBindings, ClusterRoleBindings, and ServiceAccounts, should be reviewed at defined intervals; Kubernetes documentation recommends access reviews at intervals no greater than 24 months, with guidance on what to examine during each review. Security Technical Implementation Guides for VKS components, including Supervisor and Kubernetes releases (VKrs), are available through Tanzu STIG Hardening and provide hardening benchmarks that serve as baselines for periodic configuration reviews. Administrators can compare current settings against the relevant STIG to identify configurations that deviate from hardening requirements, including enabled features or services that should be restricted.
-Pod Security Standards, configurable at the namespace level through the podSecurityStandard variable, support three enforcement modes that aid ongoing configuration visibility: audit mode records policy violations in the Kubernetes API server audit log without rejecting workloads, allowing administrators to observe which pods are running outside of hardened profiles between review cycles; warn mode issues warnings at admission time for non-compliant pods; and enforce mode blocks non-compliant pods outright. Each mode can be pinned to a specific Kubernetes minor version or set to track the latest, giving administrators explicit control over when stricter checks take effect across namespaces. Seccomp profiles, applied at the pod and container level via security contexts, restrict which Linux system calls workloads are permitted to make, reducing the kernel attack surface for running containers. The Security Profiles Operator can manage and distribute seccomp, AppArmor, and SELinux profiles at scale across clusters, supporting consistent configuration review and enforcement across large deployments. Harbor, available as a standard package for VKS clusters, provides vulnerability scanning of container images and policy-based access control for registries, with scan results informing periodic reviews of the software components running in clusters.
-VKS cluster management also provides out-of-the-box security policy templates, including baseline and restricted profiles, that mirror Pod Security Standards. These templates give administrators a defined policy baseline against which cluster configurations can be evaluated during periodic reviews, helping identify workloads or namespaces operating outside an expected security profile.
-To support periodic scheduling of configuration reviews, VCF Operations report generation can be configured with a periodicity of every two weeks or on monthly intervals. This allows organizations to establish a regular cadence for generating configuration review reports, which can then be used to drive remediation activities. Alert definitions within VCF Operations can be configured to monitor infrastructure for configuration changes or deviations. Custom alert policies can be created to govern how alert definitions are evaluated, including which virtual machines and related hosts to monitor. VCF Operations tracks whether the same alert has been triggered on an object in the past 30 days to help distinguish recurring problems from new issues. Combined with proactive monitoring capabilities that continuously track the state of the environment, VCF provides both scheduled and ongoing mechanisms for configuration oversight.
-VMware Private AI Services (PAIS) centralizes its configuration in the PAISConfiguration custom resource, a YAML-defined Kubernetes artifact that governs the configurable aspects of the platform. Operators have a single, versioned object that can be examined, patched with kubectl patch PAISConfiguration, or updated through the VCF Automation UI to reflect the intended state of the platform. This gives administrators a discrete configuration surface to review and adjust during periodic baseline checks.
-PAIS supports client TLS configuration with CA bundle references for OIDC provider and Harbor authentication through the clientTls.caBundleRefs field. Administrators can review the configured trust bundles and rotate them in step with the organization's certificate lifecycle. Harbor registries are the recommended image and model registry for PAIS deployments, with OCI-compliant registries from other vendors also supported, giving operators a defined artifact set to examine for unnecessary repositories or stale content.
-Observability is configured through the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, which activates Prometheus metrics collection with a configurable storage class and a metrics retention period that defaults to 14 days. LLM traces can be sent to an OpenTelemetry Collector through the same configuration surface. PAIS Controller metrics are exposed at a Prometheus endpoint on the pais-controller-manager service, and a Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for visualization in VCF Operations or Grafana. These surfaces give operators the data needed to detect anomalies, identify idle or underutilized GPU devices in passthrough mode, monitor vGPU licensing status, and flag pods with frequent container restarts during periodic reviews.
-Model Gallery supports validation and upload of ML models, including evaluation of a model's performance and safety against inference requests for malicious behavior before deployment. The Gallery assigns a unique digest to each revision when the same model is pushed multiple times, giving administrators a stable identifier to use when reviewing which model versions are present and active across organizations and environments.
-Periodic review of PAIS configurations depends on organizational processes to define review schedules, document configuration baselines, and act on findings. PAIS provides the configuration surfaces and observability tooling; the cadence and scope of review are organizational responsibilities the platform does not enforce on its own.</t>
+          <t>VCF provides layered mechanisms to restrict execution of unauthorized software across the hypervisor, virtual machine, container, and automation layers.
+At the host level, VMware ESX enforces UEFI Secure Boot, which verifies the digital signature of every component in the boot chain before execution. The vSphere Security Configuration Guide recommends enabling Secure Boot and Trusted Platform Module (TPM) as part of ESX host hardening. Hosts equipped with TPMs provide hardware-rooted attestation, and VMware vCenter monitors host attestation state to confirm that each host has booted into a known-good configuration. The vCenter trusted infrastructure API provides interfaces for retrieving TPM event logs, endorsement keys, and attestation data from host hardware. ESX also supports Intel Trusted Execution Technology (TXT) for hardware-based verification of the hypervisor launch environment. The hypervisor enforces acceptance levels for VIBs (vSphere Installation Bundles), restricting installation and execution of unsigned or untrusted software packages on hosts. ESX also supports the execInstalledOnly enforcement setting, which requires that all executables running on the host originate from installed VIBs, directly blocking execution of unsigned or ad hoc binaries outside the VIB-managed software baseline.
+vSphere Lifecycle Manager (vLCM) manages all hosts in a cluster collectively with a single image, and upon remediation, the image is installed on all hosts in the cluster. This desired-state model, combined with configuration profiles and drift detection, restricts unauthorized changes to the host software baseline. VCF Operations detects configuration drifts by comparing current vCenter values against configuration template values, notifying administrators of deviations from assigned baselines. Configuration drift detection can be scheduled for vCenter instances and vSphere clusters, and configuration templates can be integrated with source control for versioning and audit. VCF Operations compliance management detects violations, flags risk areas, and provides actionable remediation recommendations.
+Host security configuration hardening rules can be enforced through workflows such as Apply Host Security Configuration Rules, which apply security baselines that restrict host-level software execution and configuration changes. VCF's hardening guidance for vCenter covers securing the installation, configuring roles and permissions, securing access and authentication, and enabling auditing and logging. These hardening practices, aligned with industry-standard best practices and the Security Configuration Guide, provide a layered approach to restricting unauthorized software execution across the platform.
+For virtual machines, VCF supports UEFI Secure Boot at the guest level, allowing guest operating systems to verify the integrity of their own boot process. Virtual Trusted Platform Modules (vTPMs) extend hardware-rooted trust into virtual machines without requiring physical TPM hardware. The vTPM capability is integrated with VCF Automation for VM Apps, which requires the cryptographic operations direct access privilege in vCenter to support vTPM when deploying Windows 11 VMs. PowerCLI provides the VMware.VimAutomation.Security module for managing vTPMs programmatically. VCF Operations management pack PAK files are signed with a digital signature that indicates the original developer or publisher and provides authenticity verification. At the virtual machine level, the isolation.device.edit.disable setting, available through both vCenter and VCF Operations, restricts unauthorized modification of virtual machine devices, limiting the ability to attach or alter devices that could be used to introduce unauthorized software into a guest operating system. VCF Operations also provides a setting to disable automatic installation of VMware Tools (disable tools auto install), which restricts software from being installed on virtual machines without explicit administrator action. Virtual machines can also be configured with the restrict-user-commands setting to restrict users from running commands within the guest, providing a guest-level enforcement layer that complements the RBAC-based guest operations privilege restriction.
+For Kubernetes workloads running on VMware Kubernetes Service (VKS), the platform provides a layered set of enforcement mechanisms at the container, pod, and admission control layers. VKS cluster management image registry policies restrict the specific images that can be pulled from a registry for deployment in managed cluster namespaces, with a policy enforcement setting that defaults to Deny, fully enforcing the policy and blocking admission requests with violations; a Dry run mode is available for testing without enforcement. VKS ships with a vmware-system-restricted Pod Security Policy by default that does not permit privileged access to pod containers, blocks privilege escalation to root, and requires security controls across running workloads. The vmware-system-privileged policy, which permits unrestricted workload execution, requires explicit binding through a RoleBinding or ClusterRoleBinding and is accessible only to cluster administrators by default. Namespaces can be configured to operate under the Baseline or Restricted Pod Security Standard, which restricts unprivileged processes from loading kernel modules, providing an additional boundary against unauthorized code execution. VKS clusters apply the RuntimeDefault seccomp profile to pods by default, restricting the set of system calls available to containerized processes; custom seccomp profiles with SCMP_ACT_ERRNO deny-by-default semantics can be assigned to workloads requiring tighter restrictions. For Linux-based workloads, AppArmor profiles restrict program access to specific system resources by specifying a loaded profile in the container specification; AppArmor can operate in enforcing mode, which blocks access to disallowed resources, or complain mode for audit-only monitoring of violations. AppArmor is available on both Ubuntu and Photon OS VKS node images, restricting container capabilities, file system access, and network access in VMware-native node configurations. Linux Security Modules such as SELinux can be configured to deny the module_request permission to containers entirely, blocking the kernel from loading modules on behalf of containerized processes. Admission control through ValidatingAdmissionPolicy blocks or constrains deployment of workloads that do not satisfy defined criteria, including protecting platform namespaces from non-conforming resources. Content libraries in VKS support assigning a Security Policy at creation time, scoping which artifacts can be sourced from that library and, in internet-restricted environments, limiting deployable artifacts to administrator-approved sources. Running containers can be restricted to an immutable state through the readOnlyRootFilesystem security context field, limiting the ability of a running process to introduce new executable code at runtime. Security Technical Implementation Guides (STIGs) covering Supervisor and VKr system components are available through Tanzu STIG Hardening, providing validated hardening baselines for VKS cluster node software execution environments.
+PowerShell, which is the primary scripting and automation interface for VCF through PowerCLI, supports an execution policy feature that determines whether scripts are allowed to run and whether they must be digitally signed. The execution policy defaults to Restricted, the most secure setting, restricting unauthorized script execution in management contexts. Administrators can configure this policy to allow only signed scripts from trusted publishers.
+VCF Automation for VM Apps allows administrators to create a list of permitted day-2 actions that users can run on deployments. By defining an explicit allow list of operations, administrators restrict users from initiating actions outside the approved set, limiting the ability to deploy or execute unauthorized software through the automation platform.
+ESX Agent Manager provides privilege-based restrictions on operations performed against ESX agent virtual machines. By integrating solutions with ESX Agent Manager, administrators can limit operations such as powering off agent VMs to users who hold the EAM.Modify privilege, restricting unauthorized users from interfering with or substituting managed agent software.
+The vCenter authorization model enforces consistent role-based access control across the environment. Software components require authorization to perform operations on behalf of a user, and vSphere implements mechanisms to restrict access to virtual infrastructure components to valid, authenticated users.
+Across the full VCF platform, mechanisms exist at every layer to restrict execution of unauthorized software: Secure Boot and VIB acceptance levels at the host, VM-level attestation and device restriction at the guest, and Pod Security policies, seccomp syscall filtering, AppArmor and SELinux enforcement, admission control, and image registry policies at the Kubernetes workload layer. The combination of these natively available mechanisms, including defaults such as the vmware-system-restricted Pod Security Policy and the RuntimeDefault seccomp profile applied to VKS workloads, satisfies the control's requirement that mechanisms exist to configure systems against unauthorized software execution. Determining which software is authorized and selecting appropriate enforcement strictness levels for the organization's specific environment remains an organizational responsibility.</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -5476,12 +5455,12 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides several capabilities that support the periodic review of security configurations to identify unnecessary or non-secure functions, ports, protocols, and services within the network security domain.
-Security Intelligence, a capability within the Security Services Platform (SSP), continuously analyzes network traffic flows and generates policy recommendations based on observed communication patterns. Recommendation analysis jobs progress through status states including Waiting, Discovery in Progress, Ready to Publish, and Published. Administrators should review generated recommendations when the status reaches Ready to Publish before publishing them to enforcement. When the applied-to scope of a security policy changes, or when new effective members are added or removed from the originally selected entities, existing Security Intelligence recommendations should be reviewed and rerun to reflect the updated environment. This recommendation engine identifies rules that may be overly permissive or unnecessary based on actual traffic patterns, directly supporting the periodic review process described in this control.
-The vDefend documentation recommends that administrators periodically audit and remove unused or outdated Distributed Firewall policies and rules, using flow inactivity data and Security Intelligence recommendations to identify stale rules that can be safely removed. Policy Recommendations can be reviewed through the Monitoring Applications interface before being published, and the Review and Rerun interface allows administrators to revisit recommendations when environment changes are detected.
-The Security Overview Dashboard provides a Configuration tab that summarizes the current state of all security policies, including counts and links for Firewall Policies, IDS/IPS Policies, Malware Prevention Policies, and TLS Inspection Policies. This centralized view gives administrators a starting point for periodic configuration reviews across all vDefend policy types.
-The Security Intelligence Flow Insights Dashboard provides selectable time period options from real-time to the last month, and the Flow Trends panel supports analysis over the last 24 hours, last week, and last month. These views help administrators identify ports, protocols, and services that are no longer actively used and may be candidates for removal from firewall policies.
-SSP collects host-level security monitoring statistics tracking the top ten ports and protocols by packet count at a given point in time, providing a data-driven view of the most active communication paths on each transport node. Security Intelligence continuously monitors infrastructure services to detect new servers in the environment. The IDS/IPS engine combines port verification with application identification to detect obsolete or non-secure protocols in active use, directly supporting the identification of protocols that should be disabled.</t>
+          <t>VMware vDefend contributes to preventing the execution of unauthorized software through its Malware Prevention Service, which operates at the hypervisor layer to detect and block malicious executables and scripts within guest workloads.
+The Distributed Malware Prevention feature intercepts and analyzes executable files across a range of formats, including portable executables (.exe), ELF executables (.elf), Microsoft installers (.msi), Windows shortcuts (.lnk), and related binary categories. The analysis runs through the Security Services Platform (SSP), and the Malware Prevention Service intercepts process start and stop events on endpoints to gather critical details including Process ID (PID), command lines, binary paths, and hashes. On Windows workloads, Guest Introspection drivers are required to receive the full distributed protection. When a file is identified as malicious, Distributed Malware Prevention with Guest Introspection provides interfaces for remediation actions, including denying access to suspicious files or deleting files identified as malicious.
+vDefend's Malware Prevention Service also addresses fileless attacks that bypass traditional file-based controls. The Fileless Malware Detection capability monitors Indicators of Compromise (IoC) including process command lines, process hash, process execution trees, and in-memory executions. In 9.1, the service intercepts in-memory scripts through Microsoft's Antimalware Scan Interface (AMSI), capturing execution traces of scripts running directly within process memory, including PowerShell, VBScript, and JScript. This detection path addresses script-based attacks that operate within system memory using existing binaries and in-memory operations without leaving executable artifacts on disk.
+Administrators can manage software execution policy through the Malware Prevention Allowlist, which lets them override or suppress the verdict that vDefend has computed for specific files, providing a mechanism to approve known-good software. Malware Prevention profiles can be configured to send files to the cloud for analysis or to process files locally, providing flexibility for environments with cloud connectivity constraints.
+The Malware Prevention Dashboard supports monitoring by tracking Process Name, PID, Command Line, and Binary Path for processes associated with in-memory script buffer execution. A Process Analysis Report provides detailed results for inspected processes and in-memory script buffers, including verdict information for each, supporting investigation and incident response workflows.
+These capabilities complement VCF platform controls (Secure Boot, code signing, container image trust) by adding a runtime detection and prevention layer within guest workloads, including coverage of fileless and in-memory techniques that static boot-time and installation-time controls cannot address.</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -5816,12 +5795,20 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple mechanisms for detecting, attributing, and responding to unauthorized configuration changes across its component products.
-VCF Operations performs daily checks that compare current configuration settings against authorized changes executed during defined change windows. When settings do not match the expected baseline, administrators are alerted to investigate the discrepancy. Beyond periodic checks, VCF Operations raises a Configuration Change alert whenever any property of a monitored entity changes, giving administrators immediate visibility into modifications across the managed infrastructure. This detection capability works in conjunction with VCF's requirement that configuration updates be performed only during maintenance windows, establishing a clear boundary between authorized and unauthorized changes. The VCF security baseline provides an additional reference point for evaluating both default and non-default configurations, helping organizations identify deviations that may indicate unauthorized modifications. vSphere Configuration Profiles can also be configured to trigger alarms for cluster and host configuration out-of-compliance events, notifying administrators via email or SNMP traps; the com.vmware.vcIntegrity.ClusterConfigurationOutOfCompliance event is used to fire these alarms when a cluster configuration falls out of compliance. At the VMware Kubernetes Service (VKS) layer, the cluster management system generates an Incompatibility insight on the Policy Insights page when it detects a Gatekeeper installation that was not deployed through cluster management, flagging unauthorized component deployments for administrative review.
-Audit logging across VCF components supports incident investigation when unauthorized changes are detected. VCF Operations audit logging tracks each configuration change to an authenticated user, recording the principal identifier of the user who initiated the change, the object affected, and the time of the modification. The NSX management plane audits configuration changes to security policies and firewall rules (the Distributed Firewall and Gateway Firewall are provided by vDefend, a separate product layered on NSX), capturing the username of the user making the change, the resource being modified, and the timestamp. Changes to local user accounts in NSX Manager are also audited. User permission changes can be tracked to determine when they were made and by whom. Kubernetes audit logging in VKS clusters records every write request to the Kubernetes API server, covering configuration changes to Deployments, ConfigMaps, Secrets, Roles, RoleBindings, and VKS-specific objects such as TanzuKubernetesCluster and VirtualMachine resources; each event captures the requesting identity, the action taken, the object affected, and the outcome. Pod Security Admission (PSA) in VKS clusters supports an audit mode that logs security-policy violations without rejecting pods, feeding violation events into operator dashboards and audit streams. These audit trails provide the attribution data needed to investigate unauthorized changes as security incidents.
-VCF also provides preventive controls that restrict unauthorized device-level changes. The isolation.device.edit.disable setting restricts unauthorized modification of devices on virtual machines, and the isolation.device.connectable.disable setting restricts unauthorized removal and connection of devices. These settings reduce the attack surface by limiting what changes can be made to VM hardware configurations outside of approved processes. At the Kubernetes API layer, ValidatingAdmissionPolicy and MutatingAdmissionPolicy can inspect write requests before they are persisted and reject those that do not conform to defined configuration baselines; ValidatingAdmissionPolicy is the preferred mechanism for preventing specific kinds of changes to resources, such as protecting platform namespaces from deletion. Tooling that manages ApplySet-based configurations is expected to refuse mutations from other tools, enforcing configuration ownership and reducing the risk that unauthorized changes persist undetected.
-For remediation, VCF has both automated and manual response capabilities. The auto-remediation feature in the Management Pack for VCF Operations Orchestrator can enforce host security hardening rules automatically, reverting unauthorized changes to host configurations without manual intervention. The Configure Host Security Config Data workflow allows administrators to selectively enforce specific hardening rules through configurable enforcement options. VMware vCenter configuration export provides a mechanism to revert to the last known good configuration when unauthorized changes are discovered, restoring the environment to a validated state. The vSphere Distributed Switch configuration can similarly be exported and saved as a backup file; if unauthorized changes are made to switch policies or host associations, the saved configuration file can be used to restore the distributed switch to its prior state. For the Kubernetes workload layer, VKS enforces immutability for platform-managed resources: system-managed Kubernetes ConfigMaps are not intended to be user-modifiable, and any unauthorized modifications are automatically overwritten by the platform. Organizations can deploy GitOps tooling such as Argo CD, available as a vSphere Supervisor Service, to continuously reconcile cluster configuration against a declared source of truth in Git, automatically reverting configuration drift and maintaining a complete change history for auditing and rollback.
-Integration with external security information and event management (SIEM) platforms allows configuration change events to be correlated and escalated through an organization's incident response process. The vSphere Security Configuration Guide recommends using SIEM tools for monitoring vSphere components, and VCF Operations receives change event information from adapters configured for external applications, supporting centralized event correlation. Kubernetes audit log streams from VKS clusters can be forwarded to a SIEM or log aggregation platform, where configuration change events from the Kubernetes API server join the broader incident response workflow. DISA STIGs are available for vSphere Supervisor and VMware Kubernetes Releases (VKrs), providing hardening requirements that establish the configuration baseline against which deviations in the Kubernetes layer are measured.</t>
+          <t>VCF provides several integrated automated mechanisms for governing, monitoring, and reporting on baseline configurations across the infrastructure stack.
+VCF Operations is the centralized configuration monitoring engine through its Configuration Drifts feature. Administrators define desired-state configuration templates and assign them to VMware vCenter instances and vSphere clusters. When a configuration value changes from the assigned template value, VCF Operations generates a drift notification, allowing administrators to identify and remediate unauthorized or unintended changes. The Configuration Drift dashboard provides a consolidated view of all detected drifts, and drift status reports can be downloaded for offline review or evidence collection. Configuration templates can be integrated with a source control repository, enabling versioned and auditable management of configuration baselines. This integration supports change control workflows with reviews and automated validation through continuous integration and continuous delivery pipelines. Drift detection is skipped if the template does not exist in the source control repository, so maintaining the repository is a prerequisite for continuous monitoring.
+VCF Operations alert definitions provide an additional layer of configuration monitoring. Administrators can configure alerts that use Metric/Property symptoms based on operational or performance values and configuration properties collected from target objects. These alert definitions monitor infrastructure components and notify administrators when configuration properties deviate from expected baselines. Associated remediation recommendations are attached to each alert, providing actionable guidance when violations are detected. Custom groups can be designated to update automatically with membership criteria, supporting structured monitoring strategies and enabling automated policy application across managed objects.
+VCF Operations Diagnostics extends configuration verification by providing integrated issue detection and remediation. The Diagnostic Findings feature discovers known issues and applies fixes based on industry-standard best practices and knowledge base articles. Diagnostics derives its findings from properties and product log data collected across the full VCF stack, including VMware vCenter, VMware ESX, NSX, VCF Operations, vSAN, and VCF Automation. This cross-component visibility enables centralized verification of configuration baselines across all major platform services. Diagnostic Findings consolidates log-based and property-based findings with specific resolution guidance, integrating with VCF Log Management for additional depth in identifying configuration drift or misalignment.
+VCF includes built-in compliance benchmarks based on the VCF Security Baseline and the Security Configuration Guide. These benchmarks evaluate both default and non-default settings across infrastructure components and report on compliance status. DISA STIG regulatory benchmarks are available for securing and configuring systems, and organizations can create, import, and export custom compliance benchmarks that monitor selected alert definitions and policies. Compliance management continuously monitors infrastructure objects against these benchmarks and provides actionable remediation recommendations when violations are detected.
+For automated remediation and configuration enforcement, Automation Central in VCF Operations allows administrators to create scheduled jobs that automate management actions. Jobs with ten or fewer resources run immediately, while larger jobs run in parallel groups of ten. The VCF Automation plug-in provides out-of-the-box workflows for common tasks such as host configuration and infrastructure management, reducing reliance on manual configuration processes. Infrastructure operations can be further automated through integration with tools such as Terraform and Ansible for agile templating and workflow-driven configuration management.
+VCF supports centralized agent-based configuration distribution. Once connected to its server, the agent automatically retrieves and applies configuration settings based on defined Agent Groups, providing a push-based mechanism for maintaining baseline configurations across managed endpoints.
+At the host level, vSphere Lifecycle Manager (vLCM) defines desired software state images for ESX clusters and supports validation of the desired state and detecting drifts from it. VCF Operations supports up to 25 simultaneous cluster compliance checks per instance, and the VCF Operations API provides endpoints for performing image compliance checks programmatically. vSphere Host Profiles provide a complementary automated mechanism for host configuration compliance. Administrators define a reference host configuration that is captured as a Host Profile and applied across managed hosts; scheduled compliance checks then determine whether any configuration parameters on a host differ from those specified in the profile, and deviations are flagged for remediation.
+VCF Automation integrates with VCF Operations to expose metrics and monitoring data for deployments. When monitoring is enabled, VCF Automation retrieves VCF Operations health status and associated alerts, providing a unified view of deployment health and configuration state. Tags applied to deployments support governance by expressing capabilities and constraints that define how resources are provisioned and managed. VCF Automation IaaS Resource Policies extend this governance to the Kubernetes cluster tier, supporting baseline pod security level enforcement that requires provisioned clusters to meet a defined pod security standard before resources are deployed into them.
+The VMware Kubernetes Service (VKS) and vSphere Supervisor layer extends baseline configuration governance to containerized workloads through a declarative model. All Kubernetes resources, including Deployments, ConfigMaps, NetworkPolicies, Pod Security Admission labels, ResourceQuotas, and LimitRanges, are defined as desired-state manifests enforced through the Kubernetes API server. Pod Security Admission is applied at the namespace level in three configurable modes: enforce mode rejects non-compliant pods at admission time, audit mode records violations in the cluster audit log without blocking admission, and warn mode generates warnings for non-compliant submissions. The security standard applied to a namespace can be set to privileged, baseline, or restricted using pod-security.kubernetes.io/ labels; VKS applies Pod Security Admission to namespaces by default, with the standard configurable per cluster and namespace. System namespaces such as kube-system, tkg-system, and vmware-system-cloudprovider are excluded from enforcement by default. The three-mode design enables automated reporting on pod security baseline violations through the audit and warn modes independently of enforcement, supporting continuous assessment of compliance posture across the workload layer. Controllers continuously reconcile the actual cluster state against the declared desired state, automatically correcting configuration drift without manual intervention. This continuous reconciliation loop addresses the real-time verification requirement for the workload consumption layer in the same way that CDM-style programs require continuous verification of all technology assets.
+The Argo CD Supervisor Service extends this declarative model to GitOps-based configuration governance. Desired configurations are stored in Git as the authoritative baseline, and Argo CD continuously compares the live cluster state against that baseline, surfacing discrepancies through its dashboard, health status indicators, and alerting integrations. Depending on the sync policy configured, Argo CD can automatically reconcile the cluster to the declared state or flag deviations for operator review. The service is designed to minimize manual intervention through automation. When configuration is managed as immutable infrastructure in version control, the combination of Git history and Kubernetes audit logs creates a durable, chronological record of every authorized change to the cluster configuration.
+VKS Cluster Management provides policy-driven governance of the VKS cluster estate. Security policies can be assigned to clusters and enforced across the organization, and custom policies are implemented using OPA Gatekeeper as the policy engine. VKS cluster management proactively monitors the cluster estate to verify that assigned policies are enforced correctly and generates Policy Insights when configuration conflicts or environmental errors are detected, providing automated reporting of policy compliance status across all managed clusters.
+Admission controllers built into the Supervisor API server enforce baseline security and configuration requirements at the point of resource admission. A validating admission webhook rejects Kubernetes resources that do not conform to the organization's defined configuration baseline before they are persisted to etcd, making off-baseline configurations inexpressible at submission time rather than relying on after-the-fact detection. Kubernetes Operators extend this model to application-level configuration governance by automating repeatable configuration tasks and continuously monitoring and enforcing configuration requirements for the applications they manage.
+The Kubernetes audit logging subsystem records all API server interactions, including configuration creates, updates, and deletes, according to a configurable audit policy. Audit events can be captured at multiple stages and shipped to an external log backend via webhook, providing an automated and continuous record of all configuration changes across the cluster. Node Problem Detector runs as a DaemonSet across cluster nodes, continuously monitoring node-level health conditions and reporting anomalies through Kubernetes Events and Node status conditions, providing automated detection of node-level configuration deviations that may indicate drift from the expected baseline.</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -5831,11 +5818,12 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to detecting and responding to unauthorized configuration changes within its security policy domain through draft management, signature tracking, and policy validation mechanisms.
-The Distributed Firewall uses a draft-based configuration model. Configuration changes are staged as drafts before publishing, and an auto-draft is created during each publish operation, allowing administrators to restore the previous published configuration by republishing that auto-draft. Drafts can be locked with a required comment, adding an explicit authorization step and an attribution record for configuration changes.
-For IDS/IPS signature management, vDefend provides a bulk Reset function that restores selected signatures to their default configuration, giving administrators a direct path to reverse unauthorized signature changes. The IDS/IPS Global Signature Management view tracks signatures that have been globally changed by users, including excluded signatures, providing visibility into which signature settings have been modified. The Global Manager can manage signature version deployment across Local Manager sites, providing centralized oversight of signature configuration.
-Security Services Platform validates configurations through its deployment wizard before implementing changes, reducing the likelihood of erroneous or unauthorized configurations being applied. Initial security policies published through Security Services Platform cannot be modified from the user interface after publishing, providing an immutability control for baseline segmentation policy. When configuration synchronization between Security Services Platform and NSX Manager fails or degrades, the platform displays a config agent health alarm in the NSX user interface, signaling that configuration state may be inconsistent.
-These capabilities address configuration change detection, rollback, and remediation within vDefend's security policy domain. Broader incident response orchestration, cross-infrastructure configuration drift detection, and escalation workflows are handled by VCF Operations and integration with external SIEM and ITSM platforms.</t>
+          <t>VMware vDefend contributes to automated baseline configuration management through several network-security-layer mechanisms in 9.1.
+Security Intelligence, part of the Security Services Platform, runs an automated classification cron job at 2:00 AM local time and every 24 hours thereafter. The job analyzes traffic flows from the past 30 days to classify compute entities as infrastructure service providers or workloads. Administrators can review and accept or modify the inferred classifications through the Security Explorer interface, and can supplement automatic detection by providing CSV files listing known infrastructure servers. Security Intelligence also classifies detected application assets as critical or regular applications, and a Rerun Analysis function re-initiates classification analysis automatically when NSX inventory changes occur, such as deleted groups or manually updated tags.
+Platform Inventory monitoring in the Security Services Platform collects infrastructure asset status across Regions, Zones, Environments, and Virtual Machines, showing success, timeout, or out-of-sync conditions. Administrators can filter by name and status to identify specific assets and expand environment rows to view assigned tags and verify hierarchy accuracy.
+Security Intelligence Policy Recommendations includes a Monitoring capability that checks for changes in the scope of input entities every hour when the Monitoring toggle is enabled, supporting continuous awareness of scope drift.
+In federated deployments, the Global Manager centralizes management of IDS/IPS signatures, profiles, Distributed Firewall (DFW) and Gateway Firewall (GFW) policies, oversubscription settings, and syslog settings across all Local Managers. vDefend also supports centralized management of custom IDS/IPS signatures from the Global Manager across multiple Local Managers.
+These capabilities address automated discovery, workload classification, asset status monitoring, and centralized policy management within the network security layer. They do not constitute a full CDM platform and should be supplemented with broader configuration management tooling for complete TAAS baseline governance.</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -5869,11 +5857,11 @@
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) maintains a Config Audit Trail that records all user activity and configuration changes over a selectable time period. This trail is accessible through the Avi Controller at Operations &gt; Events &gt; Config Audit Trail and provides a history of who changed what and when. Administrators can review this trail to identify configuration changes that fall outside authorized activity.
-At the event level, Avi generates CONFIG_CREATE and CONFIG_DELETE events that include client_IP and user_agent fields, enabling attribution of each change to the initiating source. When syslog forwarding is configured, these events can be sent to an external SIEM or alerting platform, supporting automated detection of unexpected changes and integration with organizational security incident workflows.
-The Service Engine Analytics interface includes a Config Events overlay that allows administrators to correlate traffic changes with configuration modifications. This overlay helps identify whether a change in observed traffic behavior was caused by a configuration change, such as modifications to virtual service security settings, helping narrow the scope of incident investigation.
-Avi also supports configuration warnings through the Enable Configuration Warnings setting, which notifies users of supported configuration changes. Alert configurations can be customized to set severity levels and descriptions, allowing operators to tune which events trigger notifications and how those notifications are routed.
-Responding to unauthorized configuration changes as formal security incidents requires organizational processes, including incident classification, escalation procedures, and investigation workflows, that Avi does not orchestrate. Avi provides the detection and notification inputs that those processes consume.</t>
+          <t>VMware Avi Load Balancer provides technical mechanisms that contribute to automated baseline configuration governance. Avi Load Balancer events are the building blocks of configuration automation: every change made through the web interface, CLI, or REST API is recorded as an event and automatically propagated to all Controller cluster members, giving operators a continuous record of what changed and maintaining cluster consistency.
+User-Defined Metrics allow administrators to define and extract highly customized telemetry data for specific enterprise compliance or reporting needs via API calls. This supports continuous monitoring of configuration state against defined thresholds and provides the raw data for compliance-oriented reporting workflows.
+Avi's REST API and CLI provide the interfaces for infrastructure-as-code configuration management. Official Ansible and Terraform integrations allow organizations to declare Avi Load Balancer baseline configurations as code, enforce those baselines through CI/CD pipeline runs, and detect drift when the running configuration diverges from the declared state. Ansible can be integrated with CI/CD pipelines to trigger automated Controller deployments upon code changes. Terraform modules support automatic scaling of service pool members through Network Infrastructure Automation (NIA) integration with Consul backend state management.
+In VCF deployments, Avi integrates with VCF Automation's Provider Management Portal, which enables provider administrators to define infrastructure boundaries, create regions and organizations, and set region quotas for capacity allocation. This integration extends Avi's configuration governance surface to include multi-tenant resource governance and capacity planning for organizations consuming load-balancing services through the VCF stack.
+Defining the configuration baselines, scheduling continuous comparison across the broader environment, and reporting deviation findings to management are organizational responsibilities fulfilled outside Avi through tooling and processes that operate against Avi's API and audit data.</t>
         </is>
       </c>
     </row>
@@ -6187,17 +6175,17 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>VCF provides centralized authentication, authorization, and auditing through VCF SSO, which acts as the identity broker for all VCF management components. All user and service authentication flows through VCF SSO, providing a single point of control for identity management across VMware vCenter, VMware ESX, NSX, VCF Operations, and VCF Automation. VCF SSO is configured via the VCF Operations console and provides a unified authentication source for VCF components.
-VCF supports multiple authentication mechanisms for organizational users. VCF SSO issues SAML tokens for authenticated sessions and supports multiple authentication context methods, including PasswordProtectedTransport (password over HTTPS) and holder-of-key tokens that embed security artifacts for delegation scenarios. vCenter supports built-in identity source authentication using local domain credentials and basic authentication through the OAuth 2.0 Password grant type when federated to an external identity provider. VCF SSO also supports the use of SSPI (Security Support Provider Interface) for client authentication.
-Identity federation with enterprise identity providers (via SAML or OIDC) enables organizations to extend their existing AAA infrastructure to VCF. Federating vCenter to an enterprise identity provider supports multifactor authentication and automatic registration and termination of users across services. vCenter has documented federation configurations for specific providers including Okta and PingFederate. VCF SSO also supports the System for Cross-domain Identity Management (SCIM) protocol for automating the exchange of user identity information between identity domains and external identity providers. Organizations using Microsoft Active Directory can use user identities contained in a Windows Server domain controller or Active Directory service across their virtual infrastructure. VCF Automation allows each organization to define its own identity provider that it shares with other applications; users authenticate to the identity provider to obtain a token that they then use to log in to the organization. Every organization in VCF Automation has its own identity source for user import. The Supervisor component supports registration of external OIDC identity providers for authentication using Pinniped, which inspects upstream identity tokens from the external provider to determine user identity and group membership before passing that information to the Kubernetes API server. Supervisor can be configured with any OIDC-compliant provider, including Okta, Workspace ONE Access, and Dex, to authenticate users connecting to VMware Kubernetes Service (VKS) clusters. Custom ClusterClass configurations for VKS clusters can be used to authenticate developers using existing corporate identity systems. The Kubernetes API server also supports integration with organizational authentication infrastructure such as LDAP or Kerberos through authentication plugins, enabling Supervisor to participate in existing centralized identity management. An Identity API is available to programmatically authenticate and manage the authorization provider, supporting automated identity lifecycle management.
-Authorization is enforced through role-based access control across all VCF components. vCenter maps authorization levels to groups and roles, providing consistent security controls regardless of operational context. VCF verifies what objects principals have access to as part of its authorization model. NSX has a set of built-in roles including Enterprise Admin, Auditor, Cloud Admin, Cloud Operator, Network Admin, Network Operator, Project Admin, Security Admin, and others. Local guest user accounts in NSX have the Auditor role by default, and only a user with the Enterprise Admin role can create new local guest user accounts. VCF Automation provides Organization Administrator, Organization Auditor (read-only), and Organization Owner roles, along with the ability to create custom roles scoped to an organization. Organization Administrators can view the rights associated with roles and create roles local to their organization. For Kubernetes workloads, vSphere Supervisor supports Namespace Owner, Edit, and View permission roles that allow consumers of vSphere Namespaces to provision VKS clusters and vSphere Pods using kubectl. Kubernetes RBAC evaluates Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings against the username, UID, group membership, and extra fields supplied by authenticator modules to determine whether a request is permitted. Users authenticated through external OIDC providers are referenced in ClusterRoleBindings using the oidc:user@example.com naming convention; users authenticated through VCF SSO use the sso:&lt;username&gt;@&lt;domain&gt; convention. The AuthorizeWithSelectors feature gate passes field and label selector information to authorization webhooks, supporting more granular per-resource authorization decisions. User impersonation is governed by Kubernetes RBAC: the "impersonate" verb on user, group, and ServiceAccount resources under authentication.k8s.io allows designated administrators to act on behalf of other principals in a traceable manner. Kubernetes also distinguishes human user accounts, whose identities are managed externally by the identity provider, from ServiceAccounts, which are namespace-scoped API objects used by automated workloads and processes; separating their lifecycle management supports differentiated audit strategies for each category. IAM role trust policies for VKS clusters can be scoped to specific service accounts and namespaces to enforce least privilege.
-VCF provides role-based visibility into policy enforcements. The Organization Administrator and Organization Auditor roles can view policy enforcements within their organizations. VCF's logging infrastructure captures authentication and authorization events across management components. The Kubernetes API server records API server activity with structured per-event metadata. Audit annotations include authorization.k8s.io/decision and authorization.k8s.io/reason, which record each authorization decision and its human-readable justification in the audit log, providing per-request traceability of who performed what action and how the authorization decision was reached. An audit event is logged for each impersonation request, enabling tracking of how impersonation is used over time. Audit rules can be configured to alert on specific events, such as concurrent reading of multiple Secrets by a single user. Authentication context, including username and group memberships, can be retrieved and logged using kubectl auth whoami for verification purposes. Administrators can use kubectl auth can-i with user impersonation to determine what actions other users are permitted to perform.
-Service-to-service authentication uses certificate-based Principal Identity users rather than password credentials. Principal identity user certificates must be SHA256-based and use RSA/DSA message algorithm with 2048 bits or above key size. Each VCF component registers with VCF SSO as a solution user. VCF Operations integrates with VCF SSO for centralized user and group authentication and management, and also supports LDAP authentication sources for additional monitoring and management access.
-Additional Consumption-layer services extend the AAA model to workload infrastructure. Harbor Registry, available as a standard package on VKS clusters, enforces role-based access control for container image artifacts and artifact security policies. The Secret Store Supervisor Service enforces RBAC across administrators, DevOps engineers, and application tenants for access to secrets and credentials. Argo CD, deployable as a Supervisor Service, supports OIDC authentication with PKCE via the enablePKCEAuthentication field and defines access through global RBAC policies using policy rules and group mappings.
-While VCF provides the technical mechanisms for authentication, authorization, and audit, centralizing these capabilities requires the organization to deploy and manage an external identity provider (such as Active Directory or an OIDC-compliant provider), define identity governance policies, and establish processes for user lifecycle management including provisioning, periodic access reviews, and de-provisioning. Role assignment procedures and access review processes are organizational responsibilities that fall outside VCF's direct control.
-VMware Private AI Services (PAIS) integrates with an external OIDC identity provider to authenticate organizational users accessing AI infrastructure on VCF. The PAISConfiguration custom resource is configured with an OIDC authentication block specifying the issuer URL, the client ID (`pais-authentication-id`), and the scopes `openid`, `groups`, and `offline_access`. When a region is created for a supervisor in PAIS, an identity provider is automatically created in VMware vCenter for that supervisor, establishing a consistent authentication entry point for AI workloads. Activating PAIS in an organization namespace requires coordination with the OIDC provider administrator, who supplies the issuer URL and client ID.
-Authorization for PAIS is enforced through OIDC group-based access control. The `authorizedGroups` setting in the PAISConfiguration restricts service access to user accounts that belong to designated OIDC groups (for example, `group-for-pais-access-01` or `group-for-pais-access-02`). The `oidc-groups-claim` setting names the claim used to identify group membership in the Access Token, and `oidc-extra-audiences` accepts additional OAuth 2.0 client IDs that PAIS will recognize when validating tokens. Grafana, used for PAIS metrics visualization, extends the same model through the `grafana-oidc-role-mapping` configuration: users in a designated PAIS access group are assigned the Admin role automatically, while remaining authenticated users receive the Viewer role.
-Harbor Registry imposes its own credential boundaries for AI artifact access. PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. Processes that push artifacts to Harbor authenticate using the `oras login` command with username and password credentials. Knowledge Base integrations support per-source authentication: Confluence connections accept a user name and password or a personal access token, and SharePoint On-Premises connections use user name and password authentication. These mechanisms restrict access to organizational AI artifacts and reference data to authorized accounts.</t>
+          <t>VCF provides automated mechanisms that support system account management and integrate with directory services across VCF SSO, VCF Automation, VCF Operations, VMware vCenter, and VMware ESX.
+VCF supports integration with LDAP-based directory services such as Microsoft Active Directory for centralized identity management. VCF SSO offers multiple automated user and group provisioning methods, including System for Cross-domain Identity Management (SCIM), Just-In-Time Provisioning (JIT), and Active Directory/LDAP (AD/LDAP). These provisioning mechanisms allow account creation and group membership to be driven by the directory service rather than managed manually within each VCF component.
+VCF Operations includes multiple built-in system accounts (backup, vcf, root, admin@local), each with distinct password update procedures. A System Administrator can create additional system administrator and user accounts within the provider organization. VCF Automation extends this further by supporting provider management accounts with specific service account privileges.
+For service accounts used by automated processes and third-party integrations, VCF Automation provides a dedicated management interface at Infrastructure &gt; Access Control &gt; Service Accounts. System administrators with the View Service Accounts and Manage Service Accounts privileges can create service accounts through the user interface or programmatically via the REST API. These service accounts support automated access for third-party applications and can create assets such as virtual machines, catalogs, and templates, with all actions properly attributed to the originating service account. VCF Automation also provides a Rotate service account capability that deletes and recreates service accounts, which can be used to remediate disconnected accounts in VMware vCenter and NSX. User account lifecycle management is handled through the Access Control interface, which supports activation, deactivation, and deletion of accounts.
+VCF Operations provides user account management capabilities including account creation, editing, deletion, export, and import. It supports obtaining and importing user accounts from external sources including LDAP databases and SSO servers, with an authorization source configured before import. Exported user accounts are password-protected, and the same password must be used when importing those accounts into another instance. VCF Automation can similarly be configured to use an LDAP server as a source of users and groups for its identity management.
+At the hypervisor layer, VMware ESX host local user accounts can be managed programmatically through the HostLocalAccountManager API. The vCenter UserDirectory service provides a look-up mechanism that returns user-account information to the AuthorizationManager or to client applications, supporting automated account discovery and validation. vCenter also includes the dir-cli command-line utility for managing accounts, solution users, certificates, and passwords in VMware Directory Service (vmdir), providing a scriptable interface for directory-level account operations. ESX hosts can be consistently configured to use Active Directory authentication through vSphere Host Profiles, which allow administrators to define directory service settings on a reference host and apply them uniformly across the environment.
+VCF Operations includes an Active Directory plug-in workflow library that allows administrators to run automated processes related to the management of Active Directory objects. Administrators can also create custom workflows using the Active Directory plug-in API to automate account management tasks within their Active Directory environment, such as account provisioning, modification, and deprovisioning.
+At the Kubernetes workload layer, VMware Kubernetes Service (VKS) on Supervisor extends automated system account management to containerized workloads. Kubernetes represents service accounts as first-class API objects (ServiceAccount) scoped to namespaces; the API server creates a default ServiceAccount in each namespace automatically, and additional service accounts can be provisioned through API calls, kubectl, or GitOps pipelines. The ServiceAccount admission controller enforces service account binding automatically, assigning accounts to pods at creation time when no explicit account is specified. Permissions are granted to service accounts through RBAC Role and ClusterRole bindings, making access control a declarative, API-driven operation that supports least-privilege patterns and separates workload identity lifecycle from human user onboarding. The LegacyServiceAccountTokenCleanup feature gate enables automatic cleanup of unused Secret-based service account tokens after a configurable retention period, preventing accumulation of stale credentials.
+For Windows workloads on VKS, VKS Service 3.3 and later support Group Managed Service Accounts (gMSA) through integration with Active Directory. Windows nodes can be joined to an on-premises Active Directory instance, enabling automatic password management, simplified service principal name (SPN) management, and delegation capabilities for Windows containers. The gmsaControlSecurityGroupDN setting specifies which Active Directory security group has rights to retrieve the gMSA password, providing controlled and automated access to Windows workload credentials. This integration connects the Kubernetes workload layer to the organization's existing directory service infrastructure.
+When the Argo CD Supervisor Service is deployed for GitOps-based workload management, service account creation is further automated: cluster registration creates an argocd-manager service account with appropriate cluster-level privileges and associates it with a ClusterRole and ClusterRoleBinding. Argo CD RBAC policy rules control account permissions through declarative configuration, supporting the assignment of local accounts to role groups and the granting of administrative roles to specific accounts. IAM role trust policies should be scoped to specific service accounts and namespaces to enforce least privilege for workload identities accessing cloud-native resources.
+To verify these capabilities, an auditor should confirm that VCF SSO is configured with an appropriate provisioning method (SCIM, JIT, or AD/LDAP), that VCF components are connected to the organization's directory service, and that service account lifecycle management procedures are in place. The Active Directory plug-in workflows in VCF Operations can be reviewed for any custom automation that has been implemented for account management tasks. At the Kubernetes layer, an auditor should verify that VKS clusters have appropriate RBAC bindings for service accounts, that gMSA is configured for any Windows workloads requiring Active Directory integration, and that any deployed Argo CD Supervisor Service instances are using RBAC policy rules for account permission management.</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -6233,13 +6221,12 @@
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) addresses the authentication component of this control through a two-tier identity model. DSM supports both local user accounts and LDAPS-integrated directory service accounts, and administrators can configure one or both identity sources simultaneously. Local users are authenticated by matching their email address and validating their password directly within DSM. LDAPS users are authenticated by matching the email domain name against the registered LDAPS server and validating credentials against the directory service. DSM can be configured to use an LDAP server for both authentication and authorization of platform-level users.
-Authentication for the managed databases is handled through database-native mechanisms that DSM exposes and configures. PostgreSQL databases use host-based authentication (HBA), with rules managed through DSM. The HBA configuration applies ordered matching rules where the first entry matching the connection type, client address, requested database, and user name is applied. The default final entry uses SCRAM-SHA-256, providing strong password-based authentication; an optional LDAP entry can also be included. MySQL databases support LDAPS integration using a simple authentication plug-in, with a unique LDAPS user entry per user and support for Active Directory authentication. PostgreSQL and MySQL databases also support LDAPS user accounts linked to organizational directory services, with LDAPS user creation managed through the DSM interface.
-DSM adds SQL Server as a supported database engine. SQL Server clusters support two administrator identity types: SQL User credentials and Windows Principal accounts for clusters integrated with Active Directory. DSM's Active Directory integration supports Kerberos-based authentication for domain-joined SQL Server clients, allowing tools such as SQL Server Management Studio running on a Windows machine to authenticate using domain credentials. DSM maps the dbo user, the database object owner, to administrator-controlled identities for SQL Server database access. SQL Server clusters can also use contained database users, where each user authenticates directly against the database rather than a server-level login, keeping identity information self-contained within the database.
-Authorization is handled through a role-based model. DSM provides two platform-level roles, DSM Admin and DSM User, which determine the capabilities available to each user within the DSM management interface and API. Custom user roles can be configured for directory service group members, providing scoped monitoring and management access. The Permissions view in DSM supports the creation, monitoring, and management of configured users, giving administrators visibility into who has access. Role assignments also affect behavior in database operations; DSM automatically establishes trust between primary and secondary PostgreSQL instances for Admin-role users, while User-role accounts require manual trust establishment.
-DSM produces audit records covering both user-initiated and system-initiated actions. Audit events are generated for actions performed through the DSM UI and API, and each audit log entry includes a Source field identifying the initiating entity: either a user's email address or "System" when the action was initiated by DSM itself. Gateway Audit Logs provide visibility into gateway-level events, and the System Audit Events view is the designated location in the DSM UI for tracking nondatabase-related operations and tasks. For SQL Server clusters, DSM provides configurable server auditing with preset audits for login tracking and log retention; the Login Auditing option can automatically create a simple audit for login events.
-In self-service consumption deployments, the DSM Consumption Operator authenticates with the DSM infrastructure using a dedicated authentication secret (dsm-auth-creds), providing a defined authentication path for Kubernetes-native database provisioning.
-DSM's authentication, authorization, and audit capabilities are scoped to the DSM platform and its managed databases. Centralized AAA for the broader organizational user population, including account lifecycle management, privileged access governance, and enterprise-wide log aggregation, requires organizational identity governance programs and security tooling outside DSM's scope.</t>
+          <t>VMware Data Services Manager (DSM) supports integration with LDAP and Active Directory (AD) as external directory services, allowing organizations to centralize system account management for DSM users. When configured, DSM imports users from a connected LDAPS server rather than requiring separate local account creation for each user. This integration is configured under the Directory Service Settings in the DSM administration interface, where administrators specify the LDAPS server address and upload the directory service server certificate for validation. When Directory Service credentials become non-functional, DSM falls back to local user authentication to maintain access continuity.
+For DSM administrative accounts, user accounts can originate from two identity sources: the DSM local database (local users) or a configured LDAPS server (LDAPS users). DSM manages these two populations independently, allowing an organization to use one or both sources. By connecting DSM to an LDAPS server, organizations can have users authenticate using their existing enterprise credentials, and account lifecycle events in the directory (such as account disabling or group membership changes) directly affect access within DSM. The Directory Service status can be inspected through the Settings interface, allowing administrators to monitor LDAP and AD connectivity and confirm that credentials remain functional.
+Group-based access control is supported through the Directory Service Group role assignment feature. DSM administrators can assign DSM roles to Directory Service Groups, so a user's access level within DSM follows their directory group membership. When an administrator changes a user's group membership in the directory service, that change is reflected automatically in DSM without requiring a separate DSM role update.
+Database instances provisioned through DSM can also be configured to use LDAP or AD-based authentication for database connections. The Enable Directory Service Authentication toggle, available during database creation and editable afterward, activates directory-backed login for individual PostgreSQL and MySQL databases. This extends the reach of centralized account management to the data plane, so database access can be governed through the same directory service as DSM administrative access.
+SQL Server instances managed by DSM support Windows Authentication via Active Directory and Kerberos integration. Administrators can provide a privileged Active Directory account during configuration, allowing DSM to automate the registration of Service Principal Names (SPNs) and DNS records for SQL Server clusters. Each SQL Server cluster requires a dedicated service account that is a standard Active Directory Domain Users member. DSM deactivates the default SQL Server sa account and uses a reserved internal account, dsm_mgmt, for management operations, reducing the exposure of privileged credentials while directory group membership governs end-user access.
+DSM also maintains service account rotation logs that can be reviewed to diagnose authentication failures related to its own vCenter service account, providing visibility into the lifecycle of the service account DSM uses to provision and manage resources.</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -6787,15 +6774,87 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>IA.L2-3.5.9</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>IAC-10</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Allow temporary password use for system logons with an immediate change to a permanent password.</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>VCF provides a layered authentication infrastructure that supports secure management of authenticators across the platform's components and the Kubernetes workload consumption layer, though the broader organizational policies governing authenticator lifecycle management require processes and governance beyond what VCF itself provides.
 VCF Identity Broker integrates with a selected identity provider for user authentication, establishing trust through metadata exchange between the service provider and the identity provider. This centralized approach allows organizations to manage authenticators through their existing identity management systems rather than maintaining separate credential stores for each VCF component. VCF SSO provides a single sign-on environment where a user provides credentials once, and components in the environment perform operations based on the original authentication. Administrators can federate VMware vCenter with an enterprise identity provider, which enables multifactor authentication (MFA), automatic user provisioning and deprovisioning, and token-based authentication that reduces the risk of credential exposure. VCF SSO supports SCIM (System for Cross-domain Identity Management) for automating user identity exchange across identity domains, and named providers including Okta are supported through the identity provider federation mechanism. When configured for identity provider federation, the external provider handles all authentication mechanisms, including passwords, MFA, and biometrics, delegating full authenticator management to the organization's existing identity infrastructure. The Authorization Code grant type in VMware Identity Broker supports MFA workflows, while the Password OAuth 2.0 grant type is incompatible with MFA requirements, so organizations should use the Authorization Code flow when MFA is needed.
@@ -6818,104 +6877,6 @@
 The underlying user accounts, credential storage, password policies, and OIDC provider administration are owned by VCF SSO or an external identity provider. PAIS configures and enforces authentication using those systems but does not manage authenticator lifecycle itself.</t>
         </is>
       </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms for managing authenticators across both the administrative plane and the database layer, supporting the secure credential management aspect of this control.
-For administrative access to the DSM platform, the system supports two authentication paths: local user accounts authenticated by email ID and password, and LDAPS-integrated accounts authenticated by matching the email domain against a registered LDAPS server. When directory service credentials are non-functional, DSM falls back to local user authentication, maintaining access continuity. Administrators configure and manage these authentication sources through the DSM Admin UI, which also provides a Permissions view for creating, monitoring, and managing configured users. LDAPS integration supports certificate-based validation of the directory service connection, with administrators able to upload directory service server certificates through the Admin UI to establish trusted connections. LDAP groups can be assigned roles within DSM, enabling group-based access control aligned with directory service group membership.
-At the database layer, DSM supports directory service authentication for PostgreSQL, MySQL, SQL Server, and MinIO databases. For PostgreSQL, host-based authentication (HBA) rules determine how clients are authenticated, using ordered matching rules that evaluate connection type, client address, requested database, and user name. The default HBA configuration includes a final catch-all entry using scram-sha-256, with optional LDAP entries for directory-integrated authentication. This HBA configuration can be modified through the DSM interface. For MySQL databases, LDAPS authentication is available using Active Directory Global Catalog, with support for multi-domain controller deployments via the AD Secure/SSL Global Catalog on port 3269. Directory service authentication for individual database instances can be enabled or disabled through the Enable Directory Service Authentication toggle in the database settings.
-For SQL Server databases, DSM uses contained database users, where users authenticate directly against the database and identity information resides within the database. DSM supports Windows Authentication for SQL Server server-level logins through Active Directory integration, enabling Kerberos-based single sign-on for clients joined to the same domain. SQL Server Authentication logins can also be created on all DSM clusters. Administrators configure which user types are permitted per data service policy, selecting between Windows Principal authentication using Active Directory credentials and SQL User authentication using standard SQL Server logins. An internal management login (dsm_mgmt) restricts access to system-level objects, keeping administrative operations within an isolated context.
-DSM enforces password policies for local accounts, including complexity requirements, and applies a root password expiry on a three-month rotation cycle. For service-to-service communication, DSM uses authentication secrets (dsm-auth-creds) containing endpoint credentials and root CA certificates, with automatic secret generation available through the Consumption Operator installation. Prometheus metrics forwarding supports configurable authentication options, including no authentication, certificate-only authentication, basic authentication with username and password, or a combination of certificate and basic authentication.
-Regarding authentication strength appropriate to data classification, DSM provides the authentication mechanisms that administrators can configure to match organizational security policies, but it does not automatically enforce differentiated authentication strength based on data classification. Organizations must define their data classification scheme and determine which DSM authentication options (local credentials, LDAPS, HBA rules, certificate validation, Kerberos) apply to each tier of sensitivity. DSM contributes the technical controls; the alignment between authentication strength and data classification requires organizational governance to establish and maintain.</t>
-        </is>
-      </c>
-      <c r="M70" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="N70" s="10" t="inlineStr">
-        <is>
-          <t>VMware Avi Load Balancer provides mechanisms to securely manage authenticators across two distinct planes: the Controller management plane (admin access) and the application data plane (end-user client authentication for load-balanced applications).
-For the management plane, Avi maintains user accounts in two categories: local users managed directly on the Controller, and remote users authenticated through an external authentication, authorization, and accounting (AAA) server. Avi uses Authentication Profiles to configure how administrators authenticate to the Controller. Authentication Profiles support LDAP for credential validation against a directory service, SAML for federated authentication that delegates the process to a centralized identity provider (IdP), and basic authentication. The recommended approach is federated authentication, which centralizes the authentication process by delegating to an external IdP rather than managing credentials locally on the Controller. SAML profiles verify user identity without storing credentials on untrusted systems, and Avi Controller SAML authentication profiles can be integrated with Workspace ONE Access for catalog-based application access. Admin users can also authenticate using password-less SSH-based login as an alternative to password-based authentication. On every user login, the Auth Mapping Profile evaluates authorization mapping rules and updates the user record with tenant and role pairs drawn from the IdP's assertions.
-For the application data plane, Avi acts as a proxy that applies client authentication policies to inbound application traffic. Supported methods include LDAP authentication (checking client credentials against a directory service), SAML single sign-on (enabling federated application access with a single credential set), OAuth and OIDC (where Avi acts as a client and resource server, with the authorization server authenticating clients and validating authorization codes before issuing tokens), and JSON Web Token (JWT) validation. The SSO Policy supports configurable Authentication Rules and Authorization Rules with path-based matching criteria, allowing different authentication requirements to be applied to different application paths. More granular authorization in OAuth/OIDC flows is available through Authorization Policies or DataScript.
-Organizations configure which authentication method applies to each virtual service or application based on the sensitivity of the data accessed. Avi's Authentication Profiles and SSO Policies provide the technical enforcement points to apply different authentication strengths across the application portfolio, but the mapping from data classification tier to required authentication method is an organizational governance decision that must be defined and maintained by the organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>IA.L2-3.5.9</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>IAC-10</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Allow temporary password use for system logons with an immediate change to a permanent password.</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>VCF provides a layered authentication infrastructure that supports secure management of authenticators across the platform's components and the Kubernetes workload consumption layer, though the broader organizational policies governing authenticator lifecycle management require processes and governance beyond what VCF itself provides.
-VCF Identity Broker integrates with a selected identity provider for user authentication, establishing trust through metadata exchange between the service provider and the identity provider. This centralized approach allows organizations to manage authenticators through their existing identity management systems rather than maintaining separate credential stores for each VCF component. VCF SSO provides a single sign-on environment where a user provides credentials once, and components in the environment perform operations based on the original authentication. Administrators can federate VMware vCenter with an enterprise identity provider, which enables multifactor authentication (MFA), automatic user provisioning and deprovisioning, and token-based authentication that reduces the risk of credential exposure. VCF SSO supports SCIM (System for Cross-domain Identity Management) for automating user identity exchange across identity domains, and named providers including Okta are supported through the identity provider federation mechanism. When configured for identity provider federation, the external provider handles all authentication mechanisms, including passwords, MFA, and biometrics, delegating full authenticator management to the organization's existing identity infrastructure. The Authorization Code grant type in VMware Identity Broker supports MFA workflows, while the Password OAuth 2.0 grant type is incompatible with MFA requirements, so organizations should use the Authorization Code flow when MFA is needed.
-VMware Kubernetes Service (VKS) extends this identity architecture to the workload consumption layer. VKS clusters support two authentication methods: VCF SSO and any OIDC-compliant external identity provider, including Okta, so identity lifecycle management, including onboarding, offboarding, and group membership changes, can remain in the organization's central identity system. Users authenticated through an external identity provider are granted Kubernetes RBAC permissions using the sso:&lt;username&gt;@&lt;domain&gt; naming convention in ClusterRoleBindings. Custom ClusterClass configurations allow organizations to authenticate developers against existing corporate identity systems. When provisioning clusters based on a custom ClusterClass, the authentication Secret can be configured with multiple JWT issuers to support distinct identity providers simultaneously, such as Keycloak for contractors and Microsoft Entra ID for employees. At the kube-apiserver level, VKS supports multiple authenticator types: client certificates, bearer tokens, an authenticating proxy, and HTTP basic auth. The --authentication-config file provides structured control, allowing multiple JWT authenticators each with a unique issuer URL and discovery URL, and CEL expressions to map claims to user attributes and validate claims. When multiple authenticator modules are active, the first to successfully authenticate a request short-circuits further evaluation, making authenticator order significant; Kubernetes hardening guidance recommends enabling as few authentication mechanisms as possible to simplify user management and reduce the risk of users retaining access after it is no longer needed. The kube-apiserver can also leverage existing authentication methods such as LDAP or Kerberos through plugins, and kubectl integrates with credential plugins for centralized operator credential management. The system:auth-delegator ClusterRole provides unified authentication and authorization flows for add-on API servers deployed into VKS clusters. Production VKS clusters should enable Kubelet authentication and authorization to restrict direct access to the kubelet API. For Windows node pools, VKS clusters support Group Managed Service Accounts (gMSA) for authenticating Windows nodes to Active Directory; gMSAs are managed by security groups that control password retrieval and delegation permissions, allowing Windows workloads to use Active Directory-managed identities.
-Standard packages deployable on VKS clusters extend authenticator management to workload-level services. Argo CD, available as a standard package, supports local account authentication with global RBAC policies and OIDC authentication for federated identity, allowing GitOps workflow access to be governed through the same identity infrastructure used for cluster access. The Harbor container registry package provides authentication and token management for artifact access, with role-based access control restricting image push and pull operations.
-VCF Operations integrates with VCF SSO for centralized authentication through an identity provider. NSX Manager can be configured to authenticate users from identity management providers or through a directory service such as Active Directory over LDAP or OpenLDAP. NSX authentication best practices include integrating with identity providers, enabling multi-factor authentication, and defining access controls based on user roles and permissions. NSX Manager requires authentication prior to establishing a management connection for administrative access. The VCF Automation Provider Management Portal supports authentication via local users and SAML users, and Organization Administrators use credentials configured during organization creation to access their respective organizations.
-For local accounts, each VCF component enforces password complexity and lifecycle policies. NSX Manager requires passwords of at least 12 characters with uppercase, lowercase, numeric, and special character requirements, enforced through Linux PAM modules. Each NSX user password has an expiration date tracked by NSX, with a default expiration period of 90 days. Password expiration is configurable between 1 and 9,999 days. VCF Operations enforces a minimum of 15 characters with similar complexity rules. VCF Automation passwords must also be at least 15 characters in length.
-VCF provides configurable account lockout policies across its components. VCF Operations locks accounts after five consecutive failed login attempts for 15 minutes. A separate policy locks VCF Operations accounts if a user enters an incorrect password three times within five minutes. VCF Automation supports account lockout in password policy system settings, which locks user accounts after a configurable number of invalid login attempts. VCF Automation also provides a configurable account lockout interval that specifies the duration before an account is automatically unlocked, and provider administrators can unlock a user account manually without waiting for that interval to expire.
-For service-to-service authentication, VCF uses certificate-based credentials. VCF SSO supports X.509 certificate authentication, and vCenter extensions can authenticate using loginExtensionByCertificate() with an extension key certificate. Provider management accounts authenticate using API access tokens that rotate after each use. VCF Automation provides service accounts with the same access restrictions as user API tokens, so service accounts cannot perform user management or create refresh tokens. NSX supports Principal Identity certificates for cloud management platform integration, requiring SHA256-based certificates with RSA/DSA message algorithm and 2048-bit or larger key sizes. At the Kubernetes layer, service account authentication uses bearer token secrets generated automatically for service accounts. Kubernetes hardening guidance recommends setting short lifetimes on certificates and automating their rotation, and recommends using an authentication provider that controls how long issued tokens remain valid; using short-lived Secrets helps detect or limit the impact of credential exposure. The system:masters group functions as a break-glass super-user group that bypasses the RBAC authorization layer and should be reserved for emergency access scenarios only.
-VCF Operations provides API endpoints for trusted certificate management and displays certificate expiration status for each workload domain through its Certificates tab. NSX supports non-disruptive certificate rotation in VCF and later, allowing certificate replacement without service interruption.
-VCF also provides visibility into authenticator usage through audit logging. User authentication details are viewable in VCF Operations, including user name, successful or failed authentications, and events such as user login and guest operation authentication. This logging supports detection of compromised or misused authenticators.
-While VCF provides the technical controls for authenticator strength, complexity, expiration, lockout, and rotation within its own components, as well as identity provider integration for MFA enforcement and centralized authentication, and the VKS consumption layer provides configurable multi-method kube-apiserver authentication, external identity provider integration, short-lived credential support, and gMSA for Windows workloads, the broader organizational policies for initial authenticator issuance, periodic credential rotation schedules, revocation upon personnel changes, and mapping authentication strength requirements to data classification levels require processes and governance outside VCF's scope.
-VMware Private AI Services (PAIS) provides authentication mechanisms specific to its AI infrastructure components, integrating with externally managed identity systems to control access to AI services, model endpoints, and training data.
-PAIS uses OIDC-based authentication as its primary access control mechanism. The PAISConfiguration custom resource configures the OIDC provider with issuerUrl, clientId, and scopes including openid, groups, and offline_access. Access is restricted to user accounts whose membership matches OIDC groups listed in the authorizedGroups field, and the Access Token carries a groups claim that PAIS validates against the authorized group list. The OIDC configuration also supports configurable group claim names and Extra Audiences for additional OAuth2.0 clients that PAIS will accept when validating the Access Token.
-The PAISConfiguration custom resource supports client TLS for outbound authentication to the OIDC provider and Harbor registry, configured through the worker.clientTls.caBundleRefs field. This binds certificate-based trust to identity provider and registry connections so that authentication exchanges are integrity-checked against approved CAs.
-Authenticator management for the Harbor registry that stores AI models and artifacts follows a credential-based pattern. The oras login command authenticates to a private Harbor registry using username and password credentials for artifact push operations, and docker login is used for pushing models to Harbor projects through the Model Gallery. Harbor project access capabilities restrict access to the sensitive data that is used to train and tune models. Model endpoints support authentication through harbor-pull-secret-readonly to control access to container images stored in private registries, and Harbor model retrieval requires certificate-based trust in addition to credential authentication.
-Internal service-to-service authentication is addressed at the component level. PAIS authenticates to the OpenTelemetry Collector using a Kubernetes Secret containing Authorization Bearer tokens and custom headers, and the LLM Traces flow uses the same pattern with semi-colon separated headers. The PAIS MCP server supports custom HTTP headers including User-Agent and Authorization headers for API authentication, and remote MCP servers can optionally use static authentication tokens. PAIS integrates with Grafana for metrics visualization using OIDC provider authentication.
-For Knowledge Base data sources, PAIS supports authentication to Confluence using either a username and password or a personal access token, configured according to the Confluence administrator's settings. Personal access tokens are generated from user account settings and used for programmatic access to Knowledge Bases and data sources. Microsoft SharePoint data sources require username and password authentication, with support limited to SharePoint On-Premises deployments.
-Deep Learning VMs deployed through self-service catalog items in VCF Automation, when configured with the PyTorch NGC software bundle, support optional JupyterLab authentication activation for interactive notebook access.
-The underlying user accounts, credential storage, password policies, and OIDC provider administration are owned by VCF SSO or an external identity provider. PAIS configures and enforces authentication using those systems but does not manage authenticator lifecycle itself.</t>
-        </is>
-      </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
           <t>Not Applicable</t>
@@ -8102,18 +8063,13 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>VCF provides mechanisms for authorizing, monitoring, and controlling remote maintenance and diagnostic activities across the managed infrastructure, including the Consumption layer delivered through VMware Kubernetes Service (VKS) and vSphere Supervisor.
-All remote administrative access is authorized through VCF SSO, which provides centralized authentication for VMware vCenter, ESX, NSX, VCF Operations, and VCF Automation. At the ESX host layer, lockdown mode restricts direct host access so that maintenance and diagnostic operations are routed through VMware vCenter rather than the host directly. Normal lockdown mode permits local console and vCenter access, while strict lockdown mode stops the Direct Console User Interface and allows access only through vCenter. VCF Operations integrates with VCF SSO for centralized user and group authentication and management. VCF Operations for Networks also supports VCF SSO as a login method. Role-based access control within each component determines which maintenance and diagnostic operations a given user can perform. NSX Manager implements RBAC to restrict system access to authorized users by assigning roles with specific permissions. This authorization model applies to both graphical management interfaces and programmatic access through REST APIs, SDK, and PowerCLI.
-For VKS workload clusters managed through vSphere Supervisor, the Kubernetes API server is the central control point through which all remote management and diagnostic operations pass. Access to the API server requires authentication before any action can be taken; supported methods include OIDC, X.509 client certificates, service account tokens, and webhook token authentication. Once authenticated, requests are evaluated against RBAC policies: Roles and ClusterRoles define permitted operations on specific Kubernetes resource types, and RoleBindings and ClusterRoleBindings associate those permissions with users, groups, or service accounts, scoped either to individual namespaces or cluster-wide. The built-in system:monitoring group provides read access to control-plane monitoring endpoints, including liveness, readiness, and health check endpoints (/healthz, /livez, /readyz) and /metrics, enabling authorized operators to query cluster health remotely without broader administrative access. On production clusters, Kubelet authentication and authorization should be enabled to restrict who can access node-level diagnostic operations and log retrieval remotely.
-VCF Operations supports maintenance mode to take objects offline for maintenance activities. Administrators can put objects into maintenance mode manually, either indefinitely or for a specified period, or configure recurring maintenance schedules that activate at fixed intervals. For example, a maintenance schedule can place an object in maintenance mode from midnight until 3 a.m. on recurring days. Manual and scheduled maintenance modes are not mutually exclusive, giving administrators flexibility to respond to both planned and unplanned maintenance needs. These scheduling capabilities allow organizations to define and enforce approved maintenance windows, providing structured control over when maintenance activities occur. When remediating ESX hosts through Update Manager, administrators can configure maintenance mode settings to control how hosts are transitioned during patching and update operations.
-At the Kubernetes layer, node cordoning and draining provides structured control over workload placement during planned maintenance operations. Cordoning a node prevents new pod scheduling on it, and draining it safely relocates running workloads to other available nodes before maintenance begins. Stateful applications deployed as StatefulSets maintain pod identity and persistent storage across the cluster, allowing rescheduling to available nodes during node maintenance. PodDisruptionBudgets can be defined to set availability constraints that Kubernetes respects when draining nodes during planned maintenance, helping maintain service continuity for critical workloads.
-Maintenance schedules are integrated with the monitoring system to prevent VCF Operations from generating misleading alerts when objects are intentionally offline for maintenance. This separation of planned maintenance from genuine operational issues helps administrators focus monitoring attention on actual problems rather than expected outages. VCF Automation retrieves VCF Operations health status and associated alerts about deployments, creating a feedback loop that helps administrators track the impact of maintenance activities. Proactive monitoring capabilities help maintain environmental stability by identifying issues that may arise during or after maintenance operations.
-For monitoring remote maintenance activities, VCF Operations captures platform interactions through its audit events framework, reporting on authentication and security-related events. VCF Operations audit logging tracks each configuration change to an authenticated user who initiated the change, allowing administrators to determine the principal identifier of the user who initiated a change to an object at a given time. User Activity Audit reports show the scope of user activities, including logging in, actions on clusters and nodes, changes to system passwords, activating certificates, and logging out. Audit data can be filtered by User ID, User Name, Auth Source, Session, Client IP, Category, and Message. VCF Operations for Networks provides audit logs that capture administrative actions, with access controlled by user role. VCF Operations can forward user activity audit logs to an external syslog server to meet security auditing requirements. API audit logging captures REST API calls, SDK usage, and PowerCLI commands with user attribution, providing visibility into programmatic maintenance actions. In NSX, API calls from all sources and users are audited, and this logging is always enabled and cannot be disabled.
-At the Kubernetes layer, the API server includes built-in audit logging that records every request, capturing the requesting user, action taken, target resource, and outcome. Organizations can define an audit policy to control which request types and resource types generate audit records; audit events can be written to log files or forwarded to webhook endpoints for integration with external log management systems. This logging provides visibility into all remote management and diagnostic activity directed at VKS clusters. Kubernetes system components also generate traces that can be collected and analyzed for observability during maintenance activity.
-VCF Operations provides remote monitoring capabilities including HTTP remote checks that support GET, POST, and PUT methods for application service monitoring. These remote checks support SSL certificate and key file paths for secure communication with target machines. Administrators can configure discovered services and perform custom monitoring actions including custom scripts, remote checks, Windows service monitoring, and Linux process monitoring. Service discovery and monitoring is available through VCF Operations Advanced and Enterprise editions, enabling administrators to discover and monitor services across the environment. Administrators can deploy product-managed Telegraf agents to monitor physical servers remotely, with lifecycle management available through the VCF Operations suite API. vSphere Hardware Health monitoring displays host component sensors, storage sensors, hardware alerts and warnings, and system event logs, providing hardware-level diagnostic visibility for administrators managing physical infrastructure.
-VKS clusters can be monitored and managed from the Supervisor Management &gt; Services tab in vSphere Client, giving administrators a centralized view of cluster state and component health. The Kubernetes API server exposes individual health check endpoints that operators can use for debugging system status. VCF Automation for VM Apps maintains a history of deployments that can be reviewed to retrieve information about deleted machines and diagnose deployment failures, supporting post-maintenance verification.
-VCF also provides diagnostic capabilities for remote troubleshooting. The DiagnosticManager is a managed object that works service-wide, rather than on a per-session basis, and is available on both ESX and vCenter systems. ESX also supports out-of-band remote management through hardware management interfaces, including HP Integrated Lights-Out (iLO), Dell Remote Access Card (DRAC), IBM management modules, and Fujitsu iRMC, enabling authorized remote access and control at the hardware layer independent of the host operating environment. VCF Operations supports centralized log collection for diagnostic and monitoring purposes. Log Assist extends log export functionality with diagnostic capabilities, enabling remote troubleshooting without requiring direct console access to managed components. VCF supports configuring alerts for operational monitoring, providing visibility into the state of managed infrastructure during and outside maintenance windows.
-Before performing maintenance activities such as upgrades, administrators should take on-demand backups of components like VCF Automation. This practice provides a recovery point if maintenance activities produce unexpected results, supporting controlled and reversible maintenance operations.</t>
+          <t>VCF provides native technical mechanisms for remote disconnect verification of maintenance and diagnostic sessions, covering programmatic session termination, audit logging of session start and end events, maintenance-state verification commands and APIs, connectivity monitoring with automatic offline detection, and post-maintenance state validation.
+VCF's management APIs include explicit session termination methods that allow administrators and automation scripts to close remote connections in a controlled manner. The vSphere Web Services API provides a logout method that accepts a session manager reference to close the server connection, giving programmatic control over session teardown. VCF PowerCLI complements this with the Disconnect-CIServer cmdlet, which closes all active connections to a server and removes it from the $DefaultCIServers variable, providing a verifiable way to confirm that a remote management session has been fully terminated. These mechanisms can be built into maintenance runbooks and automation workflows. For virtual machine console sessions, vSphere provides VMware Remote Console options that can lock the guest operating system when the last remote user disconnects from the console, and can limit the number of simultaneous console connections to a virtual machine, providing a session-end enforcement mechanism that does not rely solely on operator action.
+Session activity is tracked through audit event frameworks across multiple VCF components. NSX generates audit logs for events such as logon, logoff, and access to resources, with each audit log containing a timestamp, source, result, and description of the event. VCF Operations captures administrative actions including login and logout alerts in its audit logs. At a broader level, VCF Operations records interactions within the platform such as searches, logins, logouts, capability checks, and configuration modifications as audit records. This audit trail provides evidence that remote sessions were initiated and terminated, supporting after-the-fact verification of proper disconnect. At the ESX host level, when a connection to a remote audit record destination is restored after a period of disconnection, ESX generates an audit message indicating potential message loss during the gap, alerting administrators to any break in the continuity of the audit trail.
+For infrastructure-level maintenance, VCF provides commands and API endpoints to verify the maintenance state of components after remote work is completed. NSX transport node maintenance mode status can be confirmed using the get maintenance-mode admin CLI command or the corresponding API endpoint, allowing administrators to verify whether a node has properly exited maintenance mode after remote servicing. ESX host connectivity and maintenance mode status can be verified through vCenter before returning hosts to production operation. VCF operational guidance recommends that if a host remains in maintenance mode for 72 hours or more and the maintenance window is not expected, administrators should investigate and take the host out of maintenance mode, providing a time-based safeguard against orphaned maintenance sessions.
+VCF includes connectivity monitoring capabilities that detect when remote connections are lost or components become disconnected. The NSX Global Manager detects loss of connection to a Local Manager and prompts administrators to perform network recovery. When connectivity is lost between fault domains, VCF takes one fault domain offline automatically, and once connectivity is restored, an administrator must manually bring the fault domain back online, providing an explicit verification step before resuming operations. VCF Operations identifies disconnected integrations and reports that data collection and resource monitoring are unavailable on those integrations, giving administrators visibility into the state of remote management connections. Remote check configurations support response timeout and read timeout parameters, which help detect and terminate unresponsive remote connections rather than allowing them to persist indefinitely.
+VCF Operations also contributes to post-maintenance verification through configuration drift detection and connectivity validation. The Configuration Drifts feature monitors deviations from assigned configuration template values on vCenter instances and vSphere clusters, allowing administrators to detect unexpected state changes that might indicate an improperly concluded maintenance session. vSphere Lifecycle Manager and vSphere Configuration Profiles manage host configuration at a cluster level and can remediate hosts to the desired configuration, confirming that hosts return to their expected state after maintenance. Log Assist performs connectivity validation with a re-validate option to obtain the latest connectivity status for the environment before transferring diagnostic log bundles, which can serve as an additional connectivity check during or after maintenance windows.
+Together, these mechanisms support end-to-end verification of remote maintenance session termination: administrators and automation can explicitly close sessions through documented APIs and cmdlets, audit logs record the termination events, infrastructure-state commands confirm components have exited maintenance mode, connectivity monitoring alerts on orphaned or broken sessions, and configuration drift detection validates that components returned to their expected state after the window closed.</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -8186,36 +8142,27 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>The VCF platform's Consumption layer, through VMware Kubernetes Service (VKS) and vSphere Supervisor, contributes to this control by providing technical enforcement of authorization and a queryable record of who holds maintenance-scoped roles at any point in time.
-Kubernetes RBAC governs access to all operations within the Consumption layer. Roles, ClusterRoles, RoleBindings, and ClusterRoleBindings define what each principal can do within a given scope. Administrative maintenance tasks, such as deploying and managing the lifecycle of Supervisor Services and modifying cluster configurations, are the exclusive domain of vSphere administrators. DevOps engineers and Platform Operators are assigned non-admin or custom roles scoped to specific namespaces rather than platform-level access, authenticated via VCF SSO. This separation is enforced through role assignments, not merely documented in policy.
-VKS clusters integrate with VCF SSO for identity. Users or groups to whom permissions are assigned must exist in the identity source, which means access cannot be granted to principals that no longer exist in the directory. When a user's directory account is removed, VCF SSO integration removes the ability to authenticate, even if a residual role binding remains.
-Administrators can enumerate current role assignments at any time using the Kubernetes RBAC API. The RoleList resource, accessible via GET /apis/rbac.authorization.k8s.io/v1/roles, returns all Role objects in scope. The kubectl auth can-i command with user impersonation allows administrators to determine what actions any given principal can currently perform, supporting periodic authorization reviews. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege and narrow the set of principals authorized to perform maintenance operations.
-VCF Automation provides organization-level RBAC through Organization Administrator, Organization Auditor, Project Administrator, and Project Auditor roles, giving administrators visibility into who holds what permissions across the catalog and deployment layer. Policy assignment views are accessible to Organization Administrator and Auditor roles, supporting authorization review at the consumption layer. Harbor Registry, when deployed as a standard package on VKS clusters, enforces RBAC to govern access to artifacts managed through the platform.
-Kubernetes audit logging records role grant and revocation events, providing a historical record of authorization changes. Where Argo CD is deployed as a Supervisor Service, it maintains a complete history of all configuration changes in Git, supplementing the audit trail for GitOps-managed workloads.
-The control requires that an organization maintain a current list of authorized maintenance organizations or personnel. That list is an organizational artifact rather than a platform function. The Consumption layer's RBAC enforcement, identity integration, and enumerable role bindings support the underlying requirement by providing a queryable record of current authorizations, but organizations must establish the governance process for reviewing and updating that list on a defined schedule.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) 9.1 implements Role-Based Access Control (RBAC) across its components to limit what operations maintenance personnel can perform based on their assigned roles. The Security Services Platform (SSP) defines five roles with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. The Enterprise Admin role has Full Access to all SSP operations, including deployment, management, upgrades, authentication and authorization configuration, server configuration, backup and restore, and Security Intelligence activation. The Security Engineer role has Full Access to export flows, monitoring operations, Security Intelligence data collection configuration, and traffic flow visualization, with Read access only to administrative management operations such as deployment and server configuration. The Security Operator role has Restricted access to segmentation policy and group publishing, discovery and inventory operations, and monitoring functions, with Read access to administrative management operations. Modifying role assignments in SSP requires Admin privileges, so role management itself is access-controlled.
-In multi-tenant environments managed through VCF Automation, the Organization Administrator (Tenant Admin) role has full access to manage, view, and change any vDefend security component, including Transit Gateway (TGW) firewalls, Distributed Firewalls (DFW), and VPC gateway firewalls. This role requires eight specific rights covering DFW Manage/View, TGW Firewall Manage/View, VPC Gateway Firewall Manage/View, VPC Security Profiles Manage/View, and Groups.
-SSP also maintains two predefined local accounts: an admin account with full privileges to access and manage the platform, and an audit account scoped to APIs and services for auditing the system. These built-in accounts provide baseline access separation for administrative and audit functions.
-Mitigating risks from personnel who lack organizational clearances or formal access approvals beyond vDefend's RBAC boundary remains an organizational IAM and HR control outside the product's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -8230,17 +8177,12 @@
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to this control through its role-based access control system, which restricts maintenance-related activities to defined, named accounts. DSM defines two primary roles: the DSM Administrator role and the DSM User role. The Administrator role manages database backups, high availability settings, VM updates, and infrastructure policies. The User role is scoped to provisioning and managing only the objects that the user owns. DSM also supports custom user roles that can be assigned to directory service groups, allowing fine-grained access to the DSM UI for monitoring and management purposes. A vSphere administrator plans, administers, and secures database resources by creating and managing infrastructure policies in DSM. These role boundaries mean that maintenance-capable access is not granted by default and must be explicitly assigned.
-In environments using DSM with VCF Automation, a VCF Automation organization administrator manages the cloud resources allocated to the organization, manages projects and users, and enforces standardized configurations. This role is an additional maintenance-capable persona in integrated deployments, and access can be tracked through the organization's VCF Automation identity management.
-The Permissions view in the DSM dashboard provides administrators with a centralized interface for creating, monitoring, and managing configured users. This view is the operational record of who holds access within the DSM environment. Administrators can use it to review current user assignments and make changes as personnel or responsibilities shift. DSM also supports directory service integration, allowing user accounts and group memberships to be sourced from a directory service. This means that the authoritative list of authorized users can be maintained in the organization's existing identity management infrastructure, with DSM reflecting those assignments through directory-based authentication.
-Software updates to the DSM plug-in require a user with administrator credentials to authenticate to the UI before any update actions can be taken. This access control applies to both manual and automatic update workflows. The Maintenance Policy editor, accessible from the Version &amp; Upgrade section under the DSM System tab, allows administrators to configure when automatic updates are applied without bypassing the requirement for valid administrative credentials.
-DSM adds SQL Server as a supported database type. For SQL Server instances, DSM automatically creates a database user for the cluster administrator login in every database with db_owner role membership, allowing administrators to run maintenance tasks through agent jobs. Administrators can also activate SQL Server Agent configuration to schedule administrative tasks such as integrity checks, index optimization, and statistics maintenance.
-Maintaining the formal list of authorized maintenance organizations or personnel as an organizational record remains an administrative process outside DSM's scope. DSM's RBAC system, Permissions view, and directory service integration provide the technical controls that support that process by making it possible to enumerate and manage who holds maintenance-capable access at any given time. Organizations should reconcile the users visible in the Permissions view against their formal authorization records on a regular basis.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
@@ -8272,84 +8214,57 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to IT Asset Management programs through built-in inventory, discovery, and integration capabilities that provide the technical foundation for asset tracking and governance.
-VCF Operations groups discovered objects logically and provides detailed inventory lists across the environment, covering compute, storage, and networking resources. The inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group.
-The Service Discovery adapter automatically discovers applications, services, and their associated metrics (CPU, memory) running on managed infrastructure. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be exported in CSV format for use in external asset tracking systems.
-For organizations using ServiceNow, VCF provides two integration paths. The Management Pack for ServiceNow in VCF Operations populates the ServiceNow CMDB with discovered resources through the ServiceNow Table API and CMDB Meta API, providing CMDB visibility within VCF Operations. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation provides a structured data source that captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-VCF Automation adds governance through its project model, which controls who can deploy what resources and where those resources are deployed. Projects link users, catalog items, and IaaS resources together. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources.
-Tags within VCF Automation express capabilities and constraints that define deployments. Cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-The broader ITAM program responsibilities of establishing asset governance policies, defining ownership lifecycles, and maintaining organizational accountability remain outside VCF's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to data protection controls by providing network-level security mechanisms that protect data in transit and restrict unauthorized network access to systems where data is stored or processed.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level, restricting which workloads can communicate with data stores, databases, and application tiers. By segmenting the data center network into isolated security zones, vDefend limits the blast radius of a compromise and restricts lateral movement toward systems that hold sensitive data. Administrators define granular firewall rules based on workload identity, security tags, and application-level attributes, limiting access to data repositories to authorized services. Identity Firewall extends policy enforcement to user identity, allowing administrators to define access controls based on which authenticated user initiated the connection rather than solely the source workload, strengthening data access controls in environments with user-based authorization requirements. Security policies are defined, propagated, and enforced across Bare Metal servers through the Security Services Platform (SSP), extending microsegmentation protections beyond virtualized workloads to physical infrastructure connected to the environment.
-The SSP includes Security Intelligence, which identifies risky application protocols that transport data in clear text, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP. This visibility allows administrators to detect and remediate unencrypted data flows that could expose sensitive information in transit. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment flows. Security Intelligence also enables administrators to generate policy recommendations and deploy them in monitor-before-enforcement mode, allowing observation of traffic patterns before applying restrictive rules. The SSP summary panel displays the number of services that are fully protected, partially protected, or not protected, giving administrators a dashboard view of segmentation coverage gaps across the environment.
-IDS/IPS profiles attach to Distributed Firewall and Gateway Firewall rules to inspect east-west and north-south network traffic for signatures and behaviors associated with data theft, command-and-control communication, and exploitation of vulnerabilities in data-handling services. In vDefend, IDS/IPS signature rules support storing TLS/SSL certificates on disk for forensic analysis and threat investigation, providing durable artifacts for post-incident review of potential data exfiltration events.
-Malware Prevention profiles attach to DFW and Gateway Firewall rules and can be configured to send files to the cloud for detailed analysis or to process files locally without cloud connectivity, accommodating environments with data-residency or air-gap requirements. Malware Prevention collects file analysis data including file hash submissions and assigns an Analyst UUID to each submission to track its analysis lifecycle. The Malware Prevention dashboard displays trends of malicious, suspicious, and suppressed file events across the data center, and file verdict filtering allows operators to focus on specific verdict categories such as malicious-only views.
-Network Detection and Response (NDR) anonymizes sensitive customer information when sharing telemetry data to cloud services, providing a built-in data privacy mechanism for environments that enable cloud-assisted threat detection.
-These network security controls complement the data-at-rest encryption, backup, replication, and access management capabilities provided by other VCF components. vDefend does not perform data encryption, classification, backup, or recovery itself, but it protects the network paths and access patterns through which data is stored, replicated, and retrieved.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides replication-based data protection for virtual machine workloads across sites. Protection groups allow administrators to organize virtual machines and datastores under consistent snapshot and replication policies at scale, covering both local recovery via vSAN snapshots and cross-site recovery via vSphere Replication or array-based replication. Protection group membership can be modified after creation, and virtual machines can be automatically enrolled for protection using storage tag selection on designated datastores, reducing manual overhead in maintaining protection coverage across a growing environment.
-PNR introduces an immutability mode for protection groups that, when enabled, prevents the data protection group from being modified or deleted. This mechanism allows administrators to safeguard protection configurations against inadvertent or unauthorized changes. PNR Health monitoring provides consolidated visibility into data protection service health, operation issues for local and replication snapshots, storage utilization, and protection group membership changes, giving administrators a current view of protection posture across the environment.
-Site Recovery Manager (SRM) integrates with vSphere Replication to provide orchestrated failover with configurable recovery point objectives, giving organizations control over acceptable data loss thresholds for protected workloads. PNR supports additional site topologies, including shared recovery site configurations where protected site resources are mapped to isolated datacenters, networks, folders, and datastores on the recovery site. Inventory mappings allow administrators to define resource configurations once and apply them consistently across protection groups.
-vSAN Snapshots and Replication is a native, integrated snapshot-based backup capability for virtual machines running on vSAN datastores, managed through the vSphere Client. It provides VM restore and clone operations from existing snapshots, supporting both rapid recovery from operational failures and ransomware recovery scenarios. Test failover operations allow administrators to validate that recovery configurations are functional before an actual recovery event occurs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that support data protection for managed database instances, covering PostgreSQL, MySQL, and SQL Server databases.
-The most direct contribution is DSM's automated backup framework, which administrators can enable on a per-database basis or through data service policies. When configured, DSM performs scheduled full and incremental backups of database content and stores them in S3-compatible object storage at a configurable backup location. Backup retention is configurable (backup-retention-period), and DSM retains backups of deleted databases until the configured retention period expires, supporting recovery from accidental deletion. For point-in-time recovery, DSM restores a backup to a newly created database VM with a user-specified name and datastore location, and can target the most recent timestamp or a specific point in time. DSM archives binary logs in backup storage as part of its backup protection mechanism. Administrators can also initiate manual on-demand backups of primary PostgreSQL databases to safeguard data before high-impact operations or as immediate protection after major changes. For PostgreSQL multi-site deployments, DSM performs a full backup automatically during a promotion event before resuming the regular schedule.
-Data service policies give administrators control over backup behavior across all databases governed by a policy. Policies can require that databases have automated backups enabled, allow users to opt in, or disallow automated backups entirely. The allowed-backup-locations setting in the data service policy restricts users to selecting from approved backup locations, reducing the risk of backup misconfiguration. Policies can be enforced across multiple tenants and across different namespaces and namespace labels, supporting consistent data protection posture in multi-tenant deployments. A Compliance tab on data service policies displays compliance reports and allows administrators to expand each policy violation to view the noncompliant database, data service, and namespace, giving administrators visibility into where data protection requirements are not being met. In 9.1, data service policies extend to SQL Server databases in addition to MySQL and PostgreSQL.
-DSM implements role-based access control that separates administrative and user-level database access. DSM Admins can create, monitor, and manage all data services in the environment; DSM Users can only manage and monitor the data services they own. This access model limits who can modify backup configurations and policy settings. Infrastructure policies govern which storage resources are available for database VMs, including CPU, memory, storage policies, IP pool, and VM classes, giving administrators control over the storage environment in which data resides.
-Control plane recovery requires that a Provider Backup Repo has been configured at installation time. If the Provider VM fails, the restore-provider command restores it to the latest timestamp. In the VCF Automation context, tenants can perform point-in-time restores directly through the VCF Automation UI, broadening restore access to self-service scenarios.
-One limitation applies: if an incremental backup in the backup chain is deleted, DSM cannot restore the full data; a successful restore from an incremental chain requires the last full backup and all following incremental backups. Organizations must protect the integrity of the backup chain through access controls on the backup storage.
-DSM provides configurable backup, recovery, and policy enforcement mechanisms for managed database instances. The broader data protection program requires organizational decisions about backup schedules, retention periods, backup storage security, and off-site management that DSM does not prescribe on its own.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several application-layer mechanisms that support the implementation of data protection controls within a VCF deployment.
-At the transport layer, Avi performs TLS termination with configurable SSL/TLS profiles for connections between clients and virtual services. The SSL/TLS protocol at the Avi proxy secures data in transit by reducing the risk of unauthorized parties reading or modifying information transferred between end users and application workloads. SSL/TLS profiles are configurable through the Avi Controller UI under Templates &gt; Security &gt; SSL/TLS Profile. Management interface access is further restricted through configuration of allowed ciphers and HMACs for management sessions.
-Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. This allows organizations to store the private keys used in TLS termination and other cryptographic operations within a dedicated hardware key store rather than in software. The Avi Controller also stores sensitive configuration data encrypted in a local database, and backup files can be protected with a passphrase that encrypts the keys included in the backup. Backup and restore operations verify that the FIPS mode of the backup configuration matches the target controller environment.
-Avi's Web Application Firewall (WAF) applies both positive and negative security models to inspect and filter HTTP/HTTPS application traffic. WAF policies support ModSecurity rules for application protection and a Positive Security model that learns application behavior to define allowed request patterns. The Application Rules service, available through the Avi Cloud Console, provides WAF rules specifically designed to address known application vulnerabilities including CVE-tracked issues, with automatic updates to keep rules current. WAF configuration is accessible through the Controller UI under Templates &gt; Security &gt; WAF Policy.
-Avi DataScript provides a programmable layer for enforcing additional data protection behaviors at the proxy boundary. DataScripts are Lua-based scripted rules that allow inspection and manipulation of client HTTP requests and server HTTP responses, supporting content switching, redirection, header manipulation, and logging. DataScript can be used to enforce cipher suite policies by denying clients connecting with unsupported ciphers. DataScript also supports blocklist-based access control by checking client IP addresses against named IP groups and terminating connections from blocked sources while logging the violation. XML-based DataScript use cases can extract client identifiers from request payloads and compare them against configured string groups to restrict access to authorized clients.
-Access to Avi configuration objects is restricted through granular role-based access control (RBAC). Avi supports extended granular RBAC using label-based markers to restrict user permissions to specific resources based on key-value pair matching. The RBAC model differentiates Read and Write access across objects such as SSL/TLS Profiles, PKI Profiles, Authentication Profiles, IP Address Groups, and Health Monitors, allowing organizations to scope access to data protection-relevant configuration to authorized roles only. Roles can also be scoped to tenants through label group associations.
-These mechanisms address data protection at the application delivery layer. Broader organizational data protection controls, including data classification policies, data handling procedures, and data-at-rest protection beyond the Avi proxy boundary, require organizational governance and platform-level capabilities that Avi does not provide as an application delivery controller.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -8581,84 +8496,57 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to IT Asset Management programs through built-in inventory, discovery, and integration capabilities that provide the technical foundation for asset tracking and governance.
-VCF Operations groups discovered objects logically and provides detailed inventory lists across the environment, covering compute, storage, and networking resources. The inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group.
-The Service Discovery adapter automatically discovers applications, services, and their associated metrics (CPU, memory) running on managed infrastructure. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be exported in CSV format for use in external asset tracking systems.
-For organizations using ServiceNow, VCF provides two integration paths. The Management Pack for ServiceNow in VCF Operations populates the ServiceNow CMDB with discovered resources through the ServiceNow Table API and CMDB Meta API, providing CMDB visibility within VCF Operations. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation provides a structured data source that captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-VCF Automation adds governance through its project model, which controls who can deploy what resources and where those resources are deployed. Projects link users, catalog items, and IaaS resources together. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources.
-Tags within VCF Automation express capabilities and constraints that define deployments. Cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-The broader ITAM program responsibilities of establishing asset governance policies, defining ownership lifecycles, and maintaining organizational accountability remain outside VCF's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to data protection controls by providing network-level security mechanisms that protect data in transit and restrict unauthorized network access to systems where data is stored or processed.
-The vDefend distributed firewall (DFW) enforces microsegmentation policies at the vNIC level, restricting which workloads can communicate with data stores, databases, and application tiers. By segmenting the data center network into isolated security zones, vDefend limits the blast radius of a compromise and restricts lateral movement toward systems that hold sensitive data. Administrators define granular firewall rules based on workload identity, security tags, and application-level attributes, limiting access to data repositories to authorized services. Identity Firewall extends policy enforcement to user identity, allowing administrators to define access controls based on which authenticated user initiated the connection rather than solely the source workload, strengthening data access controls in environments with user-based authorization requirements. Security policies are defined, propagated, and enforced across Bare Metal servers through the Security Services Platform (SSP), extending microsegmentation protections beyond virtualized workloads to physical infrastructure connected to the environment.
-The SSP includes Security Intelligence, which identifies risky application protocols that transport data in clear text, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP. This visibility allows administrators to detect and remediate unencrypted data flows that could expose sensitive information in transit. Security Intelligence administrators can monitor traffic leakage between environments, establish exceptions, and implement lockdown protection rules to control inter-environment flows. Security Intelligence also enables administrators to generate policy recommendations and deploy them in monitor-before-enforcement mode, allowing observation of traffic patterns before applying restrictive rules. The SSP summary panel displays the number of services that are fully protected, partially protected, or not protected, giving administrators a dashboard view of segmentation coverage gaps across the environment.
-IDS/IPS profiles attach to Distributed Firewall and Gateway Firewall rules to inspect east-west and north-south network traffic for signatures and behaviors associated with data theft, command-and-control communication, and exploitation of vulnerabilities in data-handling services. In vDefend, IDS/IPS signature rules support storing TLS/SSL certificates on disk for forensic analysis and threat investigation, providing durable artifacts for post-incident review of potential data exfiltration events.
-Malware Prevention profiles attach to DFW and Gateway Firewall rules and can be configured to send files to the cloud for detailed analysis or to process files locally without cloud connectivity, accommodating environments with data-residency or air-gap requirements. Malware Prevention collects file analysis data including file hash submissions and assigns an Analyst UUID to each submission to track its analysis lifecycle. The Malware Prevention dashboard displays trends of malicious, suspicious, and suppressed file events across the data center, and file verdict filtering allows operators to focus on specific verdict categories such as malicious-only views.
-Network Detection and Response (NDR) anonymizes sensitive customer information when sharing telemetry data to cloud services, providing a built-in data privacy mechanism for environments that enable cloud-assisted threat detection.
-These network security controls complement the data-at-rest encryption, backup, replication, and access management capabilities provided by other VCF components. vDefend does not perform data encryption, classification, backup, or recovery itself, but it protects the network paths and access patterns through which data is stored, replicated, and retrieved.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides replication-based data protection for virtual machine workloads across sites. Protection groups allow administrators to organize virtual machines and datastores under consistent snapshot and replication policies at scale, covering both local recovery via vSAN snapshots and cross-site recovery via vSphere Replication or array-based replication. Protection group membership can be modified after creation, and virtual machines can be automatically enrolled for protection using storage tag selection on designated datastores, reducing manual overhead in maintaining protection coverage across a growing environment.
-PNR introduces an immutability mode for protection groups that, when enabled, prevents the data protection group from being modified or deleted. This mechanism allows administrators to safeguard protection configurations against inadvertent or unauthorized changes. PNR Health monitoring provides consolidated visibility into data protection service health, operation issues for local and replication snapshots, storage utilization, and protection group membership changes, giving administrators a current view of protection posture across the environment.
-Site Recovery Manager (SRM) integrates with vSphere Replication to provide orchestrated failover with configurable recovery point objectives, giving organizations control over acceptable data loss thresholds for protected workloads. PNR supports additional site topologies, including shared recovery site configurations where protected site resources are mapped to isolated datacenters, networks, folders, and datastores on the recovery site. Inventory mappings allow administrators to define resource configurations once and apply them consistently across protection groups.
-vSAN Snapshots and Replication is a native, integrated snapshot-based backup capability for virtual machines running on vSAN datastores, managed through the vSphere Client. It provides VM restore and clone operations from existing snapshots, supporting both rapid recovery from operational failures and ransomware recovery scenarios. Test failover operations allow administrators to validate that recovery configurations are functional before an actual recovery event occurs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides several mechanisms that support data protection for managed database instances, covering PostgreSQL, MySQL, and SQL Server databases.
-The most direct contribution is DSM's automated backup framework, which administrators can enable on a per-database basis or through data service policies. When configured, DSM performs scheduled full and incremental backups of database content and stores them in S3-compatible object storage at a configurable backup location. Backup retention is configurable (backup-retention-period), and DSM retains backups of deleted databases until the configured retention period expires, supporting recovery from accidental deletion. For point-in-time recovery, DSM restores a backup to a newly created database VM with a user-specified name and datastore location, and can target the most recent timestamp or a specific point in time. DSM archives binary logs in backup storage as part of its backup protection mechanism. Administrators can also initiate manual on-demand backups of primary PostgreSQL databases to safeguard data before high-impact operations or as immediate protection after major changes. For PostgreSQL multi-site deployments, DSM performs a full backup automatically during a promotion event before resuming the regular schedule.
-Data service policies give administrators control over backup behavior across all databases governed by a policy. Policies can require that databases have automated backups enabled, allow users to opt in, or disallow automated backups entirely. The allowed-backup-locations setting in the data service policy restricts users to selecting from approved backup locations, reducing the risk of backup misconfiguration. Policies can be enforced across multiple tenants and across different namespaces and namespace labels, supporting consistent data protection posture in multi-tenant deployments. A Compliance tab on data service policies displays compliance reports and allows administrators to expand each policy violation to view the noncompliant database, data service, and namespace, giving administrators visibility into where data protection requirements are not being met. In 9.1, data service policies extend to SQL Server databases in addition to MySQL and PostgreSQL.
-DSM implements role-based access control that separates administrative and user-level database access. DSM Admins can create, monitor, and manage all data services in the environment; DSM Users can only manage and monitor the data services they own. This access model limits who can modify backup configurations and policy settings. Infrastructure policies govern which storage resources are available for database VMs, including CPU, memory, storage policies, IP pool, and VM classes, giving administrators control over the storage environment in which data resides.
-Control plane recovery requires that a Provider Backup Repo has been configured at installation time. If the Provider VM fails, the restore-provider command restores it to the latest timestamp. In the VCF Automation context, tenants can perform point-in-time restores directly through the VCF Automation UI, broadening restore access to self-service scenarios.
-One limitation applies: if an incremental backup in the backup chain is deleted, DSM cannot restore the full data; a successful restore from an incremental chain requires the last full backup and all following incremental backups. Organizations must protect the integrity of the backup chain through access controls on the backup storage.
-DSM provides configurable backup, recovery, and policy enforcement mechanisms for managed database instances. The broader data protection program requires organizational decisions about backup schedules, retention periods, backup storage security, and off-site management that DSM does not prescribe on its own.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several application-layer mechanisms that support the implementation of data protection controls within a VCF deployment.
-At the transport layer, Avi performs TLS termination with configurable SSL/TLS profiles for connections between clients and virtual services. The SSL/TLS protocol at the Avi proxy secures data in transit by reducing the risk of unauthorized parties reading or modifying information transferred between end users and application workloads. SSL/TLS profiles are configurable through the Avi Controller UI under Templates &gt; Security &gt; SSL/TLS Profile. Management interface access is further restricted through configuration of allowed ciphers and HMACs for management sessions.
-Avi integrates with Hardware Security Modules (HSMs), including the Thales Luna (formerly SafeNet Luna) HSM, for cryptographic key storage and management. This allows organizations to store the private keys used in TLS termination and other cryptographic operations within a dedicated hardware key store rather than in software. The Avi Controller also stores sensitive configuration data encrypted in a local database, and backup files can be protected with a passphrase that encrypts the keys included in the backup. Backup and restore operations verify that the FIPS mode of the backup configuration matches the target controller environment.
-Avi's Web Application Firewall (WAF) applies both positive and negative security models to inspect and filter HTTP/HTTPS application traffic. WAF policies support ModSecurity rules for application protection and a Positive Security model that learns application behavior to define allowed request patterns. The Application Rules service, available through the Avi Cloud Console, provides WAF rules specifically designed to address known application vulnerabilities including CVE-tracked issues, with automatic updates to keep rules current. WAF configuration is accessible through the Controller UI under Templates &gt; Security &gt; WAF Policy.
-Avi DataScript provides a programmable layer for enforcing additional data protection behaviors at the proxy boundary. DataScripts are Lua-based scripted rules that allow inspection and manipulation of client HTTP requests and server HTTP responses, supporting content switching, redirection, header manipulation, and logging. DataScript can be used to enforce cipher suite policies by denying clients connecting with unsupported ciphers. DataScript also supports blocklist-based access control by checking client IP addresses against named IP groups and terminating connections from blocked sources while logging the violation. XML-based DataScript use cases can extract client identifiers from request payloads and compare them against configured string groups to restrict access to authorized clients.
-Access to Avi configuration objects is restricted through granular role-based access control (RBAC). Avi supports extended granular RBAC using label-based markers to restrict user permissions to specific resources based on key-value pair matching. The RBAC model differentiates Read and Write access across objects such as SSL/TLS Profiles, PKI Profiles, Authentication Profiles, IP Address Groups, and Health Monitors, allowing organizations to scope access to data protection-relevant configuration to authorized roles only. Roles can also be scoped to tenants through label group associations.
-These mechanisms address data protection at the application delivery layer. Broader organizational data protection controls, including data classification policies, data handling procedures, and data-at-rest protection beyond the Avi proxy boundary, require organizational governance and platform-level capabilities that Avi does not provide as an application delivery controller.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -8875,10 +8763,11 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) preserves and integrates with the data-at-rest encryption capabilities of the underlying VCF platform, so that encrypted virtual machines remain protected through replication and recovery operations. The encryption mechanisms themselves, including VM Encryption, vSphere Native Key Provider, external key management servers, and storage policies, are VCF platform capabilities; PNR's role is to maintain encryption continuity through the disaster recovery lifecycle.
-vSphere Replication within PNR supports replication of encrypted virtual machines when vSphere Native Key Provider (NKP) or a common external Key Management Server (KMS) is configured at both sites. When NKP is used, it must be configured manually on both the local and remote sites, and the NKP ID assigned to the encrypted VM on the local site must match the NKP ID on the remote site. NKP enables encryption without requiring a separately deployed external KMS; vSphere Enterprise+ licensing is required for NKP. Replica disks must be located on datastores accessible through at least one host in a VMware vCenter cluster. A VM Storage Policy with VM Encryption enabled must be applied to target disks to enforce encryption continuity during replication configuration. Replication configuration using seed disks together with a vSAN target datastore and a VM Encryption Policy storage policy is not a supported combination.
-Not all PNR replication methods support encrypted virtual machines. vSAN Snapshots and Replication, an alternative replication method within PNR, does not support replication of encrypted VMs. Organizations that require encrypted VM replication should configure protection groups using vSphere Replication rather than vSAN Snapshots and Replication.
-vSphere Replication also supports optional network encryption of replication traffic, which can be enabled during replication configuration to protect data in transit between source and target sites.</t>
+          <t>VCF Protection and Recovery (PNR) implements cryptographic protections for data in transit and at rest across its replication and recovery infrastructure, providing an alternative to physical safeguards for protecting disaster recovery data.
+PNR appliance communications are protected by TLS. PNR defaults to a modern, high-security TLS protocol version for its web endpoints, with the minimum acceptable protocol version configurable by administrators through the envoy-proxy-config.json file by setting the tls_minimum_protocol_version parameter. When the minimum protocol version is changed, the configuration must be updated consistently across all relevant locations within the system. TLS certificates and private keys protect network communication and establish authenticated connections with paired site components. The protocol version in use can be verified using standard SSL/TLS diagnostic tools against the appliance management endpoint.
+Replication traffic between protected and recovery sites can be encrypted in transit. PNR supports network encryption of replication data as a configurable option, protecting replicated data traversing inter-site network links without requiring physical isolation of those links.
+PNR maintains the cryptographic protections of virtual machines throughout the protection, replication, and recovery lifecycle. Protection groups using array-based replication and vSphere Replication both support the protection and recovery of encrypted virtual machines. Encryption covers virtual machine disks and related files, preserving the at-rest protection of replicated workloads at the recovery site.
+PNR log files are designed to exclude sensitive cryptographic material. Log entries do not contain private keys or passwords, limiting the potential for unintended credential disclosure through operational logging. For encrypted virtual machines, the supported protection group types are array-based replication and vSphere Replication; Virtual Volumes protection groups are not among the protection group types available for encrypted virtual machines.</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
@@ -9111,7 +9000,7 @@
 Backup automation through APIs
 VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
 Disaster recovery planning
-For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VMware Live Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
 VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
         </is>
       </c>
@@ -10173,15 +10062,16 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>VCF provides centralized software and firmware patching across the entire infrastructure stack through VCF Operations and vSphere Lifecycle Manager, which together form a unified lifecycle management plane. VCF Operations is the central orchestration point for patching and update operations, coordinating patch releases (such as 9.0.1.0100) that deliver time-sensitive fixes to security and operational issues between major, minor, and maintenance releases.
-VCF uses a desired-state model for host remediation through vSphere Lifecycle Manager (vLCM). Administrators define a software specification for each cluster, and vLCM brings all hosts into compliance with that specification during remediation. This approach applies uniformly to VMware-supplied components and third-party solutions alike. To make a third-party solution available on a cluster, administrators create a software specification containing the solution and remediate all hosts with that image. vLCM manages software updates for VMware ESX hosts, including patches of the ESX base image, OEM add-ons, components from different software vendors, and VMware Tools updates. Dynamic patch baselines automatically adjust their contents based on specified criteria each time Update Manager downloads new patches, keeping remediation current without manual baseline maintenance. Fixed baselines are also available for environments that require explicit control over which patches are applied. Hardware Support Manager (HSM) plugins extend vLCM to manage vendor-specific firmware and driver updates alongside software patches, providing unified lifecycle management for both software and firmware from within the same interface. Firmware updates through Hardware Support Manager are only available for clusters and hosts managed with vSphere Lifecycle Manager images; hosts managed with baselines do not support firmware updates through this mechanism.
-The remediation workflow is coordinated through multiple layers. Coordinator Manager runs pre-checks before remediation begins to evaluate how each host in the cluster is affected and whether additional steps are needed. Pre-checks verify component connectivity, version compatibility, and component status. The ESX Updater Manager then handles the actual remediation on each host. Coordinator Manager also allows administrators to query the status of the remediation operation for the cluster and for each individual host, providing centralized visibility into remediation progress. The VCF Operations cluster transition specification includes a remediationOptionsSpec with a configurable remediationFailureAction that supports automatic retry with adjustable retryCount and retryDelay parameters, allowing administrators to define consistent remediation behavior.
-VCF Operations extends lifecycle management with patch planner functionality for VCF core components, including the ability to download and manage upgrade, patch, and install binaries. Pre-update validation performs health checks and compatibility verification before patches are applied, and component interdependency management helps maintain compatibility and stability across the infrastructure during updates. All dependent elements related to package objects are added to packages automatically to help maintain compatibility between versions. VCF Operations also provides compliance management capabilities that detect violations, highlight risk areas, and provide actionable remediation recommendations, with out-of-the-box workflows mapped to recommendations and associated with specific alerts for automated remediation.
-VCF supports programmatic management of the patching process through multiple interfaces. The VMware vCenter patching API supports discovery of all available and applicable updates for vCenter instances in the environment, including minor in-place updates and major migration-based updates. REST API endpoints provide operations for checking pending updates, requirements checking, staging, and installation. The life cycle management API provides operations for listing all available updates and upgrades and generating a pre-check compatibility report before applying updates. The vSphere Automation REST API allows administrators to query effective global and cluster-specific remediation policies before initiating remediation, and the Update-Entity operation remediates hosts by applying baselines with configurable failure handling and retry behavior. PowerCLI provides the Update Manager module with cmdlets for downloading software patches, creating and modifying baselines, and scanning and remediating hosts, including a Test-Compliance command to verify entities against downloaded patches. The vCenter Appliance itself can be patched via the vCenter Appliance Management Interface (VAMI) or the appliance shell; VMware distributes vCenter patches in two forms, ISO-based and URL-based, and the `software-packages` utility in the appliance shell supports both methods, including staging patches from a repository URL, installing directly from a URL without staging, or installing from an attached ISO image. These interfaces enable integration with external change management and orchestration systems for automated remediation workflows.
-VCF includes several capabilities to reduce patching risk and support continuity during updates. Live Patching updates and restarts discrete components without requiring host evacuation or reboot, as vSphere Lifecycle Manager does not place hosts into maintenance mode when a Live Patch is enforced. Snapshots should be created before patching VCF Operations fleet management to provide a rollback path. VCF supports Ensure Accessibility maintenance mode for vSAN storage clusters, which evacuates data to maintain object accessibility during updates through durability components. The VCF Download Tool supports a patches-only option and offline depot configuration for managing patch binaries in air-gapped environments.
-VCF Operations complements patch application with patch-gap detection for server firmware. It monitors hardware properties across the fleet, including BIOS version and BIOS release date, and provides dashboards that flag hosts running outdated server BIOS. This detection capability helps administrators identify hosts that require firmware patching before they become a compliance or security gap.
-The VCF Consumption layer, implemented through vSphere Supervisor and VMware Kubernetes Service (VKS), extends this patching coverage to Kubernetes control plane components and cluster add-ons. VKS clusters use a rolling update model where updates are initiated by changing the cluster specification; the Supervisor reconciler applies changes node by node to maintain cluster availability during the process. This model covers control plane components including kube-apiserver, kube-controller-manager, kube-scheduler, etcd, kubelet configuration, and CoreDNS, all updated through the kubeadm upgrade mechanism. Kubeadm supports targeted patching of individual components through a patches directory; files named with the pattern `target[suffix][+patchtype].extension` (for example, `kube-apiserver0+merge.yaml` or `etcd.json`) apply strategic merge patches, merge patches, or JSON patches to the specified component. The patches mechanism is available through the InitConfiguration, JoinConfiguration, and UpgradeConfiguration APIs, providing consistent patching behavior across cluster initialization, node join, and upgrade operations. Instance-specific patches can also be applied over the base KubeletConfiguration through kubeadm customization.
-VKS clusters support add-on management that enables installation and updates of standard packages through versioned add-on repositories. Administrators can track and update packages such as istio, harbor, sriov-network-device-plugin, windows-gmsa-webhook, and vsphere-pv-csi-webhook as new versions become available. For container image currency, Harbor is available as a Supervisor service and provides vulnerability scanning and content trust capabilities to help identify images that require patching. Admission controllers, including validating webhooks and image pull policies, can be configured to restrict deployment of images that have not passed vulnerability scanning or that contain known vulnerabilities, integrating image patch compliance into the workload deployment workflow. Content library VM images deployed in the vSphere Supervisor environment should be created with the latest patches and required security settings aligned with organizational security policies. Security Technical Implementation Guides (STIGs) are available for Supervisor and VKS node releases (VKrs), providing prescriptive hardening guidance that defines what patches and configurations constitute a compliant deployment for the Kubernetes consumption layer.</t>
+          <t>VCF provides integrated lifecycle management that addresses new threats and vulnerabilities on an ongoing basis through a structured release model, centralized update orchestration, proactive vulnerability detection, configuration drift monitoring, and automated node health remediation for containerized workloads.
+VCF follows a tiered release cadence consisting of major, minor, maintenance, and patch releases. Major and minor releases are fully synchronized across all VCF core components, following a unified consumption pattern that advances the entire platform to a new, consistent feature level. Maintenance releases are scheduled, cumulative updates focused on platform stability, providing bug and security fixes, hardware enablement changes, driver updates, guest OS support, and backward-compatible new features with limited scope to minimize operational impact. Patch releases provide time-sensitive fixes to security and catastrophic issues impacting business operations, and can be applied selectively to individual components without requiring synchronized updates across the full stack.
+VCF Operations orchestrates centralized lifecycle management for the entire VCF stack, including pre-update validation with health checks and compatibility verification, update bundle management with download and staging for both online and offline environments, and component interdependency management that respects dependencies between VCF components during updates. VCF Operations requires a precheck to succeed before scheduling upgrades, and requires acknowledgment of any errors or warnings in the precheck report before proceeding. The upgrade planner allows administrators to select any supported version for each VCF core component, including specific patch versions and VCF Bill of Materials versions. When connected to an online or offline depot, binaries for the target versions of each core component can be downloaded in preparation for upgrading or updating. VMware Kubernetes Service (VKS) cluster version upgrades are managed through this same VCF lifecycle management framework, providing a controlled path for remediating vulnerabilities in the Kubernetes control plane and node components. The VCF Automation Provider Management UI exposes a VKS cluster management interface that verifies cluster management functions and overall health status across all elements.
+For vCenter specifically, administrators can automate the installation of software updates to keep the system stable and protected, including automated checks for new updates and staging of updates through update policies that reduce waiting time. VCF Operations Marketplace displays the latest published version of each management pack by default and provides a version selector to view all available versions or choose a different version to download. VMware provides proactive notification when management packs are updated to maintain compatibility, emailing customers on older versions when a new update is released.
+VCF supports rollback capabilities for updates. vCenter RDU upgrades perform automatic rollback if the upgrade fails. VCF Operations HCX supports rollback using vSphere snapshots if an unexpected issue in a new version cannot be resolved in a timely manner. Live Patching capabilities allow security updates to be applied to ESX hosts without requiring a host reboot, reducing maintenance windows and accelerating the deployment of time-sensitive security fixes. For containerized workloads running on VKS, Kubernetes Deployments support rolling updates that allow workload operators to replace container images with patched versions while maintaining service availability; rolling update strategies limit the number of unavailable pods during an update, and Kubernetes tracks revision history to support rollback if a patched image introduces regressions.
+vSphere Lifecycle Manager (vLCM) manages the full software and firmware lifecycle for ESX hosts. vLCM images can have firmware add-ons added, replaced, removed, upgraded, or downgraded, enabling vendor-specific firmware and driver management alongside software updates. Administrators can initiate ESX host remediation manually or schedule recurring remediation tasks to run during defined maintenance windows, supporting a consistent patch deployment cadence. Build recommendations for vSAN and other components include all patches and driver updates for the current release, giving administrators a clear target for what constitutes the latest stable configuration. VCF supports Ensure Accessibility maintenance mode for vSAN storage clusters, using durability components to maintain data availability during updates.
+At the Kubernetes layer, MachineHealthCheck provides an automated remediation mechanism for VKS workload clusters that is equivalent to scheduled host remediation at the infrastructure layer. MachineHealthCheck monitors node health and automatically replaces nodes that fall outside defined health thresholds, with configurable parameters including max-unhealthy (which prevents mass remediation when the number of degraded nodes exceeds a specified absolute count or percentage), node-startup-timeout, and unhealthy-conditions to define what constitutes a degraded node. In ClusterClass-based VKS clusters, the machineHealthCheck.enabled parameter activates this capability. The VCF CLI provides vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands to inspect the current health status of worker and control plane nodes, and MachineHealthCheck specifications can be updated via kubectl patch with JSON merge patch for ongoing policy adjustments.
+VCF Operations Diagnostics automatically detects known issues and critical vulnerabilities within the VCF software stack, providing descriptions, root cause insights, and actionable remediation steps. Broadcom publishes security advisories for critical known vulnerabilities with step-by-step remediation instructions. VCF documentation explicitly recommends keeping infrastructure up to date by running current component versions as part of operations best practices, noting that running outdated components that are too far behind the latest version can cause support problems, upgrade problems, and higher operating costs, and that fixes for known issues are often only available in later versions. The vSphere documentation also recommends that organizations run vulnerability scans against their systems and applications on a defined schedule and document the frequency of scanning as part of ongoing vulnerability management. This guidance extends to individual platform services, with specific recommendations to run the latest version of VCF Operations for Networks for security fixes for all known vulnerabilities, and to upgrade VCF Operations HCX when updated releases become available to have the most recent fixes and security patches. At the container image level, the Harbor registry integrated with the VKS Supervisor cluster provides vulnerability scanning, content trust, and policy-based replication to support the security and integrity of containerized workloads. Kubernetes operational guidance recommends that container images be regularly scanned during creation and in deployment and that known vulnerable software be patched as part of an ongoing practice. VKS Cluster Management Policy Insights surface compliance findings with direct links to the affected cluster, project, and policy to streamline the remediation workflow. VCF Supervisor documentation also recommends creating VM images with the latest patches and required security settings for production environments.
+VCF uses Configuration Profiles and Image-Based Lifecycle Management to periodically assess host configuration against a desired state. VCF Operations provides unified configuration management that enables scheduled drift detection for vCenter and cluster objects to proactively detect configuration deviations from the desired state. When drift is detected, the system alerts administrators. VCF Operations compliance management detects violations, highlights risk areas, and provides actionable remediation recommendations. Depending on the severity of non-compliance, administrators can configure automated remediation actions to bring objects back into compliance.
+Security and operations teams can use the management interface, CLI tools, and APIs to automate security posture assessment and remediation workflows, including integration with third-party monitoring and SIEM tools for continuous vulnerability awareness.</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -10214,12 +10104,14 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) provides a structured update management workflow for the DSM plug-in and the database services it manages. Software updates must be obtained from the Broadcom Support Portal and uploaded into the DSM environment before deployment, establishing a controlled software intake process. Plug-in and database template software updates can be initiated by a vSphere administrator or a DSM user in the DSM Admin role.
-The update process includes a staged review step before administrators initiate installation. Updates can be checked and initiated directly from the DSM UI or managed from the vSphere Client. The upgrade process is designed to attempt at least one complete chain of software updates regardless of the configured maintenance window duration, reducing the risk of a partially applied update chain. When automatic updates are enabled, DSM retries the update a maximum of three times, with a 10-minute interval between each attempt during the configured maintenance duration. If automatic plug-in updates fail, DSM supports manual updates as a fallback.
-For automated patching, DSM provides a configurable Maintenance Policy that allows administrators to schedule automatic software updates for DSM Provider Appliances. The policy specifies a start date, a start time, and a duration window, and is accessible from both the DSM UI and the vSphere Client. The maintenance policy can be edited during the 10-minute interval between automatic update attempts, which cancels the next scheduled attempt and applies the updated configuration.
-For database engine patching, DSM supports database version upgrades, including major version upgrades of PostgreSQL. Minor version database upgrades can be configured to run automatically during maintenance windows and may include CVE fixes, bug fixes, and performance improvements. For SQL Server databases managed by DSM, administrators can define maintenance windows for operating system patching.
-When deploying DSM through the Consumption Operator, the deployment process includes Signature Verification to validate package integrity before installation.
-DSM provides the tooling to manage patching of the DSM platform and its managed database services. Patching of the underlying VCF infrastructure (VMware ESX hosts, VMware vCenter, NSX, storage systems, firmware) is handled through VCF's lifecycle management capabilities and falls outside DSM's scope. An organizational patch management program is needed to track patch applicability, establish patch windows across all technology assets, test patches before production deployment, and verify successful application across the full environment.</t>
+          <t>VMware Data Services Manager (DSM) supports continuous vulnerability remediation through software update management, patch scheduling controls, and infrastructure health monitoring, though the broader organizational processes for vulnerability identification, tracking, and lifecycle management fall outside DSM's direct scope.
+DSM provides a Maintenance Policy that controls the scheduling and duration of software updates to the DSM plug-in. Administrators configure this policy from the vSphere Client under "Managing Data Services Manager Plug-in Software Updates," setting the duration window for applying software updates. Upgrade operations performed during the maintenance window may include CVE fixes, bug fixes, and performance improvements, making the maintenance window the primary vehicle for applying security-relevant patches to the database platform. The documentation also recommends always using database versions with the latest DSM components to maintain optimal performance and security.
+Administrators who deploy DSM through VCF Automation can configure maintenance windows with greater granularity. The Monthly Occurrences setting allows selection of a specific day and one or more occurrences of that day within the month; if no specific occurrence is selected, the maintenance window runs on a weekly cadence by default.
+For SQL Server workloads, DSM introduces per-engine maintenance windows for operating system patching, configurable by SQL Server administrators within the DSM UI. The documentation recommends that SQL Server instances follow the Cumulative Update (CU) branch, which packages functional, performance, and security updates for each major version, keeping the data service current with vendor-issued fixes.
+The DSM controller monitors component and feature dependencies continuously, performing automated remediation when dependency status violations are detected. This mechanism also manages compatibility requirements when upgrading DSM within a VCF environment.
+For ongoing health visibility, DSM generates alerts across multiple categories that surface conditions requiring remediation attention. Administrators can configure alert threshold values for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters, with separate thresholds for warning and critical severity. Infrastructure compliance is monitored through alerts such as INFRASTRUCTURE_POLICY_VC_ALARMS, which fires when active infrastructure resource alarms are detected in vCenter. When alerts trigger, DSM provides guidance to help administrators identify underlying causes; administrators are advised to verify active vCenter alarms before performing maintenance or scale operations and to resolve active CPU or memory alarms on ESX hosts before scaling database instances.
+DSM integrates with VCF Operations, which automatically discovers and monitors PostgreSQL and MySQL database clusters in the Ready state. When configured, VCF Operations displays performance data at three levels: cluster-level for overall health, node-level for infrastructure resource utilization, and database-level for KPIs such as Active Connections, Commits, Rollbacks, and Deadlocks. This integration provides operational visibility that supports remediation workflows.
+Continuous vulnerability remediation also depends on activities outside DSM's direct scope. Identifying new CVEs and vulnerabilities in the database engines that DSM manages (PostgreSQL, MySQL, SQL Server, MinIO), evaluating their applicability to a specific deployment, prioritizing remediation, and tracking remediation status all require organizational vulnerability management processes and tools. Organizations should integrate DSM update notifications with their broader patch management workflows and maintain a vulnerability management program covering both the DSM management plane and the database engines it provisions.</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
@@ -10229,14 +10121,14 @@
       </c>
       <c r="N110" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides dedicated patch management mechanisms for its two primary components: the Avi Controller (the management and control plane) and Service Engines (the data plane VMs that handle application traffic). The Controller is the central point through which patches are delivered and applied to both component types.
-Patch images are uploaded to the Controller via the REST API or through the CLI. Once a patch image is available, operators select from four patching modes: Controller Patch, SE Group Patch, System Patch, and Disruptive Patch. The patch segroup command accepts an se_group_refs parameter to target a specific Service Engine group for patching; when se_group_refs is not specified, all Service Engine groups are patched. If more than one Service Engine group requires patching, each group requires a separate patch command.
-A best practice in 9.1 is to apply patches only to the Service Engine groups that require them, using Service Engine group segmentation to scope patching operations rather than applying patches system-wide when not necessary. Patch packages are selected based on the current Controller and Service Engine versions.
-Before applying Controller patches, the system runs pre-checks that validate patch compatibility. These checks use the SYSERR_CHECK_CONTROLLER_PATCH_COMPATIBILITY mechanism to confirm the patch is appropriate for the installed version. Pre-check status and progress are accessible via Administration &gt; Update &gt; System, and a dry run option is available for upgrade operations to verify object operational state before the patch is applied.
-Patches within a given patch family are cumulative. Patch 1p2 contains all fixes from 1p1 plus its own new fixes, and 1p3 includes all fixes from both 1p1 and 1p2. This design means an operator applying the latest patch in a family receives all prior fixes without needing to apply them sequentially. Applying a patch from a different patch family once one family is already in place is not advisable, and once a patch from a specific series is applied, all entities in the system can only be upgraded to patches within that series or higher.
-For REST API-driven workflows, the Controller supports asynchronous patch operations that queue and consolidate patch requests at fixed intervals. This approach reduces latency during high-rate configuration updates and is recommended for large Avi deployments.
-Avi also supports virtual patching for application-layer vulnerabilities through its Web Application Firewall (WAF). Operators can import Dynamic Application Security Testing (DAST) scanner results into the WAF to identify and help block exploitation of known application vulnerabilities while formal software patches are being developed and tested.
-Patching of the underlying VCF platform infrastructure on which Avi's Controller and Service Engine VMs run, including compute hosts, storage, and networking components, is handled by VCF lifecycle management and is reflected in VCF Coverage.</t>
+          <t>VMware Avi Load Balancer (Avi) contributes to continuous vulnerability remediation through several application-layer mechanisms that address evolving threats as they are identified.
+The Avi WAF includes a Core Rule Set structured around CVE-based signature rules. As vulnerabilities are publicly disclosed and assigned CVE identifiers, rules targeting those vulnerabilities can be incorporated into the rule set, allowing the WAF to block requests matching known exploit patterns. Avi WAF also supports a Positive Security model that reduces the attack surface by permitting only known-good traffic patterns rather than relying solely on signature detection. Traffic that falls outside defined allowed patterns is blocked by default, which provides protection against newly discovered attack variants that have not yet been added to signature databases.
+The 9.1 release introduces a Live Security Threat Intelligence service, available through the Avi Cloud Console, that delivers real-time security threat feeds covering known vulnerabilities in over 5,000 applications including WordPress, Drupal, and Apache. The Application Rules Service, part of Live Security Threat Intelligence, provides rules specifically designed to block attacks on known application vulnerabilities with CVE assignments. These rules are automatically updated as new vulnerabilities are disclosed, giving organizations a continuously refreshed layer of protection at the application delivery boundary without requiring manual rule management.
+Avi supports virtual patching through integration with Dynamic Application Security Testing (DAST) scanners. Administrators can import scan results from supported scanners such as OWASP ZAP Attack Proxy and Qualys Web App Scanning into the WAF to identify and address potential security issues in applications. This allows known vulnerabilities discovered during scanning to be mitigated at the load balancer before application-level patches are applied.
+Avi cipher scores are updated as new cryptographic vulnerabilities are discovered. When a cipher's score changes to reflect a newly identified weakness, the security penalty applied to affected virtual services changes, signaling to administrators that reconfiguration may be needed to maintain an acceptable security posture. The security penalty component also detects and reports active DoS attacks and SSL configuration vulnerabilities in real time. Avi publishes responses to notable CVEs affecting Avi Load Balancer or software it uses, such as SSL and Linux libraries.
+The IP Reputation service provides ongoing threat intelligence by classifying source IP addresses across active threat categories including DoS/DDoS attacks, malware-infected hosts, phishing sites, proxy services, cloud origins, mobile threats, Tor exit nodes, and general network threats. Administrators can attach an IP Reputation Database to virtual services through Network Security Policy, including the System-IPReputation-Webroot-DB option, which draws on Webroot threat intelligence. Webroot publishes a full IPv4 and IPv6 database daily and pushes incremental IPv4 updates every few minutes, keeping the threat intelligence current. An "All threats" classification is also available, allowing Avi to act on traffic from any suspicious source regardless of specific category.
+Alert Actions can trigger ControlScripts in response to system events, enabling automated remediation actions in place of manual administrator intervention.
+These mechanisms allow Avi to address application-layer threats at the proxy boundary as the threat landscape changes. Full satisfaction of this control requires an organizational vulnerability remediation program covering patch scheduling, remediation tracking, and scope decisions across all assets in the environment.</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10259,13 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides automated IoC identification and alerting through IDS/IPS signature matching, Network Detection and Response (NDR) event correlation, and Malware Prevention file analysis with threat scoring, all accessible through the Security Services Platform (SSP) interface.
-The NDR Campaign Blueprint presents an interactive graph visualizing correlated security events that maps the different stages of an attack. Graph nodes represent Threats, Custom IDS Signatures, and Indicators of Compromise. The IoC Summary for each File IOC and Malware IOC presents file score, verdict, SHA hashes, and a View Reports link; directional arrows indicate when a workload is affected by an IoC, and node colors reflect severity based on the highest impact score from associated detections. The Campaign Blueprint's Triage and Investigate feature allows filtering detections by threat, affected workload, or MITRE tactics, enabling security teams to scope the impact of detected IoCs.
-The IDS/IPS Monitoring page provides a timeline graph visualization of intrusion events, with colored dots indicating unique event types and dot size indicating event frequency over a selectable time span. Events can be filtered by severity rating: Critical, High, Medium, Low, or Suspicious. Security Intelligence within the SSP provides a visualization canvas displaying granular IDS/IPS event data, including a blast radius view that highlights affected connections and can be filtered by specific signature ID. The SSP also collects and provides IDS/IPS metrics to monitor the readiness and performance of vDefend IDS/IPS across the environment. vDefend IDS/IPS maintains a detailed event log on ESX hosts capturing all alerts, drops, and rejects with metadata including source port, destination IP, IP protocol, and timestamps.
-The Threat Monitoring dashboard in the Security Services Platform displays file event statistics and recently detected threats, providing summary-level visibility into Malware Prevention activity. An alarm is triggered on the Security Overview dashboard when dropped events are detected, alerting administrators via both the alarm page and a notification banner, and the alarm remains active until no dropped events are detected.
-NDR integrates with external SIEM platforms, including VCF Log Management and Splunk, sending campaign and event logs as they occur. Events forwarded to the SIEM include new detections, detection updates, and new campaign creation, supporting automated alerting to organizational monitoring infrastructure. Security Intelligence also continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic.
-To configure IoC monitoring in a vDefend deployment: enable IDS/IPS profiles on Distributed Firewall rules, configure NDR in the Security Services Platform, enable the Malware Prevention service, and configure SIEM integration under NDR settings to receive real-time event forwarding.</t>
+          <t>VMware vDefend supports threat hunting at the network layer through Network Detection and Response (NDR), Security Intelligence campaign correlation, and IDS/IPS detection capabilities.
+NDR correlates related detection events into campaigns and organizes threat events into a timeline that security analysts can view and triage by correlating threat signals. A campaign provides a view of a threat by correlating detection events to identify the different stages of an attack, and security teams can investigate individual threat events and correlated campaigns to assess impact, identify root causes, and take appropriate mitigation actions.
+The Campaign Blueprint graph in Security Intelligence visualizes IoC relationships as directed connections, displaying node information that includes Threats, Custom IDS Signatures, and Indicators of Compromise (IOC). Nodes represent relationships such as "IOC for Threat" (a connection from an Indicator of Compromise to a threat) and "Source of Threat" (traffic flowing from a workload to a threat, indicating the workload is the origin). Campaign Correlation Rules assign impact scores ranging from 0 through 100, with 100 indicating highest severity, and can escalate combinations of lower-severity detections based on correlation logic, enabling analysts to prioritize their investigation queue.
+The Security Intelligence blast radius view helps analysts determine whether a detection represents a targeted attack on specific systems or a widespread campaign affecting multiple parts of the infrastructure. The threat visualization canvas supports rapid threat containment, compromised asset identification, and microsegmentation policy adjustment. IDS/IPS events and NDR findings support date range filtering for temporal analysis of security events and intrusion attempts.
+Custom IDS/IPS signatures can be added to profiles and applied to Distributed Firewall or Gateway Firewall rules to encode known IoC patterns directly into detection policy. The signature language supports DNP3 application data object matching for industrial control system threat detection. Threat Event Monitoring provides visibility into intrusions detected based on custom signatures, and the IDS/IPS Monitoring page lets administrators view details of actions taken when rules are triggered. IDS/IPS logs include the category of the detected threat along with other structured metadata for analyst triage.
+The Security Overview Dashboard includes a Threat Event Monitoring view that provides insights about the current state of security issues in the data center, helping security teams understand network activity and focus investigation areas. Suspicious Traffic detection through Network Traffic Analysis detectors is part of the vDefend Advanced Threat Prevention capability set.
+vDefend contributes the network-layer visibility, detection, and correlation capabilities for threat hunting; broader orchestration, endpoint telemetry, and analyst workflows remain outside its scope.</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -10798,17 +10691,23 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in mechanisms for implementing and governing network security controls across the infrastructure stack, spanning virtual switching, network segmentation, policy management, role-based access control, audit logging, and documented hardening procedures.
-NSX, the networking component of VCF, delivers a hierarchical security policy framework organized around domains, security policies, and individual rules. Each rule can be configured with action, direction, IP protocol, source groups, destination groups, services, and scope, providing administrators a structured and repeatable model for defining network security posture. Security policies are organized into categories (Emergency, Infrastructure, Environment, Application) so that multiple administrators can create and manage policies without conflicts or overrides. Firewall rules within each category are organized into sections, supporting logical grouping and ordered evaluation. This hierarchical structure supports both centralized governance and delegated administration, allowing organizations to maintain consistent security standards while enabling application teams to manage policies within their assigned boundaries.
-VCF's network security governance model is built on role-based access control (RBAC) that spans networking and security functions. NSX Projects and VPCs support scoped role assignments including VPC Admin, Security Admin, Network Admin, Security Operator, and Network Operator roles. These roles can be assigned at the project or VPC level, enabling least-privilege access to network security configuration. A VPC Admin has full access to networking and security objects within their assigned VPC, while Enterprise Admins retain overarching control. NSX Advanced Network Management extends RBAC to specific networking components including static routes, locale services, segments, segment profiles, IP address pools, forwarding policies, DNS, DHCP, load balancing, and NAT. This separation of duties allows organizations to delegate day-to-day network security operations while retaining centralized oversight.
-The NSX VPC workflow provides a structured mechanism for implementing network security controls at the application level. Application owners can add subnets inside their assigned VPC and configure security policies to meet workload requirements without dependency on the Enterprise Admin. VPC Admins and Security Admins add security policies within the VPC to address the security requirements of connected workloads. Default East-West firewall rules are activated automatically when an appropriate security license is applied and can be adjusted as needed. This self-service model, bounded by RBAC, allows security policy implementation to scale across the organization while maintaining governance guardrails.
-VCF includes multiple layers of network security controls. VMware vDefend, a separately licensed product that extends NSX, provides Distributed Firewall enforcement across deployment and operational scenarios, while its Gateway Firewall provides perimeter security. Context profiles and Layer 7 access profiles enable firewall rules with application-level and domain-based attributes for both distributed and gateway firewall enforcement. For containerized workloads, the Antrea Container Network Interface (CNI) plugin in VMware Kubernetes Service (VKS) enforces Kubernetes NetworkPolicy at the namespace and pod level. The AntreaPolicy feature gate enables AntreaNetworkPolicy and ClusterNetworkPolicy objects that extend standard NetworkPolicy with richer Layer 4 rule sets; traffic not explicitly permitted is blocked by default when a policy applies to a pod. The Antrea NetworkPolicyStats feature gate collects enforcement statistics, giving operators visibility into which policies are matching traffic and at what volume to support operational monitoring and periodic policy review. A Kubernetes cluster must provide and enforce NetworkPolicy for network security controls to be effective.
-The VKS networking layer within VCF integrates directly with the broader NSX security framework. Supervisors using NSX VPC networking operate in the system VPC while VKS clusters reside in vSphere Namespace VPCs, providing topology-level isolation between the management plane and workload clusters. NSX VPC pod IP pools are configured as Private, restricting direct external accessibility of pod addresses. Antrea EgressSeparateSubnet allows egress traffic from specific workloads to originate from a subnet distinct from the default node subnet, supporting more granular traffic segmentation. The Network Control Plane (NCP) component bridges Kubernetes networking objects with NSX, realizing VirtualNetwork, VirtualNetworkInterface, and LoadBalancer resources for the VKS control plane; communication between Supervisor and NSX is secured using TLS. Kubernetes control plane services communicate using certificates by default, and connections from nodes and pods to the control plane are secured by default and can run over untrusted networks. Supervisor networking architecture requires a deliberate deployment-time choice: NSX with embedded load balancer, or vSphere Distributed Switch with external load balancer. This choice determines which network security mechanisms are available downstream, and organizational procedures should reflect which path is in use. VKS Cluster Management Custom Policies provide a governance mechanism that should be reviewed and updated to ensure policy logic reflects current security and operational requirements. The Argo CD Supervisor Service deployment implements network segmentation and firewall rules to secure communication between its components. Organizations operating service meshes alongside VKS gain OSI Layer 7 network policies based on workload identity and mutual TLS encryption for pod-to-pod traffic, providing an additional isolation layer beyond namespace boundaries.
-At the virtual infrastructure layer, vSphere Distributed Switches provide centralized management of virtual networking, handling traffic for all associated hosts in a data center. Distributed switches support network segmentation using Private VLAN (PVLAN) and VLAN-based SPAN for distributed port mirroring. Network segmentation is built into the VCF architecture: management traffic, vMotion, and storage traffic are isolated on separate networks. Network I/O Control allocates bandwidth to traffic types based on share values, and the Storage Traffic Separation network profile creates dedicated vSphere Distributed Switches with separate physical NICs for storage traffic isolation. NSX distributed port groups and uplink port groups support Traffic Filtering and Marking policies configurable at the port level, providing additional granularity for layer 2 security controls. ESX hosts also support IPsec for VMkernel network communication, with security associations and policies configurable via esxcli network ip ipsec commands, supporting both transport and tunnel mode with upper layer protocol filtering for tcp, udp, icmp6, or any traffic.
-vSphere Lifecycle Manager enforces desired-state configuration for hosts and clusters, applying and remediating configuration to match the defined software specification. This helps detect and address configuration drift that could weaken network security posture, and the remediation process can be managed programmatically through the vSphere Automation API.
-VCF publishes security baselines through the Security Configuration Guide and DISA STIGs. The NSX Security Configuration Guide provides documented procedures for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes. Recommendations cover configuring strong authentication, implementing RBAC, and securing administrative access. NSX security best practices address creating and managing security groups, implementing distributed firewalling, configuring security policies, and enforcing microsegmentation to control network traffic. Security Technical Implementation Guides for Supervisor and VMware Kubernetes Release (VKr) components are available to provide hardening guidance for VKS deployments, extending the documented security baseline to the containerized workload layer. These documented hardening procedures, aligned with industry-standard best practices, give organizations a baseline for developing and updating their network security control procedures.
-Audit logging supports ongoing governance by recording security policy changes with full traceability. NSX firewall audit logs capture the user performing the operation, the module name, operation type, operation status, and modified resource details including the security policy display name, identifier, path, and rule configurations. This audit trail enables organizations to track who changed network security policies, what was changed, and when, supporting both compliance review and change management processes.
-Programmatic management capabilities, including PowerCLI cmdlets such as InvokePatchSecurityPolicyForDomain for creating distributed firewall policies, support infrastructure-as-code approaches to network security governance, enabling version-controlled and repeatable policy deployment.</t>
+          <t>VCF provides networking infrastructure and monitoring capabilities that support boundary protection at both external network boundaries and key internal boundaries within the virtual environment.
+At the external boundary, NSX Edge nodes serve as the communication gateway for inter-location and northbound traffic, establishing a defined perimeter through which external communications traverse. NSX Edge supports policy-based and route-based IPSec VPN services on Tier-0, Tier-0 VRF, and Tier-1 gateways, enabling secure connectivity between sites and to external networks. NAT rules can be configured at the VPC level to perform IP translation between internal and external networks, controlling which workloads are reachable from outside the environment. External IP configurations allow outside connectivity for virtual machines on private networks by performing address translation through 1:1 NAT, granting access to specific workloads rather than exposing entire network segments.
+For internal boundary control, VCF provides several layers of network segmentation. NSX segments, VLANs, and Private VLANs (PVLANs) allow administrators to create logical network boundaries that separate traffic at Layer 2. VMware distributed virtual switches support Private VLAN and VLAN-based SPAN for virtual distributed port mirroring. ESX port groups function as communication boundaries and can be configured with security policies to segment traffic between different groups of virtual machines. vSphere Distributed Switch port groups also support a Traffic Filtering and Marking Policy, which can permit or stop traffic on a per-port-group or per-port basis; port blocking policies provide a complementary mechanism to selectively prevent individual distributed ports from sending or receiving data. vSphere Distributed Switches provide centralized management of these boundaries across all hosts in a workload domain, applying consistent VLAN configurations and traffic shaping rules.
+VCF supports multiple distributed switch models that isolate traffic at the physical layer. The Storage Separation Distributed Switch model isolates storage traffic onto a separate vSphere Distributed Switch from management and virtual networking traffic. The Workload Separation Distributed Switch model isolates VM Management traffic onto a separate switch from ESX Management, vMotion, Storage, and Virtual Networking traffic. In secure environments, these separation models can provide physical air-gapped separation of network traffic.
+NSX Virtual Private Clouds (VPCs) provide isolated network environments within a shared infrastructure. VPCs support on-demand logical networks that can be advertised as public subnets or exposed through networking services like External IPs or NAT, providing project-level boundary isolation with their own topology, IP address management, and permission models. VCF Automation maintains secure organizational boundaries that isolate tenants from one another, providing additional logical separation within the environment.
+Network I/O Control (NIOC) determines the bandwidth that different network traffic types are given on a vSphere distributed switch. When NIOC is enabled, distributed switch traffic is divided into predefined network resource pools covering Fault Tolerance, iSCSI, vMotion, management, vSphere Replication, NFS, and virtual machine traffic. Bandwidth reservation and shares allocation enforce performance boundaries between traffic types under contention. Avi Load Balancer provides Layer 4 load balancing for services, distributing traffic across server pools with configurable load balancing algorithms and health monitoring.
+VCF provides network monitoring through multiple components. NSX supports IPFIX profile configuration on segments to enable flow-based network monitoring, giving administrators visibility into traffic traversing the network. At the vSphere layer, NetFlow can be enabled on individual distributed port groups or ports through the vSphere Distributed Switch monitoring policy, providing IP packet flow data independent of NSX. The pktcap-uw command-line utility on ESX hosts supports packet capture at specific points in the network stack, including at physical adapters and at the boundary between the distributed switch and physical adapters, enabling packet-level traffic inspection without additional tools. NSX Manager monitors control plane connections between transport nodes and manager nodes, providing awareness of the network infrastructure state.
+VCF Operations extends monitoring capabilities with network metrics including inbound and outbound connection tracking (net|allInboundTotal and net|allOutboundTotal). The Management Pack for Network Devices provides alerts and notifications for key network events including throughput totals and packet counts, and monitors outgoing errors on network interfaces. VCF Operations can detect protected flows, identifying traffic that has a specific firewall rule associated with it beyond a default allow-all policy, which helps administrators understand which communications are governed by explicit security policies. Outbound flow limits serve as a protection mechanism, with TCP flows limited to 1,000 allowed and 50 denied outbound, and UDP flows limited to 500 allowed and 50 denied outbound. VCF Operations also supports firewall hardening that restricts network access to its own internal services, demonstrating boundary protection for management interfaces.
+VCF Operations for Networks adds flow analysis and troubleshooting capabilities, including application discovery based on flows, network topology visualization through the Topology Graph Widget, and traffic flow visualization between applications, application tiers, shared services, and the Internet. VCF Operations for Networks provides intents for network design and verification, helping validate that the network configuration matches the intended design. Distributed virtual switches support health check operations for NIC teaming and VLAN/MTU verification, while vSAN network partition health checks detect VLAN misconfigurations and uplink losses. VCF Operations for Networks also provides visibility into vDefend distributed firewall rule activity, including identification of inactive rules that have had no matching flows.
+VMware Kubernetes Service (VKS) clusters and the vSphere Supervisor control plane extend boundary protection to the workload consumption layer. Within VKS clusters, Kubernetes NetworkPolicy objects provide declarative packet-filtering rules at OSI Layer 3 and Layer 4, defining permitted ingress and egress traffic based on pod label selectors, namespace selectors, and CIDR blocks. By default, pods accept all traffic; NetworkPolicy objects restrict communication to only the flows required for each workload or namespace, establishing internal boundaries between application tiers. Antrea, the CNI plugin integrated with Supervisor in NSX VPC deployments, enforces these NetworkPolicy rules and exposes NetworkPolicyStats, giving administrators measurable visibility into how boundary controls are applied across cluster-internal traffic. At the cluster perimeter, distributed firewall isolation rules on cluster nodes block external networks from reaching VKS cluster pods by default; Supervisor control plane nodes can reach cluster pods, but traffic originating outside the Supervisor control plane is dropped. Connections from worker nodes and pods to the Kubernetes API server use the API server's secure port by default, and SSH tunnels restrict control plane-to-node communications from exposure outside the cluster network. Kubernetes Ingress resources backed by ingress controllers perform TLS termination and route external requests to backend services, establishing a defined and controlled entry point at each cluster's external-facing edge. Network segmentation and firewall rules are applied to secure inter-component communication within Supervisor Service deployments such as Argo CD.
+For stateful firewall inspection, microsegmentation, IDS/IPS, and deep packet inspection at network boundaries, organizations can deploy VMware vDefend, which extends VCF's networking foundation with Layer 2 through Layer 7 firewall capabilities and advanced threat prevention. VCF's networking layer provides the segmentation, routing, and monitoring infrastructure on which boundary enforcement policies operate, but the active enforcement of traffic at those boundaries requires either vDefend or integration with external security tools. Organizational processes for defining boundary policies, reviewing traffic logs, managing firewall rule sets, and maintaining network diagrams are also required.
+VMware Private AI Services (PAIS) contributes to boundary protection through AI-infrastructure-specific network isolation patterns for both connected and air-gapped deployments. The core boundary enforcement capabilities, including distributed firewall rules, IDS/IPS inspection, and traffic analysis, are provided by VCF and VMware vDefend.
+PAIS setup is configured according to environment Internet connectivity, supporting either connected or disconnected air-gapped deployment models. In a disconnected air-gapped environment, files are downloaded from the Internet to a bastion host VM and then transferred to an admin host VM that has no Internet access, from which VI administrators interact with the environment. This pattern removes direct Internet exposure from the AI infrastructure components and constrains the path by which external content enters the trusted enclave.
+In air-gapped deployments, PAIS configures components to pull container images from a local internal registry rather than from public sources. The NVIDIA GPU Operator deploys validator, operator, driver, manager, toolkit, and devicePlugin components as separate container images pulled from the local registry. PAIS model endpoints authenticate to private registries through harbor-pull-secret-readonly to control access to container images.
+PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive data used to train and tune models, providing an internal boundary between AI workload data stores and other platform consumers. PAIS uses a CA trust bundle for secure communication with external services and databases.
+The NSX Edge cluster or Virtual Network Appliance (VNA) cluster provides two-tier north-south routing for the Supervisor instance and the workloads it runs, while the Workload Domain NSX Manager provides VPC networking services to private AI workloads. VPC networking for the VCF Automation organization is configured with a Public IP range, a transit gateway IP range, and a VPC private IP range to delineate external, transit, and internal address space for AI tenants.
+Organizations should refer to the VCF and vDefend Coverages for the underlying boundary monitoring and enforcement infrastructure.</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -10818,11 +10717,12 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides the technical enforcement layer that underlies Network Security Control (NSC) implementation, though the procedural and governance aspects of developing and updating NSC procedures remain organizational responsibilities.
-Security Services Platform enables monitoring of traffic after publishing assets and security policies to NSX Manager, allowing administrators to refine policies and adjust security posture based on observed traffic behavior. Security Intelligence Policy Recommendations correlate observed traffic patterns within the NSX environment to assist with enforcing more dynamic security policies; these recommendations can be reviewed and published directly to the Distributed Firewall (DFW) rule set. The Security Intelligence infrastructure classification feature identifies compute entities providing network infrastructure services in the NSX environment, supporting structured policy development around infrastructure traffic categories.
-Dynamic NSGroups enable DFW and Gateway Firewall (GFW) rules to update automatically as workloads are deployed or modified in the environment. Security Services Platform provides a workflow to import data center hierarchy from CSV, which translates IP addresses to virtual machines, tags those VMs, and creates NSX groups necessary for segmentation planning. This supports the initial development of network security control structures from existing IP-based inventories.
-vDefend DFW security posture is applied to VPCs through system-defined Security Profiles accessible in NSX Manager. When a Security Profile is applied to a VPC in VCF Automation, the system automatically generates and realizes system-managed DFW rules within the NSX Project space. DFW policies extend to Bare Metal servers, with Bare Metal server groups, vDefend DFW policies, and rules defined in NSX Manager and managed through Security Services Platform. Malware Prevention Service is configured through the IDS/IPS &amp; Malware Prevention Setup wizard, which provides a guided sequence of steps to prepare the data center.
-NSX Federation Security provides centralized management of security policies across multiple sites through a Global Manager, supporting consistent policy enforcement in distributed and multi-site environments. The Security Overview dashboard in NSX Manager displays threat detection and response features, a visual summary of the overall security configuration, and the capacity of NSX objects, giving administrators visibility into the state of deployed network security controls.</t>
+          <t>VMware vDefend provides monitoring and control of communications at both external and internal network boundaries within the virtual infrastructure through stateful firewall inspection, microsegmentation, and behavioral traffic analysis.
+At the external boundary, vDefend enforces zone boundaries and provides stateful North-South traffic inspection at the network perimeter. Gateway Firewall policies apply to traffic entering and leaving edge gateways, and Gateway Firewall IDS/IPS events can be monitored on nodes, providing inspection-layer visibility at the external boundary.
+At internal boundaries, vDefend enforces East-West traffic policies between virtual machines, containers, and workloads regardless of their physical location. Distributed Firewall rules operate at the vNIC level, creating per-workload enforcement points that function as internal boundary controls. Distributed Firewall manages East-West traffic control for both inter-VPC and intra-VPC communication within Organizations, and Distributed Firewall rules protect traffic between objects within a VPC, enforcing boundaries within project-scoped network environments. This microsegmentation approach allows organizations to define fine-grained internal boundaries beyond traditional VLAN-based segmentation. The policy-level Applied-To field defines a clear boundary around a set of VMs, such as an entire application, allowing targeted policies for specific zones, tenants, or applications without interfering with policies defined for other applications, tenants, or zones. Distributed Firewall policies can explicitly block unsecure protocols such as Telnet, FTP, and TFTP across the data center, supporting protocol-level boundary enforcement. Distributed Firewall also supports targeted deny rules scoped to infrastructure groups via the Applied-To field to protect critical services, facilitating phased Zero Trust adoption. Distributed Firewall governance implements least-privilege security by preventing overly permissive rules such as any-to-any-allow configurations. Distributed Firewall policies manage security for Bare Metal servers through traffic-control rules, extending boundary enforcement beyond virtual workloads. For federated environments, Distributed Firewall policies applied globally allow sources or destinations to be any object without span restrictions, supporting multi-site boundary enforcement.
+Security Services Platform adds environment-level boundary enforcement through Protection Rules, which define how traffic flows between environment pairs such as production, development, and test. Protection Rule actions can be set to Drop or Reject to block all traffic between specified environment pairs, or Allow for more selective enforcement. Security Services Platform Environment Protection evaluates whether workloads are protected by environment-specific segmentation policies and measures coverage including the percentage of environment pairs in blocked mode. Application Protection in Strict Mode enforces application-level firewall rules on all application workloads except infrastructure, with scoring based on workload coverage, traffic coverage, and lock-down policies. Security Intelligence, a capability within Security Services Platform, defines private IP ranges as the boundary for internal workloads, treating traffic that crosses this boundary as external. The Secure External Communications project identifies workloads with inbound or outbound connections to external IP addresses to mitigate vulnerability to attacks. Security Intelligence recommends identifying all inter-environment flows and securing them with specific policies before enforcing strict block rules, supporting a methodical approach to boundary hardening.
+Network Detection and Response (NDR) monitors traffic across boundaries and collects detection events representing security-relevant activity that has occurred in the network. NDR can be integrated with SIEMs to send security event logs about network infrastructure for centralized boundary monitoring. In sensitive or classified environments, NDR can be configured for air-gapped networks, executing all detection, correlation, and response activities entirely within closed networks using local storage and processing without requiring external connectivity. NDR remediations for events detected on the Gateway Firewall are applied on the Distributed Firewall, providing a unified enforcement response across both the internal and external boundary layers.
+vDefend does not define which boundaries an organization should establish or set the policies governing boundary placement decisions. Those are organizational architecture and governance responsibilities. The underlying networking infrastructure of VCF, comprising NSX segments, VLANs, and edge gateways, provides the segmentation and routing fabric on which vDefend's boundary enforcement operates.</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -10857,12 +10757,15 @@
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer network security policy mechanisms that help organizations implement network access controls at the application delivery boundary. These Avi-native capabilities operate at the Virtual Service level and give administrators structured objects for defining, governing, and updating access rules as requirements change.
-Avi's Network Security Policy evaluates incoming client traffic based on network-level parameters and determines whether a connection should be accepted, discarded, or rate-limited. IP Group-based access control lists applied per Virtual Service are the most scalable method for implementing network-layer ACLs, allowing administrators to specify which source addresses may reach individual application services. Policies can be created and modified through the Avi Controller CLI using the configure networksecuritypolicy command, and updated programmatically through the REST API using the Modify Network Security ACL endpoint and IP Group UUID references.
-Starting with Avi Load Balancer version 32.1, NSX security groups can be used directly in both HTTP Policies and Network policies. Security groups defined once in NSX are reused across Avi Virtual Service security policies, removing the need to manually maintain IP address lists in Avi. When an IP address changes in NSX, the update propagates automatically to Avi Load Balancer, keeping Virtual Service security policies current without manual intervention. This integration provides a unified governance model where network security group membership is managed centrally in NSX and reflected automatically in Avi policy enforcement.
-Avi's DDoS Policy detects and mitigates Layer 4 through Layer 7 network attacks through the Network Security policy framework, providing additional network security control at the application delivery layer.
-Within the broader VCF platform, NSX provides underlay routing and network infrastructure for Avi Service Engines. East-west firewall enforcement between application tiers is provided by VMware vDefend, a separate product that extends the platform's network security posture beyond what Avi provides at the application proxy boundary.
-Satisfying this control fully requires the organization to document procedures for governing and updating network security controls across the Avi tier and the broader platform, assign ownership of Avi policy objects, and establish change management processes covering both Avi Network Security Policies and VCF-layer controls.</t>
+          <t>VMware Avi Load Balancer provides boundary protection mechanisms at the application delivery layer for traffic it proxies. Network Security Policies in Avi evaluate incoming client traffic based on network-level parameters and determine whether a connection should be accepted, discarded, or rate-limited. These policies apply IP-based traffic filtering at the virtual service level; a deny rule stops further policy evaluation, preventing downstream HTTP Security, Request, or Response policies from executing for that traffic. Network security policies are configurable per virtual service and per Virtual IP address, giving administrators auditable and consistent access controls across the deployment.
+Avi's Web Application Firewall (WAF) inspects application-layer traffic at the proxy boundary using positive and negative security models. Positive Security rules define what constitutes allowed application behavior and enforce restrictions on traffic that does not conform to that model. WAF Application Rules provide protection against known attack patterns, including rules targeting specific CVEs; rules are automatically updated through the Controller Cloud Services connection, and existing rules continue to protect applications when that connection is unavailable. WAF rule actions support pass and deny options for controlling traffic based on policy matches. Administrators can also enable the Application Rules service through the Avi Cloud Console, which delivers automatically updated CVE-targeted rules directly to Avi Controllers.
+For DDoS mitigation, Avi's DDoS Policy detects and mitigates Layer 4 through Layer 7 network attacks through the Network Security policy framework. This includes protection against DNS Reflection Ingress attacks, which involve sending DNS queries with spoofed IP addresses to flood a victim with unsolicited DNS server responses.
+In Kubernetes deployments, the Avi Kubernetes Operator (AKO) extends boundary controls to Kubernetes ingress traffic. The L4 Rule custom resource definition (CRD) in AKO allows administrators to express custom Security Policies applied to virtual service traffic, including configuration for DDoS attack detection and mitigation. The `insecureEdgeTerminationPolicy` setting in AKO controls handling of insecure traffic, with a redirect option that enforces secure traffic routing through HTTP Request policies applied per FQDN.
+Avi Service Engines implement traffic isolation between the data plane and the management and control plane using a dedicated management vNIC bound to the default Linux network namespace, with health monitor traffic further isolated through Linux network namespace features in the kernel. Service Engine IP addresses egressing the Data Plane vNIC are routed through the external network and subjected to routing isolation and ACL/firewalling controls present in that external network. A dedicated management network is required for communication between Avi Controllers and Service Engines. In isolated network deployments, each Avi Controller supports a second management IP address or DNS-resolvable FQDN for Service Engines connecting from an isolated segment, configured via the `isolated-network-management-address` setting.
+In VCF deployments using the Avi-for-VCF integration, the Management Network hosts the Avi Controller and provides connectivity to vCenter, ESX hosts, and Supervisor control plane nodes, maintaining a defined boundary between management and workload traffic.
+Incoming HTTP(S) traffic can be replicated to logging and sideband servers at the protocol level via the Virtual Service Sideband Profile, enabling deep traffic inspection by external appliances such as web application firewalls and supporting compliance and auditing requirements.
+Avi also supports a Firewall Sandwich Topology, where virtual services and firewall pool members are chained so that application traffic traverses configured firewall members on its path from the Internet to internal servers. In this topology, a sample of traffic is inspected by the firewall while remaining traffic considered trusted is directly routed to the internal network.
+Boundary protection for segments and layers outside Avi's application delivery scope, including network-level perimeter controls, east-west enforcement between application tiers, and internal boundary protection across the broader VCF environment, requires the VCF networking infrastructure and VMware vDefend, which is a separate product.</t>
         </is>
       </c>
     </row>
@@ -10982,17 +10885,23 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>VCF provides built-in mechanisms for implementing and governing network security controls across the infrastructure stack, spanning virtual switching, network segmentation, policy management, role-based access control, audit logging, and documented hardening procedures.
-NSX, the networking component of VCF, delivers a hierarchical security policy framework organized around domains, security policies, and individual rules. Each rule can be configured with action, direction, IP protocol, source groups, destination groups, services, and scope, providing administrators a structured and repeatable model for defining network security posture. Security policies are organized into categories (Emergency, Infrastructure, Environment, Application) so that multiple administrators can create and manage policies without conflicts or overrides. Firewall rules within each category are organized into sections, supporting logical grouping and ordered evaluation. This hierarchical structure supports both centralized governance and delegated administration, allowing organizations to maintain consistent security standards while enabling application teams to manage policies within their assigned boundaries.
-VCF's network security governance model is built on role-based access control (RBAC) that spans networking and security functions. NSX Projects and VPCs support scoped role assignments including VPC Admin, Security Admin, Network Admin, Security Operator, and Network Operator roles. These roles can be assigned at the project or VPC level, enabling least-privilege access to network security configuration. A VPC Admin has full access to networking and security objects within their assigned VPC, while Enterprise Admins retain overarching control. NSX Advanced Network Management extends RBAC to specific networking components including static routes, locale services, segments, segment profiles, IP address pools, forwarding policies, DNS, DHCP, load balancing, and NAT. This separation of duties allows organizations to delegate day-to-day network security operations while retaining centralized oversight.
-The NSX VPC workflow provides a structured mechanism for implementing network security controls at the application level. Application owners can add subnets inside their assigned VPC and configure security policies to meet workload requirements without dependency on the Enterprise Admin. VPC Admins and Security Admins add security policies within the VPC to address the security requirements of connected workloads. Default East-West firewall rules are activated automatically when an appropriate security license is applied and can be adjusted as needed. This self-service model, bounded by RBAC, allows security policy implementation to scale across the organization while maintaining governance guardrails.
-VCF includes multiple layers of network security controls. VMware vDefend, a separately licensed product that extends NSX, provides Distributed Firewall enforcement across deployment and operational scenarios, while its Gateway Firewall provides perimeter security. Context profiles and Layer 7 access profiles enable firewall rules with application-level and domain-based attributes for both distributed and gateway firewall enforcement. For containerized workloads, the Antrea Container Network Interface (CNI) plugin in VMware Kubernetes Service (VKS) enforces Kubernetes NetworkPolicy at the namespace and pod level. The AntreaPolicy feature gate enables AntreaNetworkPolicy and ClusterNetworkPolicy objects that extend standard NetworkPolicy with richer Layer 4 rule sets; traffic not explicitly permitted is blocked by default when a policy applies to a pod. The Antrea NetworkPolicyStats feature gate collects enforcement statistics, giving operators visibility into which policies are matching traffic and at what volume to support operational monitoring and periodic policy review. A Kubernetes cluster must provide and enforce NetworkPolicy for network security controls to be effective.
-The VKS networking layer within VCF integrates directly with the broader NSX security framework. Supervisors using NSX VPC networking operate in the system VPC while VKS clusters reside in vSphere Namespace VPCs, providing topology-level isolation between the management plane and workload clusters. NSX VPC pod IP pools are configured as Private, restricting direct external accessibility of pod addresses. Antrea EgressSeparateSubnet allows egress traffic from specific workloads to originate from a subnet distinct from the default node subnet, supporting more granular traffic segmentation. The Network Control Plane (NCP) component bridges Kubernetes networking objects with NSX, realizing VirtualNetwork, VirtualNetworkInterface, and LoadBalancer resources for the VKS control plane; communication between Supervisor and NSX is secured using TLS. Kubernetes control plane services communicate using certificates by default, and connections from nodes and pods to the control plane are secured by default and can run over untrusted networks. Supervisor networking architecture requires a deliberate deployment-time choice: NSX with embedded load balancer, or vSphere Distributed Switch with external load balancer. This choice determines which network security mechanisms are available downstream, and organizational procedures should reflect which path is in use. VKS Cluster Management Custom Policies provide a governance mechanism that should be reviewed and updated to ensure policy logic reflects current security and operational requirements. The Argo CD Supervisor Service deployment implements network segmentation and firewall rules to secure communication between its components. Organizations operating service meshes alongside VKS gain OSI Layer 7 network policies based on workload identity and mutual TLS encryption for pod-to-pod traffic, providing an additional isolation layer beyond namespace boundaries.
-At the virtual infrastructure layer, vSphere Distributed Switches provide centralized management of virtual networking, handling traffic for all associated hosts in a data center. Distributed switches support network segmentation using Private VLAN (PVLAN) and VLAN-based SPAN for distributed port mirroring. Network segmentation is built into the VCF architecture: management traffic, vMotion, and storage traffic are isolated on separate networks. Network I/O Control allocates bandwidth to traffic types based on share values, and the Storage Traffic Separation network profile creates dedicated vSphere Distributed Switches with separate physical NICs for storage traffic isolation. NSX distributed port groups and uplink port groups support Traffic Filtering and Marking policies configurable at the port level, providing additional granularity for layer 2 security controls. ESX hosts also support IPsec for VMkernel network communication, with security associations and policies configurable via esxcli network ip ipsec commands, supporting both transport and tunnel mode with upper layer protocol filtering for tcp, udp, icmp6, or any traffic.
-vSphere Lifecycle Manager enforces desired-state configuration for hosts and clusters, applying and remediating configuration to match the defined software specification. This helps detect and address configuration drift that could weaken network security posture, and the remediation process can be managed programmatically through the vSphere Automation API.
-VCF publishes security baselines through the Security Configuration Guide and DISA STIGs. The NSX Security Configuration Guide provides documented procedures for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes. Recommendations cover configuring strong authentication, implementing RBAC, and securing administrative access. NSX security best practices address creating and managing security groups, implementing distributed firewalling, configuring security policies, and enforcing microsegmentation to control network traffic. Security Technical Implementation Guides for Supervisor and VMware Kubernetes Release (VKr) components are available to provide hardening guidance for VKS deployments, extending the documented security baseline to the containerized workload layer. These documented hardening procedures, aligned with industry-standard best practices, give organizations a baseline for developing and updating their network security control procedures.
-Audit logging supports ongoing governance by recording security policy changes with full traceability. NSX firewall audit logs capture the user performing the operation, the module name, operation type, operation status, and modified resource details including the security policy display name, identifier, path, and rule configurations. This audit trail enables organizations to track who changed network security policies, what was changed, and when, supporting both compliance review and change management processes.
-Programmatic management capabilities, including PowerCLI cmdlets such as InvokePatchSecurityPolicyForDomain for creating distributed firewall policies, support infrastructure-as-code approaches to network security governance, enabling version-controlled and repeatable policy deployment.</t>
+          <t>VCF provides networking infrastructure and monitoring capabilities that support boundary protection at both external network boundaries and key internal boundaries within the virtual environment.
+At the external boundary, NSX Edge nodes serve as the communication gateway for inter-location and northbound traffic, establishing a defined perimeter through which external communications traverse. NSX Edge supports policy-based and route-based IPSec VPN services on Tier-0, Tier-0 VRF, and Tier-1 gateways, enabling secure connectivity between sites and to external networks. NAT rules can be configured at the VPC level to perform IP translation between internal and external networks, controlling which workloads are reachable from outside the environment. External IP configurations allow outside connectivity for virtual machines on private networks by performing address translation through 1:1 NAT, granting access to specific workloads rather than exposing entire network segments.
+For internal boundary control, VCF provides several layers of network segmentation. NSX segments, VLANs, and Private VLANs (PVLANs) allow administrators to create logical network boundaries that separate traffic at Layer 2. VMware distributed virtual switches support Private VLAN and VLAN-based SPAN for virtual distributed port mirroring. ESX port groups function as communication boundaries and can be configured with security policies to segment traffic between different groups of virtual machines. vSphere Distributed Switch port groups also support a Traffic Filtering and Marking Policy, which can permit or stop traffic on a per-port-group or per-port basis; port blocking policies provide a complementary mechanism to selectively prevent individual distributed ports from sending or receiving data. vSphere Distributed Switches provide centralized management of these boundaries across all hosts in a workload domain, applying consistent VLAN configurations and traffic shaping rules.
+VCF supports multiple distributed switch models that isolate traffic at the physical layer. The Storage Separation Distributed Switch model isolates storage traffic onto a separate vSphere Distributed Switch from management and virtual networking traffic. The Workload Separation Distributed Switch model isolates VM Management traffic onto a separate switch from ESX Management, vMotion, Storage, and Virtual Networking traffic. In secure environments, these separation models can provide physical air-gapped separation of network traffic.
+NSX Virtual Private Clouds (VPCs) provide isolated network environments within a shared infrastructure. VPCs support on-demand logical networks that can be advertised as public subnets or exposed through networking services like External IPs or NAT, providing project-level boundary isolation with their own topology, IP address management, and permission models. VCF Automation maintains secure organizational boundaries that isolate tenants from one another, providing additional logical separation within the environment.
+Network I/O Control (NIOC) determines the bandwidth that different network traffic types are given on a vSphere distributed switch. When NIOC is enabled, distributed switch traffic is divided into predefined network resource pools covering Fault Tolerance, iSCSI, vMotion, management, vSphere Replication, NFS, and virtual machine traffic. Bandwidth reservation and shares allocation enforce performance boundaries between traffic types under contention. Avi Load Balancer provides Layer 4 load balancing for services, distributing traffic across server pools with configurable load balancing algorithms and health monitoring.
+VCF provides network monitoring through multiple components. NSX supports IPFIX profile configuration on segments to enable flow-based network monitoring, giving administrators visibility into traffic traversing the network. At the vSphere layer, NetFlow can be enabled on individual distributed port groups or ports through the vSphere Distributed Switch monitoring policy, providing IP packet flow data independent of NSX. The pktcap-uw command-line utility on ESX hosts supports packet capture at specific points in the network stack, including at physical adapters and at the boundary between the distributed switch and physical adapters, enabling packet-level traffic inspection without additional tools. NSX Manager monitors control plane connections between transport nodes and manager nodes, providing awareness of the network infrastructure state.
+VCF Operations extends monitoring capabilities with network metrics including inbound and outbound connection tracking (net|allInboundTotal and net|allOutboundTotal). The Management Pack for Network Devices provides alerts and notifications for key network events including throughput totals and packet counts, and monitors outgoing errors on network interfaces. VCF Operations can detect protected flows, identifying traffic that has a specific firewall rule associated with it beyond a default allow-all policy, which helps administrators understand which communications are governed by explicit security policies. Outbound flow limits serve as a protection mechanism, with TCP flows limited to 1,000 allowed and 50 denied outbound, and UDP flows limited to 500 allowed and 50 denied outbound. VCF Operations also supports firewall hardening that restricts network access to its own internal services, demonstrating boundary protection for management interfaces.
+VCF Operations for Networks adds flow analysis and troubleshooting capabilities, including application discovery based on flows, network topology visualization through the Topology Graph Widget, and traffic flow visualization between applications, application tiers, shared services, and the Internet. VCF Operations for Networks provides intents for network design and verification, helping validate that the network configuration matches the intended design. Distributed virtual switches support health check operations for NIC teaming and VLAN/MTU verification, while vSAN network partition health checks detect VLAN misconfigurations and uplink losses. VCF Operations for Networks also provides visibility into vDefend distributed firewall rule activity, including identification of inactive rules that have had no matching flows.
+VMware Kubernetes Service (VKS) clusters and the vSphere Supervisor control plane extend boundary protection to the workload consumption layer. Within VKS clusters, Kubernetes NetworkPolicy objects provide declarative packet-filtering rules at OSI Layer 3 and Layer 4, defining permitted ingress and egress traffic based on pod label selectors, namespace selectors, and CIDR blocks. By default, pods accept all traffic; NetworkPolicy objects restrict communication to only the flows required for each workload or namespace, establishing internal boundaries between application tiers. Antrea, the CNI plugin integrated with Supervisor in NSX VPC deployments, enforces these NetworkPolicy rules and exposes NetworkPolicyStats, giving administrators measurable visibility into how boundary controls are applied across cluster-internal traffic. At the cluster perimeter, distributed firewall isolation rules on cluster nodes block external networks from reaching VKS cluster pods by default; Supervisor control plane nodes can reach cluster pods, but traffic originating outside the Supervisor control plane is dropped. Connections from worker nodes and pods to the Kubernetes API server use the API server's secure port by default, and SSH tunnels restrict control plane-to-node communications from exposure outside the cluster network. Kubernetes Ingress resources backed by ingress controllers perform TLS termination and route external requests to backend services, establishing a defined and controlled entry point at each cluster's external-facing edge. Network segmentation and firewall rules are applied to secure inter-component communication within Supervisor Service deployments such as Argo CD.
+For stateful firewall inspection, microsegmentation, IDS/IPS, and deep packet inspection at network boundaries, organizations can deploy VMware vDefend, which extends VCF's networking foundation with Layer 2 through Layer 7 firewall capabilities and advanced threat prevention. VCF's networking layer provides the segmentation, routing, and monitoring infrastructure on which boundary enforcement policies operate, but the active enforcement of traffic at those boundaries requires either vDefend or integration with external security tools. Organizational processes for defining boundary policies, reviewing traffic logs, managing firewall rule sets, and maintaining network diagrams are also required.
+VMware Private AI Services (PAIS) contributes to boundary protection through AI-infrastructure-specific network isolation patterns for both connected and air-gapped deployments. The core boundary enforcement capabilities, including distributed firewall rules, IDS/IPS inspection, and traffic analysis, are provided by VCF and VMware vDefend.
+PAIS setup is configured according to environment Internet connectivity, supporting either connected or disconnected air-gapped deployment models. In a disconnected air-gapped environment, files are downloaded from the Internet to a bastion host VM and then transferred to an admin host VM that has no Internet access, from which VI administrators interact with the environment. This pattern removes direct Internet exposure from the AI infrastructure components and constrains the path by which external content enters the trusted enclave.
+In air-gapped deployments, PAIS configures components to pull container images from a local internal registry rather than from public sources. The NVIDIA GPU Operator deploys validator, operator, driver, manager, toolkit, and devicePlugin components as separate container images pulled from the local registry. PAIS model endpoints authenticate to private registries through harbor-pull-secret-readonly to control access to container images.
+PAIS integrates with Harbor registries as a model storage backend, requiring authentication and certificate-based trust for model retrieval. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive data used to train and tune models, providing an internal boundary between AI workload data stores and other platform consumers. PAIS uses a CA trust bundle for secure communication with external services and databases.
+The NSX Edge cluster or Virtual Network Appliance (VNA) cluster provides two-tier north-south routing for the Supervisor instance and the workloads it runs, while the Workload Domain NSX Manager provides VPC networking services to private AI workloads. VPC networking for the VCF Automation organization is configured with a Public IP range, a transit gateway IP range, and a VPC private IP range to delineate external, transit, and internal address space for AI tenants.
+Organizations should refer to the VCF and vDefend Coverages for the underlying boundary monitoring and enforcement infrastructure.</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -11002,11 +10911,12 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides the technical enforcement layer that underlies Network Security Control (NSC) implementation, though the procedural and governance aspects of developing and updating NSC procedures remain organizational responsibilities.
-Security Services Platform enables monitoring of traffic after publishing assets and security policies to NSX Manager, allowing administrators to refine policies and adjust security posture based on observed traffic behavior. Security Intelligence Policy Recommendations correlate observed traffic patterns within the NSX environment to assist with enforcing more dynamic security policies; these recommendations can be reviewed and published directly to the Distributed Firewall (DFW) rule set. The Security Intelligence infrastructure classification feature identifies compute entities providing network infrastructure services in the NSX environment, supporting structured policy development around infrastructure traffic categories.
-Dynamic NSGroups enable DFW and Gateway Firewall (GFW) rules to update automatically as workloads are deployed or modified in the environment. Security Services Platform provides a workflow to import data center hierarchy from CSV, which translates IP addresses to virtual machines, tags those VMs, and creates NSX groups necessary for segmentation planning. This supports the initial development of network security control structures from existing IP-based inventories.
-vDefend DFW security posture is applied to VPCs through system-defined Security Profiles accessible in NSX Manager. When a Security Profile is applied to a VPC in VCF Automation, the system automatically generates and realizes system-managed DFW rules within the NSX Project space. DFW policies extend to Bare Metal servers, with Bare Metal server groups, vDefend DFW policies, and rules defined in NSX Manager and managed through Security Services Platform. Malware Prevention Service is configured through the IDS/IPS &amp; Malware Prevention Setup wizard, which provides a guided sequence of steps to prepare the data center.
-NSX Federation Security provides centralized management of security policies across multiple sites through a Global Manager, supporting consistent policy enforcement in distributed and multi-site environments. The Security Overview dashboard in NSX Manager displays threat detection and response features, a visual summary of the overall security configuration, and the capacity of NSX objects, giving administrators visibility into the state of deployed network security controls.</t>
+          <t>VMware vDefend provides monitoring and control of communications at both external and internal network boundaries within the virtual infrastructure through stateful firewall inspection, microsegmentation, and behavioral traffic analysis.
+At the external boundary, vDefend enforces zone boundaries and provides stateful North-South traffic inspection at the network perimeter. Gateway Firewall policies apply to traffic entering and leaving edge gateways, and Gateway Firewall IDS/IPS events can be monitored on nodes, providing inspection-layer visibility at the external boundary.
+At internal boundaries, vDefend enforces East-West traffic policies between virtual machines, containers, and workloads regardless of their physical location. Distributed Firewall rules operate at the vNIC level, creating per-workload enforcement points that function as internal boundary controls. Distributed Firewall manages East-West traffic control for both inter-VPC and intra-VPC communication within Organizations, and Distributed Firewall rules protect traffic between objects within a VPC, enforcing boundaries within project-scoped network environments. This microsegmentation approach allows organizations to define fine-grained internal boundaries beyond traditional VLAN-based segmentation. The policy-level Applied-To field defines a clear boundary around a set of VMs, such as an entire application, allowing targeted policies for specific zones, tenants, or applications without interfering with policies defined for other applications, tenants, or zones. Distributed Firewall policies can explicitly block unsecure protocols such as Telnet, FTP, and TFTP across the data center, supporting protocol-level boundary enforcement. Distributed Firewall also supports targeted deny rules scoped to infrastructure groups via the Applied-To field to protect critical services, facilitating phased Zero Trust adoption. Distributed Firewall governance implements least-privilege security by preventing overly permissive rules such as any-to-any-allow configurations. Distributed Firewall policies manage security for Bare Metal servers through traffic-control rules, extending boundary enforcement beyond virtual workloads. For federated environments, Distributed Firewall policies applied globally allow sources or destinations to be any object without span restrictions, supporting multi-site boundary enforcement.
+Security Services Platform adds environment-level boundary enforcement through Protection Rules, which define how traffic flows between environment pairs such as production, development, and test. Protection Rule actions can be set to Drop or Reject to block all traffic between specified environment pairs, or Allow for more selective enforcement. Security Services Platform Environment Protection evaluates whether workloads are protected by environment-specific segmentation policies and measures coverage including the percentage of environment pairs in blocked mode. Application Protection in Strict Mode enforces application-level firewall rules on all application workloads except infrastructure, with scoring based on workload coverage, traffic coverage, and lock-down policies. Security Intelligence, a capability within Security Services Platform, defines private IP ranges as the boundary for internal workloads, treating traffic that crosses this boundary as external. The Secure External Communications project identifies workloads with inbound or outbound connections to external IP addresses to mitigate vulnerability to attacks. Security Intelligence recommends identifying all inter-environment flows and securing them with specific policies before enforcing strict block rules, supporting a methodical approach to boundary hardening.
+Network Detection and Response (NDR) monitors traffic across boundaries and collects detection events representing security-relevant activity that has occurred in the network. NDR can be integrated with SIEMs to send security event logs about network infrastructure for centralized boundary monitoring. In sensitive or classified environments, NDR can be configured for air-gapped networks, executing all detection, correlation, and response activities entirely within closed networks using local storage and processing without requiring external connectivity. NDR remediations for events detected on the Gateway Firewall are applied on the Distributed Firewall, providing a unified enforcement response across both the internal and external boundary layers.
+vDefend does not define which boundaries an organization should establish or set the policies governing boundary placement decisions. Those are organizational architecture and governance responsibilities. The underlying networking infrastructure of VCF, comprising NSX segments, VLANs, and edge gateways, provides the segmentation and routing fabric on which vDefend's boundary enforcement operates.</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -11041,12 +10951,15 @@
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer network security policy mechanisms that help organizations implement network access controls at the application delivery boundary. These Avi-native capabilities operate at the Virtual Service level and give administrators structured objects for defining, governing, and updating access rules as requirements change.
-Avi's Network Security Policy evaluates incoming client traffic based on network-level parameters and determines whether a connection should be accepted, discarded, or rate-limited. IP Group-based access control lists applied per Virtual Service are the most scalable method for implementing network-layer ACLs, allowing administrators to specify which source addresses may reach individual application services. Policies can be created and modified through the Avi Controller CLI using the configure networksecuritypolicy command, and updated programmatically through the REST API using the Modify Network Security ACL endpoint and IP Group UUID references.
-Starting with Avi Load Balancer version 32.1, NSX security groups can be used directly in both HTTP Policies and Network policies. Security groups defined once in NSX are reused across Avi Virtual Service security policies, removing the need to manually maintain IP address lists in Avi. When an IP address changes in NSX, the update propagates automatically to Avi Load Balancer, keeping Virtual Service security policies current without manual intervention. This integration provides a unified governance model where network security group membership is managed centrally in NSX and reflected automatically in Avi policy enforcement.
-Avi's DDoS Policy detects and mitigates Layer 4 through Layer 7 network attacks through the Network Security policy framework, providing additional network security control at the application delivery layer.
-Within the broader VCF platform, NSX provides underlay routing and network infrastructure for Avi Service Engines. East-west firewall enforcement between application tiers is provided by VMware vDefend, a separate product that extends the platform's network security posture beyond what Avi provides at the application proxy boundary.
-Satisfying this control fully requires the organization to document procedures for governing and updating network security controls across the Avi tier and the broader platform, assign ownership of Avi policy objects, and establish change management processes covering both Avi Network Security Policies and VCF-layer controls.</t>
+          <t>VMware Avi Load Balancer provides boundary protection mechanisms at the application delivery layer for traffic it proxies. Network Security Policies in Avi evaluate incoming client traffic based on network-level parameters and determine whether a connection should be accepted, discarded, or rate-limited. These policies apply IP-based traffic filtering at the virtual service level; a deny rule stops further policy evaluation, preventing downstream HTTP Security, Request, or Response policies from executing for that traffic. Network security policies are configurable per virtual service and per Virtual IP address, giving administrators auditable and consistent access controls across the deployment.
+Avi's Web Application Firewall (WAF) inspects application-layer traffic at the proxy boundary using positive and negative security models. Positive Security rules define what constitutes allowed application behavior and enforce restrictions on traffic that does not conform to that model. WAF Application Rules provide protection against known attack patterns, including rules targeting specific CVEs; rules are automatically updated through the Controller Cloud Services connection, and existing rules continue to protect applications when that connection is unavailable. WAF rule actions support pass and deny options for controlling traffic based on policy matches. Administrators can also enable the Application Rules service through the Avi Cloud Console, which delivers automatically updated CVE-targeted rules directly to Avi Controllers.
+For DDoS mitigation, Avi's DDoS Policy detects and mitigates Layer 4 through Layer 7 network attacks through the Network Security policy framework. This includes protection against DNS Reflection Ingress attacks, which involve sending DNS queries with spoofed IP addresses to flood a victim with unsolicited DNS server responses.
+In Kubernetes deployments, the Avi Kubernetes Operator (AKO) extends boundary controls to Kubernetes ingress traffic. The L4 Rule custom resource definition (CRD) in AKO allows administrators to express custom Security Policies applied to virtual service traffic, including configuration for DDoS attack detection and mitigation. The `insecureEdgeTerminationPolicy` setting in AKO controls handling of insecure traffic, with a redirect option that enforces secure traffic routing through HTTP Request policies applied per FQDN.
+Avi Service Engines implement traffic isolation between the data plane and the management and control plane using a dedicated management vNIC bound to the default Linux network namespace, with health monitor traffic further isolated through Linux network namespace features in the kernel. Service Engine IP addresses egressing the Data Plane vNIC are routed through the external network and subjected to routing isolation and ACL/firewalling controls present in that external network. A dedicated management network is required for communication between Avi Controllers and Service Engines. In isolated network deployments, each Avi Controller supports a second management IP address or DNS-resolvable FQDN for Service Engines connecting from an isolated segment, configured via the `isolated-network-management-address` setting.
+In VCF deployments using the Avi-for-VCF integration, the Management Network hosts the Avi Controller and provides connectivity to vCenter, ESX hosts, and Supervisor control plane nodes, maintaining a defined boundary between management and workload traffic.
+Incoming HTTP(S) traffic can be replicated to logging and sideband servers at the protocol level via the Virtual Service Sideband Profile, enabling deep traffic inspection by external appliances such as web application firewalls and supporting compliance and auditing requirements.
+Avi also supports a Firewall Sandwich Topology, where virtual services and firewall pool members are chained so that application traffic traverses configured firewall members on its path from the Internet to internal servers. In this topology, a sample of traffic is inspected by the firewall while remaining traffic considered trusted is directly routed to the internal network.
+Boundary protection for segments and layers outside Avi's application delivery scope, including network-level perimeter controls, east-west enforcement between application tiers, and internal boundary protection across the broader VCF environment, requires the VCF networking infrastructure and VMware vDefend, which is a separate product.</t>
         </is>
       </c>
     </row>
@@ -12372,19 +12285,17 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>VCF provides multiple cryptographic mechanisms for protecting data at rest across its infrastructure stack, primarily through vSAN data-at-rest encryption and vSphere Virtual Machine Encryption.
-vSAN data-at-rest encryption is the primary mechanism for protecting stored data within VCF. When enabled on a vSAN cluster, vSAN encrypts everything in the vSAN datastore, including all files, virtual machines, and their corresponding data. This protection extends to scenarios where a physical storage device is removed from the cluster, as the encrypted data remains unreadable without the proper keys. vSAN supports both Original Storage Architecture (OSA) and Express Storage Architecture (ESA) deployments, with encryption behavior varying by architecture. For OSA, data-at-rest encryption occurs at the Local Object Manager (LSOM) layer on the target host, and each disk has a different randomly generated Data Encryption Key. For ESA in hyperconverged infrastructure mode, data is encrypted at the VM host before network transmission, and all disks in the cluster use the same DEK to encrypt object data. In OSA, encryption occurs after other data processing operations such as deduplication and compression, preserving storage efficiency. vSAN encryption is the recommended approach for securing data on vSAN datastores because it is designed to be compatible with vSAN deduplication and compression, whereas virtual machine encryption causes these storage efficiency features to become less effective.
-vSphere Virtual Machine Encryption provides an alternative or complementary data-at-rest encryption layer that works across all datastore types, including vSAN, iSCSI, NFS, and Fibre Channel. VM Encryption occurs before data reaches the storage layer, protecting virtual machine files and disks regardless of the underlying storage technology. This can be applied on a per-VM basis and operates independently of the underlying storage layer, making it applicable to environments where granular, VM-level encryption control is required. Most virtual machine files, in particular guest data not stored in the VMDK file, are encrypted. When combined with storage-level encryption, administrators should evaluate the performance impact of multiple encryption layers on latency and throughput, as well as the potential loss of storage efficiency features like deduplication and compression.
-For organizations consuming VCF through the VCF Automation layer, VCF Encryption Management extends these VM and disk encryption capabilities to the namespace level. This service allows organization administrators to use encryption keys from their own third-party key providers to encrypt VMs and disks within a VCF Automation namespace, and also supports encrypting VMs with a Virtual Trusted Platform Module (vTPM). Provider administrators must register a default standard key provider in VMware vCenter before organization administrators can configure namespace-level encryption; the vSphere Native Key Provider cannot be used in this role, and key providers must be listed in the VMware Compatibility Guide for Key Management Servers. Organization administrators configure encryption by setting up a key provider and creating a namespace encryption class. Configuration of key providers requires either the Encryption Management Admin role or a custom role that grants the right to configure key providers.
-Both encryption mechanisms require a key management infrastructure. VCF supports integration with KMIP 1.1-compatible external Key Management Servers (KMS) or the built-in vSphere Native Key Provider (NKP). VCF establishes a cryptographic domain of trust between key providers, VMware vCenter, and VMware ESX hosts. When using a Standard Key Provider, the KMS sends keys to vCenter upon request, which are used as the Key Encryption Key (KEK) and are AES-256 keys. Standard Key Providers support key wrapping, creating a three-tier key hierarchy: Data Encryption Keys (DEK) encrypt object data, Key Encryption Keys (KEK) protect the DEK, and a wrapping key stored in the KMS protects the KEK. This approach reduces the number of keys stored in external KMS systems while maintaining cryptographic separation. When using an external KMS, the recommendation is to deploy highly available KMS clusters to distribute the keys that encrypt the vSAN datastore, avoiding a single point of failure in the encryption key chain. The vSphere Native Key Provider offers a simpler deployment model for environments that do not require an external KMS. Native Key Provider equips each participating host with decryption keys so hosts can operate independently of network-accessible key servers.
-vSAN supports key rotation for both Key Encryption Keys (KEK) and Data Encryption Keys (DEK), with the capability to re-encrypt all data on the storage using new keys. vSAN encryption supports configurable rekey intervals that can be set to default or custom values. Key wrapping supports automatic key rotation with configurable intervals. This allows organizations to meet key lifecycle management requirements without disrupting operations. Encryption can also be enforced through vSAN storage policies, where the data-at-rest encryption option can be specified as a policy attribute, allowing administrators to define which datastores require encryption when provisioning virtual machines.
-VCF supports virtual Trusted Platform Module (vTPM) 2.0 for virtual machines, enabling in-guest encryption capabilities such as Windows BitLocker and Linux disk encryption. Virtual machines can include various forms of encryption: VMs using a vTPM device, VMs with disks encrypted, and VMs with encryption enabled without disks encrypted. These guest-level encryption features work independently of or in combination with VMware's infrastructure-level encryption, supporting defense-in-depth strategies.
-ESX hosts store their configuration data in encrypted form. When the host has a physical TPM 2.0 enabled, the configuration encryption key is stored in the TPM. Core dumps on an ESX host that has encryption mode enabled are always encrypted. ESX also supports key persistence as a cache for encryption keys in environments where a KMS may be unavailable. With key persistence enabled, ESX hosts can persist the encryption keys in the Trusted Platform Module (TPM) across reboots, allowing encryption operations to continue when the key server is unavailable. Each ESX host obtains the encryption keys initially and retains them in its key cache; if the ESX host has a TPM, the encryption keys are persisted in the TPM across reboots. Key persistence requires that the ESX host has a TPM, and can be enabled using the esxcli system security keypersistence enable command.
-Memory Tiering encryption protects tiered memory without requiring external key management. VCF generates random 256-bit AES-XTS keys at the kernel level during VM power-on, unique to each VM instance. During vMotion, tiered memory pages are decrypted and transmitted over the encrypted vMotion channel, with new keys generated at the destination.
-For access control over cryptographic operations, VCF provides the No Cryptography Administrator role, which supports all Administrator privileges except for the Cryptographic Operations privileges. This allows standard VM and infrastructure management while restricting unauthorized encryption changes. The No Cryptography Administrator role can be cloned to create custom roles with only specific Cryptographic Operations privileges, providing fine-grained control over encryption-related tasks.
-The cryptographic modules used across VCF components are validated against industry-standard best practices. NSX is configured to use FIPS 140-3 validated cryptographic modules by default, with validation performed through the NIST Cryptographic Module Validation Program (CMVP). VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module compliant with FIPS 140-3 (Certificate #4743). VCF Operations for Networks uses BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 as a validated cryptographic module. The vCenter appliance uses VMware's Boring Crypto Module version 6.0, which provides FIPS-validated cryptographic algorithms including AES, ECDSA, HMAC, RSA, and SHA2 variants, as well as VMware OpenSSL FIPS Object Module versions 3.0 and 2.0.20-vmw, which collectively support AES, CKG, DRBG, DSA, ECDSA, HMAC, KAS-SSC, RSA, SHS, Triple-DES, SHA-3, and additional key derivation functions. ESX hosts use FIPS 140-2 validated cryptographic modules that implement security functions as a combination of hardware, software, and firmware. vSAN encryption uses AES-NI CPU offloading for efficient processing.
-For workloads deployed through VMware Kubernetes Service (VKS) on vSphere Supervisor, the Kubernetes control plane supports encryption at rest for API objects stored in etcd. The kube-apiserver implements this through the EncryptionConfiguration API, specified via the --encryption-provider-config argument. When configured, Secrets, ConfigMaps, and other designated resource types are encrypted on write to etcd. The kube-apiserver supports an external KMS provider as well as local encryption keys; when using local keys, the aescbc provider encrypts data using Base64-encoded secret keys specified in the EncryptionConfiguration resource. Using an external KMS is the recommended approach for production environments, as it allows keys to be managed and rotated independently of the cluster configuration. Encryption at rest for the Kubernetes control plane is not enabled by default; the default identity provider stores data in plaintext, and administrators must explicitly configure EncryptionConfiguration to activate it. After enabling EncryptionConfiguration, existing objects remain unencrypted until they are read and re-written. The Kubernetes etcd encryption mechanism does not extend to data stored in filesystems mounted into containers; for container workload data on persistent volumes, encryption depends on the underlying storage layer. vSAN File Service volumes used with vSphere Supervisor are mounted without encryption by default, so workloads relying on shared file volumes must address encryption at the storage layer or within the application. Kubernetes Secrets encrypted at rest are also protected from disclosure if an attacker gains access to etcd backup data.
-Classifying which data requires encryption, selecting between vSAN encryption, VM encryption, or both for specific workload categories, choosing the Key Provider model, and operating the key lifecycle (rotation, revocation, archive, destruction) are organizational data-policy decisions.</t>
+          <t>VCF protects endpoint device confidentiality, integrity, availability, and safety through layered controls spanning hardware trust, hypervisor integrity, encryption, workload isolation, storage resilience, agent management, network security, monitoring, and lifecycle management.
+At the hardware layer, VCF supports Secure Boot, Trusted Platform Modules (TPM), and technologies such as AMD Secure Encrypted Virtualization (SEV-ES) for confidential computing. VMware vCenter can retrieve TPM event logs to validate boot-time measurements, and host attestation state can be monitored to verify that hosts have booted in a known good configuration. TPM modules must run the latest 2.0 firmware when in use, or be disabled in the BIOS if not used. Confidential vSphere Pods can use SEV-ES to provide hardware memory encryption and help prevent CPU register state from leaking information to other components. Virtual machines support UEFI Secure Boot for guest operating system integrity verification. vSphere also supports adding a virtual Trusted Platform Module (vTPM) to virtual machines, which reduces the risk of exposing guest operating system secrets if a guest is compromised. For Windows guest operating systems, vSphere supports Virtualization Based Security (VBS), which provides hardware-backed isolation for security features including Device Guard and Credential Guard within the VM.
+The VMware ESX hypervisor enforces workload isolation between virtual machines and between VMs and the hypervisor itself. VCF Operations verifies the digital signatures on management pack PAK files to confirm authenticity and publisher identity before installation. OVF and OVA packages can be signed, and the system validates digital signatures during upload. Content libraries support security policies that enforce controls on VM images.
+VCF protects the confidentiality of data through several encryption mechanisms. vSAN data-at-rest encryption protects data on storage devices in case a device is removed from the cluster, and administrators can enable the Secure Erasure feature alongside it. When data-at-rest encryption is enabled, vSAN encrypts data after all other processing (such as deduplication) is performed. VMware software and services encrypt network traffic between components, and VCF Operations for Networks supports FIPS validated cryptographic modules for both internal and external connections, with the ability to restrict cryptographic module usage to FIPS validated modules by enabling FIPS mode. For compute-layer confidentiality, vSphere supports hardware memory encryption for confidential pods, providing memory encryption for workloads running within those pods.
+vSphere Configuration Profiles and vSphere Lifecycle Manager (vLCM) provide desired-state configuration management for ESX hosts. vLCM defines a desired software specification for a cluster or standalone host, checks compliance against that specification, and can remediate hosts that have drifted. VCF Operations extends this with scheduled configuration drift detection for vCenter instances and clusters, comparing current settings against assigned desired values and reporting deviations.
+vSAN protects stored data through end-to-end checksums that verify data integrity during read and write operations. If a checksum mismatch is detected, vSAN automatically repairs the data by overwriting the incorrect copy with correct data. RAID-5 and RAID-6 erasure coding protects against capacity device failures while providing space efficiency. vSAN tracks component failure states, distinguishing between temporary failures (network connectivity loss, host failure) and permanent failures (device failure, controller failure), and rebuilds affected data once the configurable object repair timer expires (default 60 minutes). This timer can be tuned to balance between transient and sustained failure response.
+For network-level endpoint protection, NSX segments and isolates workloads through distributed switching and routing.
+VCF includes ESX Agent Manager, which automates the deployment and lifecycle management of agents on ESX hosts. ESX Agent Manager uses the AgentOvfEnvironmentInfo object to pass configuration properties, such as IP addresses and credentials, so that agents can connect back to their managing solution once deployed. It installs one agent instance per agency per host, and can resolve deployment issues if the solution or administrator requests it. VCF Operations requires guest operation privileges to install monitoring agents on endpoint virtual machines.
+For container and virtual machine workloads, VMware Kubernetes Service (VKS) with Supervisor provisions workload clusters that are secure by default by inheriting the vSphere security features built into vCenter and ESX. VKS validates TLS certificates when fetching images from registries, helping to confirm the authenticity and integrity of container image sources. Container supply chain security is supported through Harbor, available as a standard package on VKS clusters, which provides vulnerability scanning, content trust, and policy-based replication. Pod-level security is enforced through VKS Cluster Management Security Policies, powered by Open Policy Agent (OPA) Gatekeeper, which include a Restricted profile that allows administrators to harden the cluster estate with minimal operational friction; administrators can apply stricter Pod Security Standards based on the risk posture of each cluster. For service-to-service communications, the Istio service mesh standard package available on VKS clusters provides mutual TLS authentication and encryption alongside Layer 7 network policies based on workload identity, extending isolation beyond namespace boundaries to the workload level. Secrets management for containerized workloads is provided through Kubernetes Secrets, with the Secret Store Service enforcing role-based access control for administrators, DevOps engineers, and application tenants; VKS clusters establish a default role that grants service accounts read access to guest cluster secrets in the Secret Store service. For virtual machine workloads running via VM Service, Supervisor integrates with HashiCorp Vault through agent-based secret injection configured via VirtualMachine resource annotations, with secrets delivered through a disk-based sidecar mechanism. VCF Automation provides predefined roles to establish a baseline security posture for VKS cluster management. Security Technical Implementation Guides (STIGs) for Supervisor components and VKS runtime releases (VKrs) are available to guide hardening of the workload platform layer.
+VKS Cluster Management supports backup and restore of VKS clusters and their constituent namespaces to address the availability of containerized workloads. CSI-based data protection for VKS requires a validated configuration between VKS and the underlying storage infrastructure. For on-premises deployments, CSI volume snapshots can be offloaded to external S3-compatible endpoints, providing durability where local storage arrays lack native snapshot replication across sites. Platform engineers establish authenticated connections to storage providers to enable secure backup orchestration across VKS clusters and their resident resources.
+For availability and ongoing security posture management, VCF Operations discovers and monitors application services on endpoint virtual machines where agents are installed, collecting metrics for supported operating systems and services on monitored endpoints. It displays Guest OS Services Authentication Status to reflect the authentication state of guest operating systems and tracks VM authentication status with possible values including Unknown, Failed, Guest Alias, Common Credentials, or Credential-less. VCF Operations provides visibility into virtual machines with security tags applied, displaying VM counts by security tag and showing security groups assigned to VMs. The VCF Operations Security Operations dashboard provides visibility into security across multiple areas including user security and component security for VMs, ESX hosts, and vSAN, along with compliance checks and alerting capabilities. VCF Operations also supports firewall hardening that restricts network access to its own internal services through the Administrator Settings Security Settings interface, reducing the attack surface of the management plane itself.</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -12464,23 +12375,24 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>VCF implements network security as a series of independent, layered functions that operate at distinct points in the network path. Each layer enforces its own policies without relying on the correctness or availability of other layers, satisfying the principle of layered defense with minimal inter-layer dependence.
-At the hypervisor level, VMware ESX defines network security policies through HostNetworkSecurityPolicy, which governs traffic behavior on virtual switches independently of any overlay network configuration. This provides a baseline layer of network security enforcement at the physical host boundary. The vSphere networking security policy, implemented in Layer 2 of the network protocol stack, protects traffic against MAC address impersonation and unwanted port scanning on both standard and distributed switches. ESX also supports UEFI Secure Boot and Trusted Platform Module (TPM) for boot-time integrity verification, and TPM event logs can be retrieved for attestation and boot measurement validation. Each ESX host enforces its own boot chain integrity independently of the management plane above it.
-At the virtual infrastructure layer, vSphere Distributed Switches provide centralized management of virtual networking, handling traffic for all associated hosts in a data center. Distributed switches support network segmentation using Private VLAN (PVLAN) and VLAN-based SPAN for distributed port mirroring. Network segmentation is built into the VCF architecture: management traffic, vMotion, and storage traffic are isolated on separate networks. Network I/O Control allocates bandwidth to traffic types based on share values, and the Storage Traffic Separation network profile creates dedicated vSphere Distributed Switches with separate physical NICs for storage traffic isolation. DVFilters provide a packet-level interception mechanism within the virtual switch layer, enabling security functions to inspect and act on VM traffic independently of overlay or gateway controls.
-NSX provides a tiered gateway architecture that creates a well-defined routing hierarchy. Tier-0 gateways handle North-South connectivity between the NSX logical network and the physical infrastructure, with external interfaces to upstream networks and router links to Tier-1 gateways. Tier-1 gateways connect southbound to network segments and northbound to Tier-0 gateways. Each tier enforces its own policies without relying on the other.
-NSX segment security provides stateless Layer 2 and Layer 3 filtering at the network segment boundary. This function checks ingress traffic to the segment and drops unauthorized packets by matching IP addresses, MAC addresses, and protocols against a set of allowed values. Because segment security operates statelessly at L2/L3, it functions independently of higher-layer stateful inspection or application-level controls.
-At the identity layer, VCF centralizes authentication through VCF SSO, and all VCF components use role-based access control (RBAC) to restrict access to authorized users. NSX extends RBAC with project-scoped roles, so that network and security administrators have permissions only within their assigned project rather than the entire NSX deployment. NSX VPCs support scoped role assignments including VPC Admin, Security Admin, Network Admin, Security Operator, and Network Operator roles. A VPC Admin has full access to networking and security objects within their assigned VPC, while Enterprise Admins retain overarching control. NSX Advanced Network Management extends RBAC to specific networking components including static routes, locale services, segments, segment profiles, IP address pools, forwarding policies, DNS, DHCP, load balancing, and NAT. Custom roles can be created for more granular delegation.
-NSX multi-tenancy through Projects enables isolation of networking configurations across tenants in a single NSX deployment. Network profiles support isolation through subnets, external subnets, security groups, and VLAN transport zones. NSX overlay segments provide additional network isolation, enabling separate network paths for fleet-level networks.
-At the management layer, all management interfaces and APIs use TLS encryption. NSX Manager supports configurable TLS protocol versions and cipher suites. VCF provides a security baseline that can be used to evaluate both default and non-default configurations and can assist organizations in securing information systems in a compliance context. Built-in compliance scanning measures security posture against industry-standard benchmarks. The NSX Security Configuration Guide provides documented procedures for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, with recommendations covering strong authentication, RBAC implementation, and administrative access controls.
-VCF Automation extends this layered model into workload provisioning by supporting security groups that can be associated with machine resources in cloud template designs. Administrators can define both existing and on-demand security groups within network profiles, applying consistent security grouping as workloads are deployed without requiring manual per-VM configuration.
-vSphere Lifecycle Manager enforces desired-state configuration for hosts and clusters, applying and remediating configuration to match the defined software specification. This helps detect and address configuration drift that could weaken network security posture.
-Audit logging supports ongoing governance by recording administrative actions with full traceability, so that organizations can track who changed configuration, what was changed, and when. Programmatic management through PowerCLI supports infrastructure-as-code approaches, enabling version-controlled and repeatable policy deployment.
-VMware vDefend is a separate product that builds on VCF's networking foundation to add further security layers at the VM vNIC, the overlay boundary, and the application layer. vDefend operates above VCF's native network isolation and segment security and is independent of them.
-The Consumption layer of VCF extends these layered network defenses into the Kubernetes workload tier through VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes security model requires that cluster infrastructure provide the security guarantees that higher application layers depend on, and VCF grounds the Consumption tier in the platform's NSX networking and vSphere security controls described above, so each tier remains independent from the layers above it.
-At the namespace layer, vSphere Supervisor namespaces support Pod Security Admission (PSA) enforcement, which evaluates pod specifications at admission time in the Kubernetes API server, independently of any network-layer or runtime-layer controls. Three standard PSA profiles are available: Privileged, Baseline, and Restricted. The Baseline profile mitigates common privilege escalation risks while maintaining compatibility with standard containerized workloads. The Restricted profile additionally blocks host network access, privileged containers, and unrestricted capabilities. Because PSA operates at admission time, non-conforming pods are rejected before reaching the network or runtime layers, regardless of whether a NetworkPolicy exists for that namespace.
-At the network policy layer within VKS clusters, Antrea serves as the default Container Network Interface (CNI) plugin and operates at Layer 3 and Layer 4 using Open vSwitch as the networking data plane. The AntreaPolicy feature gate enables network policy enforcement in Antrea. Kubernetes NetworkPolicy objects deployed within VKS clusters are enforced by Antrea, providing declarative control over packet filtering between pods and external endpoints. Service meshes can layer workload-identity-based OSI Layer 7 policies on top of namespace-level isolation and provide mutual TLS encryption for inter-pod traffic that would otherwise traverse the cluster network unencrypted. Cilium, available as a cluster addon, enforces network policies at L3 through L7 using an identity-based security model that is decoupled from network addressing, supporting environments where IP-based policy is insufficient.
-At the container runtime layer, Kubernetes security contexts allow administrators to restrict container privileges at the Pod or individual container level. Controls include specifying the Linux user identity, dropping Linux capabilities to the minimum required set, setting a read-only root filesystem to block writes to the container filesystem, and applying seccomp profiles that use BPF to filter system calls through allow or deny lists, reducing the kernel syscall attack surface available inside containers. AppArmor and SELinux profiles applied through security context annotations provide mandatory access control at the kernel level, extending restrictions beyond the container boundary to help mitigate container runtime vulnerabilities. VKS Cluster Management Security Policy templates in the VCF services consumption interface enable fine-tuning of individual security context parameters and support governance controls tailored to organizational requirements.
-VKS clusters use TLS encryption to secure communications among Kubernetes components, including the API server, etcd, and service clusters, independently of workload-level network policy configuration. Security Technical Implementation Guides (STIGs) for Supervisor and Kubernetes release (VKr) components are available through Tanzu STIG Hardening, providing documented hardening guidance across these layers.</t>
+          <t>VCF provides multiple layers of boundary protection to isolate technology assets, applications, and services that support critical workloads. These isolation mechanisms span network infrastructure design, software-defined networking, multi-tenant organization boundaries, security group policies, and component-level separation.
+At the network infrastructure level, VCF supports several distributed switch design models that enforce traffic isolation between management, storage, and workload domains. The Fleet Level Components on Dedicated Management Network Model places management traffic on a dedicated, VLAN-backed distributed port group that is isolated from other networks, providing separate security boundaries for fleet-level management communications. Management traffic runs on dedicated networks accessible only to administrators, and vMotion traffic is separated on distinct networks. For larger deployments with stricter isolation requirements, the Storage and Workload Separation Distributed Switch Model isolates traffic onto different physical fabrics, which also provides quality-of-service benefits. Dedicated VLANs isolate IP-based storage traffic, and vSAN deployments use dedicated storage network segments with physical network adapter separation. vSAN storage traffic separation is typically configured with a dedicated vSphere Distributed Switch for vSAN storage traffic and a separate distributed switch for all other traffic. vSAN also provides a separate network dedicated to vSphere HA isolation detection, keeping storage heartbeat traffic segmented from other network flows. vSAN Data-in-Transit encryption, a cluster-wide setting that encrypts all data and metadata traffic as it transits across hosts, adds a cryptographic boundary on top of the network-level isolation. VMware vCenter also supports SAN masking and zoning as a storage isolation practice, restricting which hosts can access specific SAN resources.
+NSX extends these capabilities with software-defined networking that supports multiple network architecture models. Virtual Private Clouds (VPCs) provide isolated network environments within a shared infrastructure, with independent permission models, topology, and IP address management, allowing discrete projects to operate in isolated network domains. VPC subnets support Private, Public, and Isolated access modes, where a private subnet is accessible only within its NSX VPC. Cross Workload Domain Networking models allow networking and security services to be extended across workload domains through a single management interface while maintaining logical separation. The distributed switch has built-in security controls to help protect traffic, and NSX Manager supports applying switch security profiles to distributed port groups.
+Network I/O Control provides bandwidth reservation and allocation based on the capacity of the physical adapters on a host, allowing administrators to assign shares across traffic types including vSAN, vSphere vMotion, and virtual machine traffic on shared physical adapters. This keeps critical workloads performing under contention by reserving bandwidth for priority traffic flows. vSphere Distributed Switches enforce consistent VLAN configurations, traffic shaping rules, and security policies across all hosts.
+VCF Automation delivers multi-tenant boundary protection through its Organizations construct. Each organization operates in a secure and isolated environment where users can access only the services and resources allocated to them. Organizations maintain secure boundaries from one another, and IT teams can monitor resource usage, control permissions, and provide managed services while maintaining network isolation across tenants. This multi-tenant model supports creating multiple tenants with secure infrastructure isolation, quotas, and chargeback, allowing critical workloads to be separated from general-purpose environments.
+Within each organization, VCF Automation provides granular network isolation through security groups and firewall rules. Security groups can be applied to deployed resources to enforce network isolation boundaries and can define isolation settings for on-demand private or outbound networks. Network profiles support isolation configurations using subnets, external subnets, security groups, or VLAN transport zones, giving administrators flexibility in how boundary protections are implemented. App isolation policies can be defined per project so that deployments requiring on-demand security groups for application isolation share a consistent policy within the same endpoint. Projects within organizations offer additional isolation boundaries with dedicated network configurations and centralized access control.
+VCF Operations supports firewall hardening that restricts network access to its internal services, providing boundary protection for the management and monitoring plane. At the compute layer, vSphere administrators set guardrails for policy and governance of virtual machines, controlling what resources are delivered to workload consumers and establishing administrative boundaries around VM classes and templates. vSphere also supports Virtualization-based Security (VBS) for virtual machines, which protects key system services from manipulation and provides an additional isolation boundary at the compute layer.
+For workloads running on VMware Kubernetes Service (VKS) within vSphere Supervisor, the platform provides multi-layered boundary protection for containerized and virtual machine workloads. Namespace isolation is the foundational unit of boundary protection: Kubernetes RBAC restricts API access so that teams and their workloads can only access or modify resources within their own namespaces, and each namespace receives its own egress IP address for communication outside of NSX. Resource quotas and limit ranges at the namespace level bound resource consumption, reducing the risk of exhaustion spreading across isolation boundaries. Pod Security Admission (PSA) can be configured per namespace to enforce Baseline, Restricted, or Privileged security standards on pods independently, making it possible to apply stricter security profiles to namespaces that host critical workloads. VCF Automation security policies use the resource hierarchy for scalable governance, with constraints applied at the organization or project level automatically inherited by all child resources, so isolation policies defined for a project propagate to every workload deployed within it.
+Network boundary enforcement within VKS is achieved through Kubernetes NetworkPolicy objects, backed by Antrea or NSX, which define per-namespace ingress and egress rules that restrict which pods and services can communicate across namespace boundaries. For workloads requiring stronger isolation at the application layer, service meshes provide Layer 7 network policies based on workload identity in addition to namespace-based isolation. Windows overlay networks provide isolation of container networks from the host underlay. For Windows container workloads, Hyper-V isolation provides kernel-level separation between containers and the host.
+Data-plane isolation can be extended beyond namespace-level policies. Kubernetes RuntimeClasses allow operators to define custom isolation profiles for individual workloads, including sandboxed containers that provide stronger kernel separation between the container and the host. Node isolation reduces the risk of information disclosure because an attacker that escapes from a container will only have access to containers and volumes mounted to that node. For multi-tenant deployments requiring the highest degree of isolation, the virtual control plane model gives each tenant a dedicated control plane; data-plane isolation techniques can be combined with this model to secure worker nodes across tenant boundaries. VM classes in vSphere Supervisor set guardrails for the policy and governance of virtual machines, controlling what resources are delivered to workload consumers. IAM role trust policies can be scoped to specific service accounts and namespaces to enforce least privilege at the VKS cluster level.
+Workload security posture is shaped by security contexts applied at the pod and container level. Settings such as runAsUser, Linux capabilities, seccomp profiles, and readOnlyRootFilesystem scope the runtime permissions of individual containers, reducing the potential for lateral movement across component boundaries. Supervisor leverages vSphere security features built into VMware vCenter and VMware ESX to provision workload clusters that are secure by default. Hardening guidance for Supervisor components is available through Defense Information Systems Agency (DISA) Security Technical Implementation Guides (STIGs) for Supervisor itself and for VKS Kubernetes releases (VKrs), available through Tanzu STIG Hardening.
+For environments with compatible hardware, vSphere Distributed Services Engine extends security isolation by offloading network and security services to a dedicated data processing unit, implementing zero-trust security at the infrastructure layer.
+VCF also integrates with VMware vDefend, a separate product that adds Distributed Firewall microsegmentation and Gateway Firewall capabilities for fine-grained traffic control between virtual machines and containers. Distributed Firewall policies can be configured to allow traffic from pods in one Kubernetes namespace to another while dropping traffic from elsewhere.
+VMware Private AI Services (PAIS) contributes to the isolation of technology assets through PAIS-specific mechanisms that operate above the boundary protections provided by VCF.
+The Model Gallery is a primary isolation boundary for AI artifacts in PAIS. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive data that is used to train and tune models, scoping access at the artifact level so only authorized roles can pull or push specific models.
+PAIS is activated within an organization namespace, bounding which workloads can reach Private AI Services endpoints. The PAIS components, including API, ingress, rex worker pods, and an optional Prometheus server pod when observability is activated, run inside that namespace. GPU-capable VM classes with GPU reservations confine GPU consumption to a single namespace, and reserved GPU VM classes can be pinned to a single zone or Supervisor for further isolation. GPU resources can be shared between workloads using time slicing or Multi-Instance GPU (MIG) to enforce resource isolation between AI consumers on the same physical accelerator. Device groups present complementary hardware devices connected over PCIe switches, NVLink, NVSwitch, or RDMA to vSphere as unified entities, so the boundary around a high-bandwidth accelerator group is treated as a single allocation unit rather than independent devices.
+PAIS supports disconnected (air-gapped) deployments where AI infrastructure has no path to the public internet. In a disconnected environment, PAIS deployment requires a Bastion host with internet access for downloading packages and images and a separate Admin host without external connectivity, with a machine running Docker, the VCF Consumption CLI, and kubectl performing the in-cluster deployment. The artifact mirroring tool (AMT), distributed as part of the pais CLI plug-in, stages components, and a private Harbor container registry stores GPU Operator images and other dependencies locally, with registry credentials supplied as environment variables during deployment.
+The foundational compute, network, and storage isolation boundaries, including Workload Domains, vSphere, vSAN, and NSX, are VCF platform capabilities, with vDefend providing distributed firewall and microsegmentation. PAIS's contribution is the AI-workload-specific isolation layer built on top of that foundation.</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -12490,10 +12402,12 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) provides layered network security enforcement spanning Layer 2 through Layer 7, with each layer operating on its own policy evaluation independently of the others. The Distributed Firewall (DFW) Ethernet category enforces Layer 2 traffic, and an Allow rule match triggers further evaluation through Layer 3-7 categories in the DFW policy hierarchy. At the network and transport layers, the DFW performs stateful packet inspection and offers protocol validation to protect against low-level IP attacks. Layer 7 enforcement uses a Deep Packet Inspection (DPI) engine that receives pending Layer 7 flows from the DFW via VSIP, enabling application-identity and user-identity-based access controls including FQDN filtering. The Gateway Firewall provides north-south enforcement at the NSX edge, analyzing application-layer content to permit or block traffic based on application-level information.
-The vDefend Advanced Threat Prevention (ATP) edition layers IDS, Network Traffic Analysis (NTA), and Network Detection and Response (NDR) as concurrent and independent detection capabilities over the base DFW enforcement. NDR provides security analysts with capabilities to understand security events, triage, and remediate them by creating policies. NDR classifies detections by Detection Type, MITRE Tactic, MITRE Technique, Threat name, Affected Workload, Campaigns, and Signature Type. These ATP capabilities operate in air-gapped environments, where IDS, NTA, and NDR provide detection in isolated networks without cloud connectivity.
-The Security Services Platform (SSP) supports security segmentation planning through a multi-level hierarchy spanning Region, Zone, Environment, Application, and Tier levels for granular segmentation design. DFW activation of malicious IP feeds and corresponding security rules provides foundational defenses within this segmentation model. Bare Metal Security extends Layer 3/4 DFW policy enforcement to physical servers, applying consistent policy across both virtual and physical workloads. The Security Segmentation Score and Report feature in SSP evaluates DFW deployment coverage, including network and transport layer protocol protections, to assess the layered defense posture.
-The vDefend security model is structured as a Security Journey, a staged approach that allows organizations to progressively adopt a Zero Trust posture, moving from initial assessment and quick wins toward application-level microsegmentation.</t>
+          <t>VMware vDefend provides boundary protections designed to isolate technology assets, applications, and services that support critical missions and business functions. vDefend delivers east-west and north-south boundary enforcement through its Distributed Firewall and Gateway Firewall, enabling organizations to define and enforce isolation policies at multiple layers of the environment.
+The vDefend distributed firewall enforces security rules at the VM vNIC level, providing microsegmentation that isolates workloads regardless of their physical location in the data center. DFW policies are organized into predefined categories: Infrastructure, Environment, and Application, which map to isolation requirements at different levels of the architecture. The Infrastructure category protects management and shared services. The Environment category establishes zone-level isolation between logical environments such as production, development, and testing. The Application category enables granular microsegmentation between individual workloads and application tiers. Zone segmentation provides macro-level security by establishing strict boundaries between large segments such as Development, QA, UAT, and Production to reduce the attack surface. Application Protection in Strict Mode enforces application-level firewall rules across all application workloads; the apply-to scope must cover all application workloads including critical applications, and scoring based on workload coverage gives administrators a measurable view of application-layer isolation. Grouping constructs support multiple isolation strategies using workload-centric attributes (VM name, tag, operating system), network-centric attributes (IP address, MAC address, subnet), or Active Directory group membership through the Identity Firewall. In federated deployments, policies can be configured with global, regional, or local span, and Security Services Platform regions can be associated with Security and Network policies to scope boundary enforcement across multiple locations.
+In VCF multi-tenant environments, vDefend provides five system-defined security strategies for VPC security posture: VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. VPC Isolation with Essential Services (System Security Profile 3) denies all lateral traffic to other VPCs in the same project while permitting infrastructure protocols (DHCP, DNS, NTP, ICMP). This profile can only be designated as the default profile rather than manually selected, which enforces a consistent baseline isolation across a project. Administrators can use the Distributed Firewall with VPC isolation strategies to implement a strict security baseline for project workloads while delegating granular control to application owners.
+The vDefend gateway firewall provides boundary protection for north-south traffic at the network perimeter. Gateway Firewall rules can be configured on tier-0, tier-0 VRF, and tier-1 gateways to secure ingress and egress traffic at perimeter points. For multi-project environments, Enterprise Administrators can enforce centralized transit gateway firewall policies in two modes: Enterprise Gateway Isolation, which denies all communication between distinct projects, and Isolation with Essential Services, which denies all inter-project communication except infrastructure protocols (DHCP, DNS, NTP, ICMP). Bridge Firewall capabilities extend boundary protection to overlay-to-VLAN and VLAN-to-VLAN boundaries where physical and virtual networks meet. vDefend TLS Inspection extends boundary enforcement to encrypted traffic at the gateway; the High Fidelity decryption profile blocks and logs connections with invalid certificates or decryption failures.
+Security Services Platform (SSP) and Security Intelligence extend these boundary protections with environment-level segmentation monitoring and policy planning. Environment segmentation divides the data center into broader security zones, and SSP inventory monitoring provides visibility into the full infrastructure hierarchy organized by region, zone, environment, application, and tier, allowing administrators to verify correct asset grouping. The Segmentation Monitoring Dashboard tracks which environment pairs have active protection policies. Administrators can identify all inter-environment flows and configure block or reject policies between environment pairs that should not communicate, such as development and production, before enforcing a strict block rule. The Security Segmentation Score quantifies overall segmentation coverage; the Environment Protection criterion evaluates whether workloads in each environment type are covered by isolation policies specific to that environment (Dev, Prod, Test). Security Intelligence Recommendations generates DFW policy recommendations based on observed traffic flows to assist with microsegmentation planning. Rule Analysis evaluates existing DFW rules for effectiveness and coverage, helping identify rules that may be redundant, shadowed, or unused.
+Role-based personas for vDefend are a factor in maintaining security boundaries between different projects and the broader organization. Administrators should note that in multi-tenant deployments, vDefend IDS/IPS has no configuration isolation between projects; IDS/IPS signature and profile configuration applies at the deployment level rather than per-project.</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -12528,13 +12442,14 @@
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer implements security functions as a discrete application-delivery layer within the broader defense architecture of VCF. At the application delivery tier, Avi enforces independent security policies at Layer 4 and Layer 7, with each layer operating without dependence on the other for its enforcement decisions.
-At Layer 4, the Network Security Policy evaluates incoming client traffic based on network-level parameters and determines whether a connection should be accepted, discarded, or rate-limited. Network Security Policy rules reference reusable IP Groups, which can be shared across multiple virtual services to apply network-layer access control at scale. NSX security groups defined in the network platform can be referenced directly as IP Group members in Avi virtual service security policies, allowing network-level groupings maintained in NSX to drive Avi's Layer 4 access control without manual IP address list duplication. The DDoS Policy detects and mitigates a range of Layer 4 through Layer 7 network attacks through the Network Security policy, with network-layer enforcement taking effect before Layer 7 HTTP processing.
-At Layer 7, Virtual Service Policies provide independent controls over HTTP security, HTTP request handling, and HTTP response rewriting. The System-Secure-HTTP application profile secures HTTP traffic by enforcing HTTPS, protecting cookies, managing client IPs, and controlling protocol behavior. The Web Application Firewall (WAF) adds an application-inspection tier with both negative security (signature-based Application Rules that detect attack patterns) and a Positive Security model maintained as a distinct policy object. The Positive Security model reduces attack surface by only allowing known-good traffic, while the signature-based rules operate independently, keeping the two security models separate within the application layer.
-In 9.1, the Avi Kubernetes Operator (AKO) provides WAF integration for VMware Kubernetes Service (VKS) clusters, extending application-layer security to Kubernetes ingress traffic within the VCF environment.
-Avi's DDoS telemetry maintains this layered organization: Service Engine DDoS Insights reports Layer 4 attack data (including IP fragmentation attacks and TCP SYN flood) separately from Layer 7 attack data, so operators can assess and respond to threats at the appropriate layer without conflating the two.
-Avi also supports integration into Firewall Sandwich topologies, where Avi Service Engines are positioned in conjunction with external firewall tiers. This architecture allows Avi to handle application-delivery and application-security functions while network-layer security appliances operate independently, each tier functioning without dependence on the other's correctness.
-The full layered network defense architecture requires platform mechanisms outside Avi's scope. NSX provides the routed underlay and network segmentation, and VMware vDefend provides microsegmentation between workloads. Together with Avi's application-delivery security tier, these form the layered defense architecture this control addresses. Organizations must configure mechanisms across all relevant tiers to implement the layered structure the control requires.</t>
+          <t>VMware Avi Load Balancer (Avi) provides several mechanisms that implement boundary isolation for application workloads at the load balancing layer.
+Service Engine Groups are the primary isolation boundary for application traffic. Each Service Engine Group acts as an isolation domain: Service Engines are bound exclusively to a single group, and a group's capacity is not shared with or borrowed by another group. Service Engines in one group cannot serve virtual services assigned to another group, providing data plane isolation between applications deployed on separate groups. This is configured under Load Balancing &gt; Service Engine Group in the Avi Controller UI.
+Within each Service Engine, Avi implements internal separation between the data plane and the control plane. The Service Engine Group datapath isolation mode (se_dp_isolation) creates two independent and exclusive CPU sets: one dedicated to datapath processing and one to control plane functions. This separates datapath from control plane processing, and is configurable under Service Engine Group Advanced Parameters.
+The tenant model provides a higher level of isolation for multi-tenant deployments. Tenants in Provider Context give control plane isolation only, while tenants in Tenant Context give both control plane and data plane isolation. Organizations can choose between Service Engine Group isolation (data plane only) and tenant-level isolation (control and data plane) depending on the boundary protection requirements of the application environment.
+At the network layer, Avi VRF Contexts provide traffic isolation between Service Engine interfaces that connect to segments of different T1 routers. This configuration is applied automatically when Avi is deployed with an NSX Cloud, keeping traffic paths for distinct network segments separate within the same Service Engine. VRF Contexts are also available for multi-tenant network isolation in bare-metal Service Engine deployments, where contexts are associated with a tenant and cloud reference.
+In VCF-integrated deployments, the Avi for VCF integration extends boundary isolation to the VCF Automation layer. Service Engine Group allocation scopes each VCF Automation project to its designated capacity boundaries. The VCF Automation Provider Management Portal allows provider administrators to define infrastructure boundaries by creating regions and organizations, with region quotas specifying accessible zones and capacity allocation.
+For Kubernetes environments, the Avi Kubernetes Operator (AKO) CRD Operator manages namespace-scoped resources with tenant isolation for multi-tenancy support, extending Avi's boundary isolation model to Kubernetes workloads.
+Boundary protection for critical assets also depends on network-level segmentation and microsegmentation from VCF and the vDefend distributed firewall, which operate at the hypervisor and underlay network level below the application delivery layer that Avi controls.</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12587,7 @@
 NSX Guest Introspection provides an agent-based framework that supports endpoint security within virtual machines. The Guest Introspection Agent must be installed and running in each guest VM, and logged-in users should not have the privilege to remove or stop the agent. This architecture enables third-party security solutions to inspect guest operating system activity without requiring agents to be installed directly on the hypervisor. The security and integrity of the guest operating system must be maintained for these integrations to function correctly.
 For container workloads, the VCF CLI supports cosign signature verification for container images through the imgpkg tool, which enables finding and copying cosign signatures. Image pull authentication through imagePullSecrets restricts container image pulls to authenticated private registries. Plugin discovery image signature verification is supported, with configurable public key paths for the cosign verifier. These capabilities help restrict deployment of images that have been tampered with.
 VCF Operations supports the deployment and monitoring of agents on endpoint virtual machines, with guest operation privileges required to install agents. Automated software update capabilities in vCenter help keep systems current with security patches, reducing the window of exposure to known malware exploits.
-For organizations that deploy VMware vDefend as an add-on to VCF, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
+For organizations that deploy VMware vDefend, a separately licensed advanced service, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
 Malware prevention activities generate log data for audit and forensic purposes. The Malware Prevention for vDefend feature writes log files that can be used for troubleshooting and security monitoring, and remote logging can be configured on the malware prevention SVMs for centralized log collection.
 VMware Private AI Services (PAIS) includes model validation capabilities that scan machine learning model files for malicious content before they are accepted into a Model Gallery. The validation runs as a sandbox process on Deep Learning VMs and covers integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference behavior testing with NVIDIA Triton Inference Server. Both the malware and serialization checks run as part of the validation workflow required before a model can be uploaded to a Model Gallery and made available to downstream model endpoints, knowledge bases, or AI agents.
 Machine learning model files are a category of artifact that traditional endpoint security tools may not inspect. Serialized models in formats such as Python pickle files can carry executable payloads that activate when an application or researcher loads the model. The PAIS Model Gallery intake workflow treats this upload boundary as a security checkpoint, requiring each artifact to pass hash, malware, serialization, and inference behavior tests before it is published for use. PAIS guidance also directs organizations to distribute only models that have been validated internally on a Deep Learning VM rather than pulling artifacts directly from the Internet, where models may contain malicious code or be tuned for malicious behavior. The validation is operated by MLOps engineers, who confirm that onboarded models meet the organization's security, privacy, and technical requirements.
@@ -12844,7 +12759,7 @@
 NSX Guest Introspection provides an agent-based framework that supports endpoint security within virtual machines. The Guest Introspection Agent must be installed and running in each guest VM, and logged-in users should not have the privilege to remove or stop the agent. This architecture enables third-party security solutions to inspect guest operating system activity without requiring agents to be installed directly on the hypervisor. The security and integrity of the guest operating system must be maintained for these integrations to function correctly.
 For container workloads, the VCF CLI supports cosign signature verification for container images through the imgpkg tool, which enables finding and copying cosign signatures. Image pull authentication through imagePullSecrets restricts container image pulls to authenticated private registries. Plugin discovery image signature verification is supported, with configurable public key paths for the cosign verifier. These capabilities help restrict deployment of images that have been tampered with.
 VCF Operations supports the deployment and monitoring of agents on endpoint virtual machines, with guest operation privileges required to install agents. Automated software update capabilities in vCenter help keep systems current with security patches, reducing the window of exposure to known malware exploits.
-For organizations that deploy VMware vDefend as an add-on to VCF, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
+For organizations that deploy VMware vDefend, a separately licensed advanced service, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
 Malware prevention activities generate log data for audit and forensic purposes. The Malware Prevention for vDefend feature writes log files that can be used for troubleshooting and security monitoring, and remote logging can be configured on the malware prevention SVMs for centralized log collection.
 VMware Private AI Services (PAIS) includes model validation capabilities that scan machine learning model files for malicious content before they are accepted into a Model Gallery. The validation runs as a sandbox process on Deep Learning VMs and covers integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference behavior testing with NVIDIA Triton Inference Server. Both the malware and serialization checks run as part of the validation workflow required before a model can be uploaded to a Model Gallery and made available to downstream model endpoints, knowledge bases, or AI agents.
 Machine learning model files are a category of artifact that traditional endpoint security tools may not inspect. Serialized models in formats such as Python pickle files can carry executable payloads that activate when an application or researcher loads the model. The PAIS Model Gallery intake workflow treats this upload boundary as a security checkpoint, requiring each artifact to pass hash, malware, serialization, and inference behavior tests before it is published for use. PAIS guidance also directs organizations to distribute only models that have been validated internally on a Deep Learning VM rather than pulling artifacts directly from the Internet, where models may contain malicious code or be tuned for malicious behavior. The validation is operated by MLOps engineers, who confirm that onboarded models meet the organization's security, privacy, and technical requirements.
@@ -13038,7 +12953,7 @@
 NSX Guest Introspection provides an agent-based framework that supports endpoint security within virtual machines. The Guest Introspection Agent must be installed and running in each guest VM, and logged-in users should not have the privilege to remove or stop the agent. This architecture enables third-party security solutions to inspect guest operating system activity without requiring agents to be installed directly on the hypervisor. The security and integrity of the guest operating system must be maintained for these integrations to function correctly.
 For container workloads, the VCF CLI supports cosign signature verification for container images through the imgpkg tool, which enables finding and copying cosign signatures. Image pull authentication through imagePullSecrets restricts container image pulls to authenticated private registries. Plugin discovery image signature verification is supported, with configurable public key paths for the cosign verifier. These capabilities help restrict deployment of images that have been tampered with.
 VCF Operations supports the deployment and monitoring of agents on endpoint virtual machines, with guest operation privileges required to install agents. Automated software update capabilities in vCenter help keep systems current with security patches, reducing the window of exposure to known malware exploits.
-For organizations that deploy VMware vDefend as an add-on to VCF, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
+For organizations that deploy VMware vDefend, a separately licensed advanced service, distributed malware prevention capabilities become available. The NSX Application Platform hosts the Malware Prevention for vDefend feature, which can be deployed from the Local Manager UI in NSX Federation environments. When host clusters are activated for Distributed Malware Prevention, a service virtual machine (SVM) is deployed on each host to perform malware scanning. vDefend also supports IDS/IPS capabilities alongside distributed malware prevention. The DistributedMps runbook is available to verify the health of the Malware Prevention Service pipeline and diagnose issues such as protection not working on a particular VM or certain files not being scanned.
 Malware prevention activities generate log data for audit and forensic purposes. The Malware Prevention for vDefend feature writes log files that can be used for troubleshooting and security monitoring, and remote logging can be configured on the malware prevention SVMs for centralized log collection.
 VMware Private AI Services (PAIS) includes model validation capabilities that scan machine learning model files for malicious content before they are accepted into a Model Gallery. The validation runs as a sandbox process on Deep Learning VMs and covers integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference behavior testing with NVIDIA Triton Inference Server. Both the malware and serialization checks run as part of the validation workflow required before a model can be uploaded to a Model Gallery and made available to downstream model endpoints, knowledge bases, or AI agents.
 Machine learning model files are a category of artifact that traditional endpoint security tools may not inspect. Serialized models in formats such as Python pickle files can carry executable payloads that activate when an application or researcher loads the model. The PAIS Model Gallery intake workflow treats this upload boundary as a security checkpoint, requiring each artifact to pass hash, malware, serialization, and inference behavior tests before it is published for use. PAIS guidance also directs organizations to distribute only models that have been validated internally on a Deep Learning VM rather than pulling artifacts directly from the Internet, where models may contain malicious code or be tuned for malicious behavior. The validation is operated by MLOps engineers, who confirm that onboarded models meet the organization's security, privacy, and technical requirements.
@@ -13407,12 +13322,12 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
+          <t>VMware vDefend provides multiple capabilities for continuously monitoring inbound and outbound communications traffic for unusual or unauthorized activities.
+Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments. The Environments Monitoring dashboard provides traffic flow analysis with protection status summaries for selected environment pairs within a configurable time range. Private IP range definitions establish the boundary between internal and external workloads, so traffic crossing that boundary is treated as external and subject to additional scrutiny. The Secure External Communications security project identifies workloads with inbound or outbound connections to external IP addresses, helping address exposure to external threats. The Monitor and Plan Overview page provides a consolidated view of pending actions, data collection status, network security posture, flow trends, and a summary of suspicious traffic. Network traffic flows in Security Intelligence are based on the distributed firewall rules in effect and on traffic flows observed during the selected time period, including traffic that matches stateful Layer 4 DFW rules.
+Network Traffic Analysis (NTA) for Suspicious Traffic continuously monitors and analyzes network traffic and flow records using advanced machine learning models and statistical techniques to establish a baseline of normal network behavior and identify deviations such as protocol misuse and unusual traffic patterns. NTA detects anomalies in the time series profile of individual hosts, identifying unusual network traffic patterns that may indicate compromise or policy violation. Suspicious traffic detectors report execution status after each run, with possible values of NOT_STARTED, SUCCESS, NOT_ENOUGH_BASELINE, or FAILURE, giving administrators visibility into detector health and data availability. Suspicious traffic events are surfaced through the Suspicious Traffic Events dashboard and the Threat Monitoring tab within Security Services Platform, providing a centralized view for security analysts.
+vDefend IDS/IPS inspects communications traffic for known attack signatures and suspicious behavior across both distributed and gateway deployments. IDS/IPS event monitoring supports filtering by traffic type, allowing administrators to focus on distributed traffic, gateway traffic, or both. Threshold and rate filters allow event triggering based on traffic behavior patterns, enabling administrators to tune detection sensitivity to their environment.
+The vDefend distributed firewall supports Monitoring Mode, which enables logging for all connectivity strategies to audit traffic flowing through the environment. DFW rules support per-rule logging of both allowed and dropped traffic. The Security Overview Dashboard provides centralized visibility into threat events, with filtering by All Traffic, Distributed Only, or Gateway Only traffic types.
+The vDefend gateway firewall secures north-south traffic at the environment boundary, providing a control point for monitoring and filtering inbound and outbound communications. Geo-Fencing capabilities allow administrators to create rules that monitor and control traffic based on geographic origin or destination, down to the country level. In multi-tenant environments, the Centralized Transit Gateway Firewall enables project administrators and providers to configure firewall rules on Transit Gateway nodes for managing incoming and outgoing traffic to external networks.</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -13452,12 +13367,12 @@
       </c>
       <c r="N146" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+          <t>VMware Avi Load Balancer (Avi) provides several mechanisms for continuous monitoring of application-layer communications traffic flowing through its configured virtual services.
+At the analytics layer, Avi Analytics continuously evaluates traffic against statistical baselines for each virtual service, detecting anomalies when traffic falls outside the statistical norm for the time period. The system assigns anomaly penalties for deviations and surfaces them in virtual service and pool analytics dashboards. Attack Visibility tools track over 500 real-time metrics across virtual services, supporting DDoS detection and response workflows.
+DataScripts extend the monitoring and mitigation capabilities by allowing custom identification of suspicious traffic and execution of appropriate mitigation actions at both L4 and L7 layers. Port-scan detection allows Avi Load Balancer to report or block sources performing port scans as part of DDoS mitigation.
+Bot Management via Avi WAF bot detection can classify traffic as dangerous bots and apply HTTP security actions including closing connections. In Cisco ACI-based deployments, integrated WAF (iWAF) provides granular security insights on traffic flows and rule matches, supporting precise policy enforcement based on observed traffic patterns.
+For integration with external monitoring infrastructure, the Virtual Service Sideband Profile replicates incoming HTTP(S) traffic at the protocol level to designated logging or sideband servers. This enables deep traffic inspection by external SIEM platforms or inspection appliances. Organizations should configure log forwarding to a centralized syslog or SIEM target to aggregate Avi's monitoring output with broader network telemetry and to satisfy continuous monitoring requirements across all communications paths, including those not routed through Avi virtual services.
+Avi's monitoring scope is bounded to traffic flowing through its configured virtual services. Communications that bypass Avi, such as east-west workload traffic not routed through the load balancer, require separate monitoring tooling at the platform level.</t>
         </is>
       </c>
     </row>
@@ -13489,13 +13404,14 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to anomalous behavior detection and user activity monitoring, though it does not include a dedicated User &amp; Entity Behavior Analytics (UEBA) or User Activity Monitoring (UAM) solution.
-VCF Operations includes anomaly detection capabilities that use both dynamic and static thresholds to identify when metrics deviate from normal operating behavior. Dynamic thresholding is enabled by default and uses historical data analysis to establish baselines for each monitored object. The Smart Early Warning feature analyzes the number of applicable metrics that violate the dynamic threshold determining normal operating behavior, triggering alerts when the number of anomalies on an object exceeds a trending threshold. When an anomalous entity is detected, VCF Operations generates an outlier violation alert (vmwAnalyticsOutlierEvent, OID 37002), notifying administrators of unexpected behavior. A Critical threshold violation alert is also generated when anomalous entities are detected.
-The Anomalies widget displays detected anomalies for a resource over the past six hours at configurable time intervals, with color-coded criticality indicators. The Anomaly Breakdown widget shows likely root causes for symptoms on a selected resource, helping operators triage issues. The Troubleshooting Workbench includes an Anomalous Metrics card that surfaces metrics exhibiting drastic changes within a selected scope and time window, ranked by degree of change with the most recent anomaly given the highest weighting. Administrators can also examine outlier VMs detected by VCF Operations to identify unexpected behavior and take corrective actions. VCF Operations supports outbound SNMP trap notifications, enabling alert delivery to external SNMP management systems with up to four configurable trap destinations.
-For user activity monitoring, VCF Operations provides a User Activity Audit report that offers traceability of user actions including logging in, operations on clusters and nodes, changes to system passwords, certificate activation, and logging out. Each audit event has a detailed view containing information that supports analysis of events in the virtual infrastructure for suspicious user actions or system issues. Event auditing across the VCF platform provides visibility into platform interaction changes and surfaces suspicious access events and policy violations. Administrators should continuously monitor user security aspects to detect security risks early and respond to potential threats. VCF SSO maintains a dedicated audit log that captures user management events, including account creation, modification, deletion, and activation or deactivation, as well as changes to account credentials and profile information. The vSphere Client's Advanced Export feature allows administrators to export tasks performed by a specific user during a specified time range, providing targeted audit data for investigating suspicious activity.
-Audit logging extends across VCF components. NSX Manager generates audit log messages that record user operations with fields for UserName, ModuleName, Operation, and Operation status, along with detailed resource change information and timestamps. NSX Manager audit logs also record failed login attempts with username and timestamp information, enabling tracking of access patterns across the environment. VCF Operations for Networks captures audit logs of administrative actions, including CRUD operations and login/logout events.
-VCF Operations supports forwarding user activity audit logs to an external syslog server, enabling integration with dedicated SIEM or UEBA platforms for broader correlation and behavioral analysis. VCF Log Management includes content packs that offer pre-built dashboards, alerts, and queries for VCF components. These content packs support security monitoring use cases such as tracking failed login attempts and privilege escalations.
-VCF's built-in anomaly detection is primarily oriented toward infrastructure metrics and operational health rather than user behavior profiling. A dedicated UEBA or UAM solution consuming VCF's audit data would be needed to establish user behavior baselines, detect credential compromise through behavioral deviation, and provide the full scope of analytics this control requires. For organizations requiring deeper behavioral analysis, VMware vDefend extends VCF's monitoring foundation with IDS/IPS, network traffic inspection, and threat intelligence integration.</t>
+          <t>VCF provides several monitoring, alerting, and network analysis capabilities that contribute to an organization's ability to define and detect Indicators of Compromise (IOC), though fully operationalizing IOC management requires integration with external threat intelligence platforms and organizational processes.
+VCF Operations includes a Security Operations dashboard that provides a consolidated view of the security posture across the managed infrastructure. This dashboard brings together user and infrastructure security elements, helping operators identify areas that might require attention based on security exposure. By centralizing security-relevant telemetry in a single pane, the dashboard supports detection of anomalous conditions that could signal a cybersecurity event.
+VCF Operations continuously monitors infrastructure by evaluating collected data against defined policies. Each object or group receives a compliance score based on how well it adheres to those policies, and alerts are triggered when deviations occur. Organizations can create custom compliance benchmarks that monitor specific alert definitions and policies, allowing security teams to codify their own detection criteria and receive notifications when infrastructure drifts from expected baselines. This policy-based alerting mechanism supports operationalizing certain classes of IOCs, particularly those related to configuration drift, unauthorized changes, or compliance violations.
+VCF Operations supports custom alert definitions that can combine metric-based and log-based symptoms, allowing administrators to define conditions that flag suspicious activity. Alert definitions can incorporate Smart Early Warning conditions and log event patterns from monitored systems. Alert definition Impact settings can be configured to Risk to indicate potential problems that require attention in the near future, providing an early-warning mechanism that organizations can incorporate into incident detection workflows. Problem alerts are logged to syslog, and outbound notification plug-ins (SNMP Trap, webhook, email) allow alerts to be forwarded to external security tools for correlation and triage. VCF Log Management enables log-based symptom definitions that can match patterns across aggregated log data from across the VCF environment.
+At the network layer, NSX provides flow-based observability capabilities. NSX flow queries support filtering and analysis of VTEP traffic, management traffic, and extended L2 network traffic for monitoring and audit purposes. NSX Traceflow provides traffic analysis by specifying source and destination information and returning tables of observed packets. These capabilities help surface unusual communication patterns that organizations can correlate with defined IOCs.
+Log forwarding across VCF components supports IOC operationalization. VMware vCenter, NSX, and VMware ESX hosts can all forward syslog data to external SIEM platforms, where IOC matching and correlation typically occur. NSX audit logs include structured syslog fields that identify security-relevant events, and remote logging can be filtered by severity level and message categories including MONITORING, SECURITY, and SYSTEM.
+For full threat intelligence correlation and signature-based IOC detection, VMware vDefend is a separate product that extends NSX networking with security-specific capabilities: IDS/IPS with support for importing custom and third-party threat intelligence signatures, custom signature bundle management for tailored IOC definitions, Malicious IP Feed integration that downloads known-malicious IP lists from the NTICS cloud service for use in network policy, virtual Deep Packet Inspection (vDPI) for payload pattern matching, and Advanced Threat Prevention combining IDS/IPS with network sandboxing, Network Traffic Analysis (NTA), and Network Detection and Response (NDR) correlation engines.
+To fully satisfy this control, organizations need to supplement VCF's built-in monitoring with processes for defining, curating, and updating IOC libraries. This typically involves integrating third-party threat intelligence feeds, establishing procedures for translating threat intelligence into detection rules across VCF Operations and network policy, and deploying a SIEM or endpoint detection platform to correlate VCF's telemetry with broader IOC databases.</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -13505,10 +13421,12 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend Network Detection and Response (NDR) correlates detection events into campaigns, comparing new detection data against existing events to identify related activity. Campaigns provide a view of a threat by correlating detection events to identify the different stages of an attack, and security analysts can view and triage threat campaigns through a campaign timeline. NDR supports SIEM integration, sending campaign and event logs to a connected SIEM in real time, allowing network security event data to be exported for broader correlation with other enterprise data sources.
-Security Intelligence detects and categorizes suspicious events using MITRE ATT&amp;CK tactics and techniques, recording event occurrences during selected time periods, and provides a View Full Event History capability that displays all events associated with a given signature ID and intrusion severity. Security Intelligence also correlates IDS events from the same source and destination hosts to connect related events and build a broader picture of an attack. This structured, MITRE-tagged event data can support SIEM-based analysis and enterprise-wide threat correlation.
-The Security Services Platform (SSP) can be configured to forward log messages to external syslog servers for centralized log collection. SSP syslog configuration supports TCP, TLS, and UDP protocols and allows administrators to specify server address and port, integrating with existing SIEM ingestion pipelines. NDR Sensors report metrics covering health, traffic trends, and data processing activity, available as point-in-time measurements or aggregated data over time.
-vDefend correlates only technical network security data and has no capability to ingest or correlate non-technical information such as HR records, physical access logs, or operational data. Satisfying the full scope of this control, which requires correlation of both technical and non-technical information across the enterprise, requires an external SIEM or equivalent platform.</t>
+          <t>VMware vDefend provides automated IoC identification and alerting through IDS/IPS signature matching, Network Detection and Response (NDR) event correlation, and Malware Prevention file analysis with threat scoring, all accessible through the Security Services Platform (SSP) interface.
+The NDR Campaign Blueprint presents an interactive graph visualizing correlated security events that maps the different stages of an attack. Graph nodes represent Threats, Custom IDS Signatures, and Indicators of Compromise. The IoC Summary for each File IOC and Malware IOC presents file score, verdict, SHA hashes, and a View Reports link; directional arrows indicate when a workload is affected by an IoC, and node colors reflect severity based on the highest impact score from associated detections. The Campaign Blueprint's Triage and Investigate feature allows filtering detections by threat, affected workload, or MITRE tactics, enabling security teams to scope the impact of detected IoCs.
+The IDS/IPS Monitoring page provides a timeline graph visualization of intrusion events, with colored dots indicating unique event types and dot size indicating event frequency over a selectable time span. Events can be filtered by severity rating: Critical, High, Medium, Low, or Suspicious. Security Intelligence within the SSP provides a visualization canvas displaying granular IDS/IPS event data, including a blast radius view that highlights affected connections and can be filtered by specific signature ID. The SSP also collects and provides IDS/IPS metrics to monitor the readiness and performance of vDefend IDS/IPS across the environment. vDefend IDS/IPS maintains a detailed event log on ESX hosts capturing all alerts, drops, and rejects with metadata including source port, destination IP, IP protocol, and timestamps.
+The Threat Monitoring dashboard in the Security Services Platform displays file event statistics and recently detected threats, providing summary-level visibility into Malware Prevention activity. An alarm is triggered on the Security Overview dashboard when dropped events are detected, alerting administrators via both the alarm page and a notification banner, and the alarm remains active until no dropped events are detected.
+NDR integrates with external SIEM platforms, including VCF Log Management and Splunk, sending campaign and event logs as they occur. Events forwarded to the SIEM include new detections, detection updates, and new campaign creation, supporting automated alerting to organizational monitoring infrastructure. Security Intelligence also continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic.
+To configure IoC monitoring in a vDefend deployment: enable IDS/IPS profiles on Distributed Firewall rules, configure NDR in the Security Services Platform, enable the Malware Prevention service, and configure SIEM integration under NDR settings to receive real-time event forwarding.</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -13538,11 +13456,11 @@
       </c>
       <c r="N147" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides application-layer anomaly detection mechanisms that contribute to meeting this control. The Anomalies Overlay feature, available in Virtual Service Analytics, Service Engine Analytics, and Pool Analytics, flags statistical deviations in traffic metrics as anomaly events when a specific metric deviates from the historical norm by more than four sigma during the anomaly period. Monitored metrics include CPU utilization, bandwidth, disk I/O, server response time, and connection rates. Each anomaly event is identified by entity name, entity type (Virtual Machine, Virtual Service, or Service Engine), and metric value, with a timestamp indicating when the deviation occurred. Anomaly detection operates against a moving-average baseline calculated from recent historical traffic. The Pool Anomalies Overlay also displays prediction interval upper and lower bounds alongside the anomalous value. Administrators can adjust detection granularity by changing the statistics time interval, and can configure alert filter sensitivity to tune the threshold for new alert generation. Note that anomaly recording is disabled when the statistics interval is set to Real Time; a non-real-time statistics interval is required for anomaly capture to function.
-The Bot Management module adds a behavioral detection layer focused on credential stuffing and web attack patterns at the application proxy boundary. Bot Management detects malicious bots responsible for online fraud and credential stuffing attacks. The IP Reputation service extends detection by maintaining a database of categorized IP addresses and identifying anomalous traffic patterns, including DoS and DDoS activity and anomalous SYN floods.
-For authentication-related anomalous behavior, Avi provides the AUDIT_COMPLIANCE_EVENT mechanism to log authentication failures for audit purposes, persisting them via the alerts infrastructure. The Web Application Firewall (WAF) App Log Analytics component captures events whenever a WAF application rule is triggered, recording the type of attack detected. Service Engines generate DOS_ATTACK alert events that include attack type, source IP addresses, virtual service UUID and name, and a report timestamp, supporting audit and forensic analysis of detected attacks. Avi also supports DataScripts for custom identification of suspicious traffic and execution of appropriate mitigation actions, enabling organizations to define custom behavioral detection logic beyond the built-in statistical baselines.
-Avi monitors over 500 real-time metrics to support DDoS detection and attack visibility. Alerts from any of these mechanisms can be forwarded proactively to email, syslog, SNMP, or custom APIs, enabling integration with a central SIEM or security operations platform. Avi integrates with Splunk via the Avi Load Balancer Splunk Add-on, generating events that serve as an audit trail for user logins, configuration changes, and runtime state changes.
-These capabilities operate at the application delivery and load balancing layer. An organization requires a dedicated UEBA or UAM platform to fulfill the full scope of this control, including identity-level behavioral baselines, user session correlation, and cross-system entity analytics that extend beyond application traffic visible to Avi.</t>
+          <t>VMware Avi Load Balancer (Avi) provides application-layer detection of Indicators of Compromise (IoC) through its Web Application Firewall (WAF) and event-driven alert framework. When WAF Application Rules match incoming requests, App Log Analytics captures attack events and records information about the type of attack, such as SQL injection or cross-site scripting. The Application Security Report surfaces these findings as ranked lists of top attack types and top attacking IP addresses, with trend summaries showing total and flagged requests over time. In Evaluation Policy Mode, Avi WAF can generate a WAF Evaluation Report with WAF Statistics that provides a high-level overview of the application's security posture without blocking traffic. Avi's scan detection system also dynamically tunes client group membership in response to changes in traffic patterns to reduce false positives.
+Avi's Alert framework processes system events and performance metrics against user-defined rules to generate alerts that trigger configured notification actions. Administrators can deliver alerts to multiple destinations configurable in the Operations &gt; Notifications page of the Avi Controller UI: email, syslog, SNMP traps (SNMPv2c and SNMPv3), and custom APIs. SNMP notifications can be configured with TLS encryption and strict certificate verification. The Controller also monitors for denial-of-service attacks, with the Avi Service Engine generating DOS_ATTACK alert events that include attack type, attack count, source IP addresses, affected virtual service name, and report timestamp at configurable severity levels. Avi's alerting and reporting tools monitor over 500 real-time metrics for DDoS and attack mitigation activity.
+For automated response, ControlScript alert actions allow Avi to react programmatically to detected security events without manual intervention. A ControlScript can add an offending client IP address to a blocklist IP group attached to a network security policy, blocking or rate-shaping traffic from attackers identified in DoS or other attack events. DataScripts provide additional capability for custom identification of suspicious traffic and execution of appropriate mitigation actions.
+Avi's ICAP integration extends threat detection to content-level indicators by forwarding content to the vDefend sandbox analyzer. The response includes X-Infection-Found and X-Virus-ID headers containing threat scores, file hashes, and task UUIDs for analysis tracking. IP reputation events can be logged for monitoring and investigation.
+Organizations seeking IoC detection across the full VCF environment should forward Avi alerts and application logs to a SIEM or external threat intelligence platform. Full infrastructure-wide IoC detection requires correlating Avi's application-layer signals with telemetry from other VCF platform components.</t>
         </is>
       </c>
     </row>
@@ -13574,17 +13492,16 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>VCF uses cryptographic hash algorithms across multiple components to validate the integrity of data and software.
-vSAN uses end-to-end checksums to confirm the integrity of stored data, verifying that each copy of a file matches the source file. When software checksum is enabled alongside deduplication and compression, vSAN performs additional integrity validation at the cost of approximately 6.2 percent capacity overhead per device. This provides a continuous, built-in mechanism for detecting data corruption or tampering at the storage layer.
-NSX Manager uses the SHA-512 cryptographic hash algorithm to hash local user passwords, configurable through the hash_algorithm parameter in the authentication policy. For certificate management, NSX Manager supports SHA-1 and SHA-256 hashing algorithms for computing certificate thumbprints, with SHA-1 as the default. NSX supports multiple digest algorithms for IPSec negotiation, including SHA-1, SHA-256, SHA-384, and SHA-512, and the IPSec VPN Phase 1 authentication algorithm defaults to SHA-256. NSX Manager also authenticates SNMP messages using a FIPS-validated Keyed-Hash Message Authentication Code (HMAC), and uses FIPS 140 approved algorithms for authentication to its cryptographic module, generating unique session identifiers using a FIPS 140 approved random number generator.
-VCF Automation secures webhook behavior requests using HMAC authentication, which verifies the authenticity and integrity of HTTP requests. Each webhook request includes two custom headers: a signature header (x-vcloud-signature) and a digest (x-vcloud-digest).
-VCF Operations supports SHA-224, SHA-256, SHA-384, and SHA-512 algorithms for SNMP trap authentication protocols, providing multiple hash algorithm options for integrity verification in monitoring communications.
-The platform's cryptographic infrastructure is built on FIPS-validated cryptographic modules that include the hash algorithm implementations used throughout the stack. NSX uses FIPS 140-3 validated cryptographic modules by default, validated through the NIST Cryptographic Module Validation Program (CMVP). VCF Automation uses the BouncyCastle FIPS 2.0.0 cryptographic module compliant with FIPS 140-3 (Certificate #4743). VCF Operations for Networks uses BC-FJA (Bouncy Castle FIPS Java API) version 2.0.0 with FIPS 140-2 Certificate #37009. The use of validated modules provides assurance that hash algorithm implementations conform to established standards. For the VMware vCenter appliance, the OpenSSL FIPS Object Module version 3.0 supports SHA-3, HMAC, KMAC, and SHS among its validated algorithms, and the VMware Boring Crypto Module version 6.0 implements SHA2 variants and HMAC.
-VCF CLI repository configuration supports GPG signature verification of repository metadata. On RHEL, GPG checking is enabled through the gpgcheck parameter. On Debian and Ubuntu, VCF CLI installation uses GPG-signed package verification with a keyring stored at /etc/apt/keyrings/vcf-archive-keyring.gpg. This allows administrators to verify the integrity of software packages before installation. vSphere Lifecycle Manager verifies the SHA-256 checksum of each software download before applying updates to hosts, and VMware ESX VIB signature validation uses a cryptographic checksum to confirm that each VMware Installation Bundle was produced by its stated author. The VCF Consumption CLI binary can be verified using a sha256sum.txt checksum file available for download from the VCF Automation Tenant Portal, providing a hash-based integrity check for the CLI tool before deployment.
-TLS connections across VCF components use cryptographic hashes within message authentication codes to protect data in transit. Basic authentication for the vSphere JSON Protocol, for example, transports credentials over HTTPS with TLS encryption.
-The VMware Kubernetes Service (VKS) and vSphere Supervisor layer, which provides workload consumption capabilities within the VCF platform, applies cryptographic hash algorithms through several mechanisms. The ClusterClass API exposes a fips.enabled variable that activates FIPS-validated cryptographic modules across cluster nodes; when this is set, hash functions and other cryptographic operations are restricted to approved algorithms. VKS cluster nodes can reference Kubernetes releases built with FIPS-validated cryptographic modules, identifiable by the -fips.1 suffix in the release name, and the Istio service mesh package available for VKS clusters provides FIPS compliance through its carvel package configuration. The Kubernetes API server (kube-apiserver), kubelet, kube-scheduler, and vSphere Cloud Provider Interface each support configurable TLS cipher suites whose message authentication components incorporate SHA-256 and SHA-384; the --tls-cipher-suites parameter on kube-apiserver and kube-scheduler and the tlsCipherSuites setting on kubelet allow administrators to restrict the cipher suites accepted. Antrea, used as the container network interface within Supervisor, exposes a tlsCipherSuites setting for CNI-layer communications. Container images deployed on VKS clusters are identified by cryptographic digests using the SHA-256 algorithm, and the kubelet uses a SHA-256 hash of image pull credentials as the CredentialHash field to track secret state. Kubernetes bootstrapping uses a SHA-256 hash of the Subject Public Key Info object (in DER-encoded ASN.1) as the certificate authority pin during cluster join operations, providing integrity assurance for the node-to-control-plane trust chain. VKS clusters include a TLS certificate infrastructure that supports cryptographic hash-based integrity assurance for communications among cluster components.
-The vSphere CryptoManager API provides programmatic access to cryptographic operations, including integration with key management servers. Access to cryptographic operations is restricted to users who hold the Cryptographic Operations privilege in vCenter, with fine-grained sub-privileges allowing precise control over which users can perform specific encryption and hashing tasks. By default, the user with the vCenter Administrator role holds all Cryptographic Operations privileges.
-The vSphere Security Configuration Guide provides recommendations for enabling security features such as Secure Boot and Trusted Platform Module (TPM) on ESX hosts, which rely on cryptographic hashes to validate boot component integrity.</t>
+          <t>VCF provides built-in integrity validation mechanisms at multiple stages of the software update lifecycle, from binary download through post-update verification.
+The VCF Installer downloads and validates binaries after selection, confirming their integrity before any installation or update proceeds. Administrators receive confirmation that downloaded software has not been tampered with or corrupted before it is applied to the environment. VCF Operations further verifies that the file size and checksum of downloaded upgrade bundles match expected values before applying them. This validation occurs whether bundles are obtained from an online depot, an offline depot, or uploaded manually using the VCF Download Tool. VCF Operations also runs version-specific prechecks on components that have available upgrade bundles, identifying potential issues before the update begins.
+This pre-update validation runs automatically as part of the update operation and checks for conditions that could cause failures during the update itself. Deactivating this validation is not recommended, as doing so can lead to blocking failures during the update process. VCF Operations can download and manage upgrade, patch, and install binaries through a single management interface, maintaining a controlled chain of custody from download through deployment.
+VMware vCenter provides a patching API with a pre-check operation that validates upgrade readiness before applying updates. The Image Manager component within vCenter runs a validation check before a draft software specification is saved. vSphere Lifecycle Manager enforces image compliance across clusters, flagging hosts that do not match the expected software specification. It manages the lifecycle of solution components, including ESX hosts and third-party add-ons, by consuming software updates from managed software depots. These depots store both the actual update payloads and their associated metadata, which vSphere Lifecycle Manager uses to verify update content. Three depot types are supported: online depots connected to VMware update sources, offline depots for air-gapped environments, and UMDS (Update Manager Download Service) depots for controlled distribution. Each vSphere Installation Bundle (VIB) package installed on an ESX host carries an associated acceptance level used for integrity verification, which determines whether the software meets the trust requirements configured for the host. For firmware updates, vSphere Lifecycle Manager provides access to vendor-specific depots through a hardware support manager module, which controls which firmware packages are available and manages the integrity of firmware delivery to the host.
+NSX provides integrity validation through its Upgrade Coordinator, which includes post-check verification to confirm that upgraded hosts and NSX components are functioning correctly, along with a consistency check API for upgrade verification. After updates are applied across the broader VCF stack, a Consistency Check Report surfaces errors and warnings encountered during the upgrade process. Administrators can review this report and perform remediation actions for any issues detected, providing a post-update verification layer.
+For management packs and extensions, VCF Operations verifies that PAK files are signed with a digital signature provided by VMware. The digital signature indicates the original developer or publisher and confirms the authenticity of the management pack. NSX verifies the signature of uploaded dynamic plugins using a public key to confirm plugin validity.
+In the container and CLI tooling layer, the VCF CLI supports cosign-based image signature verification for plugins. The imgpkg tool can find and copy cosign signatures for images, and a configurable public key path allows administrators to specify which signing authority is trusted for plugin discovery images. The VCF CLI binary itself supports integrity verification through a SHA256 checksum file (sha256sum.txt) published alongside each release download and also available from the VCF Automation Tenant Portal, allowing administrators to verify the binary before installation.
+At the workload consumption layer, VMware Kubernetes Service (VKS) extends platform-level integrity mechanisms to containerized workload environments. When rolling updates are initiated for VKS service clusters, the VKS system performs pre-checks and enforces compliance to support compatibility before updates proceed. VKS Add-on Management runs pre-checks prior to add-on and cluster upgrades to verify that dependency and compatibility constraints are not violated. VKS osConfiguration includes a trust setting that configures system-wide certificate trust for cluster nodes, establishing which certificate authorities are trusted during component verification as part of an update sequence. Harbor, available as a Supervisor Service on VKS clusters, provides content trust, vulnerability scanning, and policy-based replication to support software supply chain integrity for container images; when Harbor is configured as the pull source for workloads, its content trust model creates a verifiable chain of custody from image build through deployment. For standalone virtual machines in vSphere Supervisor, content libraries can apply an OVF security policy that enforces strict validation when deploying or updating content, importing items to a library, or synchronizing templates. DISA Security Technical Implementation Guides are available for Supervisor components and VKS Kubernetes release images (VKrs) to support hardening guidance for update-related configuration. Kubernetes supply chain security guidance for VKS cluster components describes that software distribution should use encryption in transit with a chain of trust for the software source, and that dependencies should be updated when available, particularly in response to security announcements. The guidance extends to the deploy lifecycle phase as well, where enforcement of distribute-phase measures, including verification of the cryptographic identity of container image artifacts, helps carry the supply chain trust chain through to the point of workload execution.
+VCF lifecycle management automates the process of applying updates and patches across the entire VCF software stack. This centralized approach means that integrity validation mechanisms are applied consistently to all managed components rather than relying on manual verification of individual updates.
+Organizational update governance (test and approval cadences, validation processes for staged rollouts, deviation tracking, post-deployment verification) sits above the platform's automated integrity validation. VCF's mechanisms address the cryptographic integrity of update packages; the organization's update governance program addresses the broader process of testing, approving, and tracking update deployments across the environment.</t>
         </is>
       </c>
       <c r="G148" s="10" t="inlineStr">
@@ -13594,12 +13511,10 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend uses cryptographic hash algorithms across multiple subsystems to validate the integrity of data and to identify known threats, contributing to the organization's broader use of hash-based integrity verification.
-Malware Prevention uses hash-based detection as a primary mechanism for identifying known malicious files. When files traverse the network and are intercepted for inspection, the service computes MD5, SHA-1, and SHA-256 hashes of each file and compares them against databases of known malware signatures. Custom Malware Prevention signature bundles support file hash matching using MD5, SHA-1, and SHA-256 checksums, allowing organizations to define detection rules that trigger on specific file hashes. File Analysis Report Details display the MD5, SHA-1, and SHA-256 hashes of analyzed files alongside MIME type and submission timestamps, providing auditors with a clear record of hash-based integrity checks performed on inspected files. Process Analysis Report Details similarly capture MD5, SHA-1, and SHA-256 hash values for analyzed processes, enabling forensic correlation across detection events. Malware Prevention Service generates FileInspectionEvent log messages containing SHA-256, SHA-1, and MD5 hash values for inspected files, supporting audit trails of hash-based detection activity.
-vDefend IDS/IPS custom signature rules support hash computation through buffer transformation modifiers. The to_md5, to_sha1, and to_sha256 modifiers convert arbitrary buffers to hash values within signature logic, enabling detection patterns that hash observed content before matching. Custom signature rules also support ja3.hash and ja3s.hash sticky buffer content modifiers to match on JA3 and JA3S hash fingerprints of TLS client and server handshake parameters, classifying encrypted traffic without decryption.
-The IDS/IPS signature bundle includes a SHA-256 checksum that organizations can use to verify the integrity of the downloaded signature file before applying it to detection profiles. This hash-based integrity check helps confirm that signature content has not been corrupted or modified during distribution.
-The Security Services Platform components, including the Security Services Platform Installer and NDR Sensor for vDefend, implement FIPS 140-2 and FIPS 140-3 validated cryptographic modules. Security Services Platform uses VMware BouncyCastle Module bc-fips-2.1.2 (NIST Certificate #4943) and VMware OpenSSL FIPS provider Object Module version 3.0.15 (NIST Certificate #4861). These validated modules underpin the cryptographic operations across Security Services Platform components.
-vDefend's hash usage is focused on network security functions: malware identification, signature-based detection, TLS fingerprinting, and integrity verification of downloaded signature content. The broader control encompasses hash algorithms used across all organizational systems for data and software integrity validation, including storage checksums, password hashing, code signing, and boot integrity verification, which are addressed by other VCF components.</t>
+          <t>VMware vDefend provides integrity controls for its own security component updates through IDS/IPS signature bundle management and Security Services Platform upgrade validation.
+vDefend IDS/IPS includes configurable signature bundle update modes. In automatic mode, the system retrieves signature updates through the cloud-hosted vDefend Threat Intelligence Service (vTIS) portal, which notifies administrators when new bundle versions are detected. In manual mode, administrators disable the Auto Update toggle and select a specific signature bundle version for deployment. For air-gapped environments, vDefend IDS/IPS supports offline download and upload of signature bundle files. Signature Bundle Version Management allows administrators to view available versions and set the active signature set; by default, the latest version is selected for automatic updates. Signature Bundle Realization Status tracks whether updates were successfully applied across transport nodes and Edges, confirming that the selected version is in use. In federated deployments, Local Manager sites can independently select manual bundle versions when Auto Update is disabled. Administrators can also publish validated custom signatures directly to transport nodes and Edges. Both IDS/IPS and Malware Prevention share the Auto Update toggle, so the configured mode applies across both detection features.
+Security Services Platform (SSP) performs prechecks of its components, including metrics components, during upgrade validation before proceeding. The SSP upgrade manager handles updates to Workload and Management clusters and the installer VM. The deployment wizard conducts validations before implementing configuration changes to confirm that configurations are correct and compatible. SSP monitors deployment status and raises alarms for errors that require attention during upgrade operations.
+These mechanisms operate alongside the broader VCF platform integrity controls, which include upgrade bundle checksum verification through VMware vCenter and cosign-based image signature verification via the VCF CLI.</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -13638,12 +13553,13 @@
       </c>
       <c r="N148" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides cryptographic hash capabilities within its application delivery functions. The DataScript runtime exposes three built-in hashing functions: avi.utils.sha1_hash, avi.utils.md5_hash, and avi.utils.murmurhash. These functions compute hash values of arbitrary data within virtual service policies, and operators can use them to inspect, hash, or validate content at the application delivery boundary. The DataScript hashing API is documented under DataScript Functions &gt; Utilities Functions in the Avi documentation.
-For TLS certificate operations, the Avi SSL/TLS Profile supports configurable signature algorithms including MD5, SHA-1, SHA-224, SHA-256, SHA-384, and SHA-512, governing hash algorithm negotiation during TLS handshakes. This configuration is accessible under Templates &gt; Security &gt; SSL/TLS Profile in the Avi Controller UI and can be tuned to restrict negotiation to approved algorithms only.
-Avi also supports MLDSA, a hash-based quantum-resistant signature algorithm, for certificate signing requests. This is configured under Security &gt; SSL Certificates &gt; CSR Certificates and provides a post-quantum option for certificate integrity operations.
-Service Engine NTP authentication supports MD5 and SHA1 algorithms with configurable authentication keys, providing hash-based integrity verification for time synchronization communications. This is configured under Controller Settings &gt; DNS/NTP Settings.
-When FIPS mode is enabled on the Avi Controller, all cryptographic operations are restricted to FIPS 140-3 compliant algorithms via OpenSSL FIPS Provider 3.1.2, including all hash operations throughout the system. FIPS mode is configured at the controller cluster level under FIPS Compliance &gt; Enabling FIPS Mode for a Controller Cluster Deployment. Organizations that require FIPS-validated hash operations should enable FIPS mode; note that FIPS mode does not support SSL Client Hello events in Avi DataScript, which limits certain DataScript-based TLS inspection scenarios.
-Avi's hash mechanisms are scoped to application delivery and TLS operations. Platform-level data and software integrity validation, including VM image integrity and software package verification, is provided by the underlying VCF platform (see VCF Coverage).</t>
+          <t>VMware Avi Load Balancer contributes to integrity validation for software and firmware updates through mechanisms built into its Controller upgrade pipeline, its application-security rule management, and FIPS 140-3 module integrity controls.
+Before any upgrade or patch is applied, the Avi Controller runs mandatory pre-upgrade checks that cannot be bypassed when errors are present. In 9.1 VCF-integrated deployments, these checks include verification of image checksums or digital signatures to confirm file integrity before the upgrade proceeds. The checks also verify that required patch packages and system packages are present on disk, that Service Engines are reachable, and that system resource requirements meet minimum thresholds. A dry-run mode is available via the UI (Administration &gt; Update &gt; System) or through the /api/upgrade API endpoint using the prechecks_only flag; this runs the full pre-check suite before committing to a maintenance window. Dry-run operations generate transcript logs capturing all pre-check operations and their outcomes, providing a reviewable record before the upgrade is approved.
+After an upgrade completes, Avi supports post-upgrade validation. For VCF-integrated deployments, the post-upgrade checklist specifies that Management Plane alarms, alerts, and dashboards must be confirmed operational. Pre- and post-upgrade object operational state verification should be performed on virtual services and pools to detect any unintended state changes during the upgrade process. Avi GSLB Services generates operational snapshots during upgrade and rollback operations to support state comparison.
+For application-layer security content, the Avi Cloud Console provides an Application Rules service that automatically distributes rules targeting known application vulnerabilities, including CVE-tracked threats, without requiring a Controller upgrade. A Live Security Threat Intelligence feed keeps WAF Core Rule Set content current on the same continuous basis. Both channels allow security-relevant updates to the Avi data plane to be applied independently of the main software upgrade cycle.
+Avi supports rollback of both full upgrades and patch upgrades. The enable_patch_rollback setting on Service Engine groups controls whether patch rollback is permitted during an operation. Patch rollback transitions the system to the version without the specific patch; it does not revert to a prior major version. The Controller blocks upgrade operations when the license has expired, preventing upgrades in an unlicensed state.
+Deployments operating in FIPS 140-3 mode gain enhanced controls over software and firmware module integrity and module updates, providing a higher-assurance path for environments that require validated cryptographic module integrity.
+Tracking applicable security advisories, scheduling updates within organizational patch windows, and establishing remediation procedures before re-attempting upgrades after rollback are organizational responsibilities that extend beyond Avi's automated pipeline.</t>
         </is>
       </c>
     </row>
@@ -13675,17 +13591,15 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>VCF provides network segmentation as a foundational design principle, using multiple layers of isolation to separate technology assets, applications, and services from one another.
-At the physical and logical network layer, VCF uses VLANs and vSphere Distributed Switches (VDS) to segment traffic by function. Management traffic is isolated on dedicated networks accessible only to administrators. vMotion traffic is separated on distinct networks using dedicated VMkernel interfaces. IP-based storage traffic, including vSAN and NFS, runs on dedicated VLANs and can use dedicated physical network adapters for additional isolation. vSAN storage clusters can separate external VM traffic from internal storage traffic by using dedicated VMkernel ports for each traffic type. Network I/O Control (NIOC) on distributed switches divides traffic into predefined resource pools, including fault tolerance, iSCSI, vMotion, management, vSphere replication, NFS, and virtual machine traffic. NIOC can reserve bandwidth for each traffic type and allocate shares so that one class of traffic cannot starve another during contention. Active/standby NIC teaming configurations are available for vSAN traffic to provide resiliency without mixing storage and compute traffic paths. Distributed switch port groups also support Private VLANs (PVLANs), which further subdivide a VLAN segment into promiscuous, community, and isolated port types, restricting intra-VLAN communication to only explicitly permitted paths.
-NSX extends segmentation with software-defined networking that decouples the virtual network from the physical infrastructure. NSX supports two primary segment models. The VLAN Segment Model provides isolation from other networks and can maintain separate security domains, such as isolating the fleet-level management network using VLAN-backed distributed port groups. VLAN segments can be provisioned by specifying one or more VLAN IDs on a private NSX network type. The Overlay Segment Model similarly provides isolation but decouples the virtual network infrastructure from the physical network, allowing segments to be created dynamically without reconfiguring the underlying physical network. This dual-model approach gives administrators flexibility to implement macrosegmentation using either traditional VLAN boundaries or software-defined overlay networks depending on architectural requirements.
-NSX allows administrators to create logical network topologies using the NSX UI or API, building multi-tier architectures with Tier-0 and Tier-1 gateways and segments. Segments are realized as NSX Distributed Virtual Port Groups on vSphere Distributed Switches, providing consistent policy enforcement at the hypervisor level. In topologies running multiple standard overlay VDS switches, NSX provides traffic isolation such that traffic traversing one VDS is isolated from traffic on another VDS. NSX also supports applying switch security profiles to distributed port groups, and segment security features can filter malicious traffic from VMs on the network, helping protect segment integrity. NSX Distributed Port Groups and Uplink Port Groups also support Traffic Filtering and Marking policies that can be enabled and configured at the port level, allowing administrators to qualify, filter, or remark specific traffic flows at the point of ingress or egress on each port.
-For multi-tenant and multi-department environments, NSX provides two isolation mechanisms. NSX Projects enable isolation of networking and security configurations across organizational units. NSX Virtual Private Clouds (VPCs) represent an additional layer of multi-tenancy within a project, providing self-contained virtual network environments with their own permission models, topology, and IP address management. VPCs support role-based access control through user and user group role assignments for Local User, LDAP User, or vIDM User account types. These can be allocated to discrete projects or tenants, enabling each to consume networking and security services in a self-service model.
-VCF Automation extends segmentation into provisioned workloads by providing security groups for network isolation of deployed resources. This allows segmentation policies to be applied consistently through automated deployment workflows, so that new workloads are placed into the correct network segments from the point of provisioning.
-The Consumption layer of VCF, which encompasses VMware Kubernetes Service (VKS) and vSphere Supervisor, extends network segmentation to containerized workloads using the same NSX networking infrastructure. vSphere Namespaces serve as logical isolation units within VCF Kubernetes environments, providing resource and network boundaries between workloads deployed across different namespaces. A dedicated virtual network is provisioned for each namespace where a cluster is deployed and for each VKS cluster itself. Each VKS cluster is backed by a set of NSX networking objects: a Tier-1 gateway (router), a segment (switch) linked to that gateway, a load balancer server, and virtual servers for the cluster's control plane endpoints. VKS cluster nodes attach to these NSX-backed segments through VirtualNetworkInterface objects as logical ports, assigning each node an IP address and scoping cluster traffic to a dedicated segment isolated from other clusters and from the management plane. The management plane, which hosts VMware vCenter and NSX Managers, is architecturally separated from the compute plane, which hosts NSX Edge Nodes and Supervisor nodes, so management traffic does not mix with workload traffic at the network layer.
-Within VKS clusters, Antrea serves as the CNI plugin and supports the standard Kubernetes NetworkPolicy API, allowing administrators to declare and enforce pod-level ingress and egress rules. By default, a pod is non-isolated for egress, meaning all outbound connections are permitted; a pod becomes isolated for egress only when a NetworkPolicy selects it and includes Egress in its policyTypes, at which point only connections explicitly allowed by applicable policies are permitted. A pod becomes isolated for ingress when any NetworkPolicy selects it with an Ingress rule, restricting inbound connections to those from the pod's own node and those explicitly permitted by applicable policies. Administrators can apply a namespace-scoped NetworkPolicy that denies all ingress and egress traffic, establishing a deny-all baseline from which only necessary flows are selectively opened; for environments requiring strict multi-tenant namespace isolation, the recommended approach is a default deny-all policy paired with an explicit allow for DNS resolution. Antrea distributed firewall policies can additionally restrict traffic between Kubernetes namespaces by applying filtering rules at specific pod groups, providing an enforcement layer that complements standard Kubernetes NetworkPolicies. The Antrea-NSX Adapter integrates each VKS cluster's networking with NSX Manager, enabling NSX to manage the networking behavior of the cluster and apply consistent segmentation policies across both the Kubernetes data plane and the underlying NSX infrastructure. Antrea's NetworkPolicyStats feature gate enables collection of network policy statistics, providing visibility into enforcement activity per workload. VKS cluster administrators control pod network attachment capabilities through NetworkAttachmentDefinition resources, which define the allowed network configurations that application users may request, preventing unauthorized network connections. For multi-network configurations, VKS uses SubnetConnectionBindingMap custom resources to bind overlay subnets to node vNIC subnets, with the vlanTrafficTag field specifying a unique VLAN ID for traffic isolation between parent and child subnets at the NSX data path level. The Antrea EgressSeparateSubnet feature allows egress IP allocation from a subnet distinct from the default node subnet, supporting stricter egress traffic segmentation. For SR-IOV deployments, VKS SR-IOV network configurations block cross-namespace selection of network resources, enforcing namespace-level boundaries for high-performance network access. For multi-tenant data plane separation, pod node selectors can restrict workload placement to specific nodes, preventing tenant workloads from sharing compute resources across tenant boundaries. Service meshes deployable on VKS clusters can extend segmentation to OSI Layer 7 by enforcing policies based on workload identity and providing mutual TLS encryption between workloads, adding isolation even within a shared network segment. The Argo CD Supervisor Service implements its own internal network segmentation and firewall rules to secure communication between its components.
-For ongoing management and visibility, the NSX Segment Inventory Dashboard tracks and manages network segmentation while offering insights into the dependencies between logical switches and other NSX components. The NSX Switch Dashboard displays detailed information on logical switches for efficient tracking and management. VCF Operations for Networks supports segmentation planning by analyzing traffic flows and grouping them by entities such as VLAN, security group, application tier, subnet, cluster, or individual virtual machine. The micro-segmentation planning topology shows all flows present in an environment by dividing them into segments, helping administrators understand current traffic patterns and refine segmentation boundaries over time. Distributed virtual switches support health check operations for NIC teaming and VLAN/MTU configuration, and VCF Operations provides host metrics that detect unsupported MTU configurations across the infrastructure.
-The VCF documentation states that network endpoints should be segmented. Administrators should configure VLAN or overlay segments appropriate to their environment, assign workloads to the correct segments, apply switch security profiles, and use the NSX dashboards and VCF Operations tools to verify and maintain segmentation boundaries. For microsegmentation below the network segment level, VMware vDefend provides fine-grained traffic control between individual virtual machines and containers, independent of their network placement.
-For operational technology (OT) and industrial workloads, NSX Industrial vSwitch (IvS) extends segmentation to PROFINET traffic between virtual Programmable Logic Controllers (vPLCs) running on VMware ESX hosts and I/O devices located outside the vSphere cluster. The associated NSX Industrial vSwitch Segment Profile supports the Discovery and Configuration Protocol (DCP) as part of the PROFINET protocol suite, allowing discovery of IO devices, retrieval of device identity information, and configuration of device settings such as device name and IP address. This capability brings OT traffic under the same segmentation model as standard IT workloads, enabling administrators to isolate industrial traffic on dedicated segments alongside the rest of the network architecture.</t>
+          <t>VCF provides network segmentation, multi-tenancy isolation, and per-component infrastructure service configuration that support the creation of separate network enclaves with dedicated services. However, providing a complete set of enclave-specific IT services, including dedicated directory services, antimalware, and patch management, requires organizational planning and additional tooling beyond what VCF delivers natively.
+NSX enables the construction of isolated network segments through both VLAN-backed and overlay-backed approaches. The NSX VLAN Segment Model provides isolation from other networks and can be used to maintain separate security postures for different network zones, such as the fleet-level management network. In topologies with multiple VDS switches, NSX provides traffic isolation such that traffic on one VDS is isolated from traffic on another, supporting physical and logical separation of enclave traffic from enterprise traffic. NSX segments are realized as NSX Distributed Virtual port groups in vCenter, and VLAN segments can be provisioned by specifying one or more VLAN IDs, giving administrators granular control over Layer 2 boundaries between enclaves.
+NSX also supports multi-tenancy through projects, which isolate security and networking objects across tenants within a single NSX deployment. Each project functions as an independent tenant boundary, allowing enclave-specific network configurations without cross-tenant visibility. Multi-tenancy in NSX enables isolation of networking and security configurations across tenants, so that each department or enclave can operate with its own set of network policies and security rules. Setting up multi-tenancy is optional and has no impact on existing NSX configuration, allowing organizations to adopt enclave isolation incrementally.
+VCF Automation extends this isolation model at the organizational level. Each organization in VCF Automation operates in a secure, isolated environment where users can access only allocated services and resources. Organizations provide infrastructure isolation with dedicated network setup and network isolation. Provider administrators allocate infrastructure resources to organizations using regional quotas, with CPU and memory reservations representing guaranteed capacity within a region. One organization can receive quotas from more than one region, allowing sensitive enclaves to be assigned to dedicated infrastructure tiers. Organization administrators then distribute that allocated infrastructure to different projects within the organization using namespaces, enabling fine-grained resource partitioning. VCF Operations calculates chargeback at the region quota level and aggregates at the organization level, supporting cost accountability per enclave.
+Within VCF Automation network profiles, security groups can define isolation settings for on-demand private or outbound networks. Two types of security groups are available: existing security groups selected from the Security Groups tab and on-demand security groups created using an isolation policy on the Network Policies tab. vDefend firewall rules scoped to these security groups can enforce boundaries between segments at the network layer.
+DNS services can be configured on a per-network and per-component basis within VCF. Workload networks require their own DNS server settings to resolve domain names of vSphere management components such as vCenter. ESX hosts are configured with primary and alternate DNS servers as part of their host-level network configuration. For vSphere Supervisor deployments, the DNS server IP addresses must be configured to resolve the FQDN of the associated vCenter instance. The Avi Load Balancer Controller also requires its own DNS server configuration to resolve vCenter and ESX hostnames. This per-component DNS configuration model means that isolated enclaves can be pointed at dedicated DNS servers rather than sharing corporate DNS infrastructure.
+NTP is similarly configurable at the component level. NTP service must be configured on all ESX hosts, with the service startup policy set to start and stop with the host. VMware recommends using at least three NTP servers for each ESX host to provide redundancy for time synchronization within isolated segments. ESX also supports Precision Time Protocol (PTP) as an alternative to NTP for environments that require higher clock precision; NTP and PTP cannot run simultaneously on the same host, so administrators should select the appropriate protocol for each enclave's requirements. VCF management components can be configured to use ESX NTP servers for time synchronization, and it is recommended that NTP be configured for all components in the NSX environment. VCF Operations also requires time synchronization via NTP between endpoint VMs, vCenter, ESX hosts, and cloud proxies. Each of these components can point to enclave-specific NTP servers, supporting the requirement to provide dedicated time services within isolated network segments.
+The management domain architecture in VCF inherently separates management-plane services from workload networks. IP addresses and FQDNs for vCenter and NSX Manager instances must be resolvable over DNS within their respective network zones, and the management network uses its own set of infrastructure services distinct from tenant workloads. This architectural separation provides a foundation for building enclave-specific service stacks.
+While VCF provides network isolation infrastructure, multi-tenant boundaries, per-component DNS and NTP configuration, and organizational-level resource partitioning, a complete enclave segregation strategy also requires enclave-specific directory services, asset management, antimalware, and patch management services. These capabilities fall outside VCF's scope and must be provided through organizational processes, dedicated tooling, and architectural decisions about how to deploy and configure those services within each isolated network segment.</t>
         </is>
       </c>
       <c r="G149" s="10" t="inlineStr">
@@ -13695,13 +13609,10 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) provides network segmentation capabilities at multiple layers, from macrosegmentation at the network perimeter down to microsegmentation between individual workloads. This is a core function of the product and addresses the control directly.
-VMware vDefend enforces segmentation at the workload level by applying security policies at the vNIC of every virtual machine and container. Policies follow the workload regardless of its network placement or physical location, so segmentation is not dependent on VLAN boundaries or physical network topology. Administrators can define rules based on security groups, application tiers, tags, and other logical constructs to isolate technology assets, applications, and services from one another. Layer 2 through Layer 7 inspection allows rules to be written against specific applications, protocols, and user behaviors rather than just IP addresses and ports. When using NSX Projects, firewall rules are automatically scoped to VMs connected to the segments within that Project and do not affect workloads outside the Project, providing a built-in boundary for multi-tenant or departmental segmentation.
-Starting with VCF, vDefend supports enforcement on both Distributed Virtual Port Groups (DVPGs) created in vSphere Distributed Switch and segments created in NSX within the same cluster. This extends DFW coverage to VMs connected to traditional vSphere DVPG networks in addition to NSX overlay segments, allowing organizations to apply consistent security policy across mixed-network environments. DFW policy members can include DVPGs, NSX Segments, or both, and grouping constructs support dynamic or static membership criteria based on VM name, tags, segment, or IP addresses.
-VMware vDefend provides stateful North-South traffic inspection at the network edge, controlling traffic entering and leaving each segment. Together, the Distributed Firewall and Gateway Firewall create a layered segmentation model where both East-West and North-South traffic are subject to policy enforcement.
-Security Intelligence, delivered through the vDefend Security Services Platform, provides segmentation planning and monitoring tools. The Security Segmentation Report assigns a quantitative Security Segmentation Score that measures an organization's progress toward a fully segmented network. Segmentation planning workflows help administrators discover traffic flows, identify infrastructure services, group assets by environment (such as VLAN, security group, application tier, subnet, or cluster), and apply hierarchy tags to verify that segments have appropriate controls. Infrastructure services are categorized into their own groups separate from the asset hierarchy, with dedicated groups that users can create and apply policies to. Environment segmentation divides the data center into broader security zones such as production, development, testing, or regulated environments, and Security Intelligence workflows support planning and enforcement of policies at each zone boundary. Security Intelligence generates macrosegmentation policy recommendations for environment pairs based on observed traffic flow patterns; these recommendations can be reviewed, modified, and published to enforce segmentation policies through the Distributed Firewall.
-Segmentation Monitoring continuously watches traffic for supported infrastructure services and detects new servers or services that appear on the network. The feature monitors supported infrastructure service types, including DHCP, DNS, NTP, and LDAP, and identifies both newly discovered servers and servers missing recommended security rules. Administrators can configure protection policies for environment pairs to Drop or Reject unauthorized traffic, and create lockdown rules to disallow traffic to servers outside defined infrastructure asset groups. Segmentation Monitoring provides detailed investigation capabilities to identify potential security risks in application traffic and enable corrective action. This provides ongoing assurance that the segmentation scheme remains intact as the environment evolves.
-Application-level microsegmentation implements granular isolation for individual applications. Segmentation planning supports import of application context using a flat file containing key workload attributes such as IP addresses, subnets, virtual machines, logical segments, and organizational roles. The Security Segmentation Report also identifies workloads running obsolete operating systems, workloads using risky application protocols, and workloads communicating with external IP addresses, helping administrators prioritize segmentation policy work.</t>
+          <t>VMware vDefend (DFW) and Gateway Firewall (GFW) provide network enforcement mechanisms that contribute to segregating sensitive data enclaves from corporate-provided IT resources.
+In VCF, vDefend introduces a VPC Isolation with Essential Services strategy implemented through GFW rules. This strategy denies all inter-project communication by default while explicitly permitting only specified infrastructure protocols such as DHCP, DNS, NTP, and ICMP. Enterprise Administrators can configure GFW policies that isolate project VPCs so that local workloads communicate only within the VPC boundary, while access to shared corporate infrastructure services is controlled at the network enforcement layer. This gives security teams direct control over which infrastructure protocol flows are allowed to cross enclave boundaries rather than relying on default-permit behavior.
+The DFW supports policy scoped to NSX logical groups, using dynamic or static membership criteria based on VM name, tags, segment, segment port, IP addresses, or other attributes. These grouping mechanisms allow administrators to define enclave membership precisely and apply consistent firewall policy to all members of a sensitive zone.
+vDefend does not provision the enclave-specific service instances required to fully satisfy this control, such as dedicated directory services, DNS resolvers, NTP servers, ITAM systems, or patch management infrastructure for isolated segments. Provisioning those services within the isolated segment is an organizational infrastructure decision that falls outside vDefend's scope.</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -13778,12 +13689,11 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend provides native Intrusion Detection and Prevention System (IDS/IPS) capabilities that operate at both distributed and gateway enforcement points across the VCF environment.
-Distributed IDS/IPS runs within the hypervisor on every VMware ESX host, inspecting east-west traffic at the vNIC level. This positions detection and prevention directly on the workload, covering internal network segments without requiring traffic to traverse a centralized appliance or choke point. Distributed IDS/IPS is available in the Advanced Threat Prevention edition and can be enabled across discovered clusters using the NSX management interface or API. An onboarding wizard guides administrators through the initial setup, including preparing the data center for IDS/IPS and Malware Prevention features.
-Gateway IDS/IPS operates at the perimeter, inspecting north-south traffic at gateway choke points. Together, the distributed and gateway deployment models provide layered detection across both internal segments and network boundaries.
-vDefend IDS/IPS uses knowledge-based, signature-based detection. Signature bundles incorporate custom detection logic that can be updated without recompiling or modifying the IDS engine. The latest signatures can be downloaded automatically from the cloud when Internet connectivity is available, or through a configured proxy server. Administrators can also create custom signatures to address threats related to custom applications and zero-day vulnerabilities. Custom signatures can be included in IDS/IPS profiles and applied to Distributed Firewall (DFW) and Gateway Firewall (GFW) rules. Signature thresholds can be configured to control how frequently a signature generates an event and to dynamically adjust the rule's action when specific conditions are met. Signatures can be filtered by CVSS score, products affected, service, and attack target in addition to severity and attack type, enabling prioritization based on exploitability.
-Network Detection and Response (NDR) extends IDS/IPS by correlating IDS signature matches, including matches from custom signatures, against network traffic in the protected network. NDR classifies detections by detection technology type with IDS events as a supported detection type, combining intrusion detection events with network traffic analysis to identify campaigns and advanced threats that individual signature matches might not surface on their own.
-The Distributed IDS/IPS Summary dashboard provides operational visibility into detected threats, displaying intrusion event trends organized by severity and a radar chart showing distribution of intrusion events by attack type, attack target, or severity over configurable periods from 24 hours to 14 days. IDS Packet Capture records raw network packets associated with detected intrusion events, supporting forensic investigation. Security Intelligence, available through the Security Explorer interface, detects intrusion events in real time and allows filtering of intrusion history by action, attacker IP, attacker port, PCAP UUID, profile, rule, target IP, target port, and detection location. Impact scoring and per-virtual-machine detection status visibility are available through the Security Explorer, and events can be filtered by Compute and IDS Signature ID. IDS/IPS Rule Performance Metrics identify resource-intensive rules across Distributed and Gateway enforcement points, supporting operational tuning without affecting detection coverage. The Intelligent Assist feature within the Security &gt; IDS/IPS interface allows administrators to investigate intrusion attempts by selecting specific events and reviewing the latest or historical occurrences.</t>
+          <t>VMware vDefend contributes to this control through its threat intelligence consumption and detection infrastructure. The IDS/IPS engine applies knowledge-based signatures that encode specific patterns corresponding to known attack types, detecting intrusions based on known malicious instruction sequences at distributed and gateway enforcement points within vDefend-protected segments. Threat metadata feeds for Network Detection and Response are distributed and can be refreshed from online sources, or downloaded and applied manually in air-gapped environments through NSX Manager or a workstation connected to the Security Services Platform.
+Network Detection and Response (NDR) correlates related detection events into campaigns and organizes them into a chronological timeline for security analyst review and triage. The Campaign view displays total detections and threats identified under Malicious Activity, and Campaign Correlation Rules provide structured visibility into how individual detections relate to broader attack patterns.
+Security Intelligence maps detected suspicious events to adversarial tactics and techniques from the MITRE ATT&amp;CK framework, recording the count of each tactic and technique observed during a selected time period. This TTP-level categorization supports the situational awareness the control describes for traffic traversing vDefend-protected segments. The threat visualization canvas aids rapid containment, identification of compromised assets, and adjustment of microsegmentation policies in response to detected activity. The blast radius analysis capability displays which communication paths a threat has affected, helping analysts determine whether an attack targets specific systems or represents a wider campaign.
+Security Intelligence also collects related IDS events across the same source and destination hosts to connect relevant events and build a fuller picture of an attack sequence. The vDefend Security Assessment generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows to support protection planning. Security teams investigate individual events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take mitigation actions.
+While vDefend delivers technical mechanisms for consuming threat intelligence feeds and mapping observed behavior to adversarial TTPs at the network layer, the broader organizational threat intelligence program, including sourcing intelligence from external providers, integrating with threat sharing platforms, and disseminating findings to other teams and tools, requires complementary processes and tooling outside the product.</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
